--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26024"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_520\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4450" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6444F7F4-3D73-4C4E-BB3C-30555C3483F5}"/>
+  <xr:revisionPtr revIDLastSave="4464" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{B58767D0-ACAF-4899-A369-C1277C918892}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="445" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JAN22" sheetId="38" r:id="rId1"/>
@@ -32,12 +32,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -415,12 +410,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="8" formatCode="&quot;฿&quot;#,##0.00;[Red]\-&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="187" formatCode="0.000"/>
-    <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="189" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="190" formatCode="0.0000"/>
-    <numFmt numFmtId="191" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="187" formatCode="&quot;฿&quot;#,##0.00;[Red]\-&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="188" formatCode="0.000"/>
+    <numFmt numFmtId="189" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="190" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="191" formatCode="0.0000"/>
+    <numFmt numFmtId="192" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -571,16 +566,16 @@
   <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -588,14 +583,14 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="190" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -604,58 +599,58 @@
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="190" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="190" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="192" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="187" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="191" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="191" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="192" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -663,26 +658,26 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="189" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="188" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="190" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="190" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1049,20 +1044,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="8.25" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.5703125" style="6"/>
+    <col min="10" max="10" width="12.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
@@ -1117,7 +1112,7 @@
         <v>133204.31</v>
       </c>
       <c r="H2" s="66">
-        <f>G2-E2</f>
+        <f t="shared" ref="H2:H22" si="0">G2-E2</f>
         <v>6925.2299999999959</v>
       </c>
       <c r="I2" s="15"/>
@@ -1147,7 +1142,7 @@
         <v>119734.21</v>
       </c>
       <c r="H3" s="66">
-        <f>G3-E3</f>
+        <f t="shared" si="0"/>
         <v>3477.2800000000134</v>
       </c>
       <c r="I3" s="15"/>
@@ -1177,7 +1172,7 @@
         <v>24545.52</v>
       </c>
       <c r="H4" s="66">
-        <f>G4-E4</f>
+        <f t="shared" si="0"/>
         <v>2095.9000000000015</v>
       </c>
       <c r="I4" s="15"/>
@@ -1207,7 +1202,7 @@
         <v>25144.19</v>
       </c>
       <c r="H5" s="66">
-        <f>G5-E5</f>
+        <f t="shared" si="0"/>
         <v>8607.64</v>
       </c>
       <c r="I5" s="15"/>
@@ -1237,7 +1232,7 @@
         <v>25144.19</v>
       </c>
       <c r="H6" s="66">
-        <f>G6-E6</f>
+        <f t="shared" si="0"/>
         <v>8607.64</v>
       </c>
       <c r="I6" s="15"/>
@@ -1267,7 +1262,7 @@
         <v>20055.48</v>
       </c>
       <c r="H7" s="66">
-        <f>G7-E7</f>
+        <f t="shared" si="0"/>
         <v>9031.119999999999</v>
       </c>
       <c r="I7" s="15"/>
@@ -1297,7 +1292,7 @@
         <v>138442.69</v>
       </c>
       <c r="H8" s="66">
-        <f>G8-E8</f>
+        <f t="shared" si="0"/>
         <v>12163.61</v>
       </c>
       <c r="I8" s="15"/>
@@ -1327,7 +1322,7 @@
         <v>115343.96</v>
       </c>
       <c r="H9" s="66">
-        <f>G9-E9</f>
+        <f t="shared" si="0"/>
         <v>5597.4200000000128</v>
       </c>
       <c r="I9" s="15"/>
@@ -1357,7 +1352,7 @@
         <v>60864.89</v>
       </c>
       <c r="H10" s="66">
-        <f>G10-E10</f>
+        <f t="shared" si="0"/>
         <v>7998.0599999999977</v>
       </c>
       <c r="I10" s="15"/>
@@ -1387,7 +1382,7 @@
         <v>49390.36</v>
       </c>
       <c r="H11" s="66">
-        <f>G11-E11</f>
+        <f t="shared" si="0"/>
         <v>2035.6999999999971</v>
       </c>
       <c r="I11" s="15"/>
@@ -1417,7 +1412,7 @@
         <v>115343.96</v>
       </c>
       <c r="H12" s="66">
-        <f>G12-E12</f>
+        <f t="shared" si="0"/>
         <v>5597.4200000000128</v>
       </c>
       <c r="I12" s="15"/>
@@ -1447,7 +1442,7 @@
         <v>111751.93</v>
       </c>
       <c r="H13" s="66">
-        <f>G13-E13</f>
+        <f t="shared" si="0"/>
         <v>2005.3899999999994</v>
       </c>
       <c r="I13" s="15"/>
@@ -1477,7 +1472,7 @@
         <v>115743.07</v>
       </c>
       <c r="H14" s="66">
-        <f>G14-E14</f>
+        <f t="shared" si="0"/>
         <v>10009.390000000014</v>
       </c>
       <c r="I14" s="15"/>
@@ -1507,7 +1502,7 @@
         <v>74085.539999999994</v>
       </c>
       <c r="H15" s="66">
-        <f>G15-E15</f>
+        <f t="shared" si="0"/>
         <v>7187.6999999999971</v>
       </c>
       <c r="I15" s="15"/>
@@ -1537,7 +1532,7 @@
         <v>63982.97</v>
       </c>
       <c r="H16" s="66">
-        <f>G16-E16</f>
+        <f t="shared" si="0"/>
         <v>3098.4199999999983</v>
       </c>
       <c r="I16" s="15"/>
@@ -1567,7 +1562,7 @@
         <v>138442.69</v>
       </c>
       <c r="H17" s="66">
-        <f>G17-E17</f>
+        <f t="shared" si="0"/>
         <v>12163.61</v>
       </c>
       <c r="I17" s="15"/>
@@ -1597,7 +1592,7 @@
         <v>144429.4</v>
       </c>
       <c r="H18" s="66">
-        <f>G18-E18</f>
+        <f t="shared" si="0"/>
         <v>18150.319999999992</v>
       </c>
       <c r="I18" s="15"/>
@@ -1627,7 +1622,7 @@
         <v>72838.31</v>
       </c>
       <c r="H19" s="66">
-        <f>G19-E19</f>
+        <f t="shared" si="0"/>
         <v>-10846.64</v>
       </c>
       <c r="I19" s="15"/>
@@ -1657,7 +1652,7 @@
         <v>105964.78</v>
       </c>
       <c r="H20" s="66">
-        <f>G20-E20</f>
+        <f t="shared" si="0"/>
         <v>130.88999999999942</v>
       </c>
       <c r="I20" s="15"/>
@@ -1687,7 +1682,7 @@
         <v>65554.48</v>
       </c>
       <c r="H21" s="66">
-        <f>G21-E21</f>
+        <f t="shared" si="0"/>
         <v>-1644.0299999999988</v>
       </c>
       <c r="I21" s="15"/>
@@ -1717,7 +1712,7 @@
         <v>106264.11</v>
       </c>
       <c r="H22" s="66">
-        <f>G22-E22</f>
+        <f t="shared" si="0"/>
         <v>5040.4100000000035</v>
       </c>
       <c r="I22" s="15"/>
@@ -1842,26 +1837,26 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB73B3FB-8409-48F5-A2B7-3BA9D395158E}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -1893,7 +1888,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>60</v>
       </c>
@@ -2304,26 +2299,26 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C98757-5F3D-4FA1-98E2-779A87752594}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -2355,7 +2350,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>60</v>
       </c>
@@ -2429,7 +2424,7 @@
         <v>47893.68</v>
       </c>
       <c r="H4" s="66">
-        <f>G4-E4</f>
+        <f t="shared" ref="H4:H11" si="0">G4-E4</f>
         <v>-16623.909999999996</v>
       </c>
       <c r="I4" s="11"/>
@@ -2462,7 +2457,7 @@
         <v>44151.99</v>
       </c>
       <c r="H5" s="66">
-        <f>G5-E5</f>
+        <f t="shared" si="0"/>
         <v>-13475.370000000003</v>
       </c>
       <c r="I5" s="11"/>
@@ -2495,7 +2490,7 @@
         <v>48193.02</v>
       </c>
       <c r="H6" s="66">
-        <f>G6-E6</f>
+        <f t="shared" si="0"/>
         <v>-25469.780000000006</v>
       </c>
       <c r="I6" s="11"/>
@@ -2528,7 +2523,7 @@
         <v>101774.08</v>
       </c>
       <c r="H7" s="66">
-        <f>G7-E7</f>
+        <f t="shared" si="0"/>
         <v>-13681.069999999992</v>
       </c>
       <c r="I7" s="11"/>
@@ -2561,7 +2556,7 @@
         <v>92045.67</v>
       </c>
       <c r="H8" s="66">
-        <f>G8-E8</f>
+        <f t="shared" si="0"/>
         <v>-8676.9300000000076</v>
       </c>
       <c r="I8" s="11"/>
@@ -2594,7 +2589,7 @@
         <v>32807.18</v>
       </c>
       <c r="H9" s="66">
-        <f>G9-E9</f>
+        <f t="shared" si="0"/>
         <v>-15900.46</v>
       </c>
       <c r="I9" s="11"/>
@@ -2627,7 +2622,7 @@
         <v>34004.51</v>
       </c>
       <c r="H10" s="66">
-        <f>G10-E10</f>
+        <f t="shared" si="0"/>
         <v>-14703.129999999997</v>
       </c>
       <c r="I10" s="11"/>
@@ -2660,7 +2655,7 @@
         <v>109756.36</v>
       </c>
       <c r="H11" s="66">
-        <f>G11-E11</f>
+        <f t="shared" si="0"/>
         <v>4523.8000000000029</v>
       </c>
       <c r="I11" s="11"/>
@@ -2681,11 +2676,11 @@
       </c>
       <c r="F12" s="64"/>
       <c r="G12" s="66">
-        <f t="shared" ref="G12:H12" si="0">SUM(G4:G11)</f>
+        <f t="shared" ref="G12:H12" si="1">SUM(G4:G11)</f>
         <v>510626.49</v>
       </c>
       <c r="H12" s="66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-104006.85000000002</v>
       </c>
       <c r="K12" s="7"/>
@@ -2898,26 +2893,26 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8BBD29C-D904-43CE-A7C2-0CB7DA792816}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -2949,7 +2944,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>88</v>
       </c>
@@ -2967,7 +2962,7 @@
         <v>0.3</v>
       </c>
       <c r="G2" s="65">
-        <f>C2*F2</f>
+        <f t="shared" ref="G2:G11" si="0">C2*F2</f>
         <v>6000</v>
       </c>
       <c r="H2" s="66">
@@ -2981,7 +2976,7 @@
       <c r="M2" s="15"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
         <v>9</v>
       </c>
@@ -2999,7 +2994,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G3" s="65">
-        <f>C3*F3</f>
+        <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="H3" s="66">
@@ -3013,7 +3008,7 @@
       <c r="M3" s="15"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
         <v>29</v>
       </c>
@@ -3031,7 +3026,7 @@
         <v>0.26</v>
       </c>
       <c r="G4" s="65">
-        <f>C4*F4</f>
+        <f t="shared" si="0"/>
         <v>10400</v>
       </c>
       <c r="H4" s="66">
@@ -3045,7 +3040,7 @@
       <c r="M4" s="15"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
         <v>64</v>
       </c>
@@ -3063,7 +3058,7 @@
         <v>0.23</v>
       </c>
       <c r="G5" s="65">
-        <f>C5*F5</f>
+        <f t="shared" si="0"/>
         <v>29900</v>
       </c>
       <c r="H5" s="66">
@@ -3077,7 +3072,7 @@
       <c r="M5" s="15"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
         <v>15</v>
       </c>
@@ -3095,7 +3090,7 @@
         <v>2.25</v>
       </c>
       <c r="G6" s="65">
-        <f>C6*F6</f>
+        <f t="shared" si="0"/>
         <v>54000</v>
       </c>
       <c r="H6" s="66">
@@ -3108,7 +3103,7 @@
       <c r="M6" s="15"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
         <v>79</v>
       </c>
@@ -3126,7 +3121,7 @@
         <v>0.25530000000000003</v>
       </c>
       <c r="G7" s="65">
-        <f>C7*F7</f>
+        <f t="shared" si="0"/>
         <v>7659.0000000000009</v>
       </c>
       <c r="H7" s="66">
@@ -3140,7 +3135,7 @@
       <c r="M7" s="15"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61" t="s">
         <v>80</v>
       </c>
@@ -3158,7 +3153,7 @@
         <v>0.18940000000000001</v>
       </c>
       <c r="G8" s="65">
-        <f>C8*F8</f>
+        <f t="shared" si="0"/>
         <v>7576.0000000000009</v>
       </c>
       <c r="H8" s="66">
@@ -3172,7 +3167,7 @@
       <c r="M8" s="15"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
         <v>8</v>
       </c>
@@ -3190,7 +3185,7 @@
         <v>0.4</v>
       </c>
       <c r="G9" s="65">
-        <f>C9*F9</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="H9" s="66">
@@ -3204,7 +3199,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
         <v>90</v>
       </c>
@@ -3222,7 +3217,7 @@
         <v>0.19109999999999999</v>
       </c>
       <c r="G10" s="65">
-        <f>C10*F10</f>
+        <f t="shared" si="0"/>
         <v>3822</v>
       </c>
       <c r="H10" s="66">
@@ -3236,7 +3231,7 @@
       <c r="M10" s="15"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
         <v>96</v>
       </c>
@@ -3254,7 +3249,7 @@
         <v>0.1003</v>
       </c>
       <c r="G11" s="65">
-        <f>C11*F11</f>
+        <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="H11" s="66">
@@ -3310,7 +3305,7 @@
         <v>107760.79</v>
       </c>
       <c r="H13" s="66">
-        <f>G13-E13</f>
+        <f t="shared" ref="H13:H18" si="1">G13-E13</f>
         <v>6737.5199999999895</v>
       </c>
       <c r="I13" s="11"/>
@@ -3343,7 +3338,7 @@
         <v>34962.39</v>
       </c>
       <c r="H14" s="66">
-        <f>G14-E14</f>
+        <f t="shared" si="1"/>
         <v>-13745.25</v>
       </c>
       <c r="I14" s="11"/>
@@ -3376,7 +3371,7 @@
         <v>49140.91</v>
       </c>
       <c r="H15" s="66">
-        <f>G15-E15</f>
+        <f t="shared" si="1"/>
         <v>-24772.440000000002</v>
       </c>
       <c r="I15" s="11"/>
@@ -3409,7 +3404,7 @@
         <v>50637.599999999999</v>
       </c>
       <c r="H16" s="66">
-        <f>G16-E16</f>
+        <f t="shared" si="1"/>
         <v>-23275.750000000007</v>
       </c>
       <c r="I16" s="11"/>
@@ -3442,7 +3437,7 @@
         <v>92794.01</v>
       </c>
       <c r="H17" s="66">
-        <f>G17-E17</f>
+        <f t="shared" si="1"/>
         <v>-15445.200000000012</v>
       </c>
       <c r="I17" s="11"/>
@@ -3475,7 +3470,7 @@
         <v>49390.36</v>
       </c>
       <c r="H18" s="66">
-        <f>G18-E18</f>
+        <f t="shared" si="1"/>
         <v>-1722.5999999999985</v>
       </c>
       <c r="I18" s="11"/>
@@ -3591,7 +3586,7 @@
         <v>97</v>
       </c>
       <c r="H24" s="69">
-        <v>34450</v>
+        <v>29530</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="15"/>
@@ -3609,7 +3604,7 @@
       </c>
       <c r="H25" s="77">
         <f>H23+H24</f>
-        <v>643715</v>
+        <v>638795</v>
       </c>
       <c r="I25" s="11"/>
       <c r="J25" s="7"/>
@@ -3630,7 +3625,7 @@
       </c>
       <c r="H26" s="70">
         <f>H22-H25</f>
-        <v>-193820.76799999992</v>
+        <v>-188900.76799999992</v>
       </c>
       <c r="I26" s="11"/>
       <c r="J26" s="7"/>
@@ -3671,7 +3666,7 @@
       </c>
       <c r="H28" s="79">
         <f>H26+H27</f>
-        <v>-81820.767999999924</v>
+        <v>-76900.767999999924</v>
       </c>
       <c r="I28" s="11"/>
       <c r="J28" s="7"/>
@@ -3717,26 +3712,26 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C58482DA-743D-4274-94F0-2300C47BC2D3}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="41" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="40" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="38" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.25" style="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.25" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.875" style="30" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" style="29" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="29"/>
+    <col min="12" max="12" width="10.625" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.375" style="29" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="31" customFormat="1" ht="18.75">
+    <row r="1" spans="1:14" s="31" customFormat="1" ht="18">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3774,7 +3769,7 @@
       <c r="M1" s="29"/>
       <c r="N1" s="29"/>
     </row>
-    <row r="2" spans="1:14" ht="15">
+    <row r="2" spans="1:14" ht="14.4">
       <c r="A2" s="21" t="s">
         <v>39</v>
       </c>
@@ -3797,14 +3792,14 @@
         <v>0</v>
       </c>
       <c r="H2" s="19">
-        <f>G2-E2</f>
+        <f t="shared" ref="H2:H42" si="0">G2-E2</f>
         <v>0</v>
       </c>
       <c r="I2" s="34">
         <v>0</v>
       </c>
       <c r="J2" s="19">
-        <f>C2*D2</f>
+        <f t="shared" ref="J2:J15" si="1">C2*D2</f>
         <v>4800</v>
       </c>
       <c r="K2" s="30">
@@ -3814,7 +3809,7 @@
       <c r="L2" s="38"/>
       <c r="M2" s="38"/>
     </row>
-    <row r="3" spans="1:14" ht="15">
+    <row r="3" spans="1:14" ht="14.4">
       <c r="A3" s="21" t="s">
         <v>101</v>
       </c>
@@ -3837,14 +3832,14 @@
         <v>0</v>
       </c>
       <c r="H3" s="19">
-        <f>G3-E3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I3" s="34">
         <v>0</v>
       </c>
       <c r="J3" s="19">
-        <f>C3*D3</f>
+        <f t="shared" si="1"/>
         <v>1600</v>
       </c>
       <c r="K3" s="30">
@@ -3854,7 +3849,7 @@
       <c r="L3" s="38"/>
       <c r="M3" s="38"/>
     </row>
-    <row r="4" spans="1:14" ht="15">
+    <row r="4" spans="1:14" ht="14.4">
       <c r="A4" s="21" t="s">
         <v>40</v>
       </c>
@@ -3877,14 +3872,14 @@
         <v>0</v>
       </c>
       <c r="H4" s="19">
-        <f>G4-E4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I4" s="34">
         <v>0</v>
       </c>
       <c r="J4" s="19">
-        <f>C4*D4</f>
+        <f t="shared" si="1"/>
         <v>15660</v>
       </c>
       <c r="K4" s="30">
@@ -3894,7 +3889,7 @@
       <c r="L4" s="38"/>
       <c r="M4" s="38"/>
     </row>
-    <row r="5" spans="1:14" ht="15">
+    <row r="5" spans="1:14" ht="14.4">
       <c r="A5" s="21" t="s">
         <v>44</v>
       </c>
@@ -3917,14 +3912,14 @@
         <v>0</v>
       </c>
       <c r="H5" s="19">
-        <f>G5-E5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I5" s="34">
         <v>0</v>
       </c>
       <c r="J5" s="19">
-        <f>C5*D5</f>
+        <f t="shared" si="1"/>
         <v>1738</v>
       </c>
       <c r="K5" s="30">
@@ -3933,7 +3928,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="38"/>
     </row>
-    <row r="6" spans="1:14" ht="15">
+    <row r="6" spans="1:14" ht="14.4">
       <c r="A6" s="21" t="s">
         <v>102</v>
       </c>
@@ -3956,14 +3951,14 @@
         <v>0</v>
       </c>
       <c r="H6" s="19">
-        <f>G6-E6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I6" s="34">
         <v>0</v>
       </c>
       <c r="J6" s="19">
-        <f>C6*D6</f>
+        <f t="shared" si="1"/>
         <v>5250</v>
       </c>
       <c r="K6" s="30">
@@ -3973,7 +3968,7 @@
       <c r="L6" s="38"/>
       <c r="M6" s="38"/>
     </row>
-    <row r="7" spans="1:14" ht="15">
+    <row r="7" spans="1:14" ht="14.4">
       <c r="A7" s="21" t="s">
         <v>103</v>
       </c>
@@ -3996,14 +3991,14 @@
         <v>0</v>
       </c>
       <c r="H7" s="19">
-        <f>G7-E7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I7" s="34">
         <v>0</v>
       </c>
       <c r="J7" s="19">
-        <f>C7*D7</f>
+        <f t="shared" si="1"/>
         <v>2470</v>
       </c>
       <c r="K7" s="30">
@@ -4013,7 +4008,7 @@
       <c r="L7" s="38"/>
       <c r="M7" s="38"/>
     </row>
-    <row r="8" spans="1:14" ht="15">
+    <row r="8" spans="1:14" ht="14.4">
       <c r="A8" s="21" t="s">
         <v>104</v>
       </c>
@@ -4036,14 +4031,14 @@
         <v>0</v>
       </c>
       <c r="H8" s="19">
-        <f>G8-E8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I8" s="34">
         <v>0</v>
       </c>
       <c r="J8" s="19">
-        <f>C8*D8</f>
+        <f t="shared" si="1"/>
         <v>6750</v>
       </c>
       <c r="K8" s="30">
@@ -4053,7 +4048,7 @@
       <c r="L8" s="38"/>
       <c r="M8" s="38"/>
     </row>
-    <row r="9" spans="1:14" ht="15">
+    <row r="9" spans="1:14" ht="14.4">
       <c r="A9" s="21" t="s">
         <v>105</v>
       </c>
@@ -4076,14 +4071,14 @@
         <v>0</v>
       </c>
       <c r="H9" s="19">
-        <f>G9-E9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I9" s="34">
         <v>0</v>
       </c>
       <c r="J9" s="19">
-        <f>C9*D9</f>
+        <f t="shared" si="1"/>
         <v>3300.0000000000005</v>
       </c>
       <c r="K9" s="30">
@@ -4093,7 +4088,7 @@
       <c r="L9" s="38"/>
       <c r="M9" s="38"/>
     </row>
-    <row r="10" spans="1:14" ht="15">
+    <row r="10" spans="1:14" ht="14.4">
       <c r="A10" s="21" t="s">
         <v>106</v>
       </c>
@@ -4116,14 +4111,14 @@
         <v>0</v>
       </c>
       <c r="H10" s="19">
-        <f>G10-E10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I10" s="34">
         <v>0</v>
       </c>
       <c r="J10" s="19">
-        <f>C10*D10</f>
+        <f t="shared" si="1"/>
         <v>1960.0000000000002</v>
       </c>
       <c r="K10" s="30">
@@ -4132,7 +4127,7 @@
       </c>
       <c r="L10" s="29"/>
     </row>
-    <row r="11" spans="1:14" ht="15">
+    <row r="11" spans="1:14" ht="14.4">
       <c r="A11" s="21" t="s">
         <v>41</v>
       </c>
@@ -4155,14 +4150,14 @@
         <v>0</v>
       </c>
       <c r="H11" s="19">
-        <f>G11-E11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="34">
         <v>0</v>
       </c>
       <c r="J11" s="19">
-        <f>C11*D11</f>
+        <f t="shared" si="1"/>
         <v>22000</v>
       </c>
       <c r="K11" s="30">
@@ -4171,7 +4166,7 @@
       </c>
       <c r="L11" s="29"/>
     </row>
-    <row r="12" spans="1:14" ht="15">
+    <row r="12" spans="1:14" ht="14.4">
       <c r="A12" s="21" t="s">
         <v>107</v>
       </c>
@@ -4194,14 +4189,14 @@
         <v>0</v>
       </c>
       <c r="H12" s="19">
-        <f>G12-E12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I12" s="34">
         <v>0</v>
       </c>
       <c r="J12" s="19">
-        <f>C12*D12</f>
+        <f t="shared" si="1"/>
         <v>18750</v>
       </c>
       <c r="K12" s="30">
@@ -4210,7 +4205,7 @@
       </c>
       <c r="L12" s="29"/>
     </row>
-    <row r="13" spans="1:14" ht="15">
+    <row r="13" spans="1:14" ht="14.4">
       <c r="A13" s="21" t="s">
         <v>108</v>
       </c>
@@ -4233,14 +4228,14 @@
         <v>0</v>
       </c>
       <c r="H13" s="19">
-        <f>G13-E13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I13" s="34">
         <v>0</v>
       </c>
       <c r="J13" s="19">
-        <f>C13*D13</f>
+        <f t="shared" si="1"/>
         <v>25900</v>
       </c>
       <c r="K13" s="30">
@@ -4248,7 +4243,7 @@
       </c>
       <c r="L13" s="29"/>
     </row>
-    <row r="14" spans="1:14" ht="15">
+    <row r="14" spans="1:14" ht="14.4">
       <c r="A14" s="21" t="s">
         <v>109</v>
       </c>
@@ -4271,14 +4266,14 @@
         <v>0</v>
       </c>
       <c r="H14" s="19">
-        <f>G14-E14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I14" s="34">
         <v>0</v>
       </c>
       <c r="J14" s="19">
-        <f>C14*D14</f>
+        <f t="shared" si="1"/>
         <v>1040</v>
       </c>
       <c r="K14" s="30">
@@ -4288,7 +4283,7 @@
       <c r="L14" s="38"/>
       <c r="M14" s="38"/>
     </row>
-    <row r="15" spans="1:14" ht="15">
+    <row r="15" spans="1:14" ht="14.4">
       <c r="A15" s="21" t="s">
         <v>109</v>
       </c>
@@ -4311,14 +4306,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="19">
-        <f>G15-E15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I15" s="34">
         <v>0</v>
       </c>
       <c r="J15" s="19">
-        <f>C15*D15</f>
+        <f t="shared" si="1"/>
         <v>640</v>
       </c>
       <c r="K15" s="30">
@@ -4330,7 +4325,7 @@
         <v>106496.2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15">
+    <row r="16" spans="1:14" ht="27.6">
       <c r="A16" s="21" t="s">
         <v>62</v>
       </c>
@@ -4353,24 +4348,24 @@
         <v>119734.21</v>
       </c>
       <c r="H16" s="30">
-        <f>G16-E16</f>
+        <f t="shared" si="0"/>
         <v>10993.89</v>
       </c>
       <c r="I16" s="37">
-        <f>H16/E16</f>
+        <f t="shared" ref="I16:I42" si="2">H16/E16</f>
         <v>0.10110224064082209</v>
       </c>
       <c r="J16" s="30">
         <v>0</v>
       </c>
       <c r="K16" s="30">
-        <f>H16</f>
+        <f t="shared" ref="K16:K42" si="3">H16</f>
         <v>10993.89</v>
       </c>
       <c r="M16" s="38"/>
       <c r="N16" s="38"/>
     </row>
-    <row r="17" spans="1:14" ht="15">
+    <row r="17" spans="1:14" ht="27.6">
       <c r="A17" s="21" t="s">
         <v>62</v>
       </c>
@@ -4393,18 +4388,18 @@
         <v>120732</v>
       </c>
       <c r="H17" s="30">
-        <f>G17-E17</f>
+        <f t="shared" si="0"/>
         <v>11991.679999999993</v>
       </c>
       <c r="I17" s="37">
-        <f>H17/E17</f>
+        <f t="shared" si="2"/>
         <v>0.11027813786091481</v>
       </c>
       <c r="J17" s="30">
         <v>0</v>
       </c>
       <c r="K17" s="30">
-        <f>H17</f>
+        <f t="shared" si="3"/>
         <v>11991.679999999993</v>
       </c>
       <c r="L17" s="38">
@@ -4413,7 +4408,7 @@
       </c>
       <c r="M17" s="38"/>
     </row>
-    <row r="18" spans="1:14" ht="15">
+    <row r="18" spans="1:14" ht="14.4">
       <c r="A18" s="21" t="s">
         <v>110</v>
       </c>
@@ -4436,23 +4431,23 @@
         <v>94989.15</v>
       </c>
       <c r="H18" s="30">
-        <f>G18-E18</f>
+        <f t="shared" si="0"/>
         <v>-2827.0200000000041</v>
       </c>
       <c r="I18" s="37">
-        <f>H18/E18</f>
+        <f t="shared" si="2"/>
         <v>-2.890135649351231E-2</v>
       </c>
       <c r="J18" s="30">
         <v>0</v>
       </c>
       <c r="K18" s="30">
-        <f>H18</f>
+        <f t="shared" si="3"/>
         <v>-2827.0200000000041</v>
       </c>
       <c r="L18" s="29"/>
     </row>
-    <row r="19" spans="1:14" ht="15">
+    <row r="19" spans="1:14" ht="27.6">
       <c r="A19" s="21" t="s">
         <v>8</v>
       </c>
@@ -4475,24 +4470,24 @@
         <v>128714.28</v>
       </c>
       <c r="H19" s="30">
-        <f>G19-E19</f>
+        <f t="shared" si="0"/>
         <v>2435.1999999999971</v>
       </c>
       <c r="I19" s="37">
-        <f>H19/E19</f>
+        <f t="shared" si="2"/>
         <v>1.9284270997222953E-2</v>
       </c>
       <c r="J19" s="30">
         <v>0</v>
       </c>
       <c r="K19" s="30">
-        <f>H19</f>
+        <f t="shared" si="3"/>
         <v>2435.1999999999971</v>
       </c>
       <c r="L19" s="38"/>
       <c r="M19" s="38"/>
     </row>
-    <row r="20" spans="1:14" ht="15">
+    <row r="20" spans="1:14" ht="14.4">
       <c r="A20" s="21" t="s">
         <v>68</v>
       </c>
@@ -4515,24 +4510,24 @@
         <v>92794.01</v>
       </c>
       <c r="H20" s="30">
-        <f>G20-E20</f>
+        <f t="shared" si="0"/>
         <v>12616.819999999992</v>
       </c>
       <c r="I20" s="37">
-        <f>H20/E20</f>
+        <f t="shared" si="2"/>
         <v>0.15736171347486724</v>
       </c>
       <c r="J20" s="30">
         <v>0</v>
       </c>
       <c r="K20" s="30">
-        <f>H20</f>
+        <f t="shared" si="3"/>
         <v>12616.819999999992</v>
       </c>
       <c r="L20" s="38"/>
       <c r="M20" s="38"/>
     </row>
-    <row r="21" spans="1:14" ht="15">
+    <row r="21" spans="1:14" ht="14.4">
       <c r="A21" s="21" t="s">
         <v>68</v>
       </c>
@@ -4555,24 +4550,24 @@
         <v>91047.89</v>
       </c>
       <c r="H21" s="30">
-        <f>G21-E21</f>
+        <f t="shared" si="0"/>
         <v>3855.1900000000023</v>
       </c>
       <c r="I21" s="37">
-        <f>H21/E21</f>
+        <f t="shared" si="2"/>
         <v>4.421459594667905E-2</v>
       </c>
       <c r="J21" s="30">
         <v>0</v>
       </c>
       <c r="K21" s="30">
-        <f>H21</f>
+        <f t="shared" si="3"/>
         <v>3855.1900000000023</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="38"/>
     </row>
-    <row r="22" spans="1:14" ht="15">
+    <row r="22" spans="1:14" ht="14.4">
       <c r="A22" s="21" t="s">
         <v>111</v>
       </c>
@@ -4595,23 +4590,23 @@
         <v>52383.71</v>
       </c>
       <c r="H22" s="30">
-        <f>G22-E22</f>
+        <f t="shared" si="0"/>
         <v>-10455.169999999998</v>
       </c>
       <c r="I22" s="37">
-        <f>H22/E22</f>
+        <f t="shared" si="2"/>
         <v>-0.16638059112447579</v>
       </c>
       <c r="J22" s="30">
         <v>0</v>
       </c>
       <c r="K22" s="30">
-        <f>H22</f>
+        <f t="shared" si="3"/>
         <v>-10455.169999999998</v>
       </c>
       <c r="L22" s="29"/>
     </row>
-    <row r="23" spans="1:14" ht="29.25">
+    <row r="23" spans="1:14" ht="28.8">
       <c r="A23" s="21" t="s">
         <v>111</v>
       </c>
@@ -4634,24 +4629,24 @@
         <v>52084.39</v>
       </c>
       <c r="H23" s="30">
-        <f>G23-E23</f>
+        <f t="shared" si="0"/>
         <v>-10754.489999999998</v>
       </c>
       <c r="I23" s="37">
-        <f>H23/E23</f>
+        <f t="shared" si="2"/>
         <v>-0.17114388416852749</v>
       </c>
       <c r="J23" s="30">
         <v>0</v>
       </c>
       <c r="K23" s="30">
-        <f>H23</f>
+        <f t="shared" si="3"/>
         <v>-10754.489999999998</v>
       </c>
       <c r="L23" s="29"/>
       <c r="N23" s="49"/>
     </row>
-    <row r="24" spans="1:14" ht="15">
+    <row r="24" spans="1:14" ht="27.6">
       <c r="A24" s="21" t="s">
         <v>112</v>
       </c>
@@ -4674,24 +4669,24 @@
         <v>106862.78</v>
       </c>
       <c r="H24" s="30">
-        <f>G24-E24</f>
+        <f t="shared" si="0"/>
         <v>-474.44000000000233</v>
       </c>
       <c r="I24" s="37">
-        <f>H24/E24</f>
+        <f t="shared" si="2"/>
         <v>-4.4200883905881139E-3</v>
       </c>
       <c r="J24" s="30">
         <v>0</v>
       </c>
       <c r="K24" s="30">
-        <f>H24</f>
+        <f t="shared" si="3"/>
         <v>-474.44000000000233</v>
       </c>
       <c r="L24" s="29"/>
       <c r="N24" s="15"/>
     </row>
-    <row r="25" spans="1:14" ht="15">
+    <row r="25" spans="1:14" ht="27.6">
       <c r="A25" s="21" t="s">
         <v>113</v>
       </c>
@@ -4714,18 +4709,18 @@
         <v>146674.41</v>
       </c>
       <c r="H25" s="30">
-        <f>G25-E25</f>
+        <f t="shared" si="0"/>
         <v>-20695.48000000001</v>
       </c>
       <c r="I25" s="37">
-        <f>H25/E25</f>
+        <f t="shared" si="2"/>
         <v>-0.12365115374097461</v>
       </c>
       <c r="J25" s="30">
         <v>0</v>
       </c>
       <c r="K25" s="30">
-        <f>H25</f>
+        <f t="shared" si="3"/>
         <v>-20695.48000000001</v>
       </c>
       <c r="L25" s="38">
@@ -4735,7 +4730,7 @@
       <c r="M25" s="38"/>
       <c r="N25" s="38"/>
     </row>
-    <row r="26" spans="1:14" ht="15">
+    <row r="26" spans="1:14" ht="27.6">
       <c r="A26" s="21" t="s">
         <v>114</v>
       </c>
@@ -4758,24 +4753,24 @@
         <v>114745.29</v>
       </c>
       <c r="H26" s="30">
-        <f>G26-E26</f>
+        <f t="shared" si="0"/>
         <v>-2513.8500000000058</v>
       </c>
       <c r="I26" s="37">
-        <f>H26/E26</f>
+        <f t="shared" si="2"/>
         <v>-2.1438414097186845E-2</v>
       </c>
       <c r="J26" s="30">
         <v>0</v>
       </c>
       <c r="K26" s="30">
-        <f>H26</f>
+        <f t="shared" si="3"/>
         <v>-2513.8500000000058</v>
       </c>
       <c r="L26" s="29"/>
       <c r="N26" s="50"/>
     </row>
-    <row r="27" spans="1:14" ht="15">
+    <row r="27" spans="1:14" ht="27.6">
       <c r="A27" s="21" t="s">
         <v>57</v>
       </c>
@@ -4798,25 +4793,25 @@
         <v>117738.64</v>
       </c>
       <c r="H27" s="30">
-        <f>G27-E27</f>
+        <f t="shared" si="0"/>
         <v>-16057.050000000003</v>
       </c>
       <c r="I27" s="37">
-        <f>H27/E27</f>
+        <f t="shared" si="2"/>
         <v>-0.12001171338179879</v>
       </c>
       <c r="J27" s="30">
         <v>0</v>
       </c>
       <c r="K27" s="30">
-        <f>H27</f>
+        <f t="shared" si="3"/>
         <v>-16057.050000000003</v>
       </c>
       <c r="L27" s="38"/>
       <c r="M27" s="38"/>
       <c r="N27" s="50"/>
     </row>
-    <row r="28" spans="1:14" ht="15">
+    <row r="28" spans="1:14" ht="14.4">
       <c r="A28" s="21" t="s">
         <v>57</v>
       </c>
@@ -4839,25 +4834,25 @@
         <v>35171.919999999998</v>
       </c>
       <c r="H28" s="30">
-        <f>G28-E28</f>
+        <f t="shared" si="0"/>
         <v>-4966.7799999999988</v>
       </c>
       <c r="I28" s="37">
-        <f>H28/E28</f>
+        <f t="shared" si="2"/>
         <v>-0.12374043005877119</v>
       </c>
       <c r="J28" s="30">
         <v>0</v>
       </c>
       <c r="K28" s="30">
-        <f>H28</f>
+        <f t="shared" si="3"/>
         <v>-4966.7799999999988</v>
       </c>
       <c r="L28" s="38"/>
       <c r="M28" s="38"/>
       <c r="N28" s="50"/>
     </row>
-    <row r="29" spans="1:14" ht="15">
+    <row r="29" spans="1:14" ht="14.4">
       <c r="A29" s="21" t="s">
         <v>57</v>
       </c>
@@ -4880,25 +4875,25 @@
         <v>58619.88</v>
       </c>
       <c r="H29" s="30">
-        <f>G29-E29</f>
+        <f t="shared" si="0"/>
         <v>-8277.9599999999991</v>
       </c>
       <c r="I29" s="37">
-        <f>H29/E29</f>
+        <f t="shared" si="2"/>
         <v>-0.12374031807304989</v>
       </c>
       <c r="J29" s="30">
         <v>0</v>
       </c>
       <c r="K29" s="30">
-        <f>H29</f>
+        <f t="shared" si="3"/>
         <v>-8277.9599999999991</v>
       </c>
       <c r="L29" s="38"/>
       <c r="M29" s="38"/>
       <c r="N29" s="50"/>
     </row>
-    <row r="30" spans="1:14" ht="15">
+    <row r="30" spans="1:14" ht="14.4">
       <c r="A30" s="21" t="s">
         <v>115</v>
       </c>
@@ -4921,25 +4916,25 @@
         <v>41757.31</v>
       </c>
       <c r="H30" s="30">
-        <f>G30-E30</f>
+        <f t="shared" si="0"/>
         <v>2971.5899999999965</v>
       </c>
       <c r="I30" s="37">
-        <f>H30/E30</f>
+        <f t="shared" si="2"/>
         <v>7.6615568822752195E-2</v>
       </c>
       <c r="J30" s="30">
         <v>0</v>
       </c>
       <c r="K30" s="30">
-        <f>H30</f>
+        <f t="shared" si="3"/>
         <v>2971.5899999999965</v>
       </c>
       <c r="L30" s="38"/>
       <c r="M30" s="38"/>
       <c r="N30" s="50"/>
     </row>
-    <row r="31" spans="1:14" ht="15">
+    <row r="31" spans="1:14" ht="14.4">
       <c r="A31" s="21" t="s">
         <v>115</v>
       </c>
@@ -4962,18 +4957,18 @@
         <v>72588.87</v>
       </c>
       <c r="H31" s="30">
-        <f>G31-E31</f>
+        <f t="shared" si="0"/>
         <v>7945.9999999999927</v>
       </c>
       <c r="I31" s="37">
-        <f>H31/E31</f>
+        <f t="shared" si="2"/>
         <v>0.12292152251284623</v>
       </c>
       <c r="J31" s="30">
         <v>0</v>
       </c>
       <c r="K31" s="30">
-        <f>H31</f>
+        <f t="shared" si="3"/>
         <v>7945.9999999999927</v>
       </c>
       <c r="L31" s="38">
@@ -4983,7 +4978,7 @@
       <c r="M31" s="38"/>
       <c r="N31" s="50"/>
     </row>
-    <row r="32" spans="1:14" ht="15">
+    <row r="32" spans="1:14" ht="27.6">
       <c r="A32" s="21" t="s">
         <v>13</v>
       </c>
@@ -5006,24 +5001,24 @@
         <v>167627.9</v>
       </c>
       <c r="H32" s="30">
-        <f>G32-E32</f>
+        <f t="shared" si="0"/>
         <v>9027.3899999999849</v>
       </c>
       <c r="I32" s="37">
-        <f>H32/E32</f>
+        <f t="shared" si="2"/>
         <v>5.6919047738244882E-2</v>
       </c>
       <c r="J32" s="30">
         <v>0</v>
       </c>
       <c r="K32" s="30">
-        <f>H32</f>
+        <f t="shared" si="3"/>
         <v>9027.3899999999849</v>
       </c>
       <c r="L32" s="29"/>
       <c r="N32" s="15"/>
     </row>
-    <row r="33" spans="1:14" ht="15">
+    <row r="33" spans="1:14" ht="27.6">
       <c r="A33" s="21" t="s">
         <v>116</v>
       </c>
@@ -5046,24 +5041,24 @@
         <v>172866.27</v>
       </c>
       <c r="H33" s="30">
-        <f>G33-E33</f>
+        <f t="shared" si="0"/>
         <v>3742.5099999999802</v>
       </c>
       <c r="I33" s="37">
-        <f>H33/E33</f>
+        <f t="shared" si="2"/>
         <v>2.2128824477412164E-2</v>
       </c>
       <c r="J33" s="30">
         <v>0</v>
       </c>
       <c r="K33" s="30">
-        <f>H33</f>
+        <f t="shared" si="3"/>
         <v>3742.5099999999802</v>
       </c>
       <c r="L33" s="29"/>
       <c r="N33" s="15"/>
     </row>
-    <row r="34" spans="1:14" ht="15">
+    <row r="34" spans="1:14" ht="27.6">
       <c r="A34" s="21" t="s">
         <v>76</v>
       </c>
@@ -5086,24 +5081,24 @@
         <v>305322.23999999999</v>
       </c>
       <c r="H34" s="30">
-        <f>G34-E34</f>
+        <f t="shared" si="0"/>
         <v>4657.7700000000186</v>
       </c>
       <c r="I34" s="37">
-        <f>H34/E34</f>
+        <f t="shared" si="2"/>
         <v>1.5491587682442222E-2</v>
       </c>
       <c r="J34" s="30">
         <v>0</v>
       </c>
       <c r="K34" s="30">
-        <f>H34</f>
+        <f t="shared" si="3"/>
         <v>4657.7700000000186</v>
       </c>
       <c r="L34" s="29"/>
       <c r="N34" s="15"/>
     </row>
-    <row r="35" spans="1:14" ht="15">
+    <row r="35" spans="1:14" ht="14.4">
       <c r="A35" s="21" t="s">
         <v>11</v>
       </c>
@@ -5126,24 +5121,24 @@
         <v>37716.269999999997</v>
       </c>
       <c r="H35" s="30">
-        <f>G35-E35</f>
+        <f t="shared" si="0"/>
         <v>4643.18</v>
       </c>
       <c r="I35" s="37">
-        <f>H35/E35</f>
+        <f t="shared" si="2"/>
         <v>0.14039147838922825</v>
       </c>
       <c r="J35" s="30">
         <v>0</v>
       </c>
       <c r="K35" s="30">
-        <f>H35</f>
+        <f t="shared" si="3"/>
         <v>4643.18</v>
       </c>
       <c r="L35" s="29"/>
       <c r="N35" s="15"/>
     </row>
-    <row r="36" spans="1:14" ht="15">
+    <row r="36" spans="1:14" ht="14.4">
       <c r="A36" s="21" t="s">
         <v>48</v>
       </c>
@@ -5166,24 +5161,24 @@
         <v>46895.9</v>
       </c>
       <c r="H36" s="30">
-        <f>G36-E36</f>
+        <f t="shared" si="0"/>
         <v>7809.5200000000041</v>
       </c>
       <c r="I36" s="37">
-        <f>H36/E36</f>
+        <f t="shared" si="2"/>
         <v>0.1998015677072168</v>
       </c>
       <c r="J36" s="30">
         <v>0</v>
       </c>
       <c r="K36" s="30">
-        <f>H36</f>
+        <f t="shared" si="3"/>
         <v>7809.5200000000041</v>
       </c>
       <c r="L36" s="29"/>
       <c r="N36" s="50"/>
     </row>
-    <row r="37" spans="1:14" ht="15">
+    <row r="37" spans="1:14" ht="14.4">
       <c r="A37" s="21" t="s">
         <v>48</v>
       </c>
@@ -5206,18 +5201,18 @@
         <v>47145.34</v>
       </c>
       <c r="H37" s="30">
-        <f>G37-E37</f>
+        <f t="shared" si="0"/>
         <v>8058.9599999999991</v>
       </c>
       <c r="I37" s="37">
-        <f>H37/E37</f>
+        <f t="shared" si="2"/>
         <v>0.2061833303570195</v>
       </c>
       <c r="J37" s="30">
         <v>0</v>
       </c>
       <c r="K37" s="30">
-        <f>H37</f>
+        <f t="shared" si="3"/>
         <v>8058.9599999999991</v>
       </c>
       <c r="L37" s="30">
@@ -5226,7 +5221,7 @@
       </c>
       <c r="N37" s="15"/>
     </row>
-    <row r="38" spans="1:14" ht="15">
+    <row r="38" spans="1:14" ht="14.4">
       <c r="A38" s="21" t="s">
         <v>16</v>
       </c>
@@ -5249,25 +5244,25 @@
         <v>65105.48</v>
       </c>
       <c r="H38" s="30">
-        <f>G38-E38</f>
+        <f t="shared" si="0"/>
         <v>8730.8900000000067</v>
       </c>
       <c r="I38" s="37">
-        <f>H38/E38</f>
+        <f t="shared" si="2"/>
         <v>0.15487278931873397</v>
       </c>
       <c r="J38" s="30">
         <v>0</v>
       </c>
       <c r="K38" s="30">
-        <f>H38</f>
+        <f t="shared" si="3"/>
         <v>8730.8900000000067</v>
       </c>
       <c r="L38" s="38"/>
       <c r="M38" s="38"/>
       <c r="N38" s="15"/>
     </row>
-    <row r="39" spans="1:14" ht="15">
+    <row r="39" spans="1:14" ht="14.4">
       <c r="A39" s="21" t="s">
         <v>16</v>
       </c>
@@ -5290,25 +5285,25 @@
         <v>65105.48</v>
       </c>
       <c r="H39" s="30">
-        <f>G39-E39</f>
+        <f t="shared" si="0"/>
         <v>8730.8900000000067</v>
       </c>
       <c r="I39" s="37">
-        <f>H39/E39</f>
+        <f t="shared" si="2"/>
         <v>0.15487278931873397</v>
       </c>
       <c r="J39" s="30">
         <v>0</v>
       </c>
       <c r="K39" s="30">
-        <f>H39</f>
+        <f t="shared" si="3"/>
         <v>8730.8900000000067</v>
       </c>
       <c r="L39" s="38"/>
       <c r="M39" s="38"/>
       <c r="N39" s="15"/>
     </row>
-    <row r="40" spans="1:14" ht="15">
+    <row r="40" spans="1:14" ht="14.4">
       <c r="A40" s="21" t="s">
         <v>16</v>
       </c>
@@ -5331,18 +5326,18 @@
         <v>67350.490000000005</v>
       </c>
       <c r="H40" s="30">
-        <f>G40-E40</f>
+        <f t="shared" si="0"/>
         <v>10975.900000000009</v>
       </c>
       <c r="I40" s="37">
-        <f>H40/E40</f>
+        <f t="shared" si="2"/>
         <v>0.19469587273273312</v>
       </c>
       <c r="J40" s="30">
         <v>0</v>
       </c>
       <c r="K40" s="30">
-        <f>H40</f>
+        <f t="shared" si="3"/>
         <v>10975.900000000009</v>
       </c>
       <c r="L40" s="38">
@@ -5352,7 +5347,7 @@
       <c r="M40" s="38"/>
       <c r="N40" s="38"/>
     </row>
-    <row r="41" spans="1:14" ht="15">
+    <row r="41" spans="1:14" ht="14.4">
       <c r="A41" s="21" t="s">
         <v>14</v>
       </c>
@@ -5375,24 +5370,24 @@
         <v>47893.68</v>
       </c>
       <c r="H41" s="30">
-        <f>G41-E41</f>
+        <f t="shared" si="0"/>
         <v>11062.29</v>
       </c>
       <c r="I41" s="37">
-        <f>H41/E41</f>
+        <f t="shared" si="2"/>
         <v>0.3003495116529678</v>
       </c>
       <c r="J41" s="30">
         <v>0</v>
       </c>
       <c r="K41" s="30">
-        <f>H41</f>
+        <f t="shared" si="3"/>
         <v>11062.29</v>
       </c>
       <c r="L41" s="38"/>
       <c r="M41" s="38"/>
     </row>
-    <row r="42" spans="1:14" ht="15">
+    <row r="42" spans="1:14" ht="14.4">
       <c r="A42" s="21" t="s">
         <v>14</v>
       </c>
@@ -5415,18 +5410,18 @@
         <v>49390.36</v>
       </c>
       <c r="H42" s="30">
-        <f>G42-E42</f>
+        <f t="shared" si="0"/>
         <v>12558.970000000001</v>
       </c>
       <c r="I42" s="37">
-        <f>H42/E42</f>
+        <f t="shared" si="2"/>
         <v>0.34098550176900738</v>
       </c>
       <c r="J42" s="30">
         <v>0</v>
       </c>
       <c r="K42" s="30">
-        <f>H42</f>
+        <f t="shared" si="3"/>
         <v>12558.970000000001</v>
       </c>
       <c r="L42" s="38">
@@ -5445,11 +5440,11 @@
         <v>2453271.7499999995</v>
       </c>
       <c r="G43" s="38">
-        <f t="shared" ref="G43:H43" si="0">SUM(G2:G42)</f>
+        <f t="shared" ref="G43:H43" si="4">SUM(G2:G42)</f>
         <v>2519058.1499999994</v>
       </c>
       <c r="H43" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>65786.399999999965</v>
       </c>
       <c r="I43" s="30" t="s">
@@ -5551,24 +5546,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="7.25" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="10.625" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.5703125" style="6"/>
+    <col min="16" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
@@ -5667,7 +5662,7 @@
         <v>65853.820000000007</v>
       </c>
       <c r="H4" s="66">
-        <f>G4-E4</f>
+        <f t="shared" ref="H4:H26" si="0">G4-E4</f>
         <v>5119.6000000000058</v>
       </c>
       <c r="I4" s="15"/>
@@ -5697,7 +5692,7 @@
         <v>54878.18</v>
       </c>
       <c r="H5" s="66">
-        <f>G5-E5</f>
+        <f t="shared" si="0"/>
         <v>4767.43</v>
       </c>
       <c r="I5" s="15"/>
@@ -5727,7 +5722,7 @@
         <v>73337.2</v>
       </c>
       <c r="H6" s="66">
-        <f>G6-E6</f>
+        <f t="shared" si="0"/>
         <v>-10347.75</v>
       </c>
       <c r="I6" s="15"/>
@@ -5757,7 +5752,7 @@
         <v>60465.78</v>
       </c>
       <c r="H7" s="66">
-        <f>G7-E7</f>
+        <f t="shared" si="0"/>
         <v>9954.1500000000015</v>
       </c>
       <c r="I7" s="15"/>
@@ -5787,7 +5782,7 @@
         <v>107760.79</v>
       </c>
       <c r="H8" s="66">
-        <f>G8-E8</f>
+        <f t="shared" si="0"/>
         <v>6537.0899999999965</v>
       </c>
       <c r="I8" s="15"/>
@@ -5817,7 +5812,7 @@
         <v>61962.45</v>
       </c>
       <c r="H9" s="66">
-        <f>G9-E9</f>
+        <f t="shared" si="0"/>
         <v>9045.5</v>
       </c>
       <c r="I9" s="15"/>
@@ -5847,7 +5842,7 @@
         <v>63159.8</v>
       </c>
       <c r="H10" s="66">
-        <f>G10-E10</f>
+        <f t="shared" si="0"/>
         <v>10242.850000000006</v>
       </c>
       <c r="I10" s="15"/>
@@ -5877,7 +5872,7 @@
         <v>55077.74</v>
       </c>
       <c r="H11" s="66">
-        <f>G11-E11</f>
+        <f t="shared" si="0"/>
         <v>2160.7900000000009</v>
       </c>
       <c r="I11" s="15"/>
@@ -5907,7 +5902,7 @@
         <v>107261.89</v>
       </c>
       <c r="H12" s="66">
-        <f>G12-E12</f>
+        <f t="shared" si="0"/>
         <v>6038.1900000000023</v>
       </c>
       <c r="I12" s="15"/>
@@ -5937,7 +5932,7 @@
         <v>246652.48</v>
       </c>
       <c r="H13" s="66">
-        <f>G13-E13</f>
+        <f t="shared" si="0"/>
         <v>-15526.939999999973</v>
       </c>
       <c r="I13" s="15"/>
@@ -5967,7 +5962,7 @@
         <v>92316.07</v>
       </c>
       <c r="H14" s="66">
-        <f>G14-E14</f>
+        <f t="shared" si="0"/>
         <v>-4948.8799999999901</v>
       </c>
       <c r="I14" s="15"/>
@@ -5997,7 +5992,7 @@
         <v>14696.38</v>
       </c>
       <c r="H15" s="66">
-        <f>G15-E15</f>
+        <f t="shared" si="0"/>
         <v>-787.84000000000015</v>
       </c>
       <c r="I15" s="15"/>
@@ -6027,7 +6022,7 @@
         <v>142683.26999999999</v>
       </c>
       <c r="H16" s="66">
-        <f>G16-E16</f>
+        <f t="shared" si="0"/>
         <v>-4642.320000000007</v>
       </c>
       <c r="I16" s="15"/>
@@ -6057,7 +6052,7 @@
         <v>137694.34</v>
       </c>
       <c r="H17" s="66">
-        <f>G17-E17</f>
+        <f t="shared" si="0"/>
         <v>140.33999999999651</v>
       </c>
       <c r="I17" s="15"/>
@@ -6087,7 +6082,7 @@
         <v>104767.44</v>
       </c>
       <c r="H18" s="66">
-        <f>G18-E18</f>
+        <f t="shared" si="0"/>
         <v>7552.5899999999965</v>
       </c>
       <c r="I18" s="15"/>
@@ -6117,7 +6112,7 @@
         <v>101744.08</v>
       </c>
       <c r="H19" s="66">
-        <f>G19-E19</f>
+        <f t="shared" si="0"/>
         <v>1522.5899999999965</v>
       </c>
       <c r="I19" s="15"/>
@@ -6147,7 +6142,7 @@
         <v>368182.7</v>
       </c>
       <c r="H20" s="66">
-        <f>G20-E20</f>
+        <f t="shared" si="0"/>
         <v>-7046.5599999999977</v>
       </c>
       <c r="I20" s="15"/>
@@ -6177,7 +6172,7 @@
         <v>209534.87</v>
       </c>
       <c r="H21" s="66">
-        <f>G21-E21</f>
+        <f t="shared" si="0"/>
         <v>15105.179999999993</v>
       </c>
       <c r="I21" s="15"/>
@@ -6207,7 +6202,7 @@
         <v>296342.17</v>
       </c>
       <c r="H22" s="66">
-        <f>G22-E22</f>
+        <f t="shared" si="0"/>
         <v>-64455.19</v>
       </c>
       <c r="I22" s="15"/>
@@ -6237,7 +6232,7 @@
         <v>377162.77</v>
       </c>
       <c r="H23" s="66">
-        <f>G23-E23</f>
+        <f t="shared" si="0"/>
         <v>-64814</v>
       </c>
       <c r="I23" s="15"/>
@@ -6267,7 +6262,7 @@
         <v>99778.51</v>
       </c>
       <c r="H24" s="66">
-        <f>G24-E24</f>
+        <f t="shared" si="0"/>
         <v>-4451.8400000000111</v>
       </c>
       <c r="I24" s="15"/>
@@ -6297,7 +6292,7 @@
         <v>163437.20000000001</v>
       </c>
       <c r="H25" s="66">
-        <f>G25-E25</f>
+        <f t="shared" si="0"/>
         <v>11902.309999999998</v>
       </c>
       <c r="I25" s="15"/>
@@ -6327,7 +6322,7 @@
         <v>140687.70000000001</v>
       </c>
       <c r="H26" s="66">
-        <f>G26-E26</f>
+        <f t="shared" si="0"/>
         <v>377.61000000001513</v>
       </c>
       <c r="I26" s="15"/>
@@ -6345,7 +6340,7 @@
       </c>
       <c r="F27" s="64"/>
       <c r="G27" s="66">
-        <f t="shared" ref="G27:H27" si="0">SUM(G4:G26)</f>
+        <f t="shared" ref="G27" si="1">SUM(G4:G26)</f>
         <v>3145437.63</v>
       </c>
       <c r="H27" s="68">
@@ -6479,26 +6474,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="11.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
     <col min="5" max="5" width="14" style="7" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="7.25" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75">
+    <row r="1" spans="1:11" ht="15.6">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -6525,7 +6520,7 @@
       </c>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75">
+    <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="61" t="s">
         <v>39</v>
       </c>
@@ -6545,7 +6540,7 @@
         <v>0.22220000000000001</v>
       </c>
       <c r="G2" s="65">
-        <f>C2*F2</f>
+        <f t="shared" ref="G2:G7" si="0">C2*F2</f>
         <v>2222</v>
       </c>
       <c r="H2" s="66">
@@ -6553,7 +6548,7 @@
         <v>1999.8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75">
+    <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="61" t="s">
         <v>40</v>
       </c>
@@ -6573,7 +6568,7 @@
         <v>0.26100000000000001</v>
       </c>
       <c r="G3" s="65">
-        <f>C3*F3</f>
+        <f t="shared" si="0"/>
         <v>15660</v>
       </c>
       <c r="H3" s="66">
@@ -6581,7 +6576,7 @@
         <v>15660</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75">
+    <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="61" t="s">
         <v>41</v>
       </c>
@@ -6601,7 +6596,7 @@
         <v>0.25</v>
       </c>
       <c r="G4" s="65">
-        <f>C4*F4</f>
+        <f t="shared" si="0"/>
         <v>27500</v>
       </c>
       <c r="H4" s="66">
@@ -6609,7 +6604,7 @@
         <v>27500</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75">
+    <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="61" t="s">
         <v>42</v>
       </c>
@@ -6629,7 +6624,7 @@
         <v>0.1195</v>
       </c>
       <c r="G5" s="65">
-        <f>C5*F5</f>
+        <f t="shared" si="0"/>
         <v>2390</v>
       </c>
       <c r="H5" s="66">
@@ -6637,7 +6632,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75">
+    <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="61" t="s">
         <v>43</v>
       </c>
@@ -6657,7 +6652,7 @@
         <v>0.221</v>
       </c>
       <c r="G6" s="65">
-        <f>C6*F6</f>
+        <f t="shared" si="0"/>
         <v>2210</v>
       </c>
       <c r="H6" s="66">
@@ -6665,7 +6660,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75">
+    <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="61" t="s">
         <v>44</v>
       </c>
@@ -6685,7 +6680,7 @@
         <v>0.17380000000000001</v>
       </c>
       <c r="G7" s="65">
-        <f>C7*F7</f>
+        <f t="shared" si="0"/>
         <v>6969.38</v>
       </c>
       <c r="H7" s="66">
@@ -6693,7 +6688,7 @@
         <v>6272.442</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75">
+    <row r="8" spans="1:11" ht="15.6">
       <c r="A8" s="61"/>
       <c r="B8" s="62"/>
       <c r="C8" s="63"/>
@@ -6706,7 +6701,7 @@
         <v>55572.242000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75">
+    <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="61" t="s">
         <v>45</v>
       </c>
@@ -6729,11 +6724,11 @@
         <v>139689.91</v>
       </c>
       <c r="H9" s="66">
-        <f>G9-E9</f>
+        <f t="shared" ref="H9:H17" si="1">G9-E9</f>
         <v>-12646.75</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75">
+    <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="61" t="s">
         <v>46</v>
       </c>
@@ -6756,11 +6751,11 @@
         <v>30711.83</v>
       </c>
       <c r="H10" s="66">
-        <f>G10-E10</f>
+        <f t="shared" si="1"/>
         <v>44.06000000000131</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75">
+    <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="61" t="s">
         <v>46</v>
       </c>
@@ -6783,11 +6778,11 @@
         <v>122847.3</v>
       </c>
       <c r="H11" s="66">
-        <f>G11-E11</f>
+        <f t="shared" si="1"/>
         <v>176.19000000000233</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75">
+    <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="61" t="s">
         <v>47</v>
       </c>
@@ -6810,11 +6805,11 @@
         <v>258925.23</v>
       </c>
       <c r="H12" s="66">
-        <f>G12-E12</f>
+        <f t="shared" si="1"/>
         <v>353.79000000000815</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75">
+    <row r="13" spans="1:11" ht="15.6">
       <c r="A13" s="61" t="s">
         <v>48</v>
       </c>
@@ -6837,11 +6832,11 @@
         <v>72588.87</v>
       </c>
       <c r="H13" s="66">
-        <f>G13-E13</f>
+        <f t="shared" si="1"/>
         <v>9073.4999999999927</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.75">
+    <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="61" t="s">
         <v>49</v>
       </c>
@@ -6864,11 +6859,11 @@
         <v>107760.79</v>
       </c>
       <c r="H14" s="66">
-        <f>G14-E14</f>
+        <f t="shared" si="1"/>
         <v>10345.509999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75">
+    <row r="15" spans="1:11" ht="15.6">
       <c r="A15" s="61" t="s">
         <v>48</v>
       </c>
@@ -6891,11 +6886,11 @@
         <v>75956.39</v>
       </c>
       <c r="H15" s="66">
-        <f>G15-E15</f>
+        <f t="shared" si="1"/>
         <v>12441.019999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75">
+    <row r="16" spans="1:11" ht="15.6">
       <c r="A16" s="61" t="s">
         <v>48</v>
       </c>
@@ -6918,11 +6913,11 @@
         <v>78949.740000000005</v>
       </c>
       <c r="H16" s="66">
-        <f>G16-E16</f>
+        <f t="shared" si="1"/>
         <v>15434.370000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75">
+    <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="61" t="s">
         <v>16</v>
       </c>
@@ -6945,11 +6940,11 @@
         <v>182968.84</v>
       </c>
       <c r="H17" s="66">
-        <f>G17-E17</f>
+        <f t="shared" si="1"/>
         <v>315.1699999999837</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75">
+    <row r="18" spans="1:8" ht="15.6">
       <c r="A18" s="60"/>
       <c r="B18" s="62"/>
       <c r="C18" s="63"/>
@@ -6968,7 +6963,7 @@
         <v>35536.859999999986</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75">
+    <row r="19" spans="1:8" ht="15.6">
       <c r="A19" s="60"/>
       <c r="B19" s="62"/>
       <c r="C19" s="63"/>
@@ -6983,7 +6978,7 @@
         <v>91109.101999999984</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75">
+    <row r="20" spans="1:8" ht="15.6">
       <c r="A20" s="60"/>
       <c r="B20" s="62"/>
       <c r="C20" s="63"/>
@@ -6997,7 +6992,7 @@
         <v>32424.480000000069</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75">
+    <row r="21" spans="1:8" ht="15.6">
       <c r="A21" s="60"/>
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
@@ -7012,7 +7007,7 @@
         <v>123533.58200000005</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75">
+    <row r="22" spans="1:8" ht="15.6">
       <c r="A22" s="60"/>
       <c r="B22" s="62"/>
       <c r="C22" s="63"/>
@@ -7026,7 +7021,7 @@
         <v>89870</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75">
+    <row r="23" spans="1:8" ht="15.6">
       <c r="A23" s="60"/>
       <c r="B23" s="62"/>
       <c r="C23" s="63"/>
@@ -7040,7 +7035,7 @@
         <v>97220</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75">
+    <row r="24" spans="1:8" ht="15.6">
       <c r="A24" s="60"/>
       <c r="B24" s="62"/>
       <c r="C24" s="63"/>
@@ -7055,7 +7050,7 @@
         <v>187090</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75">
+    <row r="25" spans="1:8" ht="15.6">
       <c r="A25" s="60"/>
       <c r="B25" s="62"/>
       <c r="C25" s="63"/>
@@ -7070,7 +7065,7 @@
         <v>-63556.417999999947</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.75">
+    <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="73" t="s">
         <v>54</v>
       </c>
@@ -7078,7 +7073,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75">
+    <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="73" t="s">
         <v>55</v>
       </c>
@@ -7098,26 +7093,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -7149,7 +7144,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>56</v>
       </c>
@@ -7169,7 +7164,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="65">
-        <f>C2*F2</f>
+        <f t="shared" ref="G2:G7" si="0">C2*F2</f>
         <v>8100</v>
       </c>
       <c r="H2" s="75">
@@ -7183,7 +7178,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
         <v>47</v>
       </c>
@@ -7203,7 +7198,7 @@
         <v>0.86</v>
       </c>
       <c r="G3" s="65">
-        <f>C3*F3</f>
+        <f t="shared" si="0"/>
         <v>5160</v>
       </c>
       <c r="H3" s="75">
@@ -7216,7 +7211,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
         <v>57</v>
       </c>
@@ -7236,7 +7231,7 @@
         <v>1.75</v>
       </c>
       <c r="G4" s="65">
-        <f>C4*F4</f>
+        <f t="shared" si="0"/>
         <v>15750</v>
       </c>
       <c r="H4" s="75">
@@ -7250,7 +7245,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
         <v>58</v>
       </c>
@@ -7270,7 +7265,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="65">
-        <f>C5*F5</f>
+        <f t="shared" si="0"/>
         <v>9000</v>
       </c>
       <c r="H5" s="66">
@@ -7284,7 +7279,7 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
         <v>46</v>
       </c>
@@ -7304,7 +7299,7 @@
         <v>0.45</v>
       </c>
       <c r="G6" s="65">
-        <f>C6*F6</f>
+        <f t="shared" si="0"/>
         <v>4050</v>
       </c>
       <c r="H6" s="66">
@@ -7318,7 +7313,7 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
         <v>59</v>
       </c>
@@ -7338,7 +7333,7 @@
         <v>0.8</v>
       </c>
       <c r="G7" s="65">
-        <f>C7*F7</f>
+        <f t="shared" si="0"/>
         <v>7200</v>
       </c>
       <c r="H7" s="66">
@@ -7352,7 +7347,7 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61"/>
       <c r="B8" s="62"/>
       <c r="C8" s="63"/>
@@ -7371,7 +7366,7 @@
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
         <v>60</v>
       </c>
@@ -7394,7 +7389,7 @@
         <v>115992.52</v>
       </c>
       <c r="H9" s="66">
-        <f>G9-E9</f>
+        <f t="shared" ref="H9:H14" si="1">G9-E9</f>
         <v>236.69000000000233</v>
       </c>
       <c r="I9" s="11"/>
@@ -7404,7 +7399,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
         <v>61</v>
       </c>
@@ -7427,7 +7422,7 @@
         <v>126718.71</v>
       </c>
       <c r="H10" s="66">
-        <f>G10-E10</f>
+        <f t="shared" si="1"/>
         <v>-3569.2299999999959</v>
       </c>
       <c r="I10" s="11"/>
@@ -7437,7 +7432,7 @@
       <c r="M10" s="15"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
         <v>49</v>
       </c>
@@ -7460,7 +7455,7 @@
         <v>53640.93</v>
       </c>
       <c r="H11" s="66">
-        <f>G11-E11</f>
+        <f t="shared" si="1"/>
         <v>2407.6999999999971</v>
       </c>
       <c r="I11" s="11"/>
@@ -7470,7 +7465,7 @@
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="61" t="s">
         <v>62</v>
       </c>
@@ -7493,7 +7488,7 @@
         <v>241463.99</v>
       </c>
       <c r="H12" s="66">
-        <f>G12-E12</f>
+        <f t="shared" si="1"/>
         <v>-7085.3099999999977</v>
       </c>
       <c r="I12" s="11"/>
@@ -7503,7 +7498,7 @@
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="61" t="s">
         <v>63</v>
       </c>
@@ -7526,7 +7521,7 @@
         <v>202550.38</v>
       </c>
       <c r="H13" s="66">
-        <f>G13-E13</f>
+        <f t="shared" si="1"/>
         <v>6116.2600000000093</v>
       </c>
       <c r="I13" s="11"/>
@@ -7536,7 +7531,7 @@
       <c r="M13" s="15"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="61" t="s">
         <v>64</v>
       </c>
@@ -7559,7 +7554,7 @@
         <v>109756.36</v>
       </c>
       <c r="H14" s="66">
-        <f>G14-E14</f>
+        <f t="shared" si="1"/>
         <v>-2492.3500000000058</v>
       </c>
       <c r="I14" s="11"/>
@@ -7569,7 +7564,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="60"/>
       <c r="B15" s="62"/>
       <c r="C15" s="63"/>
@@ -7594,7 +7589,7 @@
       <c r="M15" s="15"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="60"/>
       <c r="B16" s="62"/>
       <c r="C16" s="63"/>
@@ -7615,7 +7610,7 @@
       <c r="M16" s="15"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="60"/>
       <c r="B17" s="62"/>
       <c r="C17" s="63"/>
@@ -7635,7 +7630,7 @@
       <c r="M17" s="15"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="60"/>
       <c r="B18" s="62"/>
       <c r="C18" s="63"/>
@@ -7656,7 +7651,7 @@
       <c r="M18" s="15"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="60"/>
       <c r="B19" s="62"/>
       <c r="C19" s="63"/>
@@ -7676,7 +7671,7 @@
       <c r="M19" s="15"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="60"/>
       <c r="B20" s="62"/>
       <c r="C20" s="63"/>
@@ -7696,7 +7691,7 @@
       <c r="M20" s="15"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A21" s="60"/>
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
@@ -7717,7 +7712,7 @@
       <c r="M21" s="15"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="5"/>
       <c r="B22" s="12"/>
       <c r="C22" s="8"/>
@@ -7738,7 +7733,7 @@
       <c r="M22" s="15"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="5"/>
       <c r="B23" s="12"/>
       <c r="C23" s="8"/>
@@ -7758,7 +7753,7 @@
       <c r="M23" s="15"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="6"/>
       <c r="B24" s="12"/>
       <c r="C24" s="8"/>
@@ -7815,26 +7810,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC5CF25-EA22-4260-9CCB-8B4317B92A1A}">
   <dimension ref="A1:N51"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -7866,7 +7861,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>17</v>
       </c>
@@ -7886,7 +7881,7 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="65">
-        <f>C2*F2</f>
+        <f t="shared" ref="G2:G20" si="0">C2*F2</f>
         <v>25000</v>
       </c>
       <c r="H2" s="66">
@@ -7899,7 +7894,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
         <v>47</v>
       </c>
@@ -7919,7 +7914,7 @@
         <v>0.52</v>
       </c>
       <c r="G3" s="65">
-        <f>C3*F3</f>
+        <f t="shared" si="0"/>
         <v>7800</v>
       </c>
       <c r="H3" s="66">
@@ -7933,7 +7928,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
         <v>18</v>
       </c>
@@ -7953,7 +7948,7 @@
         <v>0.36</v>
       </c>
       <c r="G4" s="65">
-        <f>C4*F4</f>
+        <f t="shared" si="0"/>
         <v>9720</v>
       </c>
       <c r="H4" s="66">
@@ -7967,7 +7962,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
         <v>66</v>
       </c>
@@ -7987,7 +7982,7 @@
         <v>0.65</v>
       </c>
       <c r="G5" s="65">
-        <f>C5*F5</f>
+        <f t="shared" si="0"/>
         <v>14625</v>
       </c>
       <c r="H5" s="66">
@@ -8000,7 +7995,7 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
         <v>67</v>
       </c>
@@ -8020,7 +8015,7 @@
         <v>0.7</v>
       </c>
       <c r="G6" s="65">
-        <f>C6*F6</f>
+        <f t="shared" si="0"/>
         <v>18900</v>
       </c>
       <c r="H6" s="66">
@@ -8034,7 +8029,7 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
         <v>68</v>
       </c>
@@ -8052,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="65">
-        <f>C7*F7</f>
+        <f t="shared" si="0"/>
         <v>13000</v>
       </c>
       <c r="H7" s="66">
@@ -8065,7 +8060,7 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61" t="s">
         <v>69</v>
       </c>
@@ -8083,11 +8078,11 @@
         <v>0.75</v>
       </c>
       <c r="G8" s="65">
-        <f>C8*F8</f>
+        <f t="shared" si="0"/>
         <v>6750</v>
       </c>
       <c r="H8" s="66">
-        <f>G8*0.9</f>
+        <f t="shared" ref="H8:H14" si="1">G8*0.9</f>
         <v>6075</v>
       </c>
       <c r="I8" s="11"/>
@@ -8097,7 +8092,7 @@
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
         <v>16</v>
       </c>
@@ -8115,11 +8110,11 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="65">
-        <f>C9*F9</f>
+        <f t="shared" si="0"/>
         <v>5400</v>
       </c>
       <c r="H9" s="66">
-        <f>G9*0.9</f>
+        <f t="shared" si="1"/>
         <v>4860</v>
       </c>
       <c r="I9" s="11"/>
@@ -8129,7 +8124,7 @@
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
         <v>70</v>
       </c>
@@ -8147,11 +8142,11 @@
         <v>0.2</v>
       </c>
       <c r="G10" s="65">
-        <f>C10*F10</f>
+        <f t="shared" si="0"/>
         <v>6000</v>
       </c>
       <c r="H10" s="66">
-        <f>G10*0.9</f>
+        <f t="shared" si="1"/>
         <v>5400</v>
       </c>
       <c r="I10" s="11"/>
@@ -8161,7 +8156,7 @@
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
         <v>71</v>
       </c>
@@ -8179,11 +8174,11 @@
         <v>0.06</v>
       </c>
       <c r="G11" s="65">
-        <f>C11*F11</f>
+        <f t="shared" si="0"/>
         <v>3600</v>
       </c>
       <c r="H11" s="66">
-        <f>G11*0.9</f>
+        <f t="shared" si="1"/>
         <v>3240</v>
       </c>
       <c r="I11" s="11"/>
@@ -8193,7 +8188,7 @@
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="61" t="s">
         <v>72</v>
       </c>
@@ -8211,11 +8206,11 @@
         <v>0.32</v>
       </c>
       <c r="G12" s="65">
-        <f>C12*F12</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="H12" s="66">
-        <f>G12*0.9</f>
+        <f t="shared" si="1"/>
         <v>864</v>
       </c>
       <c r="I12" s="11"/>
@@ -8225,7 +8220,7 @@
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="61" t="s">
         <v>63</v>
       </c>
@@ -8243,11 +8238,11 @@
         <v>7.15</v>
       </c>
       <c r="G13" s="65">
-        <f>C13*F13</f>
+        <f t="shared" si="0"/>
         <v>14300</v>
       </c>
       <c r="H13" s="66">
-        <f>G13*0.9</f>
+        <f t="shared" si="1"/>
         <v>12870</v>
       </c>
       <c r="I13" s="11"/>
@@ -8257,7 +8252,7 @@
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="61" t="s">
         <v>30</v>
       </c>
@@ -8275,11 +8270,11 @@
         <v>1.35</v>
       </c>
       <c r="G14" s="65">
-        <f>C14*F14</f>
+        <f t="shared" si="0"/>
         <v>8100.0000000000009</v>
       </c>
       <c r="H14" s="66">
-        <f>G14*0.9</f>
+        <f t="shared" si="1"/>
         <v>7290.0000000000009</v>
       </c>
       <c r="I14" s="11"/>
@@ -8289,7 +8284,7 @@
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="61" t="s">
         <v>15</v>
       </c>
@@ -8307,7 +8302,7 @@
         <v>3</v>
       </c>
       <c r="G15" s="65">
-        <f>C15*F15</f>
+        <f t="shared" si="0"/>
         <v>36000</v>
       </c>
       <c r="H15" s="66">
@@ -8320,7 +8315,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="61" t="s">
         <v>73</v>
       </c>
@@ -8338,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="65">
-        <f>C16*F16</f>
+        <f t="shared" si="0"/>
         <v>18000</v>
       </c>
       <c r="H16" s="66">
@@ -8352,7 +8347,7 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="61" t="s">
         <v>74</v>
       </c>
@@ -8370,7 +8365,7 @@
         <v>0.42</v>
       </c>
       <c r="G17" s="65">
-        <f>C17*F17</f>
+        <f t="shared" si="0"/>
         <v>18900</v>
       </c>
       <c r="H17" s="66">
@@ -8384,7 +8379,7 @@
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="61" t="s">
         <v>75</v>
       </c>
@@ -8402,7 +8397,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="65">
-        <f>C18*F18</f>
+        <f t="shared" si="0"/>
         <v>4500</v>
       </c>
       <c r="H18" s="66">
@@ -8416,7 +8411,7 @@
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="61" t="s">
         <v>76</v>
       </c>
@@ -8434,7 +8429,7 @@
         <v>0.211477</v>
       </c>
       <c r="G19" s="65">
-        <f>C19*F19</f>
+        <f t="shared" si="0"/>
         <v>19032.93</v>
       </c>
       <c r="H19" s="66">
@@ -8447,7 +8442,7 @@
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="61" t="s">
         <v>9</v>
       </c>
@@ -8465,7 +8460,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G20" s="65">
-        <f>C20*F20</f>
+        <f t="shared" si="0"/>
         <v>3300</v>
       </c>
       <c r="H20" s="66">
@@ -8479,7 +8474,7 @@
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A21" s="61"/>
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
@@ -8498,7 +8493,7 @@
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="61" t="s">
         <v>69</v>
       </c>
@@ -8521,7 +8516,7 @@
         <v>66153.149999999994</v>
       </c>
       <c r="H22" s="66">
-        <f>G22-E22</f>
+        <f t="shared" ref="H22:H35" si="2">G22-E22</f>
         <v>6.9700000000011642</v>
       </c>
       <c r="I22" s="11"/>
@@ -8531,7 +8526,7 @@
       <c r="M22" s="15"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="61" t="s">
         <v>60</v>
       </c>
@@ -8554,7 +8549,7 @@
         <v>112250.82</v>
       </c>
       <c r="H23" s="66">
-        <f>G23-E23</f>
+        <f t="shared" si="2"/>
         <v>-3505.0099999999948</v>
       </c>
       <c r="I23" s="11"/>
@@ -8564,7 +8559,7 @@
       <c r="M23" s="15"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="61" t="s">
         <v>49</v>
       </c>
@@ -8587,7 +8582,7 @@
         <v>46456.87</v>
       </c>
       <c r="H24" s="66">
-        <f>G24-E24</f>
+        <f t="shared" si="2"/>
         <v>-2250.7699999999968</v>
       </c>
       <c r="I24" s="11"/>
@@ -8597,7 +8592,7 @@
       <c r="M24" s="15"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A25" s="61" t="s">
         <v>69</v>
       </c>
@@ -8620,7 +8615,7 @@
         <v>126918.27</v>
       </c>
       <c r="H25" s="66">
-        <f>G25-E25</f>
+        <f t="shared" si="2"/>
         <v>-5374.0999999999913</v>
       </c>
       <c r="I25" s="11"/>
@@ -8630,7 +8625,7 @@
       <c r="M25" s="15"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="61" t="s">
         <v>30</v>
       </c>
@@ -8653,7 +8648,7 @@
         <v>79323.91</v>
       </c>
       <c r="H26" s="66">
-        <f>G26-E26</f>
+        <f t="shared" si="2"/>
         <v>-12378.759999999995</v>
       </c>
       <c r="I26" s="11"/>
@@ -8663,7 +8658,7 @@
       <c r="M26" s="15"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="61" t="s">
         <v>30</v>
       </c>
@@ -8686,7 +8681,7 @@
         <v>77827.240000000005</v>
       </c>
       <c r="H27" s="66">
-        <f>G27-E27</f>
+        <f t="shared" si="2"/>
         <v>-13875.429999999993</v>
       </c>
       <c r="I27" s="11"/>
@@ -8696,7 +8691,7 @@
       <c r="M27" s="15"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="61" t="s">
         <v>60</v>
       </c>
@@ -8719,7 +8714,7 @@
         <v>110754.15</v>
       </c>
       <c r="H28" s="66">
-        <f>G28-E28</f>
+        <f t="shared" si="2"/>
         <v>-5001.6800000000076</v>
       </c>
       <c r="I28" s="11"/>
@@ -8729,7 +8724,7 @@
       <c r="M28" s="15"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="61" t="s">
         <v>30</v>
       </c>
@@ -8752,7 +8747,7 @@
         <v>76829.45</v>
       </c>
       <c r="H29" s="66">
-        <f>G29-E29</f>
+        <f t="shared" si="2"/>
         <v>-14873.220000000001</v>
       </c>
       <c r="I29" s="11"/>
@@ -8762,7 +8757,7 @@
       <c r="M29" s="15"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="30" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A30" s="61" t="s">
         <v>77</v>
       </c>
@@ -8785,7 +8780,7 @@
         <v>838.14</v>
       </c>
       <c r="H30" s="66">
-        <f>G30-E30</f>
+        <f t="shared" si="2"/>
         <v>-58.840000000000032</v>
       </c>
       <c r="I30" s="11"/>
@@ -8795,7 +8790,7 @@
       <c r="M30" s="15"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="31" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A31" s="61" t="s">
         <v>75</v>
       </c>
@@ -8818,7 +8813,7 @@
         <v>152661.12</v>
       </c>
       <c r="H31" s="66">
-        <f>G31-E31</f>
+        <f t="shared" si="2"/>
         <v>3832.1999999999825</v>
       </c>
       <c r="I31" s="11"/>
@@ -8828,7 +8823,7 @@
       <c r="M31" s="15"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="61" t="s">
         <v>16</v>
       </c>
@@ -8851,7 +8846,7 @@
         <v>24545.52</v>
       </c>
       <c r="H32" s="66">
-        <f>G32-E32</f>
+        <f t="shared" si="2"/>
         <v>1494.5800000000017</v>
       </c>
       <c r="I32" s="11"/>
@@ -8861,7 +8856,7 @@
       <c r="M32" s="15"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="61" t="s">
         <v>16</v>
       </c>
@@ -8884,7 +8879,7 @@
         <v>86607.74</v>
       </c>
       <c r="H33" s="66">
-        <f>G33-E33</f>
+        <f t="shared" si="2"/>
         <v>5929.4400000000023</v>
       </c>
       <c r="I33" s="11"/>
@@ -8894,7 +8889,7 @@
       <c r="M33" s="15"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="61" t="s">
         <v>26</v>
       </c>
@@ -8917,7 +8912,7 @@
         <v>151912.78</v>
       </c>
       <c r="H34" s="66">
-        <f>G34-E34</f>
+        <f t="shared" si="2"/>
         <v>77.220000000001164</v>
       </c>
       <c r="I34" s="11"/>
@@ -8927,7 +8922,7 @@
       <c r="M34" s="15"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="61" t="s">
         <v>8</v>
       </c>
@@ -8950,7 +8945,7 @@
         <v>293348.82</v>
       </c>
       <c r="H35" s="66">
-        <f>G35-E35</f>
+        <f t="shared" si="2"/>
         <v>1704.2800000000279</v>
       </c>
       <c r="I35" s="11"/>
@@ -8960,7 +8955,7 @@
       <c r="M35" s="15"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="36" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A36" s="60"/>
       <c r="B36" s="62"/>
       <c r="C36" s="63"/>
@@ -8985,7 +8980,7 @@
       <c r="M36" s="15"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="37" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A37" s="60"/>
       <c r="B37" s="62"/>
       <c r="C37" s="63"/>
@@ -9006,7 +9001,7 @@
       <c r="M37" s="15"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="38" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A38" s="60"/>
       <c r="B38" s="62"/>
       <c r="C38" s="63"/>
@@ -9026,7 +9021,7 @@
       <c r="M38" s="15"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="39" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A39" s="60"/>
       <c r="B39" s="62"/>
       <c r="C39" s="63"/>
@@ -9047,7 +9042,7 @@
       <c r="M39" s="15"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="40" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A40" s="60"/>
       <c r="B40" s="62"/>
       <c r="C40" s="63"/>
@@ -9067,7 +9062,7 @@
       <c r="M40" s="15"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="41" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A41" s="60"/>
       <c r="B41" s="62"/>
       <c r="C41" s="63"/>
@@ -9087,7 +9082,7 @@
       <c r="M41" s="15"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="42" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A42" s="60"/>
       <c r="B42" s="62"/>
       <c r="C42" s="63"/>
@@ -9108,7 +9103,7 @@
       <c r="M42" s="15"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="43" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A43" s="5"/>
       <c r="B43" s="12"/>
       <c r="C43" s="8"/>
@@ -9129,7 +9124,7 @@
       <c r="M43" s="15"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="44" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A44" s="5"/>
       <c r="B44" s="12"/>
       <c r="C44" s="8"/>
@@ -9149,7 +9144,7 @@
       <c r="M44" s="15"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="45" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A45" s="6"/>
       <c r="B45" s="12"/>
       <c r="C45" s="8"/>
@@ -9206,26 +9201,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2313C6C8-D1DE-449B-AAEA-D0B5747110E6}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -9257,7 +9252,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>29</v>
       </c>
@@ -9289,7 +9284,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
         <v>64</v>
       </c>
@@ -9321,7 +9316,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
         <v>79</v>
       </c>
@@ -9353,7 +9348,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
         <v>8</v>
       </c>
@@ -9385,7 +9380,7 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
         <v>80</v>
       </c>
@@ -9417,7 +9412,7 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61"/>
       <c r="B7" s="62"/>
       <c r="C7" s="63"/>
@@ -9436,7 +9431,7 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61" t="s">
         <v>19</v>
       </c>
@@ -9459,7 +9454,7 @@
         <v>181097.99</v>
       </c>
       <c r="H8" s="66">
-        <f>G8-E8</f>
+        <f t="shared" ref="H8:H14" si="0">G8-E8</f>
         <v>8215.9100000000035</v>
       </c>
       <c r="I8" s="11"/>
@@ -9469,7 +9464,7 @@
       <c r="M8" s="15"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
         <v>66</v>
       </c>
@@ -9492,7 +9487,7 @@
         <v>33226.239999999998</v>
       </c>
       <c r="H9" s="66">
-        <f>G9-E9</f>
+        <f t="shared" si="0"/>
         <v>453.80999999999767</v>
       </c>
       <c r="I9" s="11"/>
@@ -9502,7 +9497,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
         <v>29</v>
       </c>
@@ -9525,7 +9520,7 @@
         <v>134700.99</v>
       </c>
       <c r="H10" s="66">
-        <f>G10-E10</f>
+        <f t="shared" si="0"/>
         <v>-12624.600000000006</v>
       </c>
       <c r="I10" s="11"/>
@@ -9535,7 +9530,7 @@
       <c r="M10" s="15"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
         <v>81</v>
       </c>
@@ -9558,7 +9553,7 @@
         <v>111352.82</v>
       </c>
       <c r="H11" s="66">
-        <f>G11-E11</f>
+        <f t="shared" si="0"/>
         <v>-5906.3199999999924</v>
       </c>
       <c r="I11" s="11"/>
@@ -9568,7 +9563,7 @@
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="61" t="s">
         <v>31</v>
       </c>
@@ -9591,7 +9586,7 @@
         <v>83514.61</v>
       </c>
       <c r="H12" s="66">
-        <f>G12-E12</f>
+        <f t="shared" si="0"/>
         <v>531.2100000000064</v>
       </c>
       <c r="I12" s="11"/>
@@ -9601,7 +9596,7 @@
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="61" t="s">
         <v>82</v>
       </c>
@@ -9624,7 +9619,7 @@
         <v>124723.14</v>
       </c>
       <c r="H13" s="66">
-        <f>G13-E13</f>
+        <f t="shared" si="0"/>
         <v>-1555.9400000000023</v>
       </c>
       <c r="I13" s="11"/>
@@ -9634,7 +9629,7 @@
       <c r="M13" s="15"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="61" t="s">
         <v>17</v>
       </c>
@@ -9657,7 +9652,7 @@
         <v>58370.42</v>
       </c>
       <c r="H14" s="66">
-        <f>G14-E14</f>
+        <f t="shared" si="0"/>
         <v>1244.1699999999983</v>
       </c>
       <c r="I14" s="11"/>
@@ -9667,7 +9662,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="60"/>
       <c r="B15" s="62"/>
       <c r="C15" s="63"/>
@@ -9692,7 +9687,7 @@
       <c r="M15" s="15"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="60"/>
       <c r="B16" s="62"/>
       <c r="C16" s="63"/>
@@ -9713,7 +9708,7 @@
       <c r="M16" s="15"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="60"/>
       <c r="B17" s="62"/>
       <c r="C17" s="63"/>
@@ -9733,7 +9728,7 @@
       <c r="M17" s="15"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="60"/>
       <c r="B18" s="62"/>
       <c r="C18" s="63"/>
@@ -9754,7 +9749,7 @@
       <c r="M18" s="15"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="60"/>
       <c r="B19" s="62"/>
       <c r="C19" s="63"/>
@@ -9774,7 +9769,7 @@
       <c r="M19" s="15"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="60"/>
       <c r="B20" s="62"/>
       <c r="C20" s="63"/>
@@ -9794,7 +9789,7 @@
       <c r="M20" s="15"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A21" s="60"/>
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
@@ -9815,7 +9810,7 @@
       <c r="M21" s="15"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="5"/>
       <c r="B22" s="12"/>
       <c r="C22" s="8"/>
@@ -9836,7 +9831,7 @@
       <c r="M22" s="15"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="5"/>
       <c r="B23" s="12"/>
       <c r="C23" s="8"/>
@@ -9856,7 +9851,7 @@
       <c r="M23" s="15"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="6"/>
       <c r="B24" s="12"/>
       <c r="C24" s="8"/>
@@ -9909,26 +9904,26 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -9960,7 +9955,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>80</v>
       </c>
@@ -9991,7 +9986,7 @@
       <c r="M2" s="15"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61"/>
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
@@ -10010,7 +10005,7 @@
       <c r="M3" s="15"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
         <v>63</v>
       </c>
@@ -10043,7 +10038,7 @@
       <c r="M4" s="15"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
         <v>63</v>
       </c>
@@ -10076,7 +10071,7 @@
       <c r="M5" s="15"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
         <v>16</v>
       </c>
@@ -10109,7 +10104,7 @@
       <c r="M6" s="15"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
         <v>31</v>
       </c>
@@ -10142,7 +10137,7 @@
       <c r="M7" s="15"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75">
+    <row r="8" spans="1:14" ht="15.6">
       <c r="A8" s="60"/>
       <c r="B8" s="62"/>
       <c r="C8" s="63"/>
@@ -10164,7 +10159,7 @@
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="60"/>
       <c r="B9" s="62"/>
       <c r="C9" s="63"/>
@@ -10185,7 +10180,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14" ht="15.75">
+    <row r="10" spans="1:14" ht="15.6">
       <c r="A10" s="60"/>
       <c r="B10" s="62"/>
       <c r="C10" s="63"/>
@@ -10202,7 +10197,7 @@
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:14" ht="15.75">
+    <row r="11" spans="1:14" ht="15.6">
       <c r="A11" s="60"/>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
@@ -10220,7 +10215,7 @@
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75">
+    <row r="12" spans="1:14" ht="15.6">
       <c r="A12" s="60"/>
       <c r="B12" s="62"/>
       <c r="C12" s="63"/>
@@ -10237,7 +10232,7 @@
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75">
+    <row r="13" spans="1:14" ht="15.6">
       <c r="A13" s="60"/>
       <c r="B13" s="62"/>
       <c r="C13" s="63"/>
@@ -10254,7 +10249,7 @@
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="60"/>
       <c r="B14" s="62"/>
       <c r="C14" s="63"/>
@@ -10275,7 +10270,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="5"/>
       <c r="B15" s="12"/>
       <c r="C15" s="8"/>
@@ -10296,7 +10291,7 @@
       <c r="M15" s="15"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="5"/>
       <c r="B16" s="12"/>
       <c r="C16" s="8"/>
@@ -10316,7 +10311,7 @@
       <c r="M16" s="15"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="6"/>
       <c r="B17" s="12"/>
       <c r="C17" s="8"/>
@@ -10374,26 +10369,26 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4F5150-6BB5-4D89-BC93-31EBFDA0DB76}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -10425,7 +10420,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>85</v>
       </c>
@@ -10457,7 +10452,7 @@
       <c r="M2" s="15"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
         <v>86</v>
       </c>
@@ -10802,26 +10797,26 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7FC27F-8D9C-4413-896B-92A14FAE71F8}">
   <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.5703125" style="6"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -10853,7 +10848,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
         <v>88</v>
       </c>
@@ -10871,7 +10866,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G2" s="65">
-        <f>C2*F2</f>
+        <f t="shared" ref="G2:G22" si="0">C2*F2</f>
         <v>1400.0000000000002</v>
       </c>
       <c r="H2" s="66">
@@ -10885,7 +10880,7 @@
       <c r="M2" s="15"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
         <v>15</v>
       </c>
@@ -10903,7 +10898,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" s="65">
-        <f>C3*F3</f>
+        <f t="shared" si="0"/>
         <v>26250</v>
       </c>
       <c r="H3" s="66">
@@ -10917,7 +10912,7 @@
       <c r="M3" s="15"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
         <v>89</v>
       </c>
@@ -10935,7 +10930,7 @@
         <v>0.1</v>
       </c>
       <c r="G4" s="65">
-        <f>C4*F4</f>
+        <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="H4" s="66">
@@ -10949,7 +10944,7 @@
       <c r="M4" s="15"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
         <v>79</v>
       </c>
@@ -10967,7 +10962,7 @@
         <v>0.192</v>
       </c>
       <c r="G5" s="65">
-        <f>C5*F5</f>
+        <f t="shared" si="0"/>
         <v>5760</v>
       </c>
       <c r="H5" s="66">
@@ -10981,7 +10976,7 @@
       <c r="M5" s="15"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
         <v>29</v>
       </c>
@@ -10999,7 +10994,7 @@
         <v>0.26</v>
       </c>
       <c r="G6" s="65">
-        <f>C6*F6</f>
+        <f t="shared" si="0"/>
         <v>10400</v>
       </c>
       <c r="H6" s="66">
@@ -11013,7 +11008,7 @@
       <c r="M6" s="15"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
         <v>14</v>
       </c>
@@ -11031,7 +11026,7 @@
         <v>0.18</v>
       </c>
       <c r="G7" s="65">
-        <f>C7*F7</f>
+        <f t="shared" si="0"/>
         <v>3240</v>
       </c>
       <c r="H7" s="66">
@@ -11045,7 +11040,7 @@
       <c r="M7" s="15"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61" t="s">
         <v>9</v>
       </c>
@@ -11063,7 +11058,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G8" s="65">
-        <f>C8*F8</f>
+        <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="H8" s="66">
@@ -11077,7 +11072,7 @@
       <c r="M8" s="15"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
         <v>64</v>
       </c>
@@ -11095,7 +11090,7 @@
         <v>0.23</v>
       </c>
       <c r="G9" s="65">
-        <f>C9*F9</f>
+        <f t="shared" si="0"/>
         <v>29900</v>
       </c>
       <c r="H9" s="66">
@@ -11109,7 +11104,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
         <v>72</v>
       </c>
@@ -11127,7 +11122,7 @@
         <v>0.18</v>
       </c>
       <c r="G10" s="65">
-        <f>C10*F10</f>
+        <f t="shared" si="0"/>
         <v>1350</v>
       </c>
       <c r="H10" s="66">
@@ -11141,7 +11136,7 @@
       <c r="M10" s="15"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
         <v>18</v>
       </c>
@@ -11159,7 +11154,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G11" s="65">
-        <f>C11*F11</f>
+        <f t="shared" si="0"/>
         <v>1890.0000000000002</v>
       </c>
       <c r="H11" s="66">
@@ -11173,7 +11168,7 @@
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="61" t="s">
         <v>66</v>
       </c>
@@ -11191,7 +11186,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="65">
-        <f>C12*F12</f>
+        <f t="shared" si="0"/>
         <v>22500</v>
       </c>
       <c r="H12" s="66">
@@ -11204,7 +11199,7 @@
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="61" t="s">
         <v>70</v>
       </c>
@@ -11222,7 +11217,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G13" s="65">
-        <f>C13*F13</f>
+        <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="H13" s="66">
@@ -11236,7 +11231,7 @@
       <c r="M13" s="15"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="61" t="s">
         <v>68</v>
       </c>
@@ -11254,7 +11249,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="65">
-        <f>C14*F14</f>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
       <c r="H14" s="66">
@@ -11267,7 +11262,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="61" t="s">
         <v>76</v>
       </c>
@@ -11285,7 +11280,7 @@
         <v>0.12692000000000001</v>
       </c>
       <c r="G15" s="65">
-        <f>C15*F15</f>
+        <f t="shared" si="0"/>
         <v>13326.6</v>
       </c>
       <c r="H15" s="66">
@@ -11298,7 +11293,7 @@
       <c r="M15" s="15"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="61" t="s">
         <v>67</v>
       </c>
@@ -11316,11 +11311,11 @@
         <v>0.15</v>
       </c>
       <c r="G16" s="65">
-        <f>C16*F16</f>
+        <f t="shared" si="0"/>
         <v>7200</v>
       </c>
       <c r="H16" s="66">
-        <f>G16*0.9</f>
+        <f t="shared" ref="H16:H22" si="1">G16*0.9</f>
         <v>6480</v>
       </c>
       <c r="I16" s="11"/>
@@ -11330,7 +11325,7 @@
       <c r="M16" s="15"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="61" t="s">
         <v>74</v>
       </c>
@@ -11348,11 +11343,11 @@
         <v>0.15</v>
       </c>
       <c r="G17" s="65">
-        <f>C17*F17</f>
+        <f t="shared" si="0"/>
         <v>6750</v>
       </c>
       <c r="H17" s="66">
-        <f>G17*0.9</f>
+        <f t="shared" si="1"/>
         <v>6075</v>
       </c>
       <c r="I17" s="11"/>
@@ -11362,7 +11357,7 @@
       <c r="M17" s="15"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="61" t="s">
         <v>73</v>
       </c>
@@ -11380,11 +11375,11 @@
         <v>0.4</v>
       </c>
       <c r="G18" s="65">
-        <f>C18*F18</f>
+        <f t="shared" si="0"/>
         <v>8400</v>
       </c>
       <c r="H18" s="66">
-        <f>G18*0.9</f>
+        <f t="shared" si="1"/>
         <v>7560</v>
       </c>
       <c r="I18" s="11"/>
@@ -11394,7 +11389,7 @@
       <c r="M18" s="15"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="61" t="s">
         <v>90</v>
       </c>
@@ -11412,11 +11407,11 @@
         <v>0.20100000000000001</v>
       </c>
       <c r="G19" s="65">
-        <f>C19*F19</f>
+        <f t="shared" si="0"/>
         <v>2010.0000000000002</v>
       </c>
       <c r="H19" s="66">
-        <f>G19*0.9</f>
+        <f t="shared" si="1"/>
         <v>1809.0000000000002</v>
       </c>
       <c r="I19" s="11"/>
@@ -11426,7 +11421,7 @@
       <c r="M19" s="15"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="61" t="s">
         <v>8</v>
       </c>
@@ -11444,11 +11439,11 @@
         <v>0.4</v>
       </c>
       <c r="G20" s="65">
-        <f>C20*F20</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="H20" s="66">
-        <f>G20*0.9</f>
+        <f t="shared" si="1"/>
         <v>864</v>
       </c>
       <c r="I20" s="11"/>
@@ -11458,7 +11453,7 @@
       <c r="M20" s="15"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A21" s="61" t="s">
         <v>80</v>
       </c>
@@ -11476,11 +11471,11 @@
         <v>0.15559999999999999</v>
       </c>
       <c r="G21" s="65">
-        <f>C21*F21</f>
+        <f t="shared" si="0"/>
         <v>6223.9999999999991</v>
       </c>
       <c r="H21" s="66">
-        <f>G21*0.9</f>
+        <f t="shared" si="1"/>
         <v>5601.5999999999995</v>
       </c>
       <c r="I21" s="11"/>
@@ -11490,7 +11485,7 @@
       <c r="M21" s="15"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75">
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="61" t="s">
         <v>57</v>
       </c>
@@ -11508,11 +11503,11 @@
         <v>0.75</v>
       </c>
       <c r="G22" s="65">
-        <f>C22*F22</f>
+        <f t="shared" si="0"/>
         <v>9000</v>
       </c>
       <c r="H22" s="66">
-        <f>G22*0.9</f>
+        <f t="shared" si="1"/>
         <v>8100</v>
       </c>
       <c r="I22" s="11"/>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4464" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{B58767D0-ACAF-4899-A369-C1277C918892}"/>
+  <xr:revisionPtr revIDLastSave="4474" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50594569-E640-4484-8489-EAF7786CCB3C}"/>
   <bookViews>
-    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="JAN22" sheetId="38" r:id="rId1"/>
-    <sheet name="FEB22" sheetId="39" r:id="rId2"/>
-    <sheet name="MAR22" sheetId="40" r:id="rId3"/>
-    <sheet name="APR22" sheetId="41" r:id="rId4"/>
-    <sheet name="MAY22" sheetId="50" r:id="rId5"/>
-    <sheet name="JUN22" sheetId="52" r:id="rId6"/>
-    <sheet name="JUL22" sheetId="44" r:id="rId7"/>
-    <sheet name="AUG22 " sheetId="53" r:id="rId8"/>
-    <sheet name="SEP22" sheetId="54" r:id="rId9"/>
-    <sheet name="OCT22" sheetId="55" r:id="rId10"/>
-    <sheet name="NOV22" sheetId="56" r:id="rId11"/>
-    <sheet name="DEC22" sheetId="57" r:id="rId12"/>
-    <sheet name="DEC21" sheetId="49" r:id="rId13"/>
+    <sheet name="JAN23" sheetId="58" r:id="rId1"/>
+    <sheet name="JAN22" sheetId="38" r:id="rId2"/>
+    <sheet name="FEB22" sheetId="39" r:id="rId3"/>
+    <sheet name="MAR22" sheetId="40" r:id="rId4"/>
+    <sheet name="APR22" sheetId="41" r:id="rId5"/>
+    <sheet name="MAY22" sheetId="50" r:id="rId6"/>
+    <sheet name="JUN22" sheetId="52" r:id="rId7"/>
+    <sheet name="JUL22" sheetId="44" r:id="rId8"/>
+    <sheet name="AUG22 " sheetId="53" r:id="rId9"/>
+    <sheet name="SEP22" sheetId="54" r:id="rId10"/>
+    <sheet name="OCT22" sheetId="55" r:id="rId11"/>
+    <sheet name="NOV22" sheetId="56" r:id="rId12"/>
+    <sheet name="DEC22" sheetId="57" r:id="rId13"/>
+    <sheet name="DEC21" sheetId="49" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="122">
   <si>
     <t>Name</t>
   </si>
@@ -66,6 +72,21 @@
     <t>Net</t>
   </si>
   <si>
+    <t>GFPT</t>
+  </si>
+  <si>
+    <t>B/F Expense</t>
+  </si>
+  <si>
+    <t>January Exp</t>
+  </si>
+  <si>
+    <t>C/F Expense</t>
+  </si>
+  <si>
+    <t>Profit - Expense</t>
+  </si>
+  <si>
     <t>IVL</t>
   </si>
   <si>
@@ -100,18 +121,6 @@
   </si>
   <si>
     <t>TOP</t>
-  </si>
-  <si>
-    <t>B/F Expense</t>
-  </si>
-  <si>
-    <t>January Exp</t>
-  </si>
-  <si>
-    <t>C/F Expense</t>
-  </si>
-  <si>
-    <t>Profit - Expense</t>
   </si>
   <si>
     <t>LPF-DIV</t>
@@ -410,12 +419,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="187" formatCode="&quot;฿&quot;#,##0.00;[Red]\-&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="188" formatCode="0.000"/>
-    <numFmt numFmtId="189" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="190" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="191" formatCode="0.0000"/>
-    <numFmt numFmtId="192" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;฿&quot;#,##0.00;[Red]\-&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="187" formatCode="0.000"/>
+    <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="190" formatCode="0.0000"/>
+    <numFmt numFmtId="191" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -566,16 +575,16 @@
   <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -583,14 +592,14 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="190" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="190" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -599,58 +608,58 @@
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="190" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="190" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="192" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="190" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="191" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="192" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -658,26 +667,26 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="192" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="188" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="189" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="190" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1042,22 +1051,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D107DCB-A805-454D-A7EE-FBDCD33FF9C5}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="8.25" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="7" customWidth="1"/>
     <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.625" style="6"/>
+    <col min="10" max="10" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
@@ -1094,720 +1103,1039 @@
         <v>8</v>
       </c>
       <c r="B2" s="62">
-        <v>44566</v>
+        <v>44929</v>
       </c>
       <c r="C2" s="63">
-        <v>3000</v>
+        <v>7500</v>
       </c>
       <c r="D2" s="64">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="E2" s="65">
-        <v>126279.08</v>
+        <v>93957.64</v>
       </c>
       <c r="F2" s="64">
-        <v>44.5</v>
+        <v>13.1</v>
       </c>
       <c r="G2" s="65">
-        <v>133204.31</v>
+        <v>98032.38</v>
       </c>
       <c r="H2" s="66">
-        <f t="shared" ref="H2:H22" si="0">G2-E2</f>
-        <v>6925.2299999999959</v>
+        <f t="shared" ref="H2" si="0">G2-E2</f>
+        <v>4074.7400000000052</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="3" spans="1:11" ht="15" customHeight="1">
+      <c r="A3" s="60"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="66">
+        <f>SUM(E2:E2)</f>
+        <v>93957.64</v>
+      </c>
+      <c r="F3" s="64"/>
+      <c r="G3" s="66">
+        <f>SUM(G2:G2)</f>
+        <v>98032.38</v>
+      </c>
+      <c r="H3" s="68">
+        <f>SUM(H2:H2)</f>
+        <v>4074.7400000000052</v>
+      </c>
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1">
+      <c r="A4" s="60"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1">
+      <c r="A5" s="60"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66">
+        <f>SUM(H3:H4)</f>
+        <v>4074.7400000000052</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" customHeight="1">
+      <c r="A6" s="60"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1">
+      <c r="A7" s="60"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="69">
+        <v>62710</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1">
+      <c r="A8" s="60"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="66">
+        <f>H6+H7</f>
+        <v>62710</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1">
+      <c r="A9" s="60"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="70">
+        <f>H5-H8</f>
+        <v>-58635.259999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7FC27F-8D9C-4413-896B-92A14FAE71F8}">
+  <dimension ref="A1:N41"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A1" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A2" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="62">
+        <v>44806</v>
+      </c>
+      <c r="C2" s="63">
+        <v>5000</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="65"/>
+      <c r="F2" s="72">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G2" s="65">
+        <f t="shared" ref="G2:G22" si="0">C2*F2</f>
+        <v>1400.0000000000002</v>
+      </c>
+      <c r="H2" s="66">
+        <f>G2*0.9</f>
+        <v>1260.0000000000002</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B3" s="62">
-        <v>44567</v>
+        <v>44806</v>
       </c>
       <c r="C3" s="63">
+        <v>15000</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="65"/>
+      <c r="F3" s="72">
+        <v>1.75</v>
+      </c>
+      <c r="G3" s="65">
+        <f t="shared" si="0"/>
+        <v>26250</v>
+      </c>
+      <c r="H3" s="66">
+        <f>G3*0.9</f>
+        <v>23625</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A4" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="62">
+        <v>44806</v>
+      </c>
+      <c r="C4" s="63">
+        <v>15000</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="65"/>
+      <c r="F4" s="72">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="65">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="H4" s="66">
+        <f>G4</f>
+        <v>1500</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A5" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="62">
+        <v>44806</v>
+      </c>
+      <c r="C5" s="63">
+        <v>30000</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="65"/>
+      <c r="F5" s="72">
+        <v>0.192</v>
+      </c>
+      <c r="G5" s="65">
+        <f t="shared" si="0"/>
+        <v>5760</v>
+      </c>
+      <c r="H5" s="66">
+        <f>G5*0.9</f>
+        <v>5184</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A6" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="62">
+        <v>44809</v>
+      </c>
+      <c r="C6" s="63">
         <v>40000</v>
       </c>
-      <c r="D3" s="64">
-        <v>2.9</v>
-      </c>
-      <c r="E3" s="65">
-        <v>116256.93</v>
-      </c>
-      <c r="F3" s="64">
-        <v>3</v>
-      </c>
-      <c r="G3" s="65">
-        <v>119734.21</v>
-      </c>
-      <c r="H3" s="66">
-        <f t="shared" si="0"/>
-        <v>3477.2800000000134</v>
-      </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="62">
-        <v>44567</v>
-      </c>
-      <c r="C4" s="63">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="64">
-        <v>11.2</v>
-      </c>
-      <c r="E4" s="65">
-        <v>22449.62</v>
-      </c>
-      <c r="F4" s="64">
-        <v>12.3</v>
-      </c>
-      <c r="G4" s="65">
-        <v>24545.52</v>
-      </c>
-      <c r="H4" s="66">
-        <f t="shared" si="0"/>
-        <v>2095.9000000000015</v>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="62">
-        <v>44568</v>
-      </c>
-      <c r="C5" s="63">
-        <v>1500</v>
-      </c>
-      <c r="D5" s="64">
-        <v>11</v>
-      </c>
-      <c r="E5" s="65">
-        <v>16536.55</v>
-      </c>
-      <c r="F5" s="64">
-        <v>16.8</v>
-      </c>
-      <c r="G5" s="65">
-        <v>25144.19</v>
-      </c>
-      <c r="H5" s="66">
-        <f t="shared" si="0"/>
-        <v>8607.64</v>
-      </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="62">
-        <v>44571</v>
-      </c>
-      <c r="C6" s="63">
-        <v>1500</v>
-      </c>
-      <c r="D6" s="64">
-        <v>11</v>
-      </c>
-      <c r="E6" s="65">
-        <v>16536.55</v>
-      </c>
-      <c r="F6" s="64">
-        <v>16.8</v>
+      <c r="D6" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="65"/>
+      <c r="F6" s="72">
+        <v>0.26</v>
       </c>
       <c r="G6" s="65">
-        <v>25144.19</v>
+        <f t="shared" si="0"/>
+        <v>10400</v>
       </c>
       <c r="H6" s="66">
-        <f t="shared" si="0"/>
-        <v>8607.64</v>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+        <f>G6</f>
+        <v>10400</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B7" s="62">
-        <v>44572</v>
+        <v>44809</v>
       </c>
       <c r="C7" s="63">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="64">
-        <v>11</v>
-      </c>
-      <c r="E7" s="65">
-        <v>11024.36</v>
-      </c>
-      <c r="F7" s="64">
-        <v>20.100000000000001</v>
+        <v>18000</v>
+      </c>
+      <c r="D7" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="65"/>
+      <c r="F7" s="72">
+        <v>0.18</v>
       </c>
       <c r="G7" s="65">
-        <v>20055.48</v>
+        <f t="shared" si="0"/>
+        <v>3240</v>
       </c>
       <c r="H7" s="66">
-        <f t="shared" si="0"/>
-        <v>9031.119999999999</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+        <f>G7*0.9</f>
+        <v>2916</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B8" s="62">
-        <v>44572</v>
+        <v>44810</v>
       </c>
       <c r="C8" s="63">
-        <v>3000</v>
-      </c>
-      <c r="D8" s="64">
-        <v>42</v>
-      </c>
-      <c r="E8" s="65">
-        <v>126279.08</v>
-      </c>
-      <c r="F8" s="64">
-        <v>46.25</v>
+        <v>60000</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="65"/>
+      <c r="F8" s="72">
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G8" s="65">
-        <v>138442.69</v>
+        <f t="shared" si="0"/>
+        <v>2100</v>
       </c>
       <c r="H8" s="66">
-        <f t="shared" si="0"/>
-        <v>12163.61</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+        <f>G8*0.9</f>
+        <v>1890</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B9" s="62">
-        <v>44574</v>
+        <v>44810</v>
       </c>
       <c r="C9" s="63">
-        <v>800</v>
-      </c>
-      <c r="D9" s="64">
-        <v>136.88</v>
-      </c>
-      <c r="E9" s="65">
-        <v>109746.54</v>
-      </c>
-      <c r="F9" s="64">
-        <v>144.5</v>
+        <v>130000</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="65"/>
+      <c r="F9" s="72">
+        <v>0.23</v>
       </c>
       <c r="G9" s="65">
-        <v>115343.96</v>
+        <f t="shared" si="0"/>
+        <v>29900</v>
       </c>
       <c r="H9" s="66">
-        <f t="shared" si="0"/>
-        <v>5597.4200000000128</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+        <f>G9</f>
+        <v>29900</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="62">
+        <v>44810</v>
+      </c>
+      <c r="C10" s="63">
+        <v>7500</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="65"/>
+      <c r="F10" s="72">
+        <v>0.18</v>
+      </c>
+      <c r="G10" s="65">
+        <f t="shared" si="0"/>
+        <v>1350</v>
+      </c>
+      <c r="H10" s="66">
+        <f>G10*0.9</f>
+        <v>1215</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A11" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="62">
+        <v>44811</v>
+      </c>
+      <c r="C11" s="63">
+        <v>27000</v>
+      </c>
+      <c r="D11" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="65"/>
+      <c r="F11" s="72">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G11" s="65">
+        <f t="shared" si="0"/>
+        <v>1890.0000000000002</v>
+      </c>
+      <c r="H11" s="66">
+        <f>G11</f>
+        <v>1890.0000000000002</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A12" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="62">
+        <v>44812</v>
+      </c>
+      <c r="C12" s="63">
+        <v>22500</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="65"/>
+      <c r="F12" s="72">
+        <v>1</v>
+      </c>
+      <c r="G12" s="65">
+        <f t="shared" si="0"/>
+        <v>22500</v>
+      </c>
+      <c r="H12" s="66">
+        <v>20587.5</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A13" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="62">
+        <v>44813</v>
+      </c>
+      <c r="C13" s="63">
+        <v>30000</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="65"/>
+      <c r="F13" s="72">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G13" s="65">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="H13" s="66">
+        <f>G13*0.9</f>
+        <v>1890</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A14" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="62">
+        <v>44813</v>
+      </c>
+      <c r="C14" s="63">
+        <v>15000</v>
+      </c>
+      <c r="D14" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="65"/>
+      <c r="F14" s="72">
+        <v>1</v>
+      </c>
+      <c r="G14" s="65">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="H14" s="66">
+        <v>14085</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A15" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="62">
+        <v>44813</v>
+      </c>
+      <c r="C15" s="63">
+        <v>105000</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="65"/>
+      <c r="F15" s="72">
+        <v>0.12692000000000001</v>
+      </c>
+      <c r="G15" s="65">
+        <f t="shared" si="0"/>
+        <v>13326.6</v>
+      </c>
+      <c r="H15" s="66">
+        <v>12060.51</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A16" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="62">
+        <v>44813</v>
+      </c>
+      <c r="C16" s="63">
+        <v>48000</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="65"/>
+      <c r="F16" s="72">
+        <v>0.15</v>
+      </c>
+      <c r="G16" s="65">
+        <f t="shared" si="0"/>
+        <v>7200</v>
+      </c>
+      <c r="H16" s="66">
+        <f t="shared" ref="H16:H22" si="1">G16*0.9</f>
+        <v>6480</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A17" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="62">
+        <v>44817</v>
+      </c>
+      <c r="C17" s="63">
+        <v>45000</v>
+      </c>
+      <c r="D17" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="65"/>
+      <c r="F17" s="72">
+        <v>0.15</v>
+      </c>
+      <c r="G17" s="65">
+        <f t="shared" si="0"/>
+        <v>6750</v>
+      </c>
+      <c r="H17" s="66">
+        <f t="shared" si="1"/>
+        <v>6075</v>
+      </c>
+      <c r="I17" s="11"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A18" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="62">
+        <v>44818</v>
+      </c>
+      <c r="C18" s="63">
+        <v>21000</v>
+      </c>
+      <c r="D18" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="65"/>
+      <c r="F18" s="72">
+        <v>0.4</v>
+      </c>
+      <c r="G18" s="65">
+        <f t="shared" si="0"/>
+        <v>8400</v>
+      </c>
+      <c r="H18" s="66">
+        <f t="shared" si="1"/>
+        <v>7560</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A19" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="62">
+        <v>44818</v>
+      </c>
+      <c r="C19" s="63">
+        <v>10000</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="65"/>
+      <c r="F19" s="72">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="G19" s="65">
+        <f t="shared" si="0"/>
+        <v>2010.0000000000002</v>
+      </c>
+      <c r="H19" s="66">
+        <f t="shared" si="1"/>
+        <v>1809.0000000000002</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A20" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="62">
-        <v>44574</v>
-      </c>
-      <c r="C10" s="63">
-        <v>2500</v>
-      </c>
-      <c r="D10" s="64">
-        <v>21.1</v>
-      </c>
-      <c r="E10" s="65">
-        <v>52866.83</v>
-      </c>
-      <c r="F10" s="64">
-        <v>24.4</v>
-      </c>
-      <c r="G10" s="65">
-        <v>60864.89</v>
-      </c>
-      <c r="H10" s="66">
-        <f t="shared" si="0"/>
-        <v>7998.0599999999977</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="62">
-        <v>44574</v>
-      </c>
-      <c r="C11" s="63">
-        <v>1500</v>
-      </c>
-      <c r="D11" s="64">
-        <v>31.5</v>
-      </c>
-      <c r="E11" s="65">
-        <v>47354.66</v>
-      </c>
-      <c r="F11" s="64">
-        <v>33</v>
-      </c>
-      <c r="G11" s="65">
-        <v>49390.36</v>
-      </c>
-      <c r="H11" s="66">
-        <f t="shared" si="0"/>
-        <v>2035.6999999999971</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="62">
-        <v>44578</v>
-      </c>
-      <c r="C12" s="63">
-        <v>800</v>
-      </c>
-      <c r="D12" s="64">
-        <v>136.88</v>
-      </c>
-      <c r="E12" s="65">
-        <v>109746.54</v>
-      </c>
-      <c r="F12" s="64">
-        <v>144.5</v>
-      </c>
-      <c r="G12" s="65">
-        <v>115343.96</v>
-      </c>
-      <c r="H12" s="66">
-        <f t="shared" si="0"/>
-        <v>5597.4200000000128</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="62">
-        <v>44578</v>
-      </c>
-      <c r="C13" s="63">
-        <v>800</v>
-      </c>
-      <c r="D13" s="64">
-        <v>136.88</v>
-      </c>
-      <c r="E13" s="65">
-        <v>109746.54</v>
-      </c>
-      <c r="F13" s="64">
-        <v>140</v>
-      </c>
-      <c r="G13" s="65">
-        <v>111751.93</v>
-      </c>
-      <c r="H13" s="66">
-        <f t="shared" si="0"/>
-        <v>2005.3899999999994</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="62">
-        <v>44579</v>
-      </c>
-      <c r="C14" s="63">
-        <v>5000</v>
-      </c>
-      <c r="D14" s="64">
-        <v>21.1</v>
-      </c>
-      <c r="E14" s="65">
-        <v>105733.68</v>
-      </c>
-      <c r="F14" s="64">
-        <v>23.2</v>
-      </c>
-      <c r="G14" s="65">
-        <v>115743.07</v>
-      </c>
-      <c r="H14" s="66">
-        <f t="shared" si="0"/>
-        <v>10009.390000000014</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="62">
-        <v>44580</v>
-      </c>
-      <c r="C15" s="63">
-        <v>1500</v>
-      </c>
-      <c r="D15" s="64">
-        <v>44.5</v>
-      </c>
-      <c r="E15" s="65">
-        <v>66897.84</v>
-      </c>
-      <c r="F15" s="64">
-        <v>49.5</v>
-      </c>
-      <c r="G15" s="65">
-        <v>74085.539999999994</v>
-      </c>
-      <c r="H15" s="66">
-        <f t="shared" si="0"/>
-        <v>7187.6999999999971</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="62">
-        <v>44580</v>
-      </c>
-      <c r="C16" s="63">
-        <v>1500</v>
-      </c>
-      <c r="D16" s="64">
-        <v>40.5</v>
-      </c>
-      <c r="E16" s="65">
-        <v>60884.55</v>
-      </c>
-      <c r="F16" s="64">
-        <v>42.75</v>
-      </c>
-      <c r="G16" s="65">
-        <v>63982.97</v>
-      </c>
-      <c r="H16" s="66">
-        <f t="shared" si="0"/>
-        <v>3098.4199999999983</v>
-      </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="62">
-        <v>44585</v>
-      </c>
-      <c r="C17" s="63">
-        <v>3000</v>
-      </c>
-      <c r="D17" s="64">
-        <v>42</v>
-      </c>
-      <c r="E17" s="65">
-        <v>126279.08</v>
-      </c>
-      <c r="F17" s="64">
-        <v>46.25</v>
-      </c>
-      <c r="G17" s="65">
-        <v>138442.69</v>
-      </c>
-      <c r="H17" s="66">
-        <f t="shared" si="0"/>
-        <v>12163.61</v>
-      </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="62">
-        <v>44587</v>
-      </c>
-      <c r="C18" s="63">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="64">
-        <v>42</v>
-      </c>
-      <c r="E18" s="65">
-        <v>126279.08</v>
-      </c>
-      <c r="F18" s="64">
-        <v>48.25</v>
-      </c>
-      <c r="G18" s="65">
-        <v>144429.4</v>
-      </c>
-      <c r="H18" s="66">
-        <f t="shared" si="0"/>
-        <v>18150.319999999992</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="61" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="62">
-        <v>44588</v>
-      </c>
-      <c r="C19" s="63">
-        <v>5000</v>
-      </c>
-      <c r="D19" s="64">
-        <v>16.7</v>
-      </c>
-      <c r="E19" s="65">
-        <v>83684.95</v>
-      </c>
-      <c r="F19" s="64">
-        <v>14.6</v>
-      </c>
-      <c r="G19" s="65">
-        <v>72838.31</v>
-      </c>
-      <c r="H19" s="66">
-        <f t="shared" si="0"/>
-        <v>-10846.64</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="61" t="s">
-        <v>11</v>
-      </c>
       <c r="B20" s="62">
-        <v>44589</v>
+        <v>44819</v>
       </c>
       <c r="C20" s="63">
-        <v>6000</v>
-      </c>
-      <c r="D20" s="64">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E20" s="65">
-        <v>105833.89</v>
-      </c>
-      <c r="F20" s="64">
-        <v>17.7</v>
+        <v>2400</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="65"/>
+      <c r="F20" s="72">
+        <v>0.4</v>
       </c>
       <c r="G20" s="65">
-        <v>105964.78</v>
+        <f t="shared" si="0"/>
+        <v>960</v>
       </c>
       <c r="H20" s="66">
-        <f t="shared" si="0"/>
-        <v>130.88999999999942</v>
-      </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>864</v>
+      </c>
+      <c r="I20" s="11"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A21" s="61" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="B21" s="62">
-        <v>44592</v>
+        <v>44823</v>
       </c>
       <c r="C21" s="63">
+        <v>40000</v>
+      </c>
+      <c r="D21" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="65"/>
+      <c r="F21" s="72">
+        <v>0.15559999999999999</v>
+      </c>
+      <c r="G21" s="65">
+        <f t="shared" si="0"/>
+        <v>6223.9999999999991</v>
+      </c>
+      <c r="H21" s="66">
+        <f t="shared" si="1"/>
+        <v>5601.5999999999995</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A22" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="62">
+        <v>44825</v>
+      </c>
+      <c r="C22" s="63">
+        <v>12000</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="65"/>
+      <c r="F22" s="72">
+        <v>0.75</v>
+      </c>
+      <c r="G22" s="65">
+        <f t="shared" si="0"/>
         <v>9000</v>
       </c>
-      <c r="D21" s="64">
-        <v>7.45</v>
-      </c>
-      <c r="E21" s="65">
-        <v>67198.509999999995</v>
-      </c>
-      <c r="F21" s="64">
-        <v>7.3</v>
-      </c>
-      <c r="G21" s="65">
-        <v>65554.48</v>
-      </c>
-      <c r="H21" s="66">
-        <f t="shared" si="0"/>
-        <v>-1644.0299999999988</v>
-      </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A22" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="62">
-        <v>44592</v>
-      </c>
-      <c r="C22" s="63">
-        <v>2000</v>
-      </c>
-      <c r="D22" s="64">
-        <v>50.5</v>
-      </c>
-      <c r="E22" s="65">
-        <v>101223.7</v>
-      </c>
-      <c r="F22" s="64">
-        <v>53.25</v>
-      </c>
-      <c r="G22" s="65">
-        <v>106264.11</v>
-      </c>
       <c r="H22" s="66">
-        <f t="shared" si="0"/>
-        <v>5040.4100000000035</v>
-      </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1">
-      <c r="A23" s="60"/>
+        <f t="shared" si="1"/>
+        <v>8100</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A23" s="61"/>
       <c r="B23" s="62"/>
       <c r="C23" s="63"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="66">
-        <f>SUM(E2:E22)</f>
-        <v>1708838.5599999998</v>
-      </c>
+      <c r="D23" s="64"/>
+      <c r="E23" s="65"/>
       <c r="F23" s="64"/>
-      <c r="G23" s="66">
-        <f>SUM(G2:G22)</f>
-        <v>1826271.04</v>
-      </c>
+      <c r="G23" s="65"/>
       <c r="H23" s="68">
         <f>SUM(H2:H22)</f>
-        <v>117432.48000000004</v>
-      </c>
-      <c r="K23" s="15"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1">
-      <c r="A24" s="60"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="66"/>
+        <v>164892.61000000002</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A24" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="62">
+        <v>44805</v>
+      </c>
+      <c r="C24" s="63">
+        <v>3000</v>
+      </c>
+      <c r="D24" s="64">
+        <v>18.5</v>
+      </c>
+      <c r="E24" s="65">
+        <v>55622.93</v>
+      </c>
+      <c r="F24" s="64">
+        <v>19</v>
+      </c>
+      <c r="G24" s="65">
+        <v>56873.75</v>
+      </c>
       <c r="H24" s="66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1">
-      <c r="A25" s="60"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="66"/>
+        <f>G24-E24</f>
+        <v>1250.8199999999997</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A25" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="62">
+        <v>44809</v>
+      </c>
+      <c r="C25" s="63">
+        <v>60000</v>
+      </c>
+      <c r="D25" s="64">
+        <v>1.7</v>
+      </c>
+      <c r="E25" s="65">
+        <v>102225.92</v>
+      </c>
+      <c r="F25" s="64">
+        <v>1.71</v>
+      </c>
+      <c r="G25" s="65">
+        <v>102372.75</v>
+      </c>
       <c r="H25" s="66">
-        <f>SUM(H23:H24)</f>
-        <v>117432.48000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1">
-      <c r="A26" s="60"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="66" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1">
-      <c r="A27" s="60"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" s="69">
-        <v>62710</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1">
+        <f>G25-E25</f>
+        <v>146.83000000000175</v>
+      </c>
+      <c r="I25" s="11"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A26" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="62">
+        <v>44813</v>
+      </c>
+      <c r="C26" s="63">
+        <v>10000</v>
+      </c>
+      <c r="D26" s="64">
+        <v>7.85</v>
+      </c>
+      <c r="E26" s="65">
+        <v>78673.88</v>
+      </c>
+      <c r="F26" s="64">
+        <v>8.25</v>
+      </c>
+      <c r="G26" s="65">
+        <v>82317.27</v>
+      </c>
+      <c r="H26" s="66">
+        <f>G26-E26</f>
+        <v>3643.3899999999994</v>
+      </c>
+      <c r="I26" s="11"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A27" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="62">
+        <v>44816</v>
+      </c>
+      <c r="C27" s="63">
+        <v>7500</v>
+      </c>
+      <c r="D27" s="64">
+        <v>14</v>
+      </c>
+      <c r="E27" s="65">
+        <v>105232.56</v>
+      </c>
+      <c r="F27" s="64">
+        <v>14.5</v>
+      </c>
+      <c r="G27" s="65">
+        <v>108509.13</v>
+      </c>
+      <c r="H27" s="66">
+        <f>G27-E27</f>
+        <v>3276.570000000007</v>
+      </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" ht="21.75" customHeight="1">
       <c r="A28" s="60"/>
       <c r="B28" s="62"/>
       <c r="C28" s="63"/>
       <c r="D28" s="67"/>
-      <c r="E28" s="66"/>
+      <c r="E28" s="66">
+        <f>SUM(E24:E27)</f>
+        <v>341755.29000000004</v>
+      </c>
       <c r="F28" s="64"/>
-      <c r="G28" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="66">
-        <f>H26+H27</f>
-        <v>62710</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1">
+      <c r="G28" s="66">
+        <f>SUM(G24:G27)</f>
+        <v>350072.9</v>
+      </c>
+      <c r="H28" s="68">
+        <f>SUM(H24:H27)</f>
+        <v>8317.6100000000079</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+    </row>
+    <row r="29" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A29" s="60"/>
       <c r="B29" s="62"/>
       <c r="C29" s="63"/>
@@ -1815,45 +2143,225 @@
       <c r="E29" s="66"/>
       <c r="F29" s="64"/>
       <c r="G29" s="66" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="70">
-        <f>H25-H28</f>
-        <v>54722.48000000004</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="H29" s="68">
+        <f>H23+H28</f>
+        <v>173210.22000000003</v>
+      </c>
+      <c r="I29" s="11"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A30" s="60"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="66">
+        <v>368938.24200000014</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+    </row>
+    <row r="31" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A31" s="60"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="66" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="77">
+        <f>H29+H30</f>
+        <v>542148.46200000017</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+    </row>
+    <row r="32" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A32" s="60"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="69">
+        <v>468340</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+    </row>
+    <row r="33" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A33" s="60"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" s="69">
+        <v>35345</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A34" s="60"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="77">
+        <f>H32+H33</f>
+        <v>503685</v>
+      </c>
+      <c r="I34" s="11"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A35" s="5"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="70">
+        <f>H31-H34</f>
+        <v>38463.462000000174</v>
+      </c>
+      <c r="I35" s="11"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A36" s="5"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="H36" s="73">
+        <v>112000</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A37" s="6"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="H37" s="79">
+        <f>H35+H36</f>
+        <v>150463.46200000017</v>
+      </c>
+      <c r="I37" s="11"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="K38" s="7"/>
+      <c r="M38" s="7"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="M39" s="7"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="M40" s="7"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="C41" s="12"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="10"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="7"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H22">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N22">
     <sortCondition ref="B2:B22"/>
     <sortCondition ref="A2:A22"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB73B3FB-8409-48F5-A2B7-3BA9D395158E}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
@@ -1890,7 +2398,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="62">
         <v>44846</v>
@@ -1899,7 +2407,7 @@
         <v>4500</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65"/>
       <c r="F2" s="72">
@@ -1941,7 +2449,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="62">
         <v>44840</v>
@@ -1974,7 +2482,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="61" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B5" s="62">
         <v>44853</v>
@@ -2007,7 +2515,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="61" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" s="62">
         <v>44860</v>
@@ -2040,7 +2548,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A7" s="61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="62">
         <v>44865</v>
@@ -2101,7 +2609,7 @@
       <c r="E9" s="66"/>
       <c r="F9" s="64"/>
       <c r="G9" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H9" s="68">
         <f>H3+H8</f>
@@ -2122,7 +2630,7 @@
       <c r="E10" s="66"/>
       <c r="F10" s="64"/>
       <c r="G10" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" s="66">
         <v>542148.46200000017</v>
@@ -2139,7 +2647,7 @@
       <c r="E11" s="66"/>
       <c r="F11" s="64"/>
       <c r="G11" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" s="77">
         <f>H9+H10</f>
@@ -2157,7 +2665,7 @@
       <c r="E12" s="66"/>
       <c r="F12" s="64"/>
       <c r="G12" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H12" s="69">
         <v>503685</v>
@@ -2174,7 +2682,7 @@
       <c r="E13" s="66"/>
       <c r="F13" s="64"/>
       <c r="G13" s="66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H13" s="69">
         <v>71130</v>
@@ -2191,7 +2699,7 @@
       <c r="E14" s="66"/>
       <c r="F14" s="64"/>
       <c r="G14" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H14" s="77">
         <f>H12+H13</f>
@@ -2212,7 +2720,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H15" s="70">
         <f>H11-H14</f>
@@ -2233,7 +2741,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H16" s="73">
         <v>112000</v>
@@ -2253,7 +2761,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="79">
         <f>H15+H16</f>
@@ -2296,26 +2804,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C98757-5F3D-4FA1-98E2-779A87752594}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
@@ -2352,7 +2860,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="62">
         <v>44846</v>
@@ -2361,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65"/>
       <c r="F2" s="72">
@@ -2403,7 +2911,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4" s="62">
         <v>44866</v>
@@ -2436,7 +2944,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="61" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="62">
         <v>44866</v>
@@ -2469,7 +2977,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="61" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B6" s="62">
         <v>44867</v>
@@ -2502,7 +3010,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A7" s="61" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B7" s="62">
         <v>44872</v>
@@ -2535,7 +3043,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A8" s="61" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" s="62">
         <v>44873</v>
@@ -2568,7 +3076,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="62">
         <v>44880</v>
@@ -2601,7 +3109,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="62">
         <v>44886</v>
@@ -2634,7 +3142,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A11" s="61" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" s="62">
         <v>44887</v>
@@ -2695,7 +3203,7 @@
       <c r="E13" s="66"/>
       <c r="F13" s="64"/>
       <c r="G13" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" s="68">
         <f>H3+H12</f>
@@ -2716,7 +3224,7 @@
       <c r="E14" s="66"/>
       <c r="F14" s="64"/>
       <c r="G14" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H14" s="66">
         <v>510256.50200000015</v>
@@ -2733,7 +3241,7 @@
       <c r="E15" s="66"/>
       <c r="F15" s="64"/>
       <c r="G15" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" s="77">
         <f>H13+H14</f>
@@ -2751,7 +3259,7 @@
       <c r="E16" s="66"/>
       <c r="F16" s="64"/>
       <c r="G16" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H16" s="69">
         <v>574815</v>
@@ -2768,7 +3276,7 @@
       <c r="E17" s="66"/>
       <c r="F17" s="64"/>
       <c r="G17" s="66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H17" s="69">
         <v>34450</v>
@@ -2785,7 +3293,7 @@
       <c r="E18" s="66"/>
       <c r="F18" s="64"/>
       <c r="G18" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H18" s="77">
         <f>H16+H17</f>
@@ -2806,7 +3314,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="10"/>
       <c r="G19" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H19" s="70">
         <f>H15-H18</f>
@@ -2827,7 +3335,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H20" s="73">
         <v>112000</v>
@@ -2847,7 +3355,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H21" s="79">
         <f>H19+H20</f>
@@ -2890,26 +3398,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8BBD29C-D904-43CE-A7C2-0CB7DA792816}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
@@ -2946,7 +3454,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B2" s="62">
         <v>44897</v>
@@ -2955,7 +3463,7 @@
         <v>20000</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65"/>
       <c r="F2" s="72">
@@ -2978,7 +3486,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B3" s="62">
         <v>44901</v>
@@ -2987,7 +3495,7 @@
         <v>60000</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="65"/>
       <c r="F3" s="72">
@@ -3010,7 +3518,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="62">
         <v>44901</v>
@@ -3019,7 +3527,7 @@
         <v>40000</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="65"/>
       <c r="F4" s="72">
@@ -3042,7 +3550,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="62">
         <v>44903</v>
@@ -3051,7 +3559,7 @@
         <v>130000</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="65"/>
       <c r="F5" s="72">
@@ -3074,7 +3582,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B6" s="62">
         <v>44904</v>
@@ -3083,7 +3591,7 @@
         <v>24000</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="65"/>
       <c r="F6" s="72">
@@ -3105,7 +3613,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B7" s="62">
         <v>44908</v>
@@ -3114,7 +3622,7 @@
         <v>30000</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="65"/>
       <c r="F7" s="72">
@@ -3137,7 +3645,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="62">
         <v>44910</v>
@@ -3146,7 +3654,7 @@
         <v>40000</v>
       </c>
       <c r="D8" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="65"/>
       <c r="F8" s="72">
@@ -3169,7 +3677,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" s="62">
         <v>44910</v>
@@ -3178,7 +3686,7 @@
         <v>2400</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="65"/>
       <c r="F9" s="72">
@@ -3201,7 +3709,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" s="62">
         <v>44918</v>
@@ -3210,7 +3718,7 @@
         <v>20000</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="65"/>
       <c r="F10" s="72">
@@ -3233,7 +3741,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="62">
         <v>44923</v>
@@ -3242,7 +3750,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="65"/>
       <c r="F11" s="72">
@@ -3284,7 +3792,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A13" s="61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="62">
         <v>44915</v>
@@ -3317,7 +3825,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="62">
         <v>44918</v>
@@ -3350,7 +3858,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A15" s="61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" s="62">
         <v>44922</v>
@@ -3383,7 +3891,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A16" s="61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="62">
         <v>44923</v>
@@ -3416,7 +3924,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A17" s="61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="62">
         <v>44923</v>
@@ -3449,7 +3957,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="61" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B18" s="62">
         <v>44925</v>
@@ -3510,7 +4018,7 @@
       <c r="E20" s="66"/>
       <c r="F20" s="64"/>
       <c r="G20" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H20" s="68">
         <f>H12+H19</f>
@@ -3531,7 +4039,7 @@
       <c r="E21" s="66"/>
       <c r="F21" s="64"/>
       <c r="G21" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H21" s="66">
         <v>406249.65200000012</v>
@@ -3548,7 +4056,7 @@
       <c r="E22" s="66"/>
       <c r="F22" s="64"/>
       <c r="G22" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H22" s="77">
         <f>H20+H21</f>
@@ -3566,7 +4074,7 @@
       <c r="E23" s="66"/>
       <c r="F23" s="64"/>
       <c r="G23" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H23" s="69">
         <v>609265</v>
@@ -3583,7 +4091,7 @@
       <c r="E24" s="66"/>
       <c r="F24" s="64"/>
       <c r="G24" s="66" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H24" s="69">
         <v>29530</v>
@@ -3600,7 +4108,7 @@
       <c r="E25" s="66"/>
       <c r="F25" s="64"/>
       <c r="G25" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H25" s="77">
         <f>H23+H24</f>
@@ -3621,7 +4129,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H26" s="70">
         <f>H22-H25</f>
@@ -3642,7 +4150,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H27" s="73">
         <v>112000</v>
@@ -3662,7 +4170,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H28" s="79">
         <f>H26+H27</f>
@@ -3709,26 +4217,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C58482DA-743D-4274-94F0-2300C47BC2D3}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" style="41" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="41" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="40" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="38" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.25" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.25" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.875" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="30" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.375" style="29" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="29"/>
+    <col min="12" max="12" width="10.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" style="29" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="31" customFormat="1" ht="18">
@@ -3754,13 +4262,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J1" s="26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K1" s="28" t="s">
         <v>7</v>
@@ -3769,9 +4277,9 @@
       <c r="M1" s="29"/>
       <c r="N1" s="29"/>
     </row>
-    <row r="2" spans="1:14" ht="14.4">
+    <row r="2" spans="1:14" ht="14.45">
       <c r="A2" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="39">
         <v>44533</v>
@@ -3809,9 +4317,9 @@
       <c r="L2" s="38"/>
       <c r="M2" s="38"/>
     </row>
-    <row r="3" spans="1:14" ht="14.4">
+    <row r="3" spans="1:14" ht="14.45">
       <c r="A3" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B3" s="39">
         <v>44533</v>
@@ -3849,9 +4357,9 @@
       <c r="L3" s="38"/>
       <c r="M3" s="38"/>
     </row>
-    <row r="4" spans="1:14" ht="14.4">
+    <row r="4" spans="1:14" ht="14.45">
       <c r="A4" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="39">
         <v>44533</v>
@@ -3889,9 +4397,9 @@
       <c r="L4" s="38"/>
       <c r="M4" s="38"/>
     </row>
-    <row r="5" spans="1:14" ht="14.4">
+    <row r="5" spans="1:14" ht="14.45">
       <c r="A5" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="39">
         <v>44533</v>
@@ -3928,9 +4436,9 @@
       <c r="L5" s="38"/>
       <c r="M5" s="38"/>
     </row>
-    <row r="6" spans="1:14" ht="14.4">
+    <row r="6" spans="1:14" ht="14.45">
       <c r="A6" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" s="39">
         <v>44533</v>
@@ -3968,9 +4476,9 @@
       <c r="L6" s="38"/>
       <c r="M6" s="38"/>
     </row>
-    <row r="7" spans="1:14" ht="14.4">
+    <row r="7" spans="1:14" ht="14.45">
       <c r="A7" s="21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" s="39">
         <v>44533</v>
@@ -4008,9 +4516,9 @@
       <c r="L7" s="38"/>
       <c r="M7" s="38"/>
     </row>
-    <row r="8" spans="1:14" ht="14.4">
+    <row r="8" spans="1:14" ht="14.45">
       <c r="A8" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" s="39">
         <v>44533</v>
@@ -4048,9 +4556,9 @@
       <c r="L8" s="38"/>
       <c r="M8" s="38"/>
     </row>
-    <row r="9" spans="1:14" ht="14.4">
+    <row r="9" spans="1:14" ht="14.45">
       <c r="A9" s="21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" s="39">
         <v>44537</v>
@@ -4088,9 +4596,9 @@
       <c r="L9" s="38"/>
       <c r="M9" s="38"/>
     </row>
-    <row r="10" spans="1:14" ht="14.4">
+    <row r="10" spans="1:14" ht="14.45">
       <c r="A10" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" s="39">
         <v>44538</v>
@@ -4127,9 +4635,9 @@
       </c>
       <c r="L10" s="29"/>
     </row>
-    <row r="11" spans="1:14" ht="14.4">
+    <row r="11" spans="1:14" ht="14.45">
       <c r="A11" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="39">
         <v>44538</v>
@@ -4166,9 +4674,9 @@
       </c>
       <c r="L11" s="29"/>
     </row>
-    <row r="12" spans="1:14" ht="14.4">
+    <row r="12" spans="1:14" ht="14.45">
       <c r="A12" s="21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="39">
         <v>44538</v>
@@ -4205,9 +4713,9 @@
       </c>
       <c r="L12" s="29"/>
     </row>
-    <row r="13" spans="1:14" ht="14.4">
+    <row r="13" spans="1:14" ht="14.45">
       <c r="A13" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B13" s="39">
         <v>44539</v>
@@ -4243,9 +4751,9 @@
       </c>
       <c r="L13" s="29"/>
     </row>
-    <row r="14" spans="1:14" ht="14.4">
+    <row r="14" spans="1:14" ht="14.45">
       <c r="A14" s="21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="39">
         <v>44547</v>
@@ -4283,9 +4791,9 @@
       <c r="L14" s="38"/>
       <c r="M14" s="38"/>
     </row>
-    <row r="15" spans="1:14" ht="14.4">
+    <row r="15" spans="1:14" ht="14.45">
       <c r="A15" s="21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B15" s="39">
         <v>44547</v>
@@ -4327,7 +4835,7 @@
     </row>
     <row r="16" spans="1:14" ht="27.6">
       <c r="A16" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="35">
         <v>44531</v>
@@ -4367,7 +4875,7 @@
     </row>
     <row r="17" spans="1:14" ht="27.6">
       <c r="A17" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="35">
         <v>44531</v>
@@ -4408,9 +4916,9 @@
       </c>
       <c r="M17" s="38"/>
     </row>
-    <row r="18" spans="1:14" ht="14.4">
+    <row r="18" spans="1:14" ht="14.45">
       <c r="A18" s="21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B18" s="35">
         <v>44531</v>
@@ -4449,7 +4957,7 @@
     </row>
     <row r="19" spans="1:14" ht="27.6">
       <c r="A19" s="21" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B19" s="35">
         <v>44545</v>
@@ -4487,9 +4995,9 @@
       <c r="L19" s="38"/>
       <c r="M19" s="38"/>
     </row>
-    <row r="20" spans="1:14" ht="14.4">
+    <row r="20" spans="1:14" ht="14.45">
       <c r="A20" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="35">
         <v>44538</v>
@@ -4527,9 +5035,9 @@
       <c r="L20" s="38"/>
       <c r="M20" s="38"/>
     </row>
-    <row r="21" spans="1:14" ht="14.4">
+    <row r="21" spans="1:14" ht="14.45">
       <c r="A21" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="35">
         <v>44558</v>
@@ -4567,9 +5075,9 @@
       <c r="L21" s="38"/>
       <c r="M21" s="38"/>
     </row>
-    <row r="22" spans="1:14" ht="14.4">
+    <row r="22" spans="1:14" ht="14.45">
       <c r="A22" s="21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B22" s="35">
         <v>44543</v>
@@ -4606,9 +5114,9 @@
       </c>
       <c r="L22" s="29"/>
     </row>
-    <row r="23" spans="1:14" ht="28.8">
+    <row r="23" spans="1:14" ht="28.9">
       <c r="A23" s="21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B23" s="35">
         <v>44553</v>
@@ -4648,7 +5156,7 @@
     </row>
     <row r="24" spans="1:14" ht="27.6">
       <c r="A24" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B24" s="35">
         <v>44531</v>
@@ -4688,7 +5196,7 @@
     </row>
     <row r="25" spans="1:14" ht="27.6">
       <c r="A25" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B25" s="35">
         <v>44557</v>
@@ -4732,7 +5240,7 @@
     </row>
     <row r="26" spans="1:14" ht="27.6">
       <c r="A26" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B26" s="35">
         <v>44532</v>
@@ -4772,7 +5280,7 @@
     </row>
     <row r="27" spans="1:14" ht="27.6">
       <c r="A27" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" s="35">
         <v>44538</v>
@@ -4811,9 +5319,9 @@
       <c r="M27" s="38"/>
       <c r="N27" s="50"/>
     </row>
-    <row r="28" spans="1:14" ht="14.4">
+    <row r="28" spans="1:14" ht="14.45">
       <c r="A28" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B28" s="35">
         <v>44557</v>
@@ -4852,9 +5360,9 @@
       <c r="M28" s="38"/>
       <c r="N28" s="50"/>
     </row>
-    <row r="29" spans="1:14" ht="14.4">
+    <row r="29" spans="1:14" ht="14.45">
       <c r="A29" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B29" s="35">
         <v>44560</v>
@@ -4893,9 +5401,9 @@
       <c r="M29" s="38"/>
       <c r="N29" s="50"/>
     </row>
-    <row r="30" spans="1:14" ht="14.4">
+    <row r="30" spans="1:14" ht="14.45">
       <c r="A30" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="35">
         <v>44543</v>
@@ -4934,9 +5442,9 @@
       <c r="M30" s="38"/>
       <c r="N30" s="50"/>
     </row>
-    <row r="31" spans="1:14" ht="14.4">
+    <row r="31" spans="1:14" ht="14.45">
       <c r="A31" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" s="35">
         <v>44551</v>
@@ -4980,7 +5488,7 @@
     </row>
     <row r="32" spans="1:14" ht="27.6">
       <c r="A32" s="21" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B32" s="35">
         <v>44546</v>
@@ -5020,7 +5528,7 @@
     </row>
     <row r="33" spans="1:14" ht="27.6">
       <c r="A33" s="21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B33" s="35">
         <v>44560</v>
@@ -5060,7 +5568,7 @@
     </row>
     <row r="34" spans="1:14" ht="27.6">
       <c r="A34" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" s="35">
         <v>44547</v>
@@ -5098,9 +5606,9 @@
       <c r="L34" s="29"/>
       <c r="N34" s="15"/>
     </row>
-    <row r="35" spans="1:14" ht="14.4">
+    <row r="35" spans="1:14" ht="14.45">
       <c r="A35" s="21" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B35" s="35">
         <v>44560</v>
@@ -5138,9 +5646,9 @@
       <c r="L35" s="29"/>
       <c r="N35" s="15"/>
     </row>
-    <row r="36" spans="1:14" ht="14.4">
+    <row r="36" spans="1:14" ht="14.45">
       <c r="A36" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B36" s="35">
         <v>44537</v>
@@ -5178,9 +5686,9 @@
       <c r="L36" s="29"/>
       <c r="N36" s="50"/>
     </row>
-    <row r="37" spans="1:14" ht="14.4">
+    <row r="37" spans="1:14" ht="14.45">
       <c r="A37" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B37" s="35">
         <v>44537</v>
@@ -5221,9 +5729,9 @@
       </c>
       <c r="N37" s="15"/>
     </row>
-    <row r="38" spans="1:14" ht="14.4">
+    <row r="38" spans="1:14" ht="14.45">
       <c r="A38" s="21" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B38" s="35">
         <v>44532</v>
@@ -5262,9 +5770,9 @@
       <c r="M38" s="38"/>
       <c r="N38" s="15"/>
     </row>
-    <row r="39" spans="1:14" ht="14.4">
+    <row r="39" spans="1:14" ht="14.45">
       <c r="A39" s="21" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B39" s="35">
         <v>44533</v>
@@ -5303,9 +5811,9 @@
       <c r="M39" s="38"/>
       <c r="N39" s="15"/>
     </row>
-    <row r="40" spans="1:14" ht="14.4">
+    <row r="40" spans="1:14" ht="14.45">
       <c r="A40" s="21" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B40" s="35">
         <v>44538</v>
@@ -5347,9 +5855,9 @@
       <c r="M40" s="38"/>
       <c r="N40" s="38"/>
     </row>
-    <row r="41" spans="1:14" ht="14.4">
+    <row r="41" spans="1:14" ht="14.45">
       <c r="A41" s="21" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B41" s="35">
         <v>44533</v>
@@ -5387,9 +5895,9 @@
       <c r="L41" s="38"/>
       <c r="M41" s="38"/>
     </row>
-    <row r="42" spans="1:14" ht="14.4">
+    <row r="42" spans="1:14" ht="14.45">
       <c r="A42" s="21" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B42" s="35">
         <v>44537</v>
@@ -5448,7 +5956,7 @@
         <v>65786.399999999965</v>
       </c>
       <c r="I43" s="30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J43" s="38">
         <f>SUM(J2:J42)</f>
@@ -5466,7 +5974,7 @@
     <row r="44" spans="1:14">
       <c r="B44" s="35"/>
       <c r="J44" s="30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K44" s="30">
         <v>1064855.1700000004</v>
@@ -5475,7 +5983,7 @@
     <row r="45" spans="1:14">
       <c r="B45" s="35"/>
       <c r="J45" s="30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K45" s="51">
         <f>SUM(K43:K44)</f>
@@ -5492,7 +6000,7 @@
     <row r="46" spans="1:14">
       <c r="B46" s="35"/>
       <c r="J46" s="30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K46" s="38">
         <v>700874.5</v>
@@ -5508,7 +6016,7 @@
     <row r="47" spans="1:14">
       <c r="B47" s="35"/>
       <c r="J47" s="47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K47" s="38">
         <v>557962.62</v>
@@ -5544,26 +6052,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="7.25" style="10" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.625" style="6"/>
+    <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
@@ -5597,7 +6101,804 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="62">
+        <v>44566</v>
+      </c>
+      <c r="C2" s="63">
+        <v>3000</v>
+      </c>
+      <c r="D2" s="64">
+        <v>42</v>
+      </c>
+      <c r="E2" s="65">
+        <v>126279.08</v>
+      </c>
+      <c r="F2" s="64">
+        <v>44.5</v>
+      </c>
+      <c r="G2" s="65">
+        <v>133204.31</v>
+      </c>
+      <c r="H2" s="66">
+        <f t="shared" ref="H2:H22" si="0">G2-E2</f>
+        <v>6925.2299999999959</v>
+      </c>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="62">
+        <v>44567</v>
+      </c>
+      <c r="C3" s="63">
+        <v>40000</v>
+      </c>
+      <c r="D3" s="64">
+        <v>2.9</v>
+      </c>
+      <c r="E3" s="65">
+        <v>116256.93</v>
+      </c>
+      <c r="F3" s="64">
+        <v>3</v>
+      </c>
+      <c r="G3" s="65">
+        <v>119734.21</v>
+      </c>
+      <c r="H3" s="66">
+        <f t="shared" si="0"/>
+        <v>3477.2800000000134</v>
+      </c>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="62">
+        <v>44567</v>
+      </c>
+      <c r="C4" s="63">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="64">
+        <v>11.2</v>
+      </c>
+      <c r="E4" s="65">
+        <v>22449.62</v>
+      </c>
+      <c r="F4" s="64">
+        <v>12.3</v>
+      </c>
+      <c r="G4" s="65">
+        <v>24545.52</v>
+      </c>
+      <c r="H4" s="66">
+        <f t="shared" si="0"/>
+        <v>2095.9000000000015</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="62">
+        <v>44568</v>
+      </c>
+      <c r="C5" s="63">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="64">
+        <v>11</v>
+      </c>
+      <c r="E5" s="65">
+        <v>16536.55</v>
+      </c>
+      <c r="F5" s="64">
+        <v>16.8</v>
+      </c>
+      <c r="G5" s="65">
+        <v>25144.19</v>
+      </c>
+      <c r="H5" s="66">
+        <f t="shared" si="0"/>
+        <v>8607.64</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="62">
+        <v>44571</v>
+      </c>
+      <c r="C6" s="63">
+        <v>1500</v>
+      </c>
+      <c r="D6" s="64">
+        <v>11</v>
+      </c>
+      <c r="E6" s="65">
+        <v>16536.55</v>
+      </c>
+      <c r="F6" s="64">
+        <v>16.8</v>
+      </c>
+      <c r="G6" s="65">
+        <v>25144.19</v>
+      </c>
+      <c r="H6" s="66">
+        <f t="shared" si="0"/>
+        <v>8607.64</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A7" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="62">
+        <v>44572</v>
+      </c>
+      <c r="C7" s="63">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="64">
+        <v>11</v>
+      </c>
+      <c r="E7" s="65">
+        <v>11024.36</v>
+      </c>
+      <c r="F7" s="64">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="G7" s="65">
+        <v>20055.48</v>
+      </c>
+      <c r="H7" s="66">
+        <f t="shared" si="0"/>
+        <v>9031.119999999999</v>
+      </c>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="62">
+        <v>44572</v>
+      </c>
+      <c r="C8" s="63">
+        <v>3000</v>
+      </c>
+      <c r="D8" s="64">
+        <v>42</v>
+      </c>
+      <c r="E8" s="65">
+        <v>126279.08</v>
+      </c>
+      <c r="F8" s="64">
+        <v>46.25</v>
+      </c>
+      <c r="G8" s="65">
+        <v>138442.69</v>
+      </c>
+      <c r="H8" s="66">
+        <f t="shared" si="0"/>
+        <v>12163.61</v>
+      </c>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="62">
+        <v>44574</v>
+      </c>
+      <c r="C9" s="63">
+        <v>800</v>
+      </c>
+      <c r="D9" s="64">
+        <v>136.88</v>
+      </c>
+      <c r="E9" s="65">
+        <v>109746.54</v>
+      </c>
+      <c r="F9" s="64">
+        <v>144.5</v>
+      </c>
+      <c r="G9" s="65">
+        <v>115343.96</v>
+      </c>
+      <c r="H9" s="66">
+        <f t="shared" si="0"/>
+        <v>5597.4200000000128</v>
+      </c>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A10" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="62">
+        <v>44574</v>
+      </c>
+      <c r="C10" s="63">
+        <v>2500</v>
+      </c>
+      <c r="D10" s="64">
+        <v>21.1</v>
+      </c>
+      <c r="E10" s="65">
+        <v>52866.83</v>
+      </c>
+      <c r="F10" s="64">
+        <v>24.4</v>
+      </c>
+      <c r="G10" s="65">
+        <v>60864.89</v>
+      </c>
+      <c r="H10" s="66">
+        <f t="shared" si="0"/>
+        <v>7998.0599999999977</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A11" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="62">
+        <v>44574</v>
+      </c>
+      <c r="C11" s="63">
+        <v>1500</v>
+      </c>
+      <c r="D11" s="64">
+        <v>31.5</v>
+      </c>
+      <c r="E11" s="65">
+        <v>47354.66</v>
+      </c>
+      <c r="F11" s="64">
+        <v>33</v>
+      </c>
+      <c r="G11" s="65">
+        <v>49390.36</v>
+      </c>
+      <c r="H11" s="66">
+        <f t="shared" si="0"/>
+        <v>2035.6999999999971</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="62">
+        <v>44578</v>
+      </c>
+      <c r="C12" s="63">
+        <v>800</v>
+      </c>
+      <c r="D12" s="64">
+        <v>136.88</v>
+      </c>
+      <c r="E12" s="65">
+        <v>109746.54</v>
+      </c>
+      <c r="F12" s="64">
+        <v>144.5</v>
+      </c>
+      <c r="G12" s="65">
+        <v>115343.96</v>
+      </c>
+      <c r="H12" s="66">
+        <f t="shared" si="0"/>
+        <v>5597.4200000000128</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A13" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="62">
+        <v>44578</v>
+      </c>
+      <c r="C13" s="63">
+        <v>800</v>
+      </c>
+      <c r="D13" s="64">
+        <v>136.88</v>
+      </c>
+      <c r="E13" s="65">
+        <v>109746.54</v>
+      </c>
+      <c r="F13" s="64">
+        <v>140</v>
+      </c>
+      <c r="G13" s="65">
+        <v>111751.93</v>
+      </c>
+      <c r="H13" s="66">
+        <f t="shared" si="0"/>
+        <v>2005.3899999999994</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A14" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="62">
+        <v>44579</v>
+      </c>
+      <c r="C14" s="63">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="64">
+        <v>21.1</v>
+      </c>
+      <c r="E14" s="65">
+        <v>105733.68</v>
+      </c>
+      <c r="F14" s="64">
+        <v>23.2</v>
+      </c>
+      <c r="G14" s="65">
+        <v>115743.07</v>
+      </c>
+      <c r="H14" s="66">
+        <f t="shared" si="0"/>
+        <v>10009.390000000014</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A15" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="62">
+        <v>44580</v>
+      </c>
+      <c r="C15" s="63">
+        <v>1500</v>
+      </c>
+      <c r="D15" s="64">
+        <v>44.5</v>
+      </c>
+      <c r="E15" s="65">
+        <v>66897.84</v>
+      </c>
+      <c r="F15" s="64">
+        <v>49.5</v>
+      </c>
+      <c r="G15" s="65">
+        <v>74085.539999999994</v>
+      </c>
+      <c r="H15" s="66">
+        <f t="shared" si="0"/>
+        <v>7187.6999999999971</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A16" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="62">
+        <v>44580</v>
+      </c>
+      <c r="C16" s="63">
+        <v>1500</v>
+      </c>
+      <c r="D16" s="64">
+        <v>40.5</v>
+      </c>
+      <c r="E16" s="65">
+        <v>60884.55</v>
+      </c>
+      <c r="F16" s="64">
+        <v>42.75</v>
+      </c>
+      <c r="G16" s="65">
+        <v>63982.97</v>
+      </c>
+      <c r="H16" s="66">
+        <f t="shared" si="0"/>
+        <v>3098.4199999999983</v>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A17" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="62">
+        <v>44585</v>
+      </c>
+      <c r="C17" s="63">
+        <v>3000</v>
+      </c>
+      <c r="D17" s="64">
+        <v>42</v>
+      </c>
+      <c r="E17" s="65">
+        <v>126279.08</v>
+      </c>
+      <c r="F17" s="64">
+        <v>46.25</v>
+      </c>
+      <c r="G17" s="65">
+        <v>138442.69</v>
+      </c>
+      <c r="H17" s="66">
+        <f t="shared" si="0"/>
+        <v>12163.61</v>
+      </c>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A18" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="62">
+        <v>44587</v>
+      </c>
+      <c r="C18" s="63">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="64">
+        <v>42</v>
+      </c>
+      <c r="E18" s="65">
+        <v>126279.08</v>
+      </c>
+      <c r="F18" s="64">
+        <v>48.25</v>
+      </c>
+      <c r="G18" s="65">
+        <v>144429.4</v>
+      </c>
+      <c r="H18" s="66">
+        <f t="shared" si="0"/>
+        <v>18150.319999999992</v>
+      </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A19" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="62">
+        <v>44588</v>
+      </c>
+      <c r="C19" s="63">
+        <v>5000</v>
+      </c>
+      <c r="D19" s="64">
+        <v>16.7</v>
+      </c>
+      <c r="E19" s="65">
+        <v>83684.95</v>
+      </c>
+      <c r="F19" s="64">
+        <v>14.6</v>
+      </c>
+      <c r="G19" s="65">
+        <v>72838.31</v>
+      </c>
+      <c r="H19" s="66">
+        <f t="shared" si="0"/>
+        <v>-10846.64</v>
+      </c>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A20" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="62">
+        <v>44589</v>
+      </c>
+      <c r="C20" s="63">
+        <v>6000</v>
+      </c>
+      <c r="D20" s="64">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E20" s="65">
+        <v>105833.89</v>
+      </c>
+      <c r="F20" s="64">
+        <v>17.7</v>
+      </c>
+      <c r="G20" s="65">
+        <v>105964.78</v>
+      </c>
+      <c r="H20" s="66">
+        <f t="shared" si="0"/>
+        <v>130.88999999999942</v>
+      </c>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A21" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="62">
+        <v>44592</v>
+      </c>
+      <c r="C21" s="63">
+        <v>9000</v>
+      </c>
+      <c r="D21" s="64">
+        <v>7.45</v>
+      </c>
+      <c r="E21" s="65">
+        <v>67198.509999999995</v>
+      </c>
+      <c r="F21" s="64">
+        <v>7.3</v>
+      </c>
+      <c r="G21" s="65">
+        <v>65554.48</v>
+      </c>
+      <c r="H21" s="66">
+        <f t="shared" si="0"/>
+        <v>-1644.0299999999988</v>
+      </c>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A22" s="61" t="s">
         <v>24</v>
+      </c>
+      <c r="B22" s="62">
+        <v>44592</v>
+      </c>
+      <c r="C22" s="63">
+        <v>2000</v>
+      </c>
+      <c r="D22" s="64">
+        <v>50.5</v>
+      </c>
+      <c r="E22" s="65">
+        <v>101223.7</v>
+      </c>
+      <c r="F22" s="64">
+        <v>53.25</v>
+      </c>
+      <c r="G22" s="65">
+        <v>106264.11</v>
+      </c>
+      <c r="H22" s="66">
+        <f t="shared" si="0"/>
+        <v>5040.4100000000035</v>
+      </c>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:11" ht="15" customHeight="1">
+      <c r="A23" s="60"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="66">
+        <f>SUM(E2:E22)</f>
+        <v>1708838.5599999998</v>
+      </c>
+      <c r="F23" s="64"/>
+      <c r="G23" s="66">
+        <f>SUM(G2:G22)</f>
+        <v>1826271.04</v>
+      </c>
+      <c r="H23" s="68">
+        <f>SUM(H2:H22)</f>
+        <v>117432.48000000004</v>
+      </c>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="1:11" ht="15" customHeight="1">
+      <c r="A24" s="60"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15" customHeight="1">
+      <c r="A25" s="60"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66">
+        <f>SUM(H23:H24)</f>
+        <v>117432.48000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15" customHeight="1">
+      <c r="A26" s="60"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15" customHeight="1">
+      <c r="A27" s="60"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="69">
+        <v>62710</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15" customHeight="1">
+      <c r="A28" s="60"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="66">
+        <f>H26+H27</f>
+        <v>62710</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15" customHeight="1">
+      <c r="A29" s="60"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="70">
+        <f>H25-H28</f>
+        <v>54722.48000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H22">
+    <sortCondition ref="B2:B22"/>
+    <sortCondition ref="A2:A22"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="8.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.5703125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A1" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="61" t="s">
+        <v>25</v>
       </c>
       <c r="B2" s="62">
         <v>44607</v>
@@ -5606,10 +6907,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="64">
         <v>0.1719</v>
@@ -5641,7 +6942,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="62">
         <v>44593</v>
@@ -5671,7 +6972,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="62">
         <v>44594</v>
@@ -5701,7 +7002,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="61" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B6" s="62">
         <v>44595</v>
@@ -5731,7 +7032,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="61" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B7" s="62">
         <v>44601</v>
@@ -5761,7 +7062,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="61" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B8" s="62">
         <v>44601</v>
@@ -5791,7 +7092,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="61" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B9" s="62">
         <v>44601</v>
@@ -5821,7 +7122,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="61" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B10" s="62">
         <v>44602</v>
@@ -5851,7 +7152,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="61" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B11" s="62">
         <v>44603</v>
@@ -5881,7 +7182,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="61" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B12" s="62">
         <v>44606</v>
@@ -5911,7 +7212,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="61" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B13" s="62">
         <v>44606</v>
@@ -5941,7 +7242,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="61" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="62">
         <v>44607</v>
@@ -5971,7 +7272,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="61" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="62">
         <v>44609</v>
@@ -6001,7 +7302,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="62">
         <v>44610</v>
@@ -6031,7 +7332,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="62">
         <v>44613</v>
@@ -6061,7 +7362,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" s="62">
         <v>44613</v>
@@ -6091,7 +7392,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="62">
         <v>44614</v>
@@ -6121,7 +7422,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="62">
         <v>44615</v>
@@ -6151,7 +7452,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" s="62">
         <v>44616</v>
@@ -6181,7 +7482,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="62">
         <v>44617</v>
@@ -6211,7 +7512,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" s="62">
         <v>44617</v>
@@ -6241,7 +7542,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="62">
         <v>44617</v>
@@ -6271,7 +7572,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="61" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B25" s="62">
         <v>44620</v>
@@ -6301,7 +7602,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="61" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="62">
         <v>44620</v>
@@ -6391,7 +7692,7 @@
       <c r="E30" s="66"/>
       <c r="F30" s="64"/>
       <c r="G30" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H30" s="69">
         <v>62710</v>
@@ -6408,7 +7709,7 @@
       <c r="E31" s="66"/>
       <c r="F31" s="64"/>
       <c r="G31" s="66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H31" s="71">
         <v>27160</v>
@@ -6425,7 +7726,7 @@
       <c r="E32" s="66"/>
       <c r="F32" s="64"/>
       <c r="G32" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H32" s="66">
         <f>H30+H31</f>
@@ -6443,7 +7744,7 @@
       <c r="E33" s="66"/>
       <c r="F33" s="64"/>
       <c r="G33" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H33" s="70">
         <f>H29-H32</f>
@@ -6471,26 +7772,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
     <col min="5" max="5" width="14" style="7" customWidth="1"/>
-    <col min="6" max="6" width="7.25" style="10" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
@@ -6522,7 +7823,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="62">
         <v>44624</v>
@@ -6531,10 +7832,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="72">
         <v>0.22220000000000001</v>
@@ -6550,7 +7851,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="61" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="62">
         <v>44624</v>
@@ -6559,10 +7860,10 @@
         <v>60000</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="72">
         <v>0.26100000000000001</v>
@@ -6578,7 +7879,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="61" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="62">
         <v>44641</v>
@@ -6587,10 +7888,10 @@
         <v>110000</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="72">
         <v>0.25</v>
@@ -6606,7 +7907,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="62">
         <v>44645</v>
@@ -6615,10 +7916,10 @@
         <v>20000</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="72">
         <v>0.1195</v>
@@ -6634,7 +7935,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="62">
         <v>44648</v>
@@ -6643,10 +7944,10 @@
         <v>10000</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="72">
         <v>0.221</v>
@@ -6662,7 +7963,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="61" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="62">
         <v>44650</v>
@@ -6671,10 +7972,10 @@
         <v>40100</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="72">
         <v>0.17380000000000001</v>
@@ -6703,7 +8004,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="62">
         <v>44621</v>
@@ -6730,7 +8031,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="62">
         <v>44622</v>
@@ -6757,7 +8058,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="62">
         <v>44623</v>
@@ -6784,7 +8085,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="62">
         <v>44629</v>
@@ -6811,7 +8112,7 @@
     </row>
     <row r="13" spans="1:11" ht="15.6">
       <c r="A13" s="61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="62">
         <v>44630</v>
@@ -6838,7 +8139,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="62">
         <v>44630</v>
@@ -6865,7 +8166,7 @@
     </row>
     <row r="15" spans="1:11" ht="15.6">
       <c r="A15" s="61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="62">
         <v>44643</v>
@@ -6892,7 +8193,7 @@
     </row>
     <row r="16" spans="1:11" ht="15.6">
       <c r="A16" s="61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="62">
         <v>44648</v>
@@ -6919,7 +8220,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="61" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B17" s="62">
         <v>44651</v>
@@ -6971,7 +8272,7 @@
       <c r="E19" s="66"/>
       <c r="F19" s="64"/>
       <c r="G19" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H19" s="68">
         <f>H8+H18</f>
@@ -6986,7 +8287,7 @@
       <c r="E20" s="66"/>
       <c r="F20" s="64"/>
       <c r="G20" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H20" s="66">
         <v>32424.480000000069</v>
@@ -7000,7 +8301,7 @@
       <c r="E21" s="66"/>
       <c r="F21" s="64"/>
       <c r="G21" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H21" s="68">
         <f>H19+H20</f>
@@ -7015,7 +8316,7 @@
       <c r="E22" s="66"/>
       <c r="F22" s="64"/>
       <c r="G22" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H22" s="69">
         <v>89870</v>
@@ -7029,7 +8330,7 @@
       <c r="E23" s="66"/>
       <c r="F23" s="64"/>
       <c r="G23" s="66" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H23" s="69">
         <v>97220</v>
@@ -7043,7 +8344,7 @@
       <c r="E24" s="66"/>
       <c r="F24" s="64"/>
       <c r="G24" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H24" s="68">
         <f>H22+H23</f>
@@ -7058,7 +8359,7 @@
       <c r="E25" s="66"/>
       <c r="F25" s="64"/>
       <c r="G25" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H25" s="70">
         <f>H21-H24</f>
@@ -7067,7 +8368,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H26" s="73">
         <v>112000</v>
@@ -7075,7 +8376,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H27" s="74">
         <f>H25+H26</f>
@@ -7090,26 +8391,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="1" max="1" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
@@ -7146,7 +8447,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2" s="62">
         <v>44659</v>
@@ -7155,10 +8456,10 @@
         <v>900</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="72">
         <v>9</v>
@@ -7180,7 +8481,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="62">
         <v>44673</v>
@@ -7189,10 +8490,10 @@
         <v>6000</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="72">
         <v>0.86</v>
@@ -7213,7 +8514,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="62">
         <v>44673</v>
@@ -7222,10 +8523,10 @@
         <v>9000</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="72">
         <v>1.75</v>
@@ -7247,7 +8548,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="62">
         <v>44677</v>
@@ -7256,10 +8557,10 @@
         <v>900</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="72">
         <v>10</v>
@@ -7281,7 +8582,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="62">
         <v>44678</v>
@@ -7290,10 +8591,10 @@
         <v>9000</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="72">
         <v>0.45</v>
@@ -7315,7 +8616,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="62">
         <v>44680</v>
@@ -7324,10 +8625,10 @@
         <v>9000</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="72">
         <v>0.8</v>
@@ -7368,7 +8669,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9" s="62">
         <v>44652</v>
@@ -7401,7 +8702,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="62">
         <v>44669</v>
@@ -7434,7 +8735,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="62">
         <v>44671</v>
@@ -7467,7 +8768,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" s="62">
         <v>44669</v>
@@ -7500,7 +8801,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="62">
         <v>44673</v>
@@ -7533,7 +8834,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="62">
         <v>44680</v>
@@ -7597,7 +8898,7 @@
       <c r="E16" s="66"/>
       <c r="F16" s="64"/>
       <c r="G16" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H16" s="68">
         <f>H8+H15</f>
@@ -7618,7 +8919,7 @@
       <c r="E17" s="66"/>
       <c r="F17" s="64"/>
       <c r="G17" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" s="66">
         <v>123533.58200000005</v>
@@ -7638,7 +8939,7 @@
       <c r="E18" s="66"/>
       <c r="F18" s="64"/>
       <c r="G18" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H18" s="68">
         <f>H16+H17</f>
@@ -7659,7 +8960,7 @@
       <c r="E19" s="66"/>
       <c r="F19" s="64"/>
       <c r="G19" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H19" s="69">
         <v>187090</v>
@@ -7679,7 +8980,7 @@
       <c r="E20" s="66"/>
       <c r="F20" s="64"/>
       <c r="G20" s="66" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H20" s="69">
         <v>71150</v>
@@ -7699,7 +9000,7 @@
       <c r="E21" s="66"/>
       <c r="F21" s="64"/>
       <c r="G21" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H21" s="68">
         <f>H19+H20</f>
@@ -7720,7 +9021,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H22" s="70">
         <f>H18-H21</f>
@@ -7741,7 +9042,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H23" s="73">
         <v>112000</v>
@@ -7761,7 +9062,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H24" s="74">
         <f>H22+H23</f>
@@ -7807,26 +9108,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC5CF25-EA22-4260-9CCB-8B4317B92A1A}">
   <dimension ref="A1:N51"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="1" max="1" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
@@ -7863,7 +9164,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B2" s="62">
         <v>44686</v>
@@ -7872,10 +9173,10 @@
         <v>50000</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="72">
         <v>0.5</v>
@@ -7896,7 +9197,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="62">
         <v>44686</v>
@@ -7905,10 +9206,10 @@
         <v>15000</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="72">
         <v>0.52</v>
@@ -7930,7 +9231,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B4" s="62">
         <v>44687</v>
@@ -7939,10 +9240,10 @@
         <v>27000</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="72">
         <v>0.36</v>
@@ -7964,7 +9265,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="62">
         <v>44687</v>
@@ -7973,10 +9274,10 @@
         <v>22500</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="72">
         <v>0.65</v>
@@ -7997,7 +9298,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="62">
         <v>44687</v>
@@ -8006,10 +9307,10 @@
         <v>27000</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="72">
         <v>0.7</v>
@@ -8031,7 +9332,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" s="62">
         <v>44690</v>
@@ -8040,7 +9341,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="65"/>
       <c r="F7" s="72">
@@ -8062,7 +9363,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B8" s="62">
         <v>44693</v>
@@ -8071,7 +9372,7 @@
         <v>9000</v>
       </c>
       <c r="D8" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="65"/>
       <c r="F8" s="72">
@@ -8094,7 +9395,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B9" s="62">
         <v>44694</v>
@@ -8103,7 +9404,7 @@
         <v>4500</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="65"/>
       <c r="F9" s="72">
@@ -8126,7 +9427,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="62">
         <v>44698</v>
@@ -8135,7 +9436,7 @@
         <v>30000</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="65"/>
       <c r="F10" s="72">
@@ -8158,7 +9459,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="62">
         <v>44698</v>
@@ -8167,7 +9468,7 @@
         <v>60000</v>
       </c>
       <c r="D11" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="65"/>
       <c r="F11" s="72">
@@ -8190,7 +9491,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B12" s="62">
         <v>44700</v>
@@ -8199,7 +9500,7 @@
         <v>3000</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="65"/>
       <c r="F12" s="72">
@@ -8222,7 +9523,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="62">
         <v>44700</v>
@@ -8231,7 +9532,7 @@
         <v>2000</v>
       </c>
       <c r="D13" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="65"/>
       <c r="F13" s="72">
@@ -8254,7 +9555,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="62">
         <v>44701</v>
@@ -8263,7 +9564,7 @@
         <v>6000</v>
       </c>
       <c r="D14" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="65"/>
       <c r="F14" s="72">
@@ -8286,7 +9587,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="61" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B15" s="62">
         <v>44701</v>
@@ -8295,7 +9596,7 @@
         <v>12000</v>
       </c>
       <c r="D15" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="65"/>
       <c r="F15" s="72">
@@ -8317,7 +9618,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="61" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="62">
         <v>44705</v>
@@ -8326,7 +9627,7 @@
         <v>18000</v>
       </c>
       <c r="D16" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="65"/>
       <c r="F16" s="72">
@@ -8349,7 +9650,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" s="62">
         <v>44705</v>
@@ -8358,7 +9659,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="65"/>
       <c r="F17" s="72">
@@ -8381,7 +9682,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="61" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="62">
         <v>44705</v>
@@ -8390,7 +9691,7 @@
         <v>4500</v>
       </c>
       <c r="D18" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="65"/>
       <c r="F18" s="72">
@@ -8413,7 +9714,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="61" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="62">
         <v>44706</v>
@@ -8422,7 +9723,7 @@
         <v>90000</v>
       </c>
       <c r="D19" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="65"/>
       <c r="F19" s="72">
@@ -8444,7 +9745,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="61" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B20" s="62">
         <v>44712</v>
@@ -8453,7 +9754,7 @@
         <v>60000</v>
       </c>
       <c r="D20" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="65"/>
       <c r="F20" s="72">
@@ -8495,7 +9796,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="62">
         <v>44684</v>
@@ -8528,7 +9829,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="62">
         <v>44687</v>
@@ -8561,7 +9862,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="62">
         <v>44691</v>
@@ -8594,7 +9895,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A25" s="61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B25" s="62">
         <v>44692</v>
@@ -8627,7 +9928,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="62">
         <v>44693</v>
@@ -8660,7 +9961,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="62">
         <v>44694</v>
@@ -8693,7 +9994,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" s="62">
         <v>44698</v>
@@ -8726,7 +10027,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" s="62">
         <v>44698</v>
@@ -8759,7 +10060,7 @@
     </row>
     <row r="30" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A30" s="61" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="62">
         <v>44704</v>
@@ -8792,7 +10093,7 @@
     </row>
     <row r="31" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A31" s="61" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B31" s="62">
         <v>44704</v>
@@ -8825,7 +10126,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="61" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B32" s="62">
         <v>44707</v>
@@ -8858,7 +10159,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="61" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B33" s="62">
         <v>44707</v>
@@ -8891,7 +10192,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B34" s="62">
         <v>44711</v>
@@ -8924,7 +10225,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="61" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B35" s="62">
         <v>44712</v>
@@ -8988,7 +10289,7 @@
       <c r="E37" s="66"/>
       <c r="F37" s="64"/>
       <c r="G37" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H37" s="68">
         <f>H21+H36</f>
@@ -9009,7 +10310,7 @@
       <c r="E38" s="66"/>
       <c r="F38" s="64"/>
       <c r="G38" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H38" s="66">
         <v>163817.34200000006</v>
@@ -9029,7 +10330,7 @@
       <c r="E39" s="66"/>
       <c r="F39" s="64"/>
       <c r="G39" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H39" s="68">
         <f>H37+H38</f>
@@ -9050,7 +10351,7 @@
       <c r="E40" s="66"/>
       <c r="F40" s="64"/>
       <c r="G40" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H40" s="69">
         <v>258240</v>
@@ -9070,7 +10371,7 @@
       <c r="E41" s="66"/>
       <c r="F41" s="64"/>
       <c r="G41" s="66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H41" s="69">
         <v>56640</v>
@@ -9090,7 +10391,7 @@
       <c r="E42" s="66"/>
       <c r="F42" s="64"/>
       <c r="G42" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H42" s="77">
         <f>H40+H41</f>
@@ -9111,7 +10412,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="10"/>
       <c r="G43" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H43" s="76">
         <f>H39-H42</f>
@@ -9132,7 +10433,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H44" s="73">
         <v>112000</v>
@@ -9152,7 +10453,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H45" s="74">
         <f>H43+H44</f>
@@ -9198,26 +10499,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2313C6C8-D1DE-449B-AAEA-D0B5747110E6}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="7" max="7" width="15.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
@@ -9254,7 +10555,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="62">
         <v>44718</v>
@@ -9263,7 +10564,7 @@
         <v>50000</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65"/>
       <c r="F2" s="72">
@@ -9286,7 +10587,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="62">
         <v>44720</v>
@@ -9295,7 +10596,7 @@
         <v>110000</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="65"/>
       <c r="F3" s="72">
@@ -9318,7 +10619,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="62">
         <v>44727</v>
@@ -9327,7 +10628,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="65"/>
       <c r="F4" s="72">
@@ -9350,7 +10651,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B5" s="62">
         <v>44728</v>
@@ -9359,7 +10660,7 @@
         <v>6000</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="65"/>
       <c r="F5" s="72">
@@ -9382,7 +10683,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B6" s="62">
         <v>44736</v>
@@ -9391,7 +10692,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="65"/>
       <c r="F6" s="72">
@@ -9433,7 +10734,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="61" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B8" s="62">
         <v>44720</v>
@@ -9466,7 +10767,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="62">
         <v>44725</v>
@@ -9499,7 +10800,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="62">
         <v>44725</v>
@@ -9532,7 +10833,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="61" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B11" s="62">
         <v>44735</v>
@@ -9565,7 +10866,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="62">
         <v>44735</v>
@@ -9598,7 +10899,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="61" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="62">
         <v>44739</v>
@@ -9631,7 +10932,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="61" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B14" s="62">
         <v>44741</v>
@@ -9695,7 +10996,7 @@
       <c r="E16" s="66"/>
       <c r="F16" s="64"/>
       <c r="G16" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H16" s="68">
         <f>H7+H15</f>
@@ -9716,7 +11017,7 @@
       <c r="E17" s="66"/>
       <c r="F17" s="64"/>
       <c r="G17" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" s="66">
         <v>334428.91200000013</v>
@@ -9736,7 +11037,7 @@
       <c r="E18" s="66"/>
       <c r="F18" s="64"/>
       <c r="G18" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H18" s="68">
         <f>H16+H17</f>
@@ -9757,7 +11058,7 @@
       <c r="E19" s="66"/>
       <c r="F19" s="64"/>
       <c r="G19" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H19" s="69">
         <v>314880</v>
@@ -9777,7 +11078,7 @@
       <c r="E20" s="66"/>
       <c r="F20" s="64"/>
       <c r="G20" s="66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H20" s="69">
         <v>72560</v>
@@ -9797,7 +11098,7 @@
       <c r="E21" s="66"/>
       <c r="F21" s="64"/>
       <c r="G21" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H21" s="77">
         <f>H19+H20</f>
@@ -9818,7 +11119,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H22" s="76">
         <f>H18-H21</f>
@@ -9839,7 +11140,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H23" s="73">
         <v>112000</v>
@@ -9859,7 +11160,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H24" s="74">
         <f>H22+H23</f>
@@ -9901,26 +11202,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
@@ -9957,7 +11258,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B2" s="62">
         <v>44736</v>
@@ -9966,7 +11267,7 @@
         <v>40000</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65"/>
       <c r="F2" s="72">
@@ -10007,7 +11308,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="62">
         <v>44746</v>
@@ -10040,7 +11341,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="62">
         <v>44764</v>
@@ -10073,7 +11374,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="61" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B6" s="62">
         <v>44767</v>
@@ -10106,7 +11407,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="62">
         <v>44767</v>
@@ -10167,7 +11468,7 @@
       <c r="E9" s="66"/>
       <c r="F9" s="64"/>
       <c r="G9" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H9" s="68">
         <f>H3+H8</f>
@@ -10188,7 +11489,7 @@
       <c r="E10" s="66"/>
       <c r="F10" s="64"/>
       <c r="G10" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" s="66">
         <v>376019.25200000015</v>
@@ -10205,7 +11506,7 @@
       <c r="E11" s="66"/>
       <c r="F11" s="64"/>
       <c r="G11" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" s="68">
         <f>H9+H10</f>
@@ -10223,7 +11524,7 @@
       <c r="E12" s="66"/>
       <c r="F12" s="64"/>
       <c r="G12" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H12" s="69">
         <v>387440</v>
@@ -10240,7 +11541,7 @@
       <c r="E13" s="66"/>
       <c r="F13" s="64"/>
       <c r="G13" s="66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" s="69">
         <v>26960</v>
@@ -10257,7 +11558,7 @@
       <c r="E14" s="66"/>
       <c r="F14" s="64"/>
       <c r="G14" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H14" s="77">
         <f>H12+H13</f>
@@ -10278,7 +11579,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H15" s="76">
         <f>H11-H14</f>
@@ -10299,7 +11600,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H16" s="73">
         <v>112000</v>
@@ -10319,7 +11620,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="74">
         <f>H15+H16</f>
@@ -10366,26 +11667,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4F5150-6BB5-4D89-BC93-31EBFDA0DB76}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
@@ -10422,7 +11723,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="61" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B2" s="62">
         <v>44799</v>
@@ -10431,7 +11732,7 @@
         <v>600</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="65"/>
       <c r="F2" s="72">
@@ -10454,7 +11755,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="61" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="62">
         <v>44799</v>
@@ -10463,7 +11764,7 @@
         <v>900</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="65"/>
       <c r="F3" s="72">
@@ -10505,7 +11806,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="61" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" s="62">
         <v>44788</v>
@@ -10538,7 +11839,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="61" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B6" s="62">
         <v>44796</v>
@@ -10599,7 +11900,7 @@
       <c r="E8" s="66"/>
       <c r="F8" s="64"/>
       <c r="G8" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H8" s="77">
         <f>H4+H7</f>
@@ -10620,7 +11921,7 @@
       <c r="E9" s="66"/>
       <c r="F9" s="64"/>
       <c r="G9" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="66">
         <v>358170.00200000015</v>
@@ -10637,7 +11938,7 @@
       <c r="E10" s="66"/>
       <c r="F10" s="64"/>
       <c r="G10" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" s="77">
         <f>H8+H9</f>
@@ -10655,7 +11956,7 @@
       <c r="E11" s="66"/>
       <c r="F11" s="64"/>
       <c r="G11" s="66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H11" s="69">
         <v>414400</v>
@@ -10672,7 +11973,7 @@
       <c r="E12" s="66"/>
       <c r="F12" s="64"/>
       <c r="G12" s="66" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H12" s="69">
         <v>53940</v>
@@ -10689,7 +11990,7 @@
       <c r="E13" s="66"/>
       <c r="F13" s="64"/>
       <c r="G13" s="66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H13" s="77">
         <f>H11+H12</f>
@@ -10710,7 +12011,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="10"/>
       <c r="G14" s="66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H14" s="78">
         <f>H10-H13</f>
@@ -10731,7 +12032,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H15" s="73">
         <v>112000</v>
@@ -10751,7 +12052,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" s="79">
         <f>H14+H15</f>
@@ -10792,1107 +12093,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7FC27F-8D9C-4413-896B-92A14FAE71F8}">
-  <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A2" s="61" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="62">
-        <v>44806</v>
-      </c>
-      <c r="C2" s="63">
-        <v>5000</v>
-      </c>
-      <c r="D2" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="72">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G2" s="65">
-        <f t="shared" ref="G2:G22" si="0">C2*F2</f>
-        <v>1400.0000000000002</v>
-      </c>
-      <c r="H2" s="66">
-        <f>G2*0.9</f>
-        <v>1260.0000000000002</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A3" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="62">
-        <v>44806</v>
-      </c>
-      <c r="C3" s="63">
-        <v>15000</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="65"/>
-      <c r="F3" s="72">
-        <v>1.75</v>
-      </c>
-      <c r="G3" s="65">
-        <f t="shared" si="0"/>
-        <v>26250</v>
-      </c>
-      <c r="H3" s="66">
-        <f>G3*0.9</f>
-        <v>23625</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A4" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="62">
-        <v>44806</v>
-      </c>
-      <c r="C4" s="63">
-        <v>15000</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="65"/>
-      <c r="F4" s="72">
-        <v>0.1</v>
-      </c>
-      <c r="G4" s="65">
-        <f t="shared" si="0"/>
-        <v>1500</v>
-      </c>
-      <c r="H4" s="66">
-        <f>G4</f>
-        <v>1500</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A5" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="62">
-        <v>44806</v>
-      </c>
-      <c r="C5" s="63">
-        <v>30000</v>
-      </c>
-      <c r="D5" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="72">
-        <v>0.192</v>
-      </c>
-      <c r="G5" s="65">
-        <f t="shared" si="0"/>
-        <v>5760</v>
-      </c>
-      <c r="H5" s="66">
-        <f>G5*0.9</f>
-        <v>5184</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A6" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="62">
-        <v>44809</v>
-      </c>
-      <c r="C6" s="63">
-        <v>40000</v>
-      </c>
-      <c r="D6" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="72">
-        <v>0.26</v>
-      </c>
-      <c r="G6" s="65">
-        <f t="shared" si="0"/>
-        <v>10400</v>
-      </c>
-      <c r="H6" s="66">
-        <f>G6</f>
-        <v>10400</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A7" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="62">
-        <v>44809</v>
-      </c>
-      <c r="C7" s="63">
-        <v>18000</v>
-      </c>
-      <c r="D7" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="72">
-        <v>0.18</v>
-      </c>
-      <c r="G7" s="65">
-        <f t="shared" si="0"/>
-        <v>3240</v>
-      </c>
-      <c r="H7" s="66">
-        <f>G7*0.9</f>
-        <v>2916</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="62">
-        <v>44810</v>
-      </c>
-      <c r="C8" s="63">
-        <v>60000</v>
-      </c>
-      <c r="D8" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="65"/>
-      <c r="F8" s="72">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="G8" s="65">
-        <f t="shared" si="0"/>
-        <v>2100</v>
-      </c>
-      <c r="H8" s="66">
-        <f>G8*0.9</f>
-        <v>1890</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A9" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="62">
-        <v>44810</v>
-      </c>
-      <c r="C9" s="63">
-        <v>130000</v>
-      </c>
-      <c r="D9" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="72">
-        <v>0.23</v>
-      </c>
-      <c r="G9" s="65">
-        <f t="shared" si="0"/>
-        <v>29900</v>
-      </c>
-      <c r="H9" s="66">
-        <f>G9</f>
-        <v>29900</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A10" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="62">
-        <v>44810</v>
-      </c>
-      <c r="C10" s="63">
-        <v>7500</v>
-      </c>
-      <c r="D10" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="72">
-        <v>0.18</v>
-      </c>
-      <c r="G10" s="65">
-        <f t="shared" si="0"/>
-        <v>1350</v>
-      </c>
-      <c r="H10" s="66">
-        <f>G10*0.9</f>
-        <v>1215</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A11" s="61" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="62">
-        <v>44811</v>
-      </c>
-      <c r="C11" s="63">
-        <v>27000</v>
-      </c>
-      <c r="D11" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="72">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G11" s="65">
-        <f t="shared" si="0"/>
-        <v>1890.0000000000002</v>
-      </c>
-      <c r="H11" s="66">
-        <f>G11</f>
-        <v>1890.0000000000002</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A12" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="62">
-        <v>44812</v>
-      </c>
-      <c r="C12" s="63">
-        <v>22500</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="65"/>
-      <c r="F12" s="72">
-        <v>1</v>
-      </c>
-      <c r="G12" s="65">
-        <f t="shared" si="0"/>
-        <v>22500</v>
-      </c>
-      <c r="H12" s="66">
-        <v>20587.5</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A13" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="62">
-        <v>44813</v>
-      </c>
-      <c r="C13" s="63">
-        <v>30000</v>
-      </c>
-      <c r="D13" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="65"/>
-      <c r="F13" s="72">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G13" s="65">
-        <f t="shared" si="0"/>
-        <v>2100</v>
-      </c>
-      <c r="H13" s="66">
-        <f>G13*0.9</f>
-        <v>1890</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A14" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="62">
-        <v>44813</v>
-      </c>
-      <c r="C14" s="63">
-        <v>15000</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="65"/>
-      <c r="F14" s="72">
-        <v>1</v>
-      </c>
-      <c r="G14" s="65">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-      <c r="H14" s="66">
-        <v>14085</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A15" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="62">
-        <v>44813</v>
-      </c>
-      <c r="C15" s="63">
-        <v>105000</v>
-      </c>
-      <c r="D15" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="72">
-        <v>0.12692000000000001</v>
-      </c>
-      <c r="G15" s="65">
-        <f t="shared" si="0"/>
-        <v>13326.6</v>
-      </c>
-      <c r="H15" s="66">
-        <v>12060.51</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A16" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="62">
-        <v>44813</v>
-      </c>
-      <c r="C16" s="63">
-        <v>48000</v>
-      </c>
-      <c r="D16" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="65"/>
-      <c r="F16" s="72">
-        <v>0.15</v>
-      </c>
-      <c r="G16" s="65">
-        <f t="shared" si="0"/>
-        <v>7200</v>
-      </c>
-      <c r="H16" s="66">
-        <f t="shared" ref="H16:H22" si="1">G16*0.9</f>
-        <v>6480</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A17" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="62">
-        <v>44817</v>
-      </c>
-      <c r="C17" s="63">
-        <v>45000</v>
-      </c>
-      <c r="D17" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="65"/>
-      <c r="F17" s="72">
-        <v>0.15</v>
-      </c>
-      <c r="G17" s="65">
-        <f t="shared" si="0"/>
-        <v>6750</v>
-      </c>
-      <c r="H17" s="66">
-        <f t="shared" si="1"/>
-        <v>6075</v>
-      </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A18" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="62">
-        <v>44818</v>
-      </c>
-      <c r="C18" s="63">
-        <v>21000</v>
-      </c>
-      <c r="D18" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="65"/>
-      <c r="F18" s="72">
-        <v>0.4</v>
-      </c>
-      <c r="G18" s="65">
-        <f t="shared" si="0"/>
-        <v>8400</v>
-      </c>
-      <c r="H18" s="66">
-        <f t="shared" si="1"/>
-        <v>7560</v>
-      </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A19" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="62">
-        <v>44818</v>
-      </c>
-      <c r="C19" s="63">
-        <v>10000</v>
-      </c>
-      <c r="D19" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="65"/>
-      <c r="F19" s="72">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="G19" s="65">
-        <f t="shared" si="0"/>
-        <v>2010.0000000000002</v>
-      </c>
-      <c r="H19" s="66">
-        <f t="shared" si="1"/>
-        <v>1809.0000000000002</v>
-      </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A20" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="62">
-        <v>44819</v>
-      </c>
-      <c r="C20" s="63">
-        <v>2400</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="72">
-        <v>0.4</v>
-      </c>
-      <c r="G20" s="65">
-        <f t="shared" si="0"/>
-        <v>960</v>
-      </c>
-      <c r="H20" s="66">
-        <f t="shared" si="1"/>
-        <v>864</v>
-      </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A21" s="61" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="62">
-        <v>44823</v>
-      </c>
-      <c r="C21" s="63">
-        <v>40000</v>
-      </c>
-      <c r="D21" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="65"/>
-      <c r="F21" s="72">
-        <v>0.15559999999999999</v>
-      </c>
-      <c r="G21" s="65">
-        <f t="shared" si="0"/>
-        <v>6223.9999999999991</v>
-      </c>
-      <c r="H21" s="66">
-        <f t="shared" si="1"/>
-        <v>5601.5999999999995</v>
-      </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A22" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="62">
-        <v>44825</v>
-      </c>
-      <c r="C22" s="63">
-        <v>12000</v>
-      </c>
-      <c r="D22" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="65"/>
-      <c r="F22" s="72">
-        <v>0.75</v>
-      </c>
-      <c r="G22" s="65">
-        <f t="shared" si="0"/>
-        <v>9000</v>
-      </c>
-      <c r="H22" s="66">
-        <f t="shared" si="1"/>
-        <v>8100</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A23" s="61"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="68">
-        <f>SUM(H2:H22)</f>
-        <v>164892.61000000002</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A24" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="62">
-        <v>44805</v>
-      </c>
-      <c r="C24" s="63">
-        <v>3000</v>
-      </c>
-      <c r="D24" s="64">
-        <v>18.5</v>
-      </c>
-      <c r="E24" s="65">
-        <v>55622.93</v>
-      </c>
-      <c r="F24" s="64">
-        <v>19</v>
-      </c>
-      <c r="G24" s="65">
-        <v>56873.75</v>
-      </c>
-      <c r="H24" s="66">
-        <f>G24-E24</f>
-        <v>1250.8199999999997</v>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A25" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="62">
-        <v>44809</v>
-      </c>
-      <c r="C25" s="63">
-        <v>60000</v>
-      </c>
-      <c r="D25" s="64">
-        <v>1.7</v>
-      </c>
-      <c r="E25" s="65">
-        <v>102225.92</v>
-      </c>
-      <c r="F25" s="64">
-        <v>1.71</v>
-      </c>
-      <c r="G25" s="65">
-        <v>102372.75</v>
-      </c>
-      <c r="H25" s="66">
-        <f>G25-E25</f>
-        <v>146.83000000000175</v>
-      </c>
-      <c r="I25" s="11"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A26" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="62">
-        <v>44813</v>
-      </c>
-      <c r="C26" s="63">
-        <v>10000</v>
-      </c>
-      <c r="D26" s="64">
-        <v>7.85</v>
-      </c>
-      <c r="E26" s="65">
-        <v>78673.88</v>
-      </c>
-      <c r="F26" s="64">
-        <v>8.25</v>
-      </c>
-      <c r="G26" s="65">
-        <v>82317.27</v>
-      </c>
-      <c r="H26" s="66">
-        <f>G26-E26</f>
-        <v>3643.3899999999994</v>
-      </c>
-      <c r="I26" s="11"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A27" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="62">
-        <v>44816</v>
-      </c>
-      <c r="C27" s="63">
-        <v>7500</v>
-      </c>
-      <c r="D27" s="64">
-        <v>14</v>
-      </c>
-      <c r="E27" s="65">
-        <v>105232.56</v>
-      </c>
-      <c r="F27" s="64">
-        <v>14.5</v>
-      </c>
-      <c r="G27" s="65">
-        <v>108509.13</v>
-      </c>
-      <c r="H27" s="66">
-        <f>G27-E27</f>
-        <v>3276.570000000007</v>
-      </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="6"/>
-    </row>
-    <row r="28" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A28" s="60"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="66">
-        <f>SUM(E24:E27)</f>
-        <v>341755.29000000004</v>
-      </c>
-      <c r="F28" s="64"/>
-      <c r="G28" s="66">
-        <f>SUM(G24:G27)</f>
-        <v>350072.9</v>
-      </c>
-      <c r="H28" s="68">
-        <f>SUM(H24:H27)</f>
-        <v>8317.6100000000079</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-    </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A29" s="60"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="H29" s="68">
-        <f>H23+H28</f>
-        <v>173210.22000000003</v>
-      </c>
-      <c r="I29" s="11"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="6"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A30" s="60"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="66" t="s">
-        <v>51</v>
-      </c>
-      <c r="H30" s="66">
-        <v>368938.24200000014</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A31" s="60"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="66" t="s">
-        <v>52</v>
-      </c>
-      <c r="H31" s="77">
-        <f>H29+H30</f>
-        <v>542148.46200000017</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A32" s="60"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="66" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="69">
-        <v>468340</v>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-    </row>
-    <row r="33" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A33" s="60"/>
-      <c r="B33" s="62"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="66" t="s">
-        <v>92</v>
-      </c>
-      <c r="H33" s="69">
-        <v>35345</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-    </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A34" s="60"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="77">
-        <f>H32+H33</f>
-        <v>503685</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="6"/>
-    </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A35" s="5"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="66" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35" s="70">
-        <f>H31-H34</f>
-        <v>38463.462000000174</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="6"/>
-    </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A36" s="5"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="H36" s="73">
-        <v>112000</v>
-      </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="73" t="s">
-        <v>55</v>
-      </c>
-      <c r="H37" s="79">
-        <f>H35+H36</f>
-        <v>150463.46200000017</v>
-      </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="6"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="K38" s="7"/>
-      <c r="M38" s="7"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="M39" s="7"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="M40" s="7"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="C41" s="12"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="10"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N22">
-    <sortCondition ref="B2:B22"/>
-    <sortCondition ref="A2:A22"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4475" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{408B4FE0-8096-45F4-B354-1147F3A93E5C}"/>
+  <xr:revisionPtr revIDLastSave="4563" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{416B31E3-9DFE-44A4-8186-4A61BFADED29}"/>
   <bookViews>
-    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JAN23" sheetId="58" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="99">
   <si>
     <t>Name</t>
   </si>
@@ -128,40 +128,40 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>IP</t>
+    <t>BGRIM</t>
+  </si>
+  <si>
+    <t>CKP</t>
   </si>
   <si>
     <t>CLP</t>
   </si>
   <si>
-    <t>TSTH</t>
+    <t>DIF</t>
   </si>
   <si>
-    <t>DIF</t>
+    <t>GLOBAL</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>LPF</t>
+  </si>
+  <si>
+    <t>NOBLE</t>
   </si>
   <si>
     <t>RATCH</t>
   </si>
   <si>
-    <t>GLOBAL</t>
+    <t>TSE</t>
   </si>
   <si>
-    <t>CKP</t>
+    <t>TSTH</t>
   </si>
   <si>
     <t>TU</t>
-  </si>
-  <si>
-    <t>BGRIM</t>
-  </si>
-  <si>
-    <t>NOBLE</t>
-  </si>
-  <si>
-    <t>TSE</t>
-  </si>
-  <si>
-    <t>LPF</t>
   </si>
   <si>
     <t>February Exp</t>
@@ -230,19 +230,19 @@
     <t xml:space="preserve">PTT </t>
   </si>
   <si>
-    <t>PTT</t>
-  </si>
-  <si>
     <t>AIMIRT</t>
   </si>
   <si>
     <t>CPNCG</t>
   </si>
   <si>
-    <t>TISCO</t>
+    <t>JASIF</t>
   </si>
   <si>
-    <t>JASIF</t>
+    <t>PTT</t>
+  </si>
+  <si>
+    <t>TISCO</t>
   </si>
   <si>
     <t>April Exp</t>
@@ -355,7 +355,7 @@
     <numFmt numFmtId="190" formatCode="0.0000"/>
     <numFmt numFmtId="191" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="14"/>
       <name val="Cordia New"/>
@@ -408,6 +408,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -447,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -508,10 +514,14 @@
     <xf numFmtId="188" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="188" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="188" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="188" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1344,7 +1354,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1874,7 +1884,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -1952,7 +1962,7 @@
         <f>SUM(G24:G27)</f>
         <v>350072.9</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="44">
         <f>SUM(H24:H27)</f>
         <v>8317.6100000000079</v>
       </c>
@@ -1992,7 +2002,7 @@
         <v>52</v>
       </c>
       <c r="H30" s="32">
-        <v>368938.24200000014</v>
+        <v>378717.68200000009</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="15"/>
@@ -2008,9 +2018,9 @@
       <c r="G31" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="43">
+      <c r="H31" s="42">
         <f>H29+H30</f>
-        <v>542148.46200000017</v>
+        <v>551927.90200000012</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="15"/>
@@ -2060,7 +2070,7 @@
       <c r="G34" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="43">
+      <c r="H34" s="42">
         <f>H32+H33</f>
         <v>503685</v>
       </c>
@@ -2081,9 +2091,9 @@
       <c r="G35" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="46">
         <f>H31-H34</f>
-        <v>38463.462000000174</v>
+        <v>48242.902000000118</v>
       </c>
       <c r="I35" s="11"/>
       <c r="J35" s="7"/>
@@ -2122,9 +2132,9 @@
       <c r="G37" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="H37" s="45">
+      <c r="H37" s="43">
         <f>H35+H36</f>
-        <v>150463.46200000017</v>
+        <v>160242.90200000012</v>
       </c>
       <c r="I37" s="11"/>
       <c r="J37" s="7"/>
@@ -2223,7 +2233,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2294,7 +2304,7 @@
       <c r="G4" s="31">
         <v>156028.64000000001</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="41">
         <f>G4-E4</f>
         <v>-10840.149999999994</v>
       </c>
@@ -2327,7 +2337,7 @@
       <c r="G5" s="31">
         <v>87555.65</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="41">
         <f>G5-E5</f>
         <v>4121.2599999999948</v>
       </c>
@@ -2360,7 +2370,7 @@
       <c r="G6" s="31">
         <v>55077.74</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="41">
         <f>G6-E6</f>
         <v>-6558.4800000000032</v>
       </c>
@@ -2393,7 +2403,7 @@
       <c r="G7" s="31">
         <v>130210.95</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="41">
         <f>G7-E7</f>
         <v>-23879.590000000011</v>
       </c>
@@ -2418,7 +2428,7 @@
         <f>SUM(G4:G7)</f>
         <v>428872.98000000004</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="41">
         <f>SUM(H4:H7)</f>
         <v>-37156.960000000014</v>
       </c>
@@ -2458,7 +2468,7 @@
         <v>52</v>
       </c>
       <c r="H10" s="32">
-        <v>542148.46200000017</v>
+        <v>551927.90200000012</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
@@ -2474,9 +2484,9 @@
       <c r="G11" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="42">
         <f>H9+H10</f>
-        <v>510256.50200000015</v>
+        <v>520035.9420000001</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="15"/>
@@ -2526,7 +2536,7 @@
       <c r="G14" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="42">
         <f>H12+H13</f>
         <v>574815</v>
       </c>
@@ -2547,9 +2557,9 @@
       <c r="G15" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="46">
         <f>H11-H14</f>
-        <v>-64558.497999999847</v>
+        <v>-54779.057999999903</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="7"/>
@@ -2588,9 +2598,9 @@
       <c r="G17" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="43">
         <f>H15+H16</f>
-        <v>47441.502000000153</v>
+        <v>57220.942000000097</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="7"/>
@@ -2685,7 +2695,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -3030,7 +3040,7 @@
       <c r="G13" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="44">
         <f>H3+H12</f>
         <v>-104006.85000000002</v>
       </c>
@@ -3052,7 +3062,7 @@
         <v>52</v>
       </c>
       <c r="H14" s="32">
-        <v>510256.50200000015</v>
+        <v>520035.9420000001</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="15"/>
@@ -3068,9 +3078,9 @@
       <c r="G15" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="43">
+      <c r="H15" s="42">
         <f>H13+H14</f>
-        <v>406249.65200000012</v>
+        <v>416029.09200000006</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="15"/>
@@ -3104,7 +3114,7 @@
         <v>96</v>
       </c>
       <c r="H17" s="35">
-        <v>34450</v>
+        <v>37950</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="15"/>
@@ -3120,9 +3130,9 @@
       <c r="G18" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="43">
+      <c r="H18" s="42">
         <f>H16+H17</f>
-        <v>609265</v>
+        <v>612765</v>
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="7"/>
@@ -3141,9 +3151,9 @@
       <c r="G19" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="46">
         <f>H15-H18</f>
-        <v>-203015.34799999988</v>
+        <v>-196735.90799999994</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="7"/>
@@ -3182,9 +3192,9 @@
       <c r="G21" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="H21" s="45">
+      <c r="H21" s="43">
         <f>H19+H20</f>
-        <v>-91015.347999999882</v>
+        <v>-84735.907999999938</v>
       </c>
       <c r="I21" s="11"/>
       <c r="J21" s="7"/>
@@ -3375,7 +3385,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3827,7 +3837,7 @@
         <f>SUM(G13:G18)</f>
         <v>384686.06</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="41">
         <f>SUM(H13:H18)</f>
         <v>-72223.72000000003</v>
       </c>
@@ -3867,7 +3877,7 @@
         <v>52</v>
       </c>
       <c r="H21" s="32">
-        <v>406249.65200000012</v>
+        <v>416029.09200000006</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="15"/>
@@ -3883,9 +3893,9 @@
       <c r="G22" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="42">
         <f>H20+H21</f>
-        <v>449894.23200000008</v>
+        <v>459673.67200000002</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="15"/>
@@ -3902,7 +3912,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="35">
-        <v>609265</v>
+        <v>612765</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="15"/>
@@ -3935,9 +3945,9 @@
       <c r="G25" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="43">
+      <c r="H25" s="42">
         <f>H23+H24</f>
-        <v>638795</v>
+        <v>642295</v>
       </c>
       <c r="I25" s="11"/>
       <c r="J25" s="7"/>
@@ -3958,7 +3968,7 @@
       </c>
       <c r="H26" s="36">
         <f>H22-H25</f>
-        <v>-188900.76799999992</v>
+        <v>-182621.32799999998</v>
       </c>
       <c r="I26" s="11"/>
       <c r="J26" s="7"/>
@@ -3997,9 +4007,9 @@
       <c r="G28" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="H28" s="45">
+      <c r="H28" s="49">
         <f>H26+H27</f>
-        <v>-76900.767999999924</v>
+        <v>-70621.32799999998</v>
       </c>
       <c r="I28" s="11"/>
       <c r="J28" s="7"/>
@@ -4734,7 +4744,7 @@
         <f>SUM(G2:G22)</f>
         <v>1826271.04</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="44">
         <f>SUM(H2:H22)</f>
         <v>117432.48000000004</v>
       </c>
@@ -4818,7 +4828,7 @@
       <c r="G29" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="36">
+      <c r="H29" s="46">
         <f>H25-H28</f>
         <v>54722.48000000004</v>
       </c>
@@ -4837,7 +4847,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="5" bestFit="1" customWidth="1"/>
@@ -4936,26 +4946,26 @@
         <v>27</v>
       </c>
       <c r="B4" s="28">
-        <v>44593</v>
+        <v>44617</v>
       </c>
       <c r="C4" s="29">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="D4" s="30">
-        <v>20.2</v>
+        <v>40</v>
       </c>
       <c r="E4" s="31">
-        <v>60734.22</v>
+        <v>360797.36</v>
       </c>
       <c r="F4" s="30">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G4" s="31">
-        <v>65853.820000000007</v>
-      </c>
-      <c r="H4" s="32">
-        <f t="shared" ref="H4:H26" si="0">G4-E4</f>
-        <v>5119.6000000000058</v>
+        <v>296342.17</v>
+      </c>
+      <c r="H4" s="41">
+        <f>G4-E4</f>
+        <v>-64455.19</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
@@ -4966,26 +4976,26 @@
         <v>28</v>
       </c>
       <c r="B5" s="28">
-        <v>44594</v>
+        <v>44614</v>
       </c>
       <c r="C5" s="29">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="D5" s="30">
         <v>5</v>
       </c>
       <c r="E5" s="31">
-        <v>50110.75</v>
+        <v>100221.49</v>
       </c>
       <c r="F5" s="30">
-        <v>5.5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G5" s="31">
-        <v>54878.18</v>
-      </c>
-      <c r="H5" s="32">
-        <f t="shared" si="0"/>
-        <v>4767.43</v>
+        <v>101774.08</v>
+      </c>
+      <c r="H5" s="41">
+        <f>G5-E5</f>
+        <v>1552.5899999999965</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
@@ -4993,29 +5003,29 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B6" s="28">
-        <v>44595</v>
+        <v>44594</v>
       </c>
       <c r="C6" s="29">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D6" s="30">
-        <v>16.7</v>
+        <v>5</v>
       </c>
       <c r="E6" s="31">
-        <v>83684.95</v>
+        <v>50110.75</v>
       </c>
       <c r="F6" s="30">
-        <v>14.7</v>
+        <v>5.5</v>
       </c>
       <c r="G6" s="31">
-        <v>73337.2</v>
-      </c>
-      <c r="H6" s="32">
-        <f t="shared" si="0"/>
-        <v>-10347.75</v>
+        <v>54878.18</v>
+      </c>
+      <c r="H6" s="41">
+        <f>G6-E6</f>
+        <v>4767.43</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
@@ -5023,29 +5033,29 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B7" s="28">
-        <v>44601</v>
+        <v>44610</v>
       </c>
       <c r="C7" s="29">
-        <v>1200</v>
+        <v>10000</v>
       </c>
       <c r="D7" s="30">
-        <v>42</v>
+        <v>14.7</v>
       </c>
       <c r="E7" s="31">
-        <v>50511.63</v>
+        <v>147325.59</v>
       </c>
       <c r="F7" s="30">
-        <v>50.5</v>
+        <v>14.3</v>
       </c>
       <c r="G7" s="31">
-        <v>60465.78</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" si="0"/>
-        <v>9954.1500000000015</v>
+        <v>142683.26999999999</v>
+      </c>
+      <c r="H7" s="41">
+        <f>G7-E7</f>
+        <v>-4642.320000000007</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
@@ -5053,29 +5063,29 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B8" s="28">
-        <v>44601</v>
+        <v>44606</v>
       </c>
       <c r="C8" s="29">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="D8" s="30">
-        <v>50.5</v>
+        <v>10.9</v>
       </c>
       <c r="E8" s="31">
-        <v>101223.7</v>
+        <v>262179.42</v>
       </c>
       <c r="F8" s="30">
-        <v>54</v>
+        <v>10.3</v>
       </c>
       <c r="G8" s="31">
-        <v>107760.79</v>
-      </c>
-      <c r="H8" s="32">
-        <f t="shared" si="0"/>
-        <v>6537.0899999999965</v>
+        <v>246652.48</v>
+      </c>
+      <c r="H8" s="41">
+        <f>G8-E8</f>
+        <v>-15526.939999999973</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
@@ -5083,29 +5093,29 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B9" s="28">
-        <v>44601</v>
+        <v>44613</v>
       </c>
       <c r="C9" s="29">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="D9" s="30">
-        <v>17.600000000000001</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="E9" s="31">
-        <v>52916.95</v>
+        <v>97214.85</v>
       </c>
       <c r="F9" s="30">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="G9" s="31">
-        <v>61962.45</v>
-      </c>
-      <c r="H9" s="32">
-        <f t="shared" si="0"/>
-        <v>9045.5</v>
+        <v>104767.44</v>
+      </c>
+      <c r="H9" s="41">
+        <f>G9-E9</f>
+        <v>7552.5899999999965</v>
       </c>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
@@ -5113,29 +5123,29 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="28">
-        <v>44602</v>
+        <v>44616</v>
       </c>
       <c r="C10" s="29">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="D10" s="30">
-        <v>17.600000000000001</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="E10" s="31">
-        <v>52916.95</v>
+        <v>194429.69</v>
       </c>
       <c r="F10" s="30">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="G10" s="31">
-        <v>63159.8</v>
-      </c>
-      <c r="H10" s="32">
-        <f t="shared" si="0"/>
-        <v>10242.850000000006</v>
+        <v>209534.87</v>
+      </c>
+      <c r="H10" s="41">
+        <f>G10-E10</f>
+        <v>15105.179999999993</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
@@ -5146,7 +5156,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="28">
-        <v>44603</v>
+        <v>44601</v>
       </c>
       <c r="C11" s="29">
         <v>3000</v>
@@ -5158,14 +5168,14 @@
         <v>52916.95</v>
       </c>
       <c r="F11" s="30">
-        <v>18.399999999999999</v>
+        <v>20.7</v>
       </c>
       <c r="G11" s="31">
-        <v>55077.74</v>
-      </c>
-      <c r="H11" s="32">
-        <f t="shared" si="0"/>
-        <v>2160.7900000000009</v>
+        <v>61962.45</v>
+      </c>
+      <c r="H11" s="41">
+        <f>G11-E11</f>
+        <v>9045.5</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -5173,29 +5183,29 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B12" s="28">
-        <v>44606</v>
+        <v>44602</v>
       </c>
       <c r="C12" s="29">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="D12" s="30">
-        <v>50.5</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E12" s="31">
-        <v>101223.7</v>
+        <v>52916.95</v>
       </c>
       <c r="F12" s="30">
-        <v>53.75</v>
+        <v>21.1</v>
       </c>
       <c r="G12" s="31">
-        <v>107261.89</v>
-      </c>
-      <c r="H12" s="32">
-        <f t="shared" si="0"/>
-        <v>6038.1900000000023</v>
+        <v>63159.8</v>
+      </c>
+      <c r="H12" s="41">
+        <f>G12-E12</f>
+        <v>10242.850000000006</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
@@ -5203,29 +5213,29 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="28">
-        <v>44606</v>
+        <v>44603</v>
       </c>
       <c r="C13" s="29">
-        <v>24000</v>
+        <v>3000</v>
       </c>
       <c r="D13" s="30">
-        <v>10.9</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E13" s="31">
-        <v>262179.42</v>
+        <v>52916.95</v>
       </c>
       <c r="F13" s="30">
-        <v>10.3</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="G13" s="31">
-        <v>246652.48</v>
-      </c>
-      <c r="H13" s="32">
-        <f t="shared" si="0"/>
-        <v>-15526.939999999973</v>
+        <v>55077.74</v>
+      </c>
+      <c r="H13" s="41">
+        <f>G13-E13</f>
+        <v>2160.7900000000009</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
@@ -5233,29 +5243,29 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" s="28">
-        <v>44607</v>
+        <v>44593</v>
       </c>
       <c r="C14" s="29">
-        <v>64700</v>
+        <v>3000</v>
       </c>
       <c r="D14" s="30">
-        <v>1.5</v>
+        <v>20.2</v>
       </c>
       <c r="E14" s="31">
-        <v>97264.95</v>
+        <v>60734.22</v>
       </c>
       <c r="F14" s="30">
-        <v>1.43</v>
+        <v>22</v>
       </c>
       <c r="G14" s="31">
-        <v>92316.07</v>
-      </c>
-      <c r="H14" s="32">
-        <f t="shared" si="0"/>
-        <v>-4948.8799999999901</v>
+        <v>65853.820000000007</v>
+      </c>
+      <c r="H14" s="41">
+        <f>G14-E14</f>
+        <v>5119.6000000000058</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
@@ -5263,29 +5273,29 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B15" s="28">
-        <v>44609</v>
+        <v>44614</v>
       </c>
       <c r="C15" s="29">
-        <v>10300</v>
+        <v>1200</v>
       </c>
       <c r="D15" s="30">
-        <v>1.5</v>
+        <v>42</v>
       </c>
       <c r="E15" s="31">
-        <v>15484.22</v>
+        <v>50511.63</v>
       </c>
       <c r="F15" s="30">
-        <v>1.43</v>
+        <v>46</v>
       </c>
       <c r="G15" s="31">
-        <v>14696.38</v>
-      </c>
-      <c r="H15" s="32">
-        <f t="shared" si="0"/>
-        <v>-787.84000000000015</v>
+        <v>55077.74</v>
+      </c>
+      <c r="H15" s="41">
+        <f>G15-E15</f>
+        <v>4566.1100000000006</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
@@ -5293,29 +5303,29 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B16" s="28">
-        <v>44610</v>
+        <v>44601</v>
       </c>
       <c r="C16" s="29">
-        <v>10000</v>
+        <v>1200</v>
       </c>
       <c r="D16" s="30">
-        <v>14.7</v>
+        <v>42</v>
       </c>
       <c r="E16" s="31">
-        <v>147325.59</v>
+        <v>50511.63</v>
       </c>
       <c r="F16" s="30">
-        <v>14.3</v>
+        <v>50.5</v>
       </c>
       <c r="G16" s="31">
-        <v>142683.26999999999</v>
-      </c>
-      <c r="H16" s="32">
-        <f t="shared" si="0"/>
-        <v>-4642.320000000007</v>
+        <v>60465.78</v>
+      </c>
+      <c r="H16" s="41">
+        <f>G16-E16</f>
+        <v>9954.1500000000015</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
@@ -5323,29 +5333,29 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B17" s="28">
-        <v>44613</v>
+        <v>44620</v>
       </c>
       <c r="C17" s="29">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="D17" s="30">
-        <v>45.75</v>
+        <v>42</v>
       </c>
       <c r="E17" s="31">
-        <v>137554</v>
+        <v>151534.89000000001</v>
       </c>
       <c r="F17" s="30">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="G17" s="31">
-        <v>137694.34</v>
-      </c>
-      <c r="H17" s="32">
-        <f t="shared" si="0"/>
-        <v>140.33999999999651</v>
+        <v>163437.20000000001</v>
+      </c>
+      <c r="H17" s="41">
+        <f>G17-E17</f>
+        <v>11902.309999999998</v>
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
@@ -5353,29 +5363,29 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="28">
-        <v>44613</v>
+        <v>44620</v>
       </c>
       <c r="C18" s="29">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D18" s="30">
-        <v>19.399999999999999</v>
+        <v>14</v>
       </c>
       <c r="E18" s="31">
-        <v>97214.85</v>
+        <v>140310.09</v>
       </c>
       <c r="F18" s="30">
-        <v>21</v>
+        <v>14.1</v>
       </c>
       <c r="G18" s="31">
-        <v>104767.44</v>
-      </c>
-      <c r="H18" s="32">
-        <f t="shared" si="0"/>
-        <v>7552.5899999999965</v>
+        <v>140687.70000000001</v>
+      </c>
+      <c r="H18" s="41">
+        <f>G18-E18</f>
+        <v>377.61000000001513</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
@@ -5383,29 +5393,29 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B19" s="28">
-        <v>44614</v>
+        <v>44595</v>
       </c>
       <c r="C19" s="29">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="D19" s="30">
-        <v>5</v>
+        <v>16.7</v>
       </c>
       <c r="E19" s="31">
-        <v>100221.49</v>
+        <v>83684.95</v>
       </c>
       <c r="F19" s="30">
-        <v>5.0999999999999996</v>
+        <v>14.7</v>
       </c>
       <c r="G19" s="31">
-        <v>101744.08</v>
-      </c>
-      <c r="H19" s="32">
-        <f t="shared" si="0"/>
-        <v>1522.5899999999965</v>
+        <v>73337.2</v>
+      </c>
+      <c r="H19" s="41">
+        <f>G19-E19</f>
+        <v>-10347.75</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
@@ -5416,26 +5426,26 @@
         <v>34</v>
       </c>
       <c r="B20" s="28">
-        <v>44615</v>
+        <v>44617</v>
       </c>
       <c r="C20" s="29">
-        <v>18000</v>
+        <v>63000</v>
       </c>
       <c r="D20" s="30">
-        <v>20.8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="31">
-        <v>375229.26</v>
+        <v>441976.77</v>
       </c>
       <c r="F20" s="30">
-        <v>20.5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="31">
-        <v>368182.7</v>
-      </c>
-      <c r="H20" s="32">
-        <f t="shared" si="0"/>
-        <v>-7046.5599999999977</v>
+        <v>377162.77</v>
+      </c>
+      <c r="H20" s="41">
+        <f>G20-E20</f>
+        <v>-64814</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
@@ -5443,29 +5453,29 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B21" s="28">
-        <v>44616</v>
+        <v>44613</v>
       </c>
       <c r="C21" s="29">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="D21" s="30">
-        <v>19.399999999999999</v>
+        <v>45.75</v>
       </c>
       <c r="E21" s="31">
-        <v>194429.69</v>
+        <v>137554</v>
       </c>
       <c r="F21" s="30">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G21" s="31">
-        <v>209534.87</v>
-      </c>
-      <c r="H21" s="32">
-        <f t="shared" si="0"/>
-        <v>15105.179999999993</v>
+        <v>137694.34</v>
+      </c>
+      <c r="H21" s="41">
+        <f>G21-E21</f>
+        <v>140.33999999999651</v>
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
@@ -5473,29 +5483,29 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B22" s="28">
-        <v>44617</v>
+        <v>44601</v>
       </c>
       <c r="C22" s="29">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="D22" s="30">
-        <v>40</v>
+        <v>50.5</v>
       </c>
       <c r="E22" s="31">
-        <v>360797.36</v>
+        <v>101223.7</v>
       </c>
       <c r="F22" s="30">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="G22" s="31">
-        <v>296342.17</v>
-      </c>
-      <c r="H22" s="32">
-        <f t="shared" si="0"/>
-        <v>-64455.19</v>
+        <v>107760.79</v>
+      </c>
+      <c r="H22" s="41">
+        <f>G22-E22</f>
+        <v>6537.0899999999965</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
@@ -5503,29 +5513,29 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B23" s="28">
-        <v>44617</v>
+        <v>44606</v>
       </c>
       <c r="C23" s="29">
-        <v>63000</v>
+        <v>2000</v>
       </c>
       <c r="D23" s="30">
-        <v>7</v>
+        <v>50.5</v>
       </c>
       <c r="E23" s="31">
-        <v>441976.77</v>
+        <v>101223.7</v>
       </c>
       <c r="F23" s="30">
-        <v>6</v>
+        <v>53.75</v>
       </c>
       <c r="G23" s="31">
-        <v>377162.77</v>
-      </c>
-      <c r="H23" s="32">
-        <f t="shared" si="0"/>
-        <v>-64814</v>
+        <v>107261.89</v>
+      </c>
+      <c r="H23" s="41">
+        <f>G23-E23</f>
+        <v>6038.1900000000023</v>
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
@@ -5533,7 +5543,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5553,8 +5563,8 @@
       <c r="G24" s="31">
         <v>99778.51</v>
       </c>
-      <c r="H24" s="32">
-        <f t="shared" si="0"/>
+      <c r="H24" s="41">
+        <f>G24-E24</f>
         <v>-4451.8400000000111</v>
       </c>
       <c r="I24" s="15"/>
@@ -5563,29 +5573,29 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B25" s="28">
-        <v>44620</v>
+        <v>44607</v>
       </c>
       <c r="C25" s="29">
-        <v>3600</v>
+        <v>64700</v>
       </c>
       <c r="D25" s="30">
-        <v>42</v>
+        <v>1.5</v>
       </c>
       <c r="E25" s="31">
-        <v>151534.89000000001</v>
+        <v>97264.95</v>
       </c>
       <c r="F25" s="30">
-        <v>45.5</v>
+        <v>1.43</v>
       </c>
       <c r="G25" s="31">
-        <v>163437.20000000001</v>
-      </c>
-      <c r="H25" s="32">
-        <f t="shared" si="0"/>
-        <v>11902.309999999998</v>
+        <v>92316.07</v>
+      </c>
+      <c r="H25" s="41">
+        <f>G25-E25</f>
+        <v>-4948.8799999999901</v>
       </c>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
@@ -5593,70 +5603,85 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="28">
-        <v>44620</v>
+        <v>44609</v>
       </c>
       <c r="C26" s="29">
-        <v>10000</v>
+        <v>10300</v>
       </c>
       <c r="D26" s="30">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="E26" s="31">
-        <v>140310.09</v>
+        <v>15484.22</v>
       </c>
       <c r="F26" s="30">
-        <v>14.1</v>
+        <v>1.43</v>
       </c>
       <c r="G26" s="31">
-        <v>140687.70000000001</v>
-      </c>
-      <c r="H26" s="32">
-        <f t="shared" si="0"/>
-        <v>377.61000000001513</v>
+        <v>14696.38</v>
+      </c>
+      <c r="H26" s="41">
+        <f>G26-E26</f>
+        <v>-787.84000000000015</v>
       </c>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1">
-      <c r="A27" s="26"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="32">
-        <f>SUM(E4:E26)</f>
-        <v>3231992.73</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="32">
-        <f t="shared" ref="G27" si="1">SUM(G4:G26)</f>
-        <v>3145437.63</v>
-      </c>
-      <c r="H27" s="34">
-        <f>SUM(H4:H26)</f>
-        <v>-86555.099999999977</v>
+    <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="28">
+        <v>44615</v>
+      </c>
+      <c r="C27" s="29">
+        <v>18000</v>
+      </c>
+      <c r="D27" s="30">
+        <v>20.8</v>
+      </c>
+      <c r="E27" s="31">
+        <v>375229.26</v>
+      </c>
+      <c r="F27" s="30">
+        <v>20.5</v>
+      </c>
+      <c r="G27" s="31">
+        <v>368182.7</v>
+      </c>
+      <c r="H27" s="41">
+        <f>G27-E27</f>
+        <v>-7046.5599999999977</v>
       </c>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="6"/>
+      <c r="K27" s="6"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1">
       <c r="A28" s="26"/>
       <c r="B28" s="28"/>
       <c r="C28" s="29"/>
       <c r="D28" s="33"/>
-      <c r="E28" s="32"/>
+      <c r="E28" s="32">
+        <f>SUM(E4:E27)</f>
+        <v>3282504.3600000003</v>
+      </c>
       <c r="F28" s="30"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32">
-        <v>117432.48000000004</v>
+      <c r="G28" s="32">
+        <f t="shared" ref="G28" si="0">SUM(G4:G27)</f>
+        <v>3200545.3699999992</v>
+      </c>
+      <c r="H28" s="44">
+        <f>SUM(H4:H27)</f>
+        <v>-81958.989999999976</v>
       </c>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
       <c r="L28" s="6"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1">
@@ -5667,9 +5692,8 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32"/>
-      <c r="H29" s="34">
-        <f>SUM(H2,H27,H28)</f>
-        <v>32424.480000000069</v>
+      <c r="H29" s="32">
+        <v>117432.48000000004</v>
       </c>
       <c r="I29" s="15"/>
       <c r="J29" s="15"/>
@@ -5682,11 +5706,10 @@
       <c r="D30" s="33"/>
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
-      <c r="G30" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="35">
-        <v>62710</v>
+      <c r="G30" s="32"/>
+      <c r="H30" s="34">
+        <f>SUM(H2,H28,H29)</f>
+        <v>37020.590000000069</v>
       </c>
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
@@ -5700,10 +5723,10 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="H31" s="37">
-        <v>27160</v>
+        <v>9</v>
+      </c>
+      <c r="H31" s="35">
+        <v>62710</v>
       </c>
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
@@ -5717,11 +5740,10 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="32">
-        <f>H30+H31</f>
-        <v>89870</v>
+        <v>39</v>
+      </c>
+      <c r="H32" s="37">
+        <v>27160</v>
       </c>
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
@@ -5735,27 +5757,45 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" s="36">
-        <f>H29-H32</f>
-        <v>-57445.519999999931</v>
+        <v>11</v>
+      </c>
+      <c r="H33" s="32">
+        <f>H31+H32</f>
+        <v>89870</v>
       </c>
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12">
-      <c r="B34" s="18"/>
-      <c r="H34" s="6"/>
+    <row r="34" spans="1:12" ht="15" customHeight="1">
+      <c r="A34" s="26"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="36">
+        <f>H30-H33</f>
+        <v>-52849.409999999931</v>
+      </c>
       <c r="I34" s="15"/>
       <c r="J34" s="15"/>
       <c r="L34" s="6"/>
     </row>
+    <row r="35" spans="1:12">
+      <c r="B35" s="18"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="L35" s="6"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O26">
-    <sortCondition ref="B4:B26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:O27">
+    <sortCondition ref="A4:A27"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -6236,7 +6276,7 @@
         <v>315.1699999999837</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6">
+    <row r="18" spans="1:8" ht="15.75">
       <c r="A18" s="26"/>
       <c r="B18" s="28"/>
       <c r="C18" s="29"/>
@@ -6250,7 +6290,7 @@
         <f>SUM(G9:G17)</f>
         <v>1070398.9000000001</v>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="44">
         <f>SUM(H9:H17)</f>
         <v>35536.859999999986</v>
       </c>
@@ -6281,7 +6321,7 @@
         <v>52</v>
       </c>
       <c r="H20" s="32">
-        <v>32424.480000000069</v>
+        <v>37020.590000000069</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.6">
@@ -6296,7 +6336,7 @@
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
-        <v>123533.58200000005</v>
+        <v>128129.69200000005</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.6">
@@ -6342,7 +6382,7 @@
         <v>187090</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6">
+    <row r="25" spans="1:8" ht="15.75">
       <c r="A25" s="26"/>
       <c r="B25" s="28"/>
       <c r="C25" s="29"/>
@@ -6352,9 +6392,9 @@
       <c r="G25" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="46">
         <f>H21-H24</f>
-        <v>-63556.417999999947</v>
+        <v>-58960.307999999946</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.6">
@@ -6371,7 +6411,7 @@
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
-        <v>48443.582000000053</v>
+        <v>53039.692000000054</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6424,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -6658,31 +6698,31 @@
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
         <v>61</v>
       </c>
       <c r="B9" s="28">
-        <v>44652</v>
+        <v>44669</v>
       </c>
       <c r="C9" s="29">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="D9" s="30">
-        <v>38.5</v>
+        <v>13</v>
       </c>
       <c r="E9" s="31">
-        <v>115755.83</v>
+        <v>130287.94</v>
       </c>
       <c r="F9" s="30">
-        <v>38.75</v>
+        <v>12.7</v>
       </c>
       <c r="G9" s="31">
-        <v>115992.52</v>
-      </c>
-      <c r="H9" s="32">
-        <f t="shared" ref="H9:H14" si="1">G9-E9</f>
-        <v>236.69000000000233</v>
+        <v>126718.71</v>
+      </c>
+      <c r="H9" s="41">
+        <f>G9-E9</f>
+        <v>-3569.2299999999959</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="7"/>
@@ -6691,7 +6731,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
         <v>62</v>
       </c>
@@ -6699,23 +6739,23 @@
         <v>44669</v>
       </c>
       <c r="C10" s="29">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="D10" s="30">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="E10" s="31">
-        <v>130287.94</v>
+        <v>248549.3</v>
       </c>
       <c r="F10" s="30">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="G10" s="31">
-        <v>126718.71</v>
-      </c>
-      <c r="H10" s="32">
-        <f t="shared" si="1"/>
-        <v>-3569.2299999999959</v>
+        <v>241463.99</v>
+      </c>
+      <c r="H10" s="41">
+        <f>G10-E10</f>
+        <v>-7085.3099999999977</v>
       </c>
       <c r="I10" s="11"/>
       <c r="J10" s="7"/>
@@ -6724,7 +6764,7 @@
       <c r="M10" s="15"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
         <v>50</v>
       </c>
@@ -6746,8 +6786,8 @@
       <c r="G11" s="31">
         <v>53640.93</v>
       </c>
-      <c r="H11" s="32">
-        <f t="shared" si="1"/>
+      <c r="H11" s="41">
+        <f>G11-E11</f>
         <v>2407.6999999999971</v>
       </c>
       <c r="I11" s="11"/>
@@ -6757,31 +6797,31 @@
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
         <v>63</v>
       </c>
       <c r="B12" s="28">
-        <v>44669</v>
+        <v>44680</v>
       </c>
       <c r="C12" s="29">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="D12" s="30">
-        <v>12.4</v>
+        <v>11.2</v>
       </c>
       <c r="E12" s="31">
-        <v>248549.3</v>
+        <v>112248.07</v>
       </c>
       <c r="F12" s="30">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="G12" s="31">
-        <v>241463.99</v>
-      </c>
-      <c r="H12" s="32">
-        <f t="shared" si="1"/>
-        <v>-7085.3099999999977</v>
+        <v>109756.36</v>
+      </c>
+      <c r="H12" s="41">
+        <f>G12-E12</f>
+        <v>-2491.7100000000064</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="7"/>
@@ -6790,31 +6830,31 @@
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="B13" s="28">
-        <v>44673</v>
+        <v>44679</v>
       </c>
       <c r="C13" s="29">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="D13" s="30">
-        <v>98</v>
+        <v>12.1</v>
       </c>
       <c r="E13" s="31">
-        <v>196434.12</v>
+        <v>181902.01</v>
       </c>
       <c r="F13" s="30">
-        <v>101.5</v>
+        <v>12.5</v>
       </c>
       <c r="G13" s="31">
-        <v>202550.38</v>
-      </c>
-      <c r="H13" s="32">
-        <f t="shared" si="1"/>
-        <v>6116.2600000000093</v>
+        <v>187084.7</v>
+      </c>
+      <c r="H13" s="41">
+        <f>G13-E13</f>
+        <v>5182.6900000000023</v>
       </c>
       <c r="I13" s="11"/>
       <c r="J13" s="7"/>
@@ -6823,31 +6863,31 @@
       <c r="M13" s="15"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="28">
-        <v>44680</v>
+        <v>44652</v>
       </c>
       <c r="C14" s="29">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="D14" s="30">
-        <v>11.2</v>
+        <v>38.5</v>
       </c>
       <c r="E14" s="31">
-        <v>112248.71</v>
+        <v>115755.83</v>
       </c>
       <c r="F14" s="30">
-        <v>11</v>
+        <v>38.75</v>
       </c>
       <c r="G14" s="31">
-        <v>109756.36</v>
-      </c>
-      <c r="H14" s="32">
-        <f t="shared" si="1"/>
-        <v>-2492.3500000000058</v>
+        <v>115992.52</v>
+      </c>
+      <c r="H14" s="41">
+        <f>G14-E14</f>
+        <v>236.69000000000233</v>
       </c>
       <c r="I14" s="11"/>
       <c r="J14" s="7"/>
@@ -6856,23 +6896,31 @@
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32">
-        <f>SUM(E9:E14)</f>
-        <v>854509.13</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="32">
-        <f>SUM(G9:G14)</f>
-        <v>850122.89</v>
-      </c>
-      <c r="H15" s="34">
-        <f>SUM(H9:H14)</f>
-        <v>-4386.2399999999907</v>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
+      <c r="A15" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="28">
+        <v>44673</v>
+      </c>
+      <c r="C15" s="29">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="30">
+        <v>98</v>
+      </c>
+      <c r="E15" s="31">
+        <v>196434.12</v>
+      </c>
+      <c r="F15" s="30">
+        <v>101.5</v>
+      </c>
+      <c r="G15" s="31">
+        <v>202550.38</v>
+      </c>
+      <c r="H15" s="41">
+        <f>G15-E15</f>
+        <v>6116.2600000000093</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="7"/>
@@ -6886,14 +6934,18 @@
       <c r="B16" s="28"/>
       <c r="C16" s="29"/>
       <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
+      <c r="E16" s="32">
+        <f>SUM(E9:E15)</f>
+        <v>1036410.5</v>
+      </c>
       <c r="F16" s="30"/>
-      <c r="G16" s="32" t="s">
-        <v>51</v>
+      <c r="G16" s="32">
+        <f>SUM(G9:G15)</f>
+        <v>1037207.59</v>
       </c>
       <c r="H16" s="34">
-        <f>H8+H15</f>
-        <v>40283.760000000009</v>
+        <f>SUM(H9:H15)</f>
+        <v>797.09000000001106</v>
       </c>
       <c r="I16" s="11"/>
       <c r="J16" s="7"/>
@@ -6910,10 +6962,11 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" s="32">
-        <v>123533.58200000005</v>
+        <v>51</v>
+      </c>
+      <c r="H17" s="34">
+        <f>H8+H16</f>
+        <v>45467.090000000011</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="7"/>
@@ -6930,11 +6983,10 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="34">
-        <f>H16+H17</f>
-        <v>163817.34200000006</v>
+        <v>52</v>
+      </c>
+      <c r="H18" s="32">
+        <v>128129.69200000005</v>
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="7"/>
@@ -6951,10 +7003,11 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="35">
-        <v>187090</v>
+        <v>53</v>
+      </c>
+      <c r="H19" s="34">
+        <f>H17+H18</f>
+        <v>173596.78200000006</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="7"/>
@@ -6971,10 +7024,10 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="H20" s="35">
-        <v>71150</v>
+        <v>187090</v>
       </c>
       <c r="I20" s="11"/>
       <c r="J20" s="7"/>
@@ -6991,11 +7044,10 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="34">
-        <f>H19+H20</f>
-        <v>258240</v>
+        <v>66</v>
+      </c>
+      <c r="H21" s="35">
+        <v>71150</v>
       </c>
       <c r="I21" s="11"/>
       <c r="J21" s="7"/>
@@ -7005,18 +7057,18 @@
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A22" s="5"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="10"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="36">
-        <f>H18-H21</f>
-        <v>-94422.657999999938</v>
+        <v>11</v>
+      </c>
+      <c r="H22" s="34">
+        <f>H20+H21</f>
+        <v>258240</v>
       </c>
       <c r="I22" s="11"/>
       <c r="J22" s="7"/>
@@ -7025,18 +7077,19 @@
       <c r="M22" s="15"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A23" s="5"/>
       <c r="B23" s="12"/>
       <c r="C23" s="8"/>
       <c r="D23" s="9"/>
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
-      <c r="G23" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="H23" s="39">
-        <v>112000</v>
+      <c r="G23" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="46">
+        <f>H19-H22</f>
+        <v>-84643.217999999935</v>
       </c>
       <c r="I23" s="11"/>
       <c r="J23" s="7"/>
@@ -7046,52 +7099,71 @@
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
-      <c r="A24" s="6"/>
+      <c r="A24" s="5"/>
       <c r="B24" s="12"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="14"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="H24" s="40">
-        <f>H22+H23</f>
-        <v>17577.342000000062</v>
+        <v>55</v>
+      </c>
+      <c r="H24" s="39">
+        <v>112000</v>
       </c>
       <c r="I24" s="11"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
-      <c r="N24" s="7"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="I25" s="7"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
+      <c r="A25" s="6"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="40">
+        <f>H23+H24</f>
+        <v>27356.782000000065</v>
+      </c>
+      <c r="I25" s="11"/>
+      <c r="J25" s="7"/>
       <c r="K25" s="7"/>
-      <c r="N25" s="13"/>
-    </row>
-    <row r="26" spans="1:14" ht="15.6" customHeight="1">
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="7"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="I26" s="7"/>
       <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="N26" s="13"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.6" customHeight="1">
       <c r="K27" s="7"/>
-      <c r="M27" s="7"/>
     </row>
     <row r="28" spans="1:14">
+      <c r="K28" s="7"/>
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="1:14">
       <c r="M29" s="7"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="K30" s="7"/>
+      <c r="M30" s="7"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="K31" s="7"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:K8">
-    <sortCondition ref="B2:B8"/>
-    <sortCondition ref="A2:A8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:N15">
+    <sortCondition ref="A9:A15"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -7514,7 +7586,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7546,7 +7618,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7820,7 +7892,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -7919,7 +7991,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -7952,7 +8024,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -7985,7 +8057,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -8018,7 +8090,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8183,7 +8255,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8247,7 +8319,7 @@
       <c r="M35" s="15"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A36" s="26"/>
       <c r="B36" s="28"/>
       <c r="C36" s="29"/>
@@ -8261,7 +8333,7 @@
         <f>SUM(G22:G35)</f>
         <v>1406427.98</v>
       </c>
-      <c r="H36" s="43">
+      <c r="H36" s="45">
         <f>SUM(H22:H35)</f>
         <v>-44273.119999999959</v>
       </c>
@@ -8303,8 +8375,8 @@
       <c r="G38" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="H38" s="32">
-        <v>163817.34200000006</v>
+      <c r="H38" s="34">
+        <v>173596.78200000006</v>
       </c>
       <c r="I38" s="11"/>
       <c r="J38" s="7"/>
@@ -8325,7 +8397,7 @@
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
-        <v>334428.91200000013</v>
+        <v>344208.35200000007</v>
       </c>
       <c r="I39" s="11"/>
       <c r="J39" s="7"/>
@@ -8384,7 +8456,7 @@
       <c r="G42" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="43">
+      <c r="H42" s="42">
         <f>H40+H41</f>
         <v>314880</v>
       </c>
@@ -8395,7 +8467,7 @@
       <c r="M42" s="15"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="43" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A43" s="5"/>
       <c r="B43" s="12"/>
       <c r="C43" s="8"/>
@@ -8405,9 +8477,9 @@
       <c r="G43" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H43" s="42">
+      <c r="H43" s="47">
         <f>H39-H42</f>
-        <v>19548.912000000128</v>
+        <v>29328.352000000072</v>
       </c>
       <c r="I43" s="11"/>
       <c r="J43" s="7"/>
@@ -8448,7 +8520,7 @@
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
-        <v>131548.91200000013</v>
+        <v>141328.35200000007</v>
       </c>
       <c r="I45" s="11"/>
       <c r="J45" s="7"/>
@@ -8578,7 +8650,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8857,7 +8929,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -8954,7 +9026,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="26"/>
       <c r="B15" s="28"/>
       <c r="C15" s="29"/>
@@ -8968,7 +9040,7 @@
         <f>SUM(G8:G14)</f>
         <v>726986.21000000008</v>
       </c>
-      <c r="H15" s="43">
+      <c r="H15" s="45">
         <f>SUM(H8:H14)</f>
         <v>-9641.7599999999948</v>
       </c>
@@ -9011,7 +9083,7 @@
         <v>52</v>
       </c>
       <c r="H17" s="32">
-        <v>334428.91200000013</v>
+        <v>344208.35200000007</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="7"/>
@@ -9032,7 +9104,7 @@
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
-        <v>376019.25200000015</v>
+        <v>385798.6920000001</v>
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="7"/>
@@ -9091,7 +9163,7 @@
       <c r="G21" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="43">
+      <c r="H21" s="42">
         <f>H19+H20</f>
         <v>387440</v>
       </c>
@@ -9102,7 +9174,7 @@
       <c r="M21" s="15"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A22" s="5"/>
       <c r="B22" s="12"/>
       <c r="C22" s="8"/>
@@ -9112,9 +9184,9 @@
       <c r="G22" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="47">
         <f>H18-H21</f>
-        <v>-11420.747999999847</v>
+        <v>-1641.3079999999027</v>
       </c>
       <c r="I22" s="11"/>
       <c r="J22" s="7"/>
@@ -9155,7 +9227,7 @@
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
-        <v>100579.25200000015</v>
+        <v>110358.6920000001</v>
       </c>
       <c r="I24" s="11"/>
       <c r="J24" s="7"/>
@@ -9299,7 +9371,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9332,7 +9404,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9398,7 +9470,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9429,7 +9501,7 @@
       <c r="M7" s="15"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:14" ht="15.6">
+    <row r="8" spans="1:14" ht="15.75">
       <c r="A8" s="26"/>
       <c r="B8" s="28"/>
       <c r="C8" s="29"/>
@@ -9443,7 +9515,7 @@
         <f>SUM(G4:G7)</f>
         <v>363393.31999999995</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="45">
         <f>SUM(H4:H7)</f>
         <v>-17849.250000000015</v>
       </c>
@@ -9483,7 +9555,7 @@
         <v>52</v>
       </c>
       <c r="H10" s="32">
-        <v>376019.25200000015</v>
+        <v>385798.6920000001</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
@@ -9501,7 +9573,7 @@
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
-        <v>358170.00200000015</v>
+        <v>367949.4420000001</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="15"/>
@@ -9551,7 +9623,7 @@
       <c r="G14" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="42">
         <f>H12+H13</f>
         <v>414400</v>
       </c>
@@ -9562,7 +9634,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="5"/>
       <c r="B15" s="12"/>
       <c r="C15" s="8"/>
@@ -9572,9 +9644,9 @@
       <c r="G15" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="42">
+      <c r="H15" s="47">
         <f>H11-H14</f>
-        <v>-56229.997999999847</v>
+        <v>-46450.557999999903</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="7"/>
@@ -9615,7 +9687,7 @@
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
-        <v>55770.002000000153</v>
+        <v>65549.442000000097</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="7"/>
@@ -9784,7 +9856,7 @@
       <c r="E4" s="31"/>
       <c r="F4" s="30"/>
       <c r="G4" s="31"/>
-      <c r="H4" s="43">
+      <c r="H4" s="42">
         <f>SUM(H2:H3)</f>
         <v>7155</v>
       </c>
@@ -9875,7 +9947,7 @@
         <f>SUM(G5:G6)</f>
         <v>269701.31</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="45">
         <f>SUM(H5:H6)</f>
         <v>3613.2400000000052</v>
       </c>
@@ -9893,7 +9965,7 @@
       <c r="G8" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="42">
         <f>H4+H7</f>
         <v>10768.240000000005</v>
       </c>
@@ -9915,7 +9987,7 @@
         <v>52</v>
       </c>
       <c r="H9" s="32">
-        <v>358170.00200000015</v>
+        <v>367949.4420000001</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="15"/>
@@ -9931,9 +10003,9 @@
       <c r="G10" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="43">
+      <c r="H10" s="42">
         <f>H8+H9</f>
-        <v>368938.24200000014</v>
+        <v>378717.68200000009</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
@@ -9983,7 +10055,7 @@
       <c r="G13" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="42">
         <f>H11+H12</f>
         <v>468340</v>
       </c>
@@ -10004,9 +10076,9 @@
       <c r="G14" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="48">
         <f>H10-H13</f>
-        <v>-99401.757999999856</v>
+        <v>-89622.317999999912</v>
       </c>
       <c r="I14" s="11"/>
       <c r="J14" s="7"/>
@@ -10045,9 +10117,9 @@
       <c r="G16" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="43">
         <f>H14+H15</f>
-        <v>12598.242000000144</v>
+        <v>22377.682000000088</v>
       </c>
       <c r="I16" s="11"/>
       <c r="J16" s="7"/>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26105"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4563" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{416B31E3-9DFE-44A4-8186-4A61BFADED29}"/>
+  <xr:revisionPtr revIDLastSave="4582" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2632BFF1-625F-45D2-8CC5-619EE5520820}"/>
   <bookViews>
-    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JAN23" sheetId="58" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>GFPT</t>
+  </si>
+  <si>
+    <t>JMART</t>
+  </si>
+  <si>
+    <t>SINGER</t>
   </si>
   <si>
     <t>B/F Expense</t>
@@ -192,9 +198,6 @@
   </si>
   <si>
     <t>MEGA</t>
-  </si>
-  <si>
-    <t>SINGER</t>
   </si>
   <si>
     <t>DOHOME</t>
@@ -887,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D107DCB-A805-454D-A7EE-FBDCD33FF9C5}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
@@ -956,57 +959,92 @@
         <v>98032.38</v>
       </c>
       <c r="H2" s="32">
-        <f t="shared" ref="H2" si="0">G2-E2</f>
+        <f t="shared" ref="H2:H3" si="0">G2-E2</f>
         <v>4074.7400000000052</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="32">
-        <f>SUM(E2:E2)</f>
-        <v>93957.64</v>
-      </c>
-      <c r="F3" s="30"/>
-      <c r="G3" s="32">
-        <f>SUM(G2:G2)</f>
-        <v>98032.38</v>
-      </c>
-      <c r="H3" s="34">
-        <f>SUM(H2:H2)</f>
-        <v>4074.7400000000052</v>
-      </c>
-      <c r="K3" s="15"/>
-    </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="26"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="32"/>
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="28">
+        <v>44935</v>
+      </c>
+      <c r="C3" s="29">
+        <v>3000</v>
+      </c>
+      <c r="D3" s="30">
+        <v>40</v>
+      </c>
+      <c r="E3" s="31">
+        <v>120265.79</v>
+      </c>
+      <c r="F3" s="30">
+        <v>42</v>
+      </c>
+      <c r="G3" s="31">
+        <v>125720.92</v>
+      </c>
+      <c r="H3" s="32">
+        <f t="shared" si="0"/>
+        <v>5455.1300000000047</v>
+      </c>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="28">
+        <v>44935</v>
+      </c>
+      <c r="C4" s="29">
+        <v>3600</v>
+      </c>
+      <c r="D4" s="30">
+        <v>27.5</v>
+      </c>
+      <c r="E4" s="31">
+        <v>99219.28</v>
+      </c>
+      <c r="F4" s="30">
+        <v>29.25</v>
+      </c>
+      <c r="G4" s="31">
+        <v>105066.77</v>
+      </c>
       <c r="H4" s="32">
-        <v>0</v>
-      </c>
+        <f t="shared" ref="H4" si="1">G4-E4</f>
+        <v>5847.4900000000052</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="26"/>
       <c r="B5" s="28"/>
       <c r="C5" s="29"/>
       <c r="D5" s="33"/>
-      <c r="E5" s="32"/>
+      <c r="E5" s="32">
+        <f>SUM(E2:E4)</f>
+        <v>313442.70999999996</v>
+      </c>
       <c r="F5" s="30"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32">
-        <f>SUM(H3:H4)</f>
-        <v>4074.7400000000052</v>
-      </c>
+      <c r="G5" s="32">
+        <f t="shared" ref="G5:H5" si="2">SUM(G2:G4)</f>
+        <v>328820.07</v>
+      </c>
+      <c r="H5" s="34">
+        <f t="shared" si="2"/>
+        <v>15377.360000000015</v>
+      </c>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="26"/>
@@ -1015,10 +1053,8 @@
       <c r="D6" s="33"/>
       <c r="E6" s="32"/>
       <c r="F6" s="30"/>
-      <c r="G6" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="35">
+      <c r="G6" s="32"/>
+      <c r="H6" s="32">
         <v>0</v>
       </c>
     </row>
@@ -1029,11 +1065,10 @@
       <c r="D7" s="33"/>
       <c r="E7" s="32"/>
       <c r="F7" s="30"/>
-      <c r="G7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="35">
-        <v>62710</v>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32">
+        <f>SUM(H5:H6)</f>
+        <v>15377.360000000015</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
@@ -1046,9 +1081,8 @@
       <c r="G8" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="32">
-        <f>H6+H7</f>
-        <v>62710</v>
+      <c r="H8" s="35">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -1061,9 +1095,38 @@
       <c r="G9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="36">
-        <f>H5-H8</f>
-        <v>-58635.259999999995</v>
+      <c r="H9" s="35">
+        <v>34710</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="32">
+        <f>H8+H9</f>
+        <v>34710</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="36">
+        <f>H7-H10</f>
+        <v>-19332.639999999985</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1193,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2" s="28">
         <v>44806</v>
@@ -1139,7 +1202,7 @@
         <v>5000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -1162,7 +1225,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1171,7 +1234,7 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -1194,7 +1257,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" s="28">
         <v>44806</v>
@@ -1203,7 +1266,7 @@
         <v>15000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -1226,7 +1289,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" s="28">
         <v>44806</v>
@@ -1235,7 +1298,7 @@
         <v>30000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -1258,7 +1321,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1267,7 +1330,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -1290,7 +1353,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="28">
         <v>44809</v>
@@ -1299,7 +1362,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -1322,7 +1385,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="28">
         <v>44810</v>
@@ -1331,7 +1394,7 @@
         <v>60000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -1354,7 +1417,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1363,7 +1426,7 @@
         <v>130000</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -1386,7 +1449,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B10" s="28">
         <v>44810</v>
@@ -1395,7 +1458,7 @@
         <v>7500</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -1418,7 +1481,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1427,7 +1490,7 @@
         <v>27000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -1450,7 +1513,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" s="28">
         <v>44812</v>
@@ -1459,7 +1522,7 @@
         <v>22500</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -1481,7 +1544,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B13" s="28">
         <v>44813</v>
@@ -1490,7 +1553,7 @@
         <v>30000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -1513,7 +1576,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="28">
         <v>44813</v>
@@ -1522,7 +1585,7 @@
         <v>15000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -1544,7 +1607,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B15" s="28">
         <v>44813</v>
@@ -1553,7 +1616,7 @@
         <v>105000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -1575,7 +1638,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="28">
         <v>44813</v>
@@ -1584,7 +1647,7 @@
         <v>48000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -1607,7 +1670,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="28">
         <v>44817</v>
@@ -1616,7 +1679,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -1639,7 +1702,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="28">
         <v>44818</v>
@@ -1648,7 +1711,7 @@
         <v>21000</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -1671,7 +1734,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" s="28">
         <v>44818</v>
@@ -1680,7 +1743,7 @@
         <v>10000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -1703,7 +1766,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -1712,7 +1775,7 @@
         <v>2400</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -1735,7 +1798,7 @@
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A21" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" s="28">
         <v>44823</v>
@@ -1744,7 +1807,7 @@
         <v>40000</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="38">
@@ -1767,7 +1830,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B22" s="28">
         <v>44825</v>
@@ -1776,7 +1839,7 @@
         <v>12000</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="38">
@@ -1818,7 +1881,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" s="28">
         <v>44805</v>
@@ -1851,7 +1914,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="28">
         <v>44809</v>
@@ -1884,7 +1947,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -1917,7 +1980,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" s="28">
         <v>44816</v>
@@ -1978,7 +2041,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -1999,7 +2062,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2016,7 +2079,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2034,7 +2097,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H32" s="35">
         <v>468340</v>
@@ -2051,7 +2114,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H33" s="35">
         <v>35345</v>
@@ -2068,7 +2131,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H34" s="42">
         <f>H32+H33</f>
@@ -2089,7 +2152,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="10"/>
       <c r="G35" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H35" s="46">
         <f>H31-H34</f>
@@ -2110,7 +2173,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2130,7 +2193,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2233,7 +2296,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2242,7 +2305,7 @@
         <v>4500</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2284,7 +2347,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B4" s="28">
         <v>44840</v>
@@ -2317,7 +2380,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2350,7 +2413,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B6" s="28">
         <v>44860</v>
@@ -2383,7 +2446,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="28">
         <v>44865</v>
@@ -2444,7 +2507,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2465,7 +2528,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2482,7 +2545,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2500,7 +2563,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H12" s="35">
         <v>503685</v>
@@ -2517,7 +2580,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H13" s="35">
         <v>71130</v>
@@ -2534,7 +2597,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -2555,7 +2618,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H15" s="46">
         <f>H11-H14</f>
@@ -2576,7 +2639,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2596,7 +2659,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -2695,7 +2758,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2704,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2746,7 +2809,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="28">
         <v>44866</v>
@@ -2779,7 +2842,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="28">
         <v>44866</v>
@@ -2812,7 +2875,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" s="28">
         <v>44867</v>
@@ -2845,7 +2908,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" s="28">
         <v>44872</v>
@@ -2878,7 +2941,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B8" s="28">
         <v>44873</v>
@@ -2911,7 +2974,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -2944,7 +3007,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -2977,7 +3040,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B11" s="28">
         <v>44887</v>
@@ -3038,7 +3101,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3059,7 +3122,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3076,7 +3139,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3094,7 +3157,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="35">
         <v>574815</v>
@@ -3111,7 +3174,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H17" s="35">
         <v>37950</v>
@@ -3128,7 +3191,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" s="42">
         <f>H16+H17</f>
@@ -3149,7 +3212,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="10"/>
       <c r="G19" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H19" s="46">
         <f>H15-H18</f>
@@ -3170,7 +3233,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3190,7 +3253,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3289,7 +3352,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2" s="28">
         <v>44897</v>
@@ -3298,7 +3361,7 @@
         <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3321,7 +3384,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="28">
         <v>44901</v>
@@ -3330,7 +3393,7 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -3353,7 +3416,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3362,7 +3425,7 @@
         <v>40000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -3385,7 +3448,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3394,7 +3457,7 @@
         <v>130000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -3417,7 +3480,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3426,7 +3489,7 @@
         <v>24000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -3448,7 +3511,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B7" s="28">
         <v>44908</v>
@@ -3457,7 +3520,7 @@
         <v>30000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -3480,7 +3543,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="28">
         <v>44910</v>
@@ -3489,7 +3552,7 @@
         <v>40000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -3512,7 +3575,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3521,7 +3584,7 @@
         <v>2400</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -3544,7 +3607,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B10" s="28">
         <v>44918</v>
@@ -3553,7 +3616,7 @@
         <v>20000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -3576,7 +3639,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B11" s="28">
         <v>44923</v>
@@ -3585,7 +3648,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -3627,7 +3690,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B13" s="28">
         <v>44915</v>
@@ -3660,7 +3723,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -3693,7 +3756,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="28">
         <v>44922</v>
@@ -3726,7 +3789,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="28">
         <v>44923</v>
@@ -3759,7 +3822,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="28">
         <v>44923</v>
@@ -3792,7 +3855,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B18" s="28">
         <v>44925</v>
@@ -3853,7 +3916,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -3874,7 +3937,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -3891,7 +3954,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -3909,7 +3972,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H23" s="35">
         <v>612765</v>
@@ -3926,7 +3989,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H24" s="35">
         <v>29530</v>
@@ -3943,7 +4006,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
@@ -3964,7 +4027,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H26" s="36">
         <f>H22-H25</f>
@@ -3985,7 +4048,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4005,7 +4068,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4102,7 +4165,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="28">
         <v>44566</v>
@@ -4132,7 +4195,7 @@
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="28">
         <v>44567</v>
@@ -4162,7 +4225,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="28">
         <v>44567</v>
@@ -4192,7 +4255,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" s="28">
         <v>44568</v>
@@ -4222,7 +4285,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="28">
         <v>44571</v>
@@ -4252,7 +4315,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="28">
         <v>44572</v>
@@ -4282,7 +4345,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="28">
         <v>44572</v>
@@ -4312,7 +4375,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" s="28">
         <v>44574</v>
@@ -4342,7 +4405,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" s="28">
         <v>44574</v>
@@ -4372,7 +4435,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="28">
         <v>44574</v>
@@ -4402,7 +4465,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="28">
         <v>44578</v>
@@ -4432,7 +4495,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="28">
         <v>44578</v>
@@ -4462,7 +4525,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" s="28">
         <v>44579</v>
@@ -4492,7 +4555,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="28">
         <v>44580</v>
@@ -4522,7 +4585,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="28">
         <v>44580</v>
@@ -4552,7 +4615,7 @@
     </row>
     <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="28">
         <v>44585</v>
@@ -4582,7 +4645,7 @@
     </row>
     <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B18" s="28">
         <v>44587</v>
@@ -4612,7 +4675,7 @@
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" s="28">
         <v>44588</v>
@@ -4642,7 +4705,7 @@
     </row>
     <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B20" s="28">
         <v>44589</v>
@@ -4672,7 +4735,7 @@
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B21" s="28">
         <v>44592</v>
@@ -4702,7 +4765,7 @@
     </row>
     <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B22" s="28">
         <v>44592</v>
@@ -4783,7 +4846,7 @@
       <c r="E26" s="32"/>
       <c r="F26" s="30"/>
       <c r="G26" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H26" s="35">
         <v>0</v>
@@ -4797,7 +4860,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="30"/>
       <c r="G27" s="32" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H27" s="35">
         <v>62710</v>
@@ -4811,7 +4874,7 @@
       <c r="E28" s="32"/>
       <c r="F28" s="30"/>
       <c r="G28" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H28" s="32">
         <f>H26+H27</f>
@@ -4826,7 +4889,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H29" s="46">
         <f>H25-H28</f>
@@ -4899,7 +4962,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" s="28">
         <v>44607</v>
@@ -4908,10 +4971,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="30">
         <v>0.1719</v>
@@ -4943,7 +5006,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -4973,7 +5036,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -5003,7 +5066,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -5033,7 +5096,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -5063,7 +5126,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -5093,7 +5156,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -5123,7 +5186,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -5153,7 +5216,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -5183,7 +5246,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -5213,7 +5276,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -5243,7 +5306,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5273,7 +5336,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5303,7 +5366,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5333,7 +5396,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5363,7 +5426,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5393,7 +5456,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5423,7 +5486,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5453,7 +5516,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5483,7 +5546,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5513,7 +5576,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5543,7 +5606,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5573,7 +5636,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5603,7 +5666,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5633,7 +5696,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -5723,7 +5786,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H31" s="35">
         <v>62710</v>
@@ -5740,7 +5803,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -5757,7 +5820,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H33" s="32">
         <f>H31+H32</f>
@@ -5775,7 +5838,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H34" s="36">
         <f>H30-H33</f>
@@ -5854,7 +5917,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -5863,10 +5926,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="38">
         <v>0.22220000000000001</v>
@@ -5882,7 +5945,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -5891,10 +5954,10 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="38">
         <v>0.26100000000000001</v>
@@ -5910,7 +5973,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -5919,10 +5982,10 @@
         <v>110000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="38">
         <v>0.25</v>
@@ -5938,7 +6001,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -5947,10 +6010,10 @@
         <v>20000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="38">
         <v>0.1195</v>
@@ -5966,7 +6029,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -5975,10 +6038,10 @@
         <v>10000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="38">
         <v>0.221</v>
@@ -5994,7 +6057,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -6003,10 +6066,10 @@
         <v>40100</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="38">
         <v>0.17380000000000001</v>
@@ -6035,7 +6098,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -6062,7 +6125,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -6089,7 +6152,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -6116,7 +6179,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6143,7 +6206,7 @@
     </row>
     <row r="13" spans="1:11" ht="15.6">
       <c r="A13" s="27" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B13" s="28">
         <v>44630</v>
@@ -6170,7 +6233,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6197,7 +6260,7 @@
     </row>
     <row r="15" spans="1:11" ht="15.6">
       <c r="A15" s="27" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B15" s="28">
         <v>44643</v>
@@ -6224,7 +6287,7 @@
     </row>
     <row r="16" spans="1:11" ht="15.6">
       <c r="A16" s="27" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B16" s="28">
         <v>44648</v>
@@ -6251,7 +6314,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6303,7 +6366,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6318,7 +6381,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6332,7 +6395,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6347,7 +6410,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H22" s="35">
         <v>89870</v>
@@ -6361,7 +6424,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6375,7 +6438,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H24" s="34">
         <f>H22+H23</f>
@@ -6390,7 +6453,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H25" s="46">
         <f>H21-H24</f>
@@ -6399,7 +6462,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6407,7 +6470,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6478,7 +6541,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6487,10 +6550,10 @@
         <v>900</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="38">
         <v>9</v>
@@ -6512,7 +6575,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6521,10 +6584,10 @@
         <v>6000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="38">
         <v>0.86</v>
@@ -6545,7 +6608,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="28">
         <v>44673</v>
@@ -6554,10 +6617,10 @@
         <v>9000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="38">
         <v>1.75</v>
@@ -6579,7 +6642,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" s="28">
         <v>44677</v>
@@ -6588,10 +6651,10 @@
         <v>900</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="38">
         <v>10</v>
@@ -6613,7 +6676,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6622,10 +6685,10 @@
         <v>9000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="38">
         <v>0.45</v>
@@ -6647,7 +6710,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="28">
         <v>44680</v>
@@ -6656,10 +6719,10 @@
         <v>9000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="38">
         <v>0.8</v>
@@ -6700,7 +6763,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="28">
         <v>44669</v>
@@ -6733,7 +6796,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="28">
         <v>44669</v>
@@ -6766,7 +6829,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -6799,7 +6862,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" s="28">
         <v>44680</v>
@@ -6832,7 +6895,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -6865,7 +6928,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="28">
         <v>44652</v>
@@ -6898,7 +6961,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="28">
         <v>44673</v>
@@ -6962,7 +7025,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -6983,7 +7046,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -7003,7 +7066,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -7024,7 +7087,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H20" s="35">
         <v>187090</v>
@@ -7044,7 +7107,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="35">
         <v>71150</v>
@@ -7064,7 +7127,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H22" s="34">
         <f>H20+H21</f>
@@ -7085,7 +7148,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H23" s="46">
         <f>H19-H22</f>
@@ -7106,7 +7169,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -7126,7 +7189,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -7227,7 +7290,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7236,10 +7299,10 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="38">
         <v>0.5</v>
@@ -7260,7 +7323,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7269,10 +7332,10 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="38">
         <v>0.52</v>
@@ -7294,7 +7357,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7303,10 +7366,10 @@
         <v>27000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="38">
         <v>0.36</v>
@@ -7328,7 +7391,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" s="28">
         <v>44687</v>
@@ -7337,10 +7400,10 @@
         <v>22500</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="38">
         <v>0.65</v>
@@ -7361,7 +7424,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="28">
         <v>44687</v>
@@ -7370,10 +7433,10 @@
         <v>27000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="38">
         <v>0.7</v>
@@ -7395,7 +7458,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="28">
         <v>44690</v>
@@ -7404,7 +7467,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -7426,7 +7489,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" s="28">
         <v>44693</v>
@@ -7435,7 +7498,7 @@
         <v>9000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -7458,7 +7521,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7467,7 +7530,7 @@
         <v>4500</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -7490,7 +7553,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="28">
         <v>44698</v>
@@ -7499,7 +7562,7 @@
         <v>30000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -7522,7 +7585,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" s="28">
         <v>44698</v>
@@ -7531,7 +7594,7 @@
         <v>60000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -7554,7 +7617,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" s="28">
         <v>44700</v>
@@ -7563,7 +7626,7 @@
         <v>3000</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -7586,7 +7649,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7595,7 +7658,7 @@
         <v>2000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -7618,7 +7681,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7627,7 +7690,7 @@
         <v>6000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -7650,7 +7713,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7659,7 +7722,7 @@
         <v>12000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -7681,7 +7744,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" s="28">
         <v>44705</v>
@@ -7690,7 +7753,7 @@
         <v>18000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -7713,7 +7776,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="28">
         <v>44705</v>
@@ -7722,7 +7785,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -7745,7 +7808,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" s="28">
         <v>44705</v>
@@ -7754,7 +7817,7 @@
         <v>4500</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -7777,7 +7840,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="28">
         <v>44706</v>
@@ -7786,7 +7849,7 @@
         <v>90000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -7808,7 +7871,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B20" s="28">
         <v>44712</v>
@@ -7817,7 +7880,7 @@
         <v>60000</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -7859,7 +7922,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" s="28">
         <v>44684</v>
@@ -7892,7 +7955,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -7925,7 +7988,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -7958,7 +8021,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A25" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="28">
         <v>44692</v>
@@ -7991,7 +8054,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -8024,7 +8087,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -8057,7 +8120,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -8090,7 +8153,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8123,7 +8186,7 @@
     </row>
     <row r="30" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A30" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B30" s="28">
         <v>44704</v>
@@ -8156,7 +8219,7 @@
     </row>
     <row r="31" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A31" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B31" s="28">
         <v>44704</v>
@@ -8189,7 +8252,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8222,7 +8285,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8255,7 +8318,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8288,7 +8351,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8352,7 +8415,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8373,7 +8436,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8393,7 +8456,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8414,7 +8477,7 @@
       <c r="E40" s="32"/>
       <c r="F40" s="30"/>
       <c r="G40" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H40" s="35">
         <v>258240</v>
@@ -8434,7 +8497,7 @@
       <c r="E41" s="32"/>
       <c r="F41" s="30"/>
       <c r="G41" s="32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H41" s="35">
         <v>56640</v>
@@ -8454,7 +8517,7 @@
       <c r="E42" s="32"/>
       <c r="F42" s="30"/>
       <c r="G42" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H42" s="42">
         <f>H40+H41</f>
@@ -8475,7 +8538,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="10"/>
       <c r="G43" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H43" s="47">
         <f>H39-H42</f>
@@ -8496,7 +8559,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8516,7 +8579,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8618,7 +8681,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8627,7 +8690,7 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -8650,7 +8713,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8659,7 +8722,7 @@
         <v>110000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -8682,7 +8745,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" s="28">
         <v>44727</v>
@@ -8691,7 +8754,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -8714,7 +8777,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8723,7 +8786,7 @@
         <v>6000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -8746,7 +8809,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="28">
         <v>44736</v>
@@ -8755,7 +8818,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -8797,7 +8860,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -8830,7 +8893,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" s="28">
         <v>44725</v>
@@ -8863,7 +8926,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -8896,7 +8959,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="28">
         <v>44735</v>
@@ -8929,7 +8992,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -8962,7 +9025,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="28">
         <v>44739</v>
@@ -8995,7 +9058,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -9059,7 +9122,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -9080,7 +9143,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -9100,7 +9163,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9121,7 +9184,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H19" s="35">
         <v>314880</v>
@@ -9141,7 +9204,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H20" s="35">
         <v>72560</v>
@@ -9161,7 +9224,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H21" s="42">
         <f>H19+H20</f>
@@ -9182,7 +9245,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H22" s="47">
         <f>H18-H21</f>
@@ -9203,7 +9266,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -9223,7 +9286,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9321,7 +9384,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="28">
         <v>44736</v>
@@ -9330,7 +9393,7 @@
         <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9371,7 +9434,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9404,7 +9467,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9437,7 +9500,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9470,7 +9533,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9531,7 +9594,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9552,7 +9615,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9569,7 +9632,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9587,7 +9650,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H12" s="35">
         <v>387440</v>
@@ -9604,7 +9667,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H13" s="35">
         <v>26960</v>
@@ -9621,7 +9684,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -9642,7 +9705,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H15" s="47">
         <f>H11-H14</f>
@@ -9663,7 +9726,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9683,7 +9746,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -9786,7 +9849,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="28">
         <v>44799</v>
@@ -9795,7 +9858,7 @@
         <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9818,7 +9881,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" s="28">
         <v>44799</v>
@@ -9827,7 +9890,7 @@
         <v>900</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -9869,7 +9932,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" s="28">
         <v>44788</v>
@@ -9902,7 +9965,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -9963,7 +10026,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -9984,7 +10047,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -10001,7 +10064,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -10019,7 +10082,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H11" s="35">
         <v>414400</v>
@@ -10036,7 +10099,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H12" s="35">
         <v>53940</v>
@@ -10053,7 +10116,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H13" s="42">
         <f>H11+H12</f>
@@ -10074,7 +10137,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="10"/>
       <c r="G14" s="32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H14" s="48">
         <f>H10-H13</f>
@@ -10095,7 +10158,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -10115,7 +10178,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26111"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4582" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2632BFF1-625F-45D2-8CC5-619EE5520820}"/>
+  <xr:revisionPtr revIDLastSave="4590" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61AEA9D6-1E6D-4E36-BF08-1876A5A81342}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>SINGER</t>
+  </si>
+  <si>
+    <t>PTTGC</t>
   </si>
   <si>
     <t>B/F Expense</t>
@@ -222,9 +225,6 @@
   </si>
   <si>
     <t>SCCC</t>
-  </si>
-  <si>
-    <t>PTTGC</t>
   </si>
   <si>
     <t xml:space="preserve">SCC </t>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D107DCB-A805-454D-A7EE-FBDCD33FF9C5}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
@@ -959,7 +959,7 @@
         <v>98032.38</v>
       </c>
       <c r="H2" s="32">
-        <f t="shared" ref="H2:H3" si="0">G2-E2</f>
+        <f t="shared" ref="H2:H4" si="0">G2-E2</f>
         <v>4074.7400000000052</v>
       </c>
       <c r="I2" s="15"/>
@@ -1019,44 +1019,62 @@
         <v>105066.77</v>
       </c>
       <c r="H4" s="32">
-        <f t="shared" ref="H4" si="1">G4-E4</f>
+        <f t="shared" si="0"/>
         <v>5847.4900000000052</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <f>SUM(E2:E4)</f>
-        <v>313442.70999999996</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="32">
-        <f t="shared" ref="G5:H5" si="2">SUM(G2:G4)</f>
-        <v>328820.07</v>
-      </c>
-      <c r="H5" s="34">
-        <f t="shared" si="2"/>
-        <v>15377.360000000015</v>
-      </c>
-      <c r="K5" s="15"/>
+    <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="28">
+        <v>44943</v>
+      </c>
+      <c r="C5" s="29">
+        <v>3000</v>
+      </c>
+      <c r="D5" s="30">
+        <v>51.25</v>
+      </c>
+      <c r="E5" s="31">
+        <v>163110.47</v>
+      </c>
+      <c r="F5" s="30">
+        <v>50.75</v>
+      </c>
+      <c r="G5" s="31">
+        <v>151912.78</v>
+      </c>
+      <c r="H5" s="32">
+        <f t="shared" ref="H5" si="1">G5-E5</f>
+        <v>-11197.690000000002</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="26"/>
       <c r="B6" s="28"/>
       <c r="C6" s="29"/>
       <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
+      <c r="E6" s="32">
+        <f>SUM(E2:E5)</f>
+        <v>476553.17999999993</v>
+      </c>
       <c r="F6" s="30"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32">
-        <v>0</v>
-      </c>
+      <c r="G6" s="32">
+        <f t="shared" ref="G6:H6" si="2">SUM(G2:G5)</f>
+        <v>480732.85</v>
+      </c>
+      <c r="H6" s="34">
+        <f t="shared" si="2"/>
+        <v>4179.6700000000128</v>
+      </c>
+      <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="26"/>
@@ -1067,8 +1085,7 @@
       <c r="F7" s="30"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32">
-        <f>SUM(H5:H6)</f>
-        <v>15377.360000000015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
@@ -1078,11 +1095,10 @@
       <c r="D8" s="33"/>
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="35">
-        <v>0</v>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32">
+        <f>SUM(H6:H7)</f>
+        <v>4179.6700000000128</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -1096,7 +1112,7 @@
         <v>12</v>
       </c>
       <c r="H9" s="35">
-        <v>34710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
@@ -1109,8 +1125,7 @@
       <c r="G10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="32">
-        <f>H8+H9</f>
+      <c r="H10" s="35">
         <v>34710</v>
       </c>
     </row>
@@ -1124,9 +1139,24 @@
       <c r="G11" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="36">
-        <f>H7-H10</f>
-        <v>-19332.639999999985</v>
+      <c r="H11" s="32">
+        <f>H9+H10</f>
+        <v>34710</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="36">
+        <f>H8-H11</f>
+        <v>-30530.329999999987</v>
       </c>
     </row>
   </sheetData>
@@ -1202,7 +1232,7 @@
         <v>5000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -1225,7 +1255,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1234,7 +1264,7 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -1266,7 +1296,7 @@
         <v>15000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -1298,7 +1328,7 @@
         <v>30000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -1321,7 +1351,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1330,7 +1360,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -1353,7 +1383,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="28">
         <v>44809</v>
@@ -1362,7 +1392,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -1385,7 +1415,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="28">
         <v>44810</v>
@@ -1394,7 +1424,7 @@
         <v>60000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -1426,7 +1456,7 @@
         <v>130000</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -1458,7 +1488,7 @@
         <v>7500</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -1481,7 +1511,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1490,7 +1520,7 @@
         <v>27000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -1522,7 +1552,7 @@
         <v>22500</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -1553,7 +1583,7 @@
         <v>30000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -1585,7 +1615,7 @@
         <v>15000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -1616,7 +1646,7 @@
         <v>105000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -1647,7 +1677,7 @@
         <v>48000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -1679,7 +1709,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -1711,7 +1741,7 @@
         <v>21000</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -1743,7 +1773,7 @@
         <v>10000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -1766,7 +1796,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -1775,7 +1805,7 @@
         <v>2400</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -1807,7 +1837,7 @@
         <v>40000</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="38">
@@ -1830,7 +1860,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="27" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="B22" s="28">
         <v>44825</v>
@@ -1839,7 +1869,7 @@
         <v>12000</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="38">
@@ -2041,7 +2071,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2062,7 +2092,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2079,7 +2109,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2097,7 +2127,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H32" s="35">
         <v>468340</v>
@@ -2131,7 +2161,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H34" s="42">
         <f>H32+H33</f>
@@ -2152,7 +2182,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="10"/>
       <c r="G35" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" s="46">
         <f>H31-H34</f>
@@ -2173,7 +2203,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2193,7 +2223,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2305,7 +2335,7 @@
         <v>4500</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2380,7 +2410,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2446,7 +2476,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="B7" s="28">
         <v>44865</v>
@@ -2507,7 +2537,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2528,7 +2558,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2545,7 +2575,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2563,7 +2593,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="35">
         <v>503685</v>
@@ -2597,7 +2627,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -2618,7 +2648,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="46">
         <f>H11-H14</f>
@@ -2639,7 +2669,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2659,7 +2689,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -2767,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2875,7 +2905,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="28">
         <v>44867</v>
@@ -2974,7 +3004,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3007,7 +3037,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3101,7 +3131,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3122,7 +3152,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3139,7 +3169,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3157,7 +3187,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="35">
         <v>574815</v>
@@ -3191,7 +3221,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="42">
         <f>H16+H17</f>
@@ -3212,7 +3242,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="10"/>
       <c r="G19" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="46">
         <f>H15-H18</f>
@@ -3233,7 +3263,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3253,7 +3283,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3361,7 +3391,7 @@
         <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3384,7 +3414,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="28">
         <v>44901</v>
@@ -3393,7 +3423,7 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -3416,7 +3446,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3425,7 +3455,7 @@
         <v>40000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -3457,7 +3487,7 @@
         <v>130000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -3480,7 +3510,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3489,7 +3519,7 @@
         <v>24000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -3520,7 +3550,7 @@
         <v>30000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -3552,7 +3582,7 @@
         <v>40000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -3575,7 +3605,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3584,7 +3614,7 @@
         <v>2400</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -3616,7 +3646,7 @@
         <v>20000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -3648,7 +3678,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -3723,7 +3753,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -3855,7 +3885,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="28">
         <v>44925</v>
@@ -3916,7 +3946,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -3937,7 +3967,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -3954,7 +3984,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -3972,7 +4002,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H23" s="35">
         <v>612765</v>
@@ -4006,7 +4036,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
@@ -4027,7 +4057,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="36">
         <f>H22-H25</f>
@@ -4048,7 +4078,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4068,7 +4098,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4165,7 +4195,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="28">
         <v>44566</v>
@@ -4195,7 +4225,7 @@
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="28">
         <v>44567</v>
@@ -4225,7 +4255,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="28">
         <v>44567</v>
@@ -4255,7 +4285,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="28">
         <v>44568</v>
@@ -4285,7 +4315,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="28">
         <v>44571</v>
@@ -4315,7 +4345,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="28">
         <v>44572</v>
@@ -4345,7 +4375,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="28">
         <v>44572</v>
@@ -4375,7 +4405,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="28">
         <v>44574</v>
@@ -4405,7 +4435,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="28">
         <v>44574</v>
@@ -4435,7 +4465,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="28">
         <v>44574</v>
@@ -4465,7 +4495,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="28">
         <v>44578</v>
@@ -4495,7 +4525,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="28">
         <v>44578</v>
@@ -4525,7 +4555,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="28">
         <v>44579</v>
@@ -4555,7 +4585,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="28">
         <v>44580</v>
@@ -4585,7 +4615,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="28">
         <v>44580</v>
@@ -4615,7 +4645,7 @@
     </row>
     <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="28">
         <v>44585</v>
@@ -4645,7 +4675,7 @@
     </row>
     <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="28">
         <v>44587</v>
@@ -4675,7 +4705,7 @@
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="28">
         <v>44588</v>
@@ -4705,7 +4735,7 @@
     </row>
     <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="28">
         <v>44589</v>
@@ -4735,7 +4765,7 @@
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="28">
         <v>44592</v>
@@ -4765,7 +4795,7 @@
     </row>
     <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="28">
         <v>44592</v>
@@ -4846,7 +4876,7 @@
       <c r="E26" s="32"/>
       <c r="F26" s="30"/>
       <c r="G26" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H26" s="35">
         <v>0</v>
@@ -4860,7 +4890,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="30"/>
       <c r="G27" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27" s="35">
         <v>62710</v>
@@ -4874,7 +4904,7 @@
       <c r="E28" s="32"/>
       <c r="F28" s="30"/>
       <c r="G28" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" s="32">
         <f>H26+H27</f>
@@ -4889,7 +4919,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="46">
         <f>H25-H28</f>
@@ -4962,7 +4992,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="28">
         <v>44607</v>
@@ -4971,10 +5001,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="30">
         <v>0.1719</v>
@@ -5006,7 +5036,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -5036,7 +5066,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -5066,7 +5096,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -5096,7 +5126,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -5126,7 +5156,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -5156,7 +5186,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -5186,7 +5216,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -5216,7 +5246,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -5246,7 +5276,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -5276,7 +5306,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -5306,7 +5336,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5336,7 +5366,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5366,7 +5396,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5396,7 +5426,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5426,7 +5456,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5456,7 +5486,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5486,7 +5516,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5516,7 +5546,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5546,7 +5576,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5576,7 +5606,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5606,7 +5636,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5636,7 +5666,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5666,7 +5696,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5696,7 +5726,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -5786,7 +5816,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H31" s="35">
         <v>62710</v>
@@ -5803,7 +5833,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -5820,7 +5850,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" s="32">
         <f>H31+H32</f>
@@ -5838,7 +5868,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" s="36">
         <f>H30-H33</f>
@@ -5917,7 +5947,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -5926,10 +5956,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="38">
         <v>0.22220000000000001</v>
@@ -5945,7 +5975,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -5954,10 +5984,10 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="38">
         <v>0.26100000000000001</v>
@@ -5973,7 +6003,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -5982,10 +6012,10 @@
         <v>110000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="38">
         <v>0.25</v>
@@ -6001,7 +6031,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -6010,10 +6040,10 @@
         <v>20000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="38">
         <v>0.1195</v>
@@ -6029,7 +6059,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -6038,10 +6068,10 @@
         <v>10000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="38">
         <v>0.221</v>
@@ -6057,7 +6087,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -6066,10 +6096,10 @@
         <v>40100</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="38">
         <v>0.17380000000000001</v>
@@ -6098,7 +6128,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -6125,7 +6155,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -6152,7 +6182,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -6179,7 +6209,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6233,7 +6263,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6314,7 +6344,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6366,7 +6396,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6381,7 +6411,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6395,7 +6425,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6410,7 +6440,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H22" s="35">
         <v>89870</v>
@@ -6424,7 +6454,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6438,7 +6468,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="34">
         <f>H22+H23</f>
@@ -6453,7 +6483,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" s="46">
         <f>H21-H24</f>
@@ -6462,7 +6492,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6470,7 +6500,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6541,7 +6571,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6550,10 +6580,10 @@
         <v>900</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="38">
         <v>9</v>
@@ -6575,7 +6605,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6584,10 +6614,10 @@
         <v>6000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="38">
         <v>0.86</v>
@@ -6608,7 +6638,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="B4" s="28">
         <v>44673</v>
@@ -6617,10 +6647,10 @@
         <v>9000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="38">
         <v>1.75</v>
@@ -6651,10 +6681,10 @@
         <v>900</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="38">
         <v>10</v>
@@ -6676,7 +6706,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6685,10 +6715,10 @@
         <v>9000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="38">
         <v>0.45</v>
@@ -6719,10 +6749,10 @@
         <v>9000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="38">
         <v>0.8</v>
@@ -6829,7 +6859,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -6895,7 +6925,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -7025,7 +7055,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -7046,7 +7076,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -7066,7 +7096,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -7087,7 +7117,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" s="35">
         <v>187090</v>
@@ -7127,7 +7157,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="34">
         <f>H20+H21</f>
@@ -7148,7 +7178,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="46">
         <f>H19-H22</f>
@@ -7169,7 +7199,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -7189,7 +7219,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -7290,7 +7320,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7299,10 +7329,10 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="38">
         <v>0.5</v>
@@ -7323,7 +7353,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7332,10 +7362,10 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="38">
         <v>0.52</v>
@@ -7357,7 +7387,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7366,10 +7396,10 @@
         <v>27000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="38">
         <v>0.36</v>
@@ -7400,10 +7430,10 @@
         <v>22500</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="38">
         <v>0.65</v>
@@ -7433,10 +7463,10 @@
         <v>27000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="38">
         <v>0.7</v>
@@ -7467,7 +7497,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -7498,7 +7528,7 @@
         <v>9000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -7521,7 +7551,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7530,7 +7560,7 @@
         <v>4500</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -7562,7 +7592,7 @@
         <v>30000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -7594,7 +7624,7 @@
         <v>60000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -7626,7 +7656,7 @@
         <v>3000</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -7658,7 +7688,7 @@
         <v>2000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -7681,7 +7711,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7690,7 +7720,7 @@
         <v>6000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -7713,7 +7743,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7722,7 +7752,7 @@
         <v>12000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -7753,7 +7783,7 @@
         <v>18000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -7785,7 +7815,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -7817,7 +7847,7 @@
         <v>4500</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -7849,7 +7879,7 @@
         <v>90000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -7871,7 +7901,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="28">
         <v>44712</v>
@@ -7880,7 +7910,7 @@
         <v>60000</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -7988,7 +8018,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -8054,7 +8084,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -8087,7 +8117,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -8153,7 +8183,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8252,7 +8282,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8285,7 +8315,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8318,7 +8348,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8351,7 +8381,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8415,7 +8445,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8436,7 +8466,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8456,7 +8486,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8477,7 +8507,7 @@
       <c r="E40" s="32"/>
       <c r="F40" s="30"/>
       <c r="G40" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H40" s="35">
         <v>258240</v>
@@ -8517,7 +8547,7 @@
       <c r="E42" s="32"/>
       <c r="F42" s="30"/>
       <c r="G42" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" s="42">
         <f>H40+H41</f>
@@ -8538,7 +8568,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="10"/>
       <c r="G43" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H43" s="47">
         <f>H39-H42</f>
@@ -8559,7 +8589,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8579,7 +8609,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8681,7 +8711,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8690,7 +8720,7 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -8722,7 +8752,7 @@
         <v>110000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -8754,7 +8784,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -8777,7 +8807,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8786,7 +8816,7 @@
         <v>6000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -8818,7 +8848,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -8860,7 +8890,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -8926,7 +8956,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -8992,7 +9022,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -9058,7 +9088,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -9122,7 +9152,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -9143,7 +9173,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -9163,7 +9193,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9184,7 +9214,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H19" s="35">
         <v>314880</v>
@@ -9224,7 +9254,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="42">
         <f>H19+H20</f>
@@ -9245,7 +9275,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="47">
         <f>H18-H21</f>
@@ -9266,7 +9296,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -9286,7 +9316,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9393,7 +9423,7 @@
         <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9500,7 +9530,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9533,7 +9563,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9594,7 +9624,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9615,7 +9645,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9632,7 +9662,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9650,7 +9680,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="35">
         <v>387440</v>
@@ -9684,7 +9714,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -9705,7 +9735,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="47">
         <f>H11-H14</f>
@@ -9726,7 +9756,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9746,7 +9776,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -9858,7 +9888,7 @@
         <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9890,7 +9920,7 @@
         <v>900</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -9965,7 +9995,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -10026,7 +10056,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -10047,7 +10077,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -10064,7 +10094,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -10082,7 +10112,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" s="35">
         <v>414400</v>
@@ -10116,7 +10146,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="42">
         <f>H11+H12</f>
@@ -10137,7 +10167,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="10"/>
       <c r="G14" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="48">
         <f>H10-H13</f>
@@ -10158,7 +10188,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -10178,7 +10208,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4590" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61AEA9D6-1E6D-4E36-BF08-1876A5A81342}"/>
+  <xr:revisionPtr revIDLastSave="4598" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F95826F-23BD-44EA-BB22-6489128A70BC}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>PTTGC</t>
+  </si>
+  <si>
+    <t>STA</t>
   </si>
   <si>
     <t>B/F Expense</t>
@@ -249,9 +252,6 @@
   </si>
   <si>
     <t>April Exp</t>
-  </si>
-  <si>
-    <t>STA</t>
   </si>
   <si>
     <t>TMT</t>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D107DCB-A805-454D-A7EE-FBDCD33FF9C5}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
@@ -959,7 +959,7 @@
         <v>98032.38</v>
       </c>
       <c r="H2" s="32">
-        <f t="shared" ref="H2:H4" si="0">G2-E2</f>
+        <f t="shared" ref="H2:H5" si="0">G2-E2</f>
         <v>4074.7400000000052</v>
       </c>
       <c r="I2" s="15"/>
@@ -1049,44 +1049,62 @@
         <v>151912.78</v>
       </c>
       <c r="H5" s="32">
-        <f t="shared" ref="H5" si="1">G5-E5</f>
+        <f t="shared" si="0"/>
         <v>-11197.690000000002</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32">
-        <f>SUM(E2:E5)</f>
-        <v>476553.17999999993</v>
-      </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32">
-        <f t="shared" ref="G6:H6" si="2">SUM(G2:G5)</f>
-        <v>480732.85</v>
-      </c>
-      <c r="H6" s="34">
-        <f t="shared" si="2"/>
-        <v>4179.6700000000128</v>
-      </c>
-      <c r="K6" s="15"/>
+    <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="28">
+        <v>44945</v>
+      </c>
+      <c r="C6" s="29">
+        <v>2500</v>
+      </c>
+      <c r="D6" s="30">
+        <v>32.75</v>
+      </c>
+      <c r="E6" s="31">
+        <v>82056.34</v>
+      </c>
+      <c r="F6" s="30">
+        <v>21.2</v>
+      </c>
+      <c r="G6" s="31">
+        <v>52882.61</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" ref="H6" si="1">G6-E6</f>
+        <v>-29173.729999999996</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="26"/>
       <c r="B7" s="28"/>
       <c r="C7" s="29"/>
       <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
+      <c r="E7" s="32">
+        <f>SUM(E2:E6)</f>
+        <v>558609.5199999999</v>
+      </c>
       <c r="F7" s="30"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32">
-        <v>0</v>
-      </c>
+      <c r="G7" s="32">
+        <f t="shared" ref="G7:H7" si="2">SUM(G2:G6)</f>
+        <v>533615.46</v>
+      </c>
+      <c r="H7" s="34">
+        <f t="shared" si="2"/>
+        <v>-24994.059999999983</v>
+      </c>
+      <c r="K7" s="15"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
       <c r="A8" s="26"/>
@@ -1097,8 +1115,7 @@
       <c r="F8" s="30"/>
       <c r="G8" s="32"/>
       <c r="H8" s="32">
-        <f>SUM(H6:H7)</f>
-        <v>4179.6700000000128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -1108,11 +1125,10 @@
       <c r="D9" s="33"/>
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="35">
-        <v>0</v>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32">
+        <f>SUM(H7:H8)</f>
+        <v>-24994.059999999983</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
@@ -1126,7 +1142,7 @@
         <v>13</v>
       </c>
       <c r="H10" s="35">
-        <v>34710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
@@ -1139,8 +1155,7 @@
       <c r="G11" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="32">
-        <f>H9+H10</f>
+      <c r="H11" s="35">
         <v>34710</v>
       </c>
     </row>
@@ -1154,9 +1169,24 @@
       <c r="G12" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="36">
-        <f>H8-H11</f>
-        <v>-30530.329999999987</v>
+      <c r="H12" s="32">
+        <f>H10+H11</f>
+        <v>34710</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="36">
+        <f>H9-H12</f>
+        <v>-59704.059999999983</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1262,7 @@
         <v>5000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -1255,7 +1285,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1264,7 +1294,7 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -1296,7 +1326,7 @@
         <v>15000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -1328,7 +1358,7 @@
         <v>30000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -1351,7 +1381,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1360,7 +1390,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -1383,7 +1413,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="28">
         <v>44809</v>
@@ -1392,7 +1422,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -1415,7 +1445,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="28">
         <v>44810</v>
@@ -1424,7 +1454,7 @@
         <v>60000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -1447,7 +1477,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1456,7 +1486,7 @@
         <v>130000</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -1488,7 +1518,7 @@
         <v>7500</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -1511,7 +1541,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1520,7 +1550,7 @@
         <v>27000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -1543,7 +1573,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B12" s="28">
         <v>44812</v>
@@ -1552,7 +1582,7 @@
         <v>22500</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -1583,7 +1613,7 @@
         <v>30000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -1615,7 +1645,7 @@
         <v>15000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -1646,7 +1676,7 @@
         <v>105000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -1677,7 +1707,7 @@
         <v>48000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -1709,7 +1739,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -1741,7 +1771,7 @@
         <v>21000</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -1773,7 +1803,7 @@
         <v>10000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -1796,7 +1826,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -1805,7 +1835,7 @@
         <v>2400</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -1837,7 +1867,7 @@
         <v>40000</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="38">
@@ -1869,7 +1899,7 @@
         <v>12000</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="38">
@@ -1977,7 +2007,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -2071,7 +2101,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2092,7 +2122,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2109,7 +2139,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2127,7 +2157,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H32" s="35">
         <v>468340</v>
@@ -2161,7 +2191,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" s="42">
         <f>H32+H33</f>
@@ -2182,7 +2212,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="10"/>
       <c r="G35" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H35" s="46">
         <f>H31-H34</f>
@@ -2203,7 +2233,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2223,7 +2253,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2326,7 +2356,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2335,7 +2365,7 @@
         <v>4500</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2377,7 +2407,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="28">
         <v>44840</v>
@@ -2410,7 +2440,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2537,7 +2567,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2558,7 +2588,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2575,7 +2605,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2593,7 +2623,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="35">
         <v>503685</v>
@@ -2627,7 +2657,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -2648,7 +2678,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="46">
         <f>H11-H14</f>
@@ -2669,7 +2699,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2689,7 +2719,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -2788,7 +2818,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2797,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2839,7 +2869,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B4" s="28">
         <v>44866</v>
@@ -2905,7 +2935,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="28">
         <v>44867</v>
@@ -3004,7 +3034,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3037,7 +3067,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3131,7 +3161,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3152,7 +3182,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3169,7 +3199,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3187,7 +3217,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="35">
         <v>574815</v>
@@ -3221,7 +3251,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="42">
         <f>H16+H17</f>
@@ -3242,7 +3272,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="10"/>
       <c r="G19" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" s="46">
         <f>H15-H18</f>
@@ -3263,7 +3293,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3283,7 +3313,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3391,7 +3421,7 @@
         <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3414,7 +3444,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="28">
         <v>44901</v>
@@ -3423,7 +3453,7 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -3446,7 +3476,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3455,7 +3485,7 @@
         <v>40000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -3478,7 +3508,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3487,7 +3517,7 @@
         <v>130000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -3510,7 +3540,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3519,7 +3549,7 @@
         <v>24000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -3550,7 +3580,7 @@
         <v>30000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -3582,7 +3612,7 @@
         <v>40000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -3605,7 +3635,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3614,7 +3644,7 @@
         <v>2400</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -3646,7 +3676,7 @@
         <v>20000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -3678,7 +3708,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -3753,7 +3783,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -3786,7 +3816,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B15" s="28">
         <v>44922</v>
@@ -3819,7 +3849,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B16" s="28">
         <v>44923</v>
@@ -3885,7 +3915,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="28">
         <v>44925</v>
@@ -3946,7 +3976,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -3967,7 +3997,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -3984,7 +4014,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -4002,7 +4032,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H23" s="35">
         <v>612765</v>
@@ -4036,7 +4066,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
@@ -4057,7 +4087,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H26" s="36">
         <f>H22-H25</f>
@@ -4078,7 +4108,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4098,7 +4128,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4195,7 +4225,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="28">
         <v>44566</v>
@@ -4225,7 +4255,7 @@
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="28">
         <v>44567</v>
@@ -4255,7 +4285,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="28">
         <v>44567</v>
@@ -4285,7 +4315,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="28">
         <v>44568</v>
@@ -4315,7 +4345,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="28">
         <v>44571</v>
@@ -4345,7 +4375,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="28">
         <v>44572</v>
@@ -4375,7 +4405,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="28">
         <v>44572</v>
@@ -4405,7 +4435,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="28">
         <v>44574</v>
@@ -4435,7 +4465,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="28">
         <v>44574</v>
@@ -4465,7 +4495,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="28">
         <v>44574</v>
@@ -4495,7 +4525,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="28">
         <v>44578</v>
@@ -4525,7 +4555,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="28">
         <v>44578</v>
@@ -4555,7 +4585,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="28">
         <v>44579</v>
@@ -4585,7 +4615,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="28">
         <v>44580</v>
@@ -4615,7 +4645,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="28">
         <v>44580</v>
@@ -4645,7 +4675,7 @@
     </row>
     <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="28">
         <v>44585</v>
@@ -4675,7 +4705,7 @@
     </row>
     <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="28">
         <v>44587</v>
@@ -4705,7 +4735,7 @@
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="28">
         <v>44588</v>
@@ -4735,7 +4765,7 @@
     </row>
     <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="28">
         <v>44589</v>
@@ -4765,7 +4795,7 @@
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="28">
         <v>44592</v>
@@ -4795,7 +4825,7 @@
     </row>
     <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="28">
         <v>44592</v>
@@ -4876,7 +4906,7 @@
       <c r="E26" s="32"/>
       <c r="F26" s="30"/>
       <c r="G26" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H26" s="35">
         <v>0</v>
@@ -4890,7 +4920,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="30"/>
       <c r="G27" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="35">
         <v>62710</v>
@@ -4904,7 +4934,7 @@
       <c r="E28" s="32"/>
       <c r="F28" s="30"/>
       <c r="G28" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H28" s="32">
         <f>H26+H27</f>
@@ -4919,7 +4949,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" s="46">
         <f>H25-H28</f>
@@ -4992,7 +5022,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="28">
         <v>44607</v>
@@ -5001,10 +5031,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="30">
         <v>0.1719</v>
@@ -5036,7 +5066,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -5066,7 +5096,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -5096,7 +5126,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -5126,7 +5156,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -5156,7 +5186,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -5186,7 +5216,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -5216,7 +5246,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -5246,7 +5276,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -5276,7 +5306,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -5306,7 +5336,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -5336,7 +5366,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5366,7 +5396,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5396,7 +5426,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5426,7 +5456,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5456,7 +5486,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5486,7 +5516,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5516,7 +5546,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5546,7 +5576,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5576,7 +5606,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5606,7 +5636,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5636,7 +5666,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5666,7 +5696,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5696,7 +5726,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5726,7 +5756,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -5816,7 +5846,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H31" s="35">
         <v>62710</v>
@@ -5833,7 +5863,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -5850,7 +5880,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" s="32">
         <f>H31+H32</f>
@@ -5868,7 +5898,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H34" s="36">
         <f>H30-H33</f>
@@ -5947,7 +5977,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -5956,10 +5986,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="38">
         <v>0.22220000000000001</v>
@@ -5975,7 +6005,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -5984,10 +6014,10 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" s="38">
         <v>0.26100000000000001</v>
@@ -6003,7 +6033,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -6012,10 +6042,10 @@
         <v>110000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="38">
         <v>0.25</v>
@@ -6031,7 +6061,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -6040,10 +6070,10 @@
         <v>20000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="38">
         <v>0.1195</v>
@@ -6059,7 +6089,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -6068,10 +6098,10 @@
         <v>10000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="38">
         <v>0.221</v>
@@ -6087,7 +6117,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -6096,10 +6126,10 @@
         <v>40100</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="38">
         <v>0.17380000000000001</v>
@@ -6128,7 +6158,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -6155,7 +6185,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -6182,7 +6212,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -6209,7 +6239,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6263,7 +6293,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6344,7 +6374,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6396,7 +6426,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6411,7 +6441,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6425,7 +6455,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6440,7 +6470,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H22" s="35">
         <v>89870</v>
@@ -6454,7 +6484,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6468,7 +6498,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="34">
         <f>H22+H23</f>
@@ -6483,7 +6513,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="46">
         <f>H21-H24</f>
@@ -6492,7 +6522,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6500,7 +6530,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6571,7 +6601,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6580,10 +6610,10 @@
         <v>900</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="38">
         <v>9</v>
@@ -6605,7 +6635,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6614,10 +6644,10 @@
         <v>6000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" s="38">
         <v>0.86</v>
@@ -6647,10 +6677,10 @@
         <v>9000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="38">
         <v>1.75</v>
@@ -6672,7 +6702,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="28">
         <v>44677</v>
@@ -6681,10 +6711,10 @@
         <v>900</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="38">
         <v>10</v>
@@ -6706,7 +6736,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6715,10 +6745,10 @@
         <v>9000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="38">
         <v>0.45</v>
@@ -6740,7 +6770,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B7" s="28">
         <v>44680</v>
@@ -6749,10 +6779,10 @@
         <v>9000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="38">
         <v>0.8</v>
@@ -6793,7 +6823,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" s="28">
         <v>44669</v>
@@ -6826,7 +6856,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="28">
         <v>44669</v>
@@ -6859,7 +6889,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -6892,7 +6922,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="28">
         <v>44680</v>
@@ -6925,7 +6955,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -6958,7 +6988,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="28">
         <v>44652</v>
@@ -6991,7 +7021,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" s="28">
         <v>44673</v>
@@ -7055,7 +7085,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -7076,7 +7106,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -7096,7 +7126,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -7117,7 +7147,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20" s="35">
         <v>187090</v>
@@ -7137,7 +7167,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H21" s="35">
         <v>71150</v>
@@ -7157,7 +7187,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="34">
         <f>H20+H21</f>
@@ -7178,7 +7208,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" s="46">
         <f>H19-H22</f>
@@ -7199,7 +7229,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -7219,7 +7249,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -7320,7 +7350,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7329,10 +7359,10 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="38">
         <v>0.5</v>
@@ -7353,7 +7383,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7362,10 +7392,10 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" s="38">
         <v>0.52</v>
@@ -7387,7 +7417,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7396,10 +7426,10 @@
         <v>27000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="38">
         <v>0.36</v>
@@ -7421,7 +7451,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B5" s="28">
         <v>44687</v>
@@ -7430,10 +7460,10 @@
         <v>22500</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="38">
         <v>0.65</v>
@@ -7463,10 +7493,10 @@
         <v>27000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="38">
         <v>0.7</v>
@@ -7497,7 +7527,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -7528,7 +7558,7 @@
         <v>9000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -7551,7 +7581,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7560,7 +7590,7 @@
         <v>4500</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -7592,7 +7622,7 @@
         <v>30000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -7624,7 +7654,7 @@
         <v>60000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -7656,7 +7686,7 @@
         <v>3000</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -7679,7 +7709,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7688,7 +7718,7 @@
         <v>2000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -7711,7 +7741,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7720,7 +7750,7 @@
         <v>6000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -7743,7 +7773,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7752,7 +7782,7 @@
         <v>12000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -7783,7 +7813,7 @@
         <v>18000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -7815,7 +7845,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -7847,7 +7877,7 @@
         <v>4500</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -7879,7 +7909,7 @@
         <v>90000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -7901,7 +7931,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="28">
         <v>44712</v>
@@ -7910,7 +7940,7 @@
         <v>60000</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -7985,7 +8015,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -8018,7 +8048,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -8084,7 +8114,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -8117,7 +8147,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -8150,7 +8180,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -8183,7 +8213,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8282,7 +8312,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8315,7 +8345,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8348,7 +8378,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8381,7 +8411,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8445,7 +8475,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8466,7 +8496,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8486,7 +8516,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8507,7 +8537,7 @@
       <c r="E40" s="32"/>
       <c r="F40" s="30"/>
       <c r="G40" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H40" s="35">
         <v>258240</v>
@@ -8547,7 +8577,7 @@
       <c r="E42" s="32"/>
       <c r="F42" s="30"/>
       <c r="G42" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H42" s="42">
         <f>H40+H41</f>
@@ -8568,7 +8598,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="10"/>
       <c r="G43" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H43" s="47">
         <f>H39-H42</f>
@@ -8589,7 +8619,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8609,7 +8639,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8711,7 +8741,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8720,7 +8750,7 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -8743,7 +8773,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8752,7 +8782,7 @@
         <v>110000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -8784,7 +8814,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -8807,7 +8837,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8816,7 +8846,7 @@
         <v>6000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -8848,7 +8878,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -8890,7 +8920,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -8923,7 +8953,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B9" s="28">
         <v>44725</v>
@@ -8956,7 +8986,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -9022,7 +9052,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -9088,7 +9118,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -9152,7 +9182,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -9173,7 +9203,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -9193,7 +9223,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9214,7 +9244,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H19" s="35">
         <v>314880</v>
@@ -9254,7 +9284,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="42">
         <f>H19+H20</f>
@@ -9275,7 +9305,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" s="47">
         <f>H18-H21</f>
@@ -9296,7 +9326,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -9316,7 +9346,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9423,7 +9453,7 @@
         <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9464,7 +9494,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9497,7 +9527,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9530,7 +9560,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9563,7 +9593,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9624,7 +9654,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9645,7 +9675,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9662,7 +9692,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9680,7 +9710,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="35">
         <v>387440</v>
@@ -9714,7 +9744,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -9735,7 +9765,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="47">
         <f>H11-H14</f>
@@ -9756,7 +9786,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9776,7 +9806,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -9888,7 +9918,7 @@
         <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9920,7 +9950,7 @@
         <v>900</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -9995,7 +10025,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -10056,7 +10086,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -10077,7 +10107,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -10094,7 +10124,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -10112,7 +10142,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11" s="35">
         <v>414400</v>
@@ -10146,7 +10176,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="42">
         <f>H11+H12</f>
@@ -10167,7 +10197,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="10"/>
       <c r="G14" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="48">
         <f>H10-H13</f>
@@ -10188,7 +10218,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -10208,7 +10238,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4598" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F95826F-23BD-44EA-BB22-6489128A70BC}"/>
+  <xr:revisionPtr revIDLastSave="4599" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{274B2819-4EB8-45A7-8A89-60179CA8FA02}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1156,7 +1156,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="35">
-        <v>34710</v>
+        <v>43030</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H12" s="32">
         <f>H10+H11</f>
-        <v>34710</v>
+        <v>43030</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H13" s="36">
         <f>H9-H12</f>
-        <v>-59704.059999999983</v>
+        <v>-68024.059999999983</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4599" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{274B2819-4EB8-45A7-8A89-60179CA8FA02}"/>
+  <xr:revisionPtr revIDLastSave="4607" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{551FFB7A-ED46-4FF4-A8B1-2F3CA6EBFEE0}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>STA</t>
+  </si>
+  <si>
+    <t>MAKRO</t>
   </si>
   <si>
     <t>B/F Expense</t>
@@ -267,9 +270,6 @@
   </si>
   <si>
     <t>TPIPL</t>
-  </si>
-  <si>
-    <t>MAKRO</t>
   </si>
   <si>
     <t>BCH</t>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D107DCB-A805-454D-A7EE-FBDCD33FF9C5}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
@@ -959,7 +959,7 @@
         <v>98032.38</v>
       </c>
       <c r="H2" s="32">
-        <f t="shared" ref="H2:H5" si="0">G2-E2</f>
+        <f t="shared" ref="H2:H6" si="0">G2-E2</f>
         <v>4074.7400000000052</v>
       </c>
       <c r="I2" s="15"/>
@@ -1079,44 +1079,62 @@
         <v>52882.61</v>
       </c>
       <c r="H6" s="32">
-        <f t="shared" ref="H6" si="1">G6-E6</f>
+        <f t="shared" si="0"/>
         <v>-29173.729999999996</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32">
-        <f>SUM(E2:E6)</f>
-        <v>558609.5199999999</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32">
-        <f t="shared" ref="G7:H7" si="2">SUM(G2:G6)</f>
-        <v>533615.46</v>
-      </c>
-      <c r="H7" s="34">
-        <f t="shared" si="2"/>
-        <v>-24994.059999999983</v>
-      </c>
-      <c r="K7" s="15"/>
+    <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A7" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="28">
+        <v>44950</v>
+      </c>
+      <c r="C7" s="29">
+        <v>7500</v>
+      </c>
+      <c r="D7" s="30">
+        <v>40.4</v>
+      </c>
+      <c r="E7" s="31">
+        <v>303671.11</v>
+      </c>
+      <c r="F7" s="30">
+        <v>42.5</v>
+      </c>
+      <c r="G7" s="31">
+        <v>318044</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" ref="H7" si="1">G7-E7</f>
+        <v>14372.890000000014</v>
+      </c>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
       <c r="A8" s="26"/>
       <c r="B8" s="28"/>
       <c r="C8" s="29"/>
       <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
+      <c r="E8" s="32">
+        <f>SUM(E2:E7)</f>
+        <v>862280.62999999989</v>
+      </c>
       <c r="F8" s="30"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32">
-        <v>0</v>
-      </c>
+      <c r="G8" s="32">
+        <f t="shared" ref="G8:H8" si="2">SUM(G2:G7)</f>
+        <v>851659.46</v>
+      </c>
+      <c r="H8" s="34">
+        <f t="shared" si="2"/>
+        <v>-10621.169999999969</v>
+      </c>
+      <c r="K8" s="15"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
       <c r="A9" s="26"/>
@@ -1127,8 +1145,7 @@
       <c r="F9" s="30"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32">
-        <f>SUM(H7:H8)</f>
-        <v>-24994.059999999983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
@@ -1138,11 +1155,10 @@
       <c r="D10" s="33"/>
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="35">
-        <v>0</v>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32">
+        <f>SUM(H8:H9)</f>
+        <v>-10621.169999999969</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
@@ -1156,7 +1172,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="35">
-        <v>43030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
@@ -1169,8 +1185,7 @@
       <c r="G12" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="32">
-        <f>H10+H11</f>
+      <c r="H12" s="35">
         <v>43030</v>
       </c>
     </row>
@@ -1184,9 +1199,24 @@
       <c r="G13" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="36">
-        <f>H9-H12</f>
-        <v>-68024.059999999983</v>
+      <c r="H13" s="32">
+        <f>H11+H12</f>
+        <v>43030</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1">
+      <c r="A14" s="26"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="36">
+        <f>H10-H13</f>
+        <v>-53651.169999999969</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1292,7 @@
         <v>5000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -1285,7 +1315,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1294,7 +1324,7 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -1326,7 +1356,7 @@
         <v>15000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -1358,7 +1388,7 @@
         <v>30000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -1381,7 +1411,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1390,7 +1420,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -1413,7 +1443,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="28">
         <v>44809</v>
@@ -1422,7 +1452,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -1445,7 +1475,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="28">
         <v>44810</v>
@@ -1454,7 +1484,7 @@
         <v>60000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -1477,7 +1507,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1486,7 +1516,7 @@
         <v>130000</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -1509,7 +1539,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B10" s="28">
         <v>44810</v>
@@ -1518,7 +1548,7 @@
         <v>7500</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -1541,7 +1571,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1550,7 +1580,7 @@
         <v>27000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -1582,7 +1612,7 @@
         <v>22500</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -1604,7 +1634,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" s="28">
         <v>44813</v>
@@ -1613,7 +1643,7 @@
         <v>30000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -1636,7 +1666,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="28">
         <v>44813</v>
@@ -1645,7 +1675,7 @@
         <v>15000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -1676,7 +1706,7 @@
         <v>105000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -1698,7 +1728,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" s="28">
         <v>44813</v>
@@ -1707,7 +1737,7 @@
         <v>48000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -1739,7 +1769,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -1771,7 +1801,7 @@
         <v>21000</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -1803,7 +1833,7 @@
         <v>10000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -1826,7 +1856,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -1835,7 +1865,7 @@
         <v>2400</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -1867,7 +1897,7 @@
         <v>40000</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="38">
@@ -1899,7 +1929,7 @@
         <v>12000</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="38">
@@ -1974,7 +2004,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B25" s="28">
         <v>44809</v>
@@ -2007,7 +2037,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -2101,7 +2131,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2122,7 +2152,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2139,7 +2169,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2157,7 +2187,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" s="35">
         <v>468340</v>
@@ -2191,7 +2221,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H34" s="42">
         <f>H32+H33</f>
@@ -2212,7 +2242,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="10"/>
       <c r="G35" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" s="46">
         <f>H31-H34</f>
@@ -2233,7 +2263,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2253,7 +2283,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2356,7 +2386,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2365,7 +2395,7 @@
         <v>4500</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2407,7 +2437,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="28">
         <v>44840</v>
@@ -2440,7 +2470,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2567,7 +2597,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2588,7 +2618,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2605,7 +2635,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2623,7 +2653,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="35">
         <v>503685</v>
@@ -2657,7 +2687,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -2678,7 +2708,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" s="46">
         <f>H11-H14</f>
@@ -2699,7 +2729,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2719,7 +2749,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -2818,7 +2848,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2827,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2902,7 +2932,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="28">
         <v>44866</v>
@@ -2935,7 +2965,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="28">
         <v>44867</v>
@@ -3034,7 +3064,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3067,7 +3097,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3161,7 +3191,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3182,7 +3212,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3199,7 +3229,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3217,7 +3247,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="35">
         <v>574815</v>
@@ -3251,7 +3281,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="42">
         <f>H16+H17</f>
@@ -3272,7 +3302,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="10"/>
       <c r="G19" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="46">
         <f>H15-H18</f>
@@ -3293,7 +3323,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3313,7 +3343,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3421,7 +3451,7 @@
         <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3444,7 +3474,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="28">
         <v>44901</v>
@@ -3453,7 +3483,7 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -3476,7 +3506,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3485,7 +3515,7 @@
         <v>40000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -3508,7 +3538,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3517,7 +3547,7 @@
         <v>130000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -3540,7 +3570,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3549,7 +3579,7 @@
         <v>24000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -3580,7 +3610,7 @@
         <v>30000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -3612,7 +3642,7 @@
         <v>40000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -3635,7 +3665,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3644,7 +3674,7 @@
         <v>2400</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -3676,7 +3706,7 @@
         <v>20000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -3708,7 +3738,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -3783,7 +3813,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -3882,7 +3912,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="28">
         <v>44923</v>
@@ -3915,7 +3945,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="28">
         <v>44925</v>
@@ -3976,7 +4006,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -3997,7 +4027,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -4014,7 +4044,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -4032,7 +4062,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="35">
         <v>612765</v>
@@ -4066,7 +4096,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
@@ -4087,7 +4117,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" s="36">
         <f>H22-H25</f>
@@ -4108,7 +4138,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4128,7 +4158,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4225,7 +4255,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="28">
         <v>44566</v>
@@ -4255,7 +4285,7 @@
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="28">
         <v>44567</v>
@@ -4285,7 +4315,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="28">
         <v>44567</v>
@@ -4315,7 +4345,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="28">
         <v>44568</v>
@@ -4345,7 +4375,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="28">
         <v>44571</v>
@@ -4375,7 +4405,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="28">
         <v>44572</v>
@@ -4405,7 +4435,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="28">
         <v>44572</v>
@@ -4435,7 +4465,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="28">
         <v>44574</v>
@@ -4465,7 +4495,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="28">
         <v>44574</v>
@@ -4495,7 +4525,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="28">
         <v>44574</v>
@@ -4525,7 +4555,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="28">
         <v>44578</v>
@@ -4555,7 +4585,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="28">
         <v>44578</v>
@@ -4585,7 +4615,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="28">
         <v>44579</v>
@@ -4615,7 +4645,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="28">
         <v>44580</v>
@@ -4645,7 +4675,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="28">
         <v>44580</v>
@@ -4675,7 +4705,7 @@
     </row>
     <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" s="28">
         <v>44585</v>
@@ -4705,7 +4735,7 @@
     </row>
     <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="28">
         <v>44587</v>
@@ -4735,7 +4765,7 @@
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="28">
         <v>44588</v>
@@ -4765,7 +4795,7 @@
     </row>
     <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="28">
         <v>44589</v>
@@ -4795,7 +4825,7 @@
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="28">
         <v>44592</v>
@@ -4825,7 +4855,7 @@
     </row>
     <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="28">
         <v>44592</v>
@@ -4906,7 +4936,7 @@
       <c r="E26" s="32"/>
       <c r="F26" s="30"/>
       <c r="G26" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="35">
         <v>0</v>
@@ -4920,7 +4950,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="30"/>
       <c r="G27" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" s="35">
         <v>62710</v>
@@ -4934,7 +4964,7 @@
       <c r="E28" s="32"/>
       <c r="F28" s="30"/>
       <c r="G28" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" s="32">
         <f>H26+H27</f>
@@ -4949,7 +4979,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" s="46">
         <f>H25-H28</f>
@@ -5022,7 +5052,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="28">
         <v>44607</v>
@@ -5031,10 +5061,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="30">
         <v>0.1719</v>
@@ -5066,7 +5096,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -5096,7 +5126,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -5126,7 +5156,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -5156,7 +5186,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -5186,7 +5216,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -5216,7 +5246,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -5246,7 +5276,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -5276,7 +5306,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -5306,7 +5336,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -5336,7 +5366,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -5366,7 +5396,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5396,7 +5426,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5426,7 +5456,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5456,7 +5486,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5486,7 +5516,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5516,7 +5546,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5546,7 +5576,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5576,7 +5606,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5606,7 +5636,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5636,7 +5666,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5666,7 +5696,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5696,7 +5726,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5726,7 +5756,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5756,7 +5786,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -5846,7 +5876,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" s="35">
         <v>62710</v>
@@ -5863,7 +5893,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -5880,7 +5910,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H33" s="32">
         <f>H31+H32</f>
@@ -5898,7 +5928,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" s="36">
         <f>H30-H33</f>
@@ -5977,7 +6007,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -5986,10 +6016,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="38">
         <v>0.22220000000000001</v>
@@ -6005,7 +6035,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -6014,10 +6044,10 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="38">
         <v>0.26100000000000001</v>
@@ -6033,7 +6063,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -6042,10 +6072,10 @@
         <v>110000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="38">
         <v>0.25</v>
@@ -6061,7 +6091,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -6070,10 +6100,10 @@
         <v>20000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="38">
         <v>0.1195</v>
@@ -6089,7 +6119,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -6098,10 +6128,10 @@
         <v>10000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="38">
         <v>0.221</v>
@@ -6117,7 +6147,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -6126,10 +6156,10 @@
         <v>40100</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="38">
         <v>0.17380000000000001</v>
@@ -6158,7 +6188,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -6185,7 +6215,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -6212,7 +6242,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -6239,7 +6269,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6293,7 +6323,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6374,7 +6404,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6426,7 +6456,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6441,7 +6471,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6455,7 +6485,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6470,7 +6500,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="35">
         <v>89870</v>
@@ -6484,7 +6514,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6498,7 +6528,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" s="34">
         <f>H22+H23</f>
@@ -6513,7 +6543,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" s="46">
         <f>H21-H24</f>
@@ -6522,7 +6552,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6530,7 +6560,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6601,7 +6631,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6610,10 +6640,10 @@
         <v>900</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="38">
         <v>9</v>
@@ -6635,7 +6665,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6644,10 +6674,10 @@
         <v>6000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="38">
         <v>0.86</v>
@@ -6677,10 +6707,10 @@
         <v>9000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="38">
         <v>1.75</v>
@@ -6702,7 +6732,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="28">
         <v>44677</v>
@@ -6711,10 +6741,10 @@
         <v>900</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="38">
         <v>10</v>
@@ -6736,7 +6766,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6745,10 +6775,10 @@
         <v>9000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="38">
         <v>0.45</v>
@@ -6770,7 +6800,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" s="28">
         <v>44680</v>
@@ -6779,10 +6809,10 @@
         <v>9000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="38">
         <v>0.8</v>
@@ -6823,7 +6853,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="28">
         <v>44669</v>
@@ -6856,7 +6886,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" s="28">
         <v>44669</v>
@@ -6889,7 +6919,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -6922,7 +6952,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" s="28">
         <v>44680</v>
@@ -6955,7 +6985,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -6988,7 +7018,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="28">
         <v>44652</v>
@@ -7021,7 +7051,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="28">
         <v>44673</v>
@@ -7085,7 +7115,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -7106,7 +7136,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -7126,7 +7156,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -7147,7 +7177,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="35">
         <v>187090</v>
@@ -7167,7 +7197,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H21" s="35">
         <v>71150</v>
@@ -7187,7 +7217,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" s="34">
         <f>H20+H21</f>
@@ -7208,7 +7238,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="46">
         <f>H19-H22</f>
@@ -7229,7 +7259,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -7249,7 +7279,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -7350,7 +7380,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7359,10 +7389,10 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="38">
         <v>0.5</v>
@@ -7383,7 +7413,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7392,10 +7422,10 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="38">
         <v>0.52</v>
@@ -7417,7 +7447,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7426,10 +7456,10 @@
         <v>27000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="38">
         <v>0.36</v>
@@ -7460,10 +7490,10 @@
         <v>22500</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="38">
         <v>0.65</v>
@@ -7484,7 +7514,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B6" s="28">
         <v>44687</v>
@@ -7493,10 +7523,10 @@
         <v>27000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="38">
         <v>0.7</v>
@@ -7518,7 +7548,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="28">
         <v>44690</v>
@@ -7527,7 +7557,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -7549,7 +7579,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" s="28">
         <v>44693</v>
@@ -7558,7 +7588,7 @@
         <v>9000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -7581,7 +7611,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7590,7 +7620,7 @@
         <v>4500</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -7613,7 +7643,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" s="28">
         <v>44698</v>
@@ -7622,7 +7652,7 @@
         <v>30000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -7645,7 +7675,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B11" s="28">
         <v>44698</v>
@@ -7654,7 +7684,7 @@
         <v>60000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -7677,7 +7707,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B12" s="28">
         <v>44700</v>
@@ -7686,7 +7716,7 @@
         <v>3000</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -7709,7 +7739,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7718,7 +7748,7 @@
         <v>2000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -7741,7 +7771,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7750,7 +7780,7 @@
         <v>6000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -7773,7 +7803,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7782,7 +7812,7 @@
         <v>12000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -7813,7 +7843,7 @@
         <v>18000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -7845,7 +7875,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -7877,7 +7907,7 @@
         <v>4500</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -7909,7 +7939,7 @@
         <v>90000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -7931,7 +7961,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="28">
         <v>44712</v>
@@ -7940,7 +7970,7 @@
         <v>60000</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -7982,7 +8012,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="28">
         <v>44684</v>
@@ -8015,7 +8045,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -8048,7 +8078,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -8081,7 +8111,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A25" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" s="28">
         <v>44692</v>
@@ -8114,7 +8144,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -8147,7 +8177,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -8180,7 +8210,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -8213,7 +8243,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8312,7 +8342,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8345,7 +8375,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8378,7 +8408,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8411,7 +8441,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8475,7 +8505,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8496,7 +8526,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8516,7 +8546,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8537,7 +8567,7 @@
       <c r="E40" s="32"/>
       <c r="F40" s="30"/>
       <c r="G40" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H40" s="35">
         <v>258240</v>
@@ -8577,7 +8607,7 @@
       <c r="E42" s="32"/>
       <c r="F42" s="30"/>
       <c r="G42" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H42" s="42">
         <f>H40+H41</f>
@@ -8598,7 +8628,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="10"/>
       <c r="G43" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H43" s="47">
         <f>H39-H42</f>
@@ -8619,7 +8649,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8639,7 +8669,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8741,7 +8771,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8750,7 +8780,7 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -8773,7 +8803,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8782,7 +8812,7 @@
         <v>110000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -8814,7 +8844,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -8837,7 +8867,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8846,7 +8876,7 @@
         <v>6000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -8878,7 +8908,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -8920,7 +8950,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -8986,7 +9016,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -9052,7 +9082,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -9118,7 +9148,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -9182,7 +9212,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -9203,7 +9233,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -9223,7 +9253,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9244,7 +9274,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="35">
         <v>314880</v>
@@ -9284,7 +9314,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H21" s="42">
         <f>H19+H20</f>
@@ -9305,7 +9335,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" s="47">
         <f>H18-H21</f>
@@ -9326,7 +9356,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -9346,7 +9376,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9453,7 +9483,7 @@
         <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9494,7 +9524,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9527,7 +9557,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9560,7 +9590,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9593,7 +9623,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9654,7 +9684,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9675,7 +9705,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9692,7 +9722,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9710,7 +9740,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="35">
         <v>387440</v>
@@ -9744,7 +9774,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -9765,7 +9795,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" s="47">
         <f>H11-H14</f>
@@ -9786,7 +9816,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9806,7 +9836,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -9918,7 +9948,7 @@
         <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9950,7 +9980,7 @@
         <v>900</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -10025,7 +10055,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -10086,7 +10116,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -10107,7 +10137,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -10124,7 +10154,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -10142,7 +10172,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="35">
         <v>414400</v>
@@ -10176,7 +10206,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="42">
         <f>H11+H12</f>
@@ -10197,7 +10227,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="10"/>
       <c r="G14" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="48">
         <f>H10-H13</f>
@@ -10218,7 +10248,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -10238,7 +10268,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4607" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{551FFB7A-ED46-4FF4-A8B1-2F3CA6EBFEE0}"/>
+  <xr:revisionPtr revIDLastSave="4618" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7730FAE8-7B04-4819-BBBD-9920317896BD}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D107DCB-A805-454D-A7EE-FBDCD33FF9C5}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
@@ -959,7 +959,7 @@
         <v>98032.38</v>
       </c>
       <c r="H2" s="32">
-        <f t="shared" ref="H2:H6" si="0">G2-E2</f>
+        <f t="shared" ref="H2:H7" si="0">G2-E2</f>
         <v>4074.7400000000052</v>
       </c>
       <c r="I2" s="15"/>
@@ -1088,78 +1088,113 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="28">
-        <v>44950</v>
+        <v>44951</v>
       </c>
       <c r="C7" s="29">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="D7" s="30">
-        <v>40.4</v>
+        <v>33.25</v>
       </c>
       <c r="E7" s="31">
-        <v>303671.11</v>
+        <v>83309.11</v>
       </c>
       <c r="F7" s="30">
-        <v>42.5</v>
+        <v>21.4</v>
       </c>
       <c r="G7" s="31">
-        <v>318044</v>
+        <v>53381.5</v>
       </c>
       <c r="H7" s="32">
-        <f t="shared" ref="H7" si="1">G7-E7</f>
-        <v>14372.890000000014</v>
+        <f t="shared" si="0"/>
+        <v>-29927.61</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32">
-        <f>SUM(E2:E7)</f>
-        <v>862280.62999999989</v>
-      </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32">
-        <f t="shared" ref="G8:H8" si="2">SUM(G2:G7)</f>
-        <v>851659.46</v>
-      </c>
-      <c r="H8" s="34">
-        <f t="shared" si="2"/>
-        <v>-10621.169999999969</v>
-      </c>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32"/>
+    <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="28">
+        <v>44951</v>
+      </c>
+      <c r="C8" s="29">
+        <v>2500</v>
+      </c>
+      <c r="D8" s="30">
+        <v>35.25</v>
+      </c>
+      <c r="E8" s="31">
+        <v>88320.19</v>
+      </c>
+      <c r="F8" s="30">
+        <v>21.9</v>
+      </c>
+      <c r="G8" s="31">
+        <v>54628.74</v>
+      </c>
+      <c r="H8" s="32">
+        <f t="shared" ref="H8" si="1">G8-E8</f>
+        <v>-33691.450000000004</v>
+      </c>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="28">
+        <v>44950</v>
+      </c>
+      <c r="C9" s="29">
+        <v>7500</v>
+      </c>
+      <c r="D9" s="30">
+        <v>40.4</v>
+      </c>
+      <c r="E9" s="31">
+        <v>303671.11</v>
+      </c>
+      <c r="F9" s="30">
+        <v>42.5</v>
+      </c>
+      <c r="G9" s="31">
+        <v>318044</v>
+      </c>
       <c r="H9" s="32">
-        <v>0</v>
-      </c>
+        <f t="shared" ref="H9" si="2">G9-E9</f>
+        <v>14372.890000000014</v>
+      </c>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="26"/>
       <c r="B10" s="28"/>
       <c r="C10" s="29"/>
       <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
+      <c r="E10" s="32">
+        <f>SUM(E2:E9)</f>
+        <v>1033909.9299999998</v>
+      </c>
       <c r="F10" s="30"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32">
-        <f>SUM(H8:H9)</f>
-        <v>-10621.169999999969</v>
-      </c>
+      <c r="G10" s="32">
+        <f t="shared" ref="G10:H10" si="3">SUM(G2:G9)</f>
+        <v>959669.7</v>
+      </c>
+      <c r="H10" s="34">
+        <f t="shared" si="3"/>
+        <v>-74240.229999999981</v>
+      </c>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
       <c r="A11" s="26"/>
@@ -1168,10 +1203,8 @@
       <c r="D11" s="33"/>
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="35">
+      <c r="G11" s="32"/>
+      <c r="H11" s="32">
         <v>0</v>
       </c>
     </row>
@@ -1182,11 +1215,10 @@
       <c r="D12" s="33"/>
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
-      <c r="G12" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="35">
-        <v>43030</v>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32">
+        <f>SUM(H10:H11)</f>
+        <v>-74240.229999999981</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
@@ -1197,11 +1229,10 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="32">
-        <f>H11+H12</f>
-        <v>43030</v>
+        <v>14</v>
+      </c>
+      <c r="H13" s="35">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
@@ -1212,11 +1243,40 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="35">
+        <v>43030</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="32">
+        <f>H13+H14</f>
+        <v>43030</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="36">
-        <f>H10-H13</f>
-        <v>-53651.169999999969</v>
+      <c r="H16" s="36">
+        <f>H12-H15</f>
+        <v>-117270.22999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4618" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7730FAE8-7B04-4819-BBBD-9920317896BD}"/>
+  <xr:revisionPtr revIDLastSave="4626" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04206C2-BF6B-46D3-A178-EE049CFE7BEA}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>MAKRO</t>
+  </si>
+  <si>
+    <t>WHAIR</t>
   </si>
   <si>
     <t>B/F Expense</t>
@@ -291,9 +294,6 @@
   </si>
   <si>
     <t>WHART</t>
-  </si>
-  <si>
-    <t>WHAIR</t>
   </si>
   <si>
     <t>BDMS</t>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D107DCB-A805-454D-A7EE-FBDCD33FF9C5}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
@@ -1139,7 +1139,7 @@
         <v>54628.74</v>
       </c>
       <c r="H8" s="32">
-        <f t="shared" ref="H8" si="1">G8-E8</f>
+        <f t="shared" ref="H8:H9" si="1">G8-E8</f>
         <v>-33691.450000000004</v>
       </c>
       <c r="I8" s="15"/>
@@ -1169,44 +1169,62 @@
         <v>318044</v>
       </c>
       <c r="H9" s="32">
-        <f t="shared" ref="H9" si="2">G9-E9</f>
+        <f t="shared" si="1"/>
         <v>14372.890000000014</v>
       </c>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32">
-        <f>SUM(E2:E9)</f>
-        <v>1033909.9299999998</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32">
-        <f t="shared" ref="G10:H10" si="3">SUM(G2:G9)</f>
-        <v>959669.7</v>
-      </c>
-      <c r="H10" s="34">
-        <f t="shared" si="3"/>
-        <v>-74240.229999999981</v>
-      </c>
-      <c r="K10" s="15"/>
+    <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="28">
+        <v>44956</v>
+      </c>
+      <c r="C10" s="29">
+        <v>10000</v>
+      </c>
+      <c r="D10" s="30">
+        <v>7.7</v>
+      </c>
+      <c r="E10" s="31">
+        <v>77170.55</v>
+      </c>
+      <c r="F10" s="30">
+        <v>7.8</v>
+      </c>
+      <c r="G10" s="31">
+        <v>77827.240000000005</v>
+      </c>
+      <c r="H10" s="32">
+        <f t="shared" ref="H10" si="2">G10-E10</f>
+        <v>656.69000000000233</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
       <c r="A11" s="26"/>
       <c r="B11" s="28"/>
       <c r="C11" s="29"/>
       <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
+      <c r="E11" s="32">
+        <f>SUM(E2:E10)</f>
+        <v>1111080.4799999997</v>
+      </c>
       <c r="F11" s="30"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32">
-        <v>0</v>
-      </c>
+      <c r="G11" s="32">
+        <f t="shared" ref="G11:H11" si="3">SUM(G2:G10)</f>
+        <v>1037496.94</v>
+      </c>
+      <c r="H11" s="34">
+        <f t="shared" si="3"/>
+        <v>-73583.539999999979</v>
+      </c>
+      <c r="K11" s="15"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
       <c r="A12" s="26"/>
@@ -1217,8 +1235,7 @@
       <c r="F12" s="30"/>
       <c r="G12" s="32"/>
       <c r="H12" s="32">
-        <f>SUM(H10:H11)</f>
-        <v>-74240.229999999981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
@@ -1228,11 +1245,10 @@
       <c r="D13" s="33"/>
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
-      <c r="G13" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="35">
-        <v>0</v>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32">
+        <f>SUM(H11:H12)</f>
+        <v>-73583.539999999979</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
@@ -1246,7 +1262,7 @@
         <v>15</v>
       </c>
       <c r="H14" s="35">
-        <v>43030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
@@ -1259,8 +1275,7 @@
       <c r="G15" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="32">
-        <f>H13+H14</f>
+      <c r="H15" s="35">
         <v>43030</v>
       </c>
     </row>
@@ -1274,9 +1289,24 @@
       <c r="G16" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="36">
-        <f>H12-H15</f>
-        <v>-117270.22999999998</v>
+      <c r="H16" s="32">
+        <f>H14+H15</f>
+        <v>43030</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="36">
+        <f>H13-H16</f>
+        <v>-116613.53999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1382,7 @@
         <v>5000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -1375,7 +1405,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1384,7 +1414,7 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -1416,7 +1446,7 @@
         <v>15000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -1439,7 +1469,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="28">
         <v>44806</v>
@@ -1448,7 +1478,7 @@
         <v>30000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -1471,7 +1501,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1480,7 +1510,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -1503,7 +1533,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="28">
         <v>44809</v>
@@ -1512,7 +1542,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -1535,7 +1565,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="28">
         <v>44810</v>
@@ -1544,7 +1574,7 @@
         <v>60000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -1567,7 +1597,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1576,7 +1606,7 @@
         <v>130000</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -1608,7 +1638,7 @@
         <v>7500</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -1631,7 +1661,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1640,7 +1670,7 @@
         <v>27000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -1672,7 +1702,7 @@
         <v>22500</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -1694,7 +1724,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" s="28">
         <v>44813</v>
@@ -1703,7 +1733,7 @@
         <v>30000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -1726,7 +1756,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B14" s="28">
         <v>44813</v>
@@ -1735,7 +1765,7 @@
         <v>15000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -1757,7 +1787,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B15" s="28">
         <v>44813</v>
@@ -1766,7 +1796,7 @@
         <v>105000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -1788,7 +1818,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="28">
         <v>44813</v>
@@ -1797,7 +1827,7 @@
         <v>48000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -1820,7 +1850,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="28">
         <v>44817</v>
@@ -1829,7 +1859,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -1852,7 +1882,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="28">
         <v>44818</v>
@@ -1861,7 +1891,7 @@
         <v>21000</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -1893,7 +1923,7 @@
         <v>10000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -1916,7 +1946,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -1925,7 +1955,7 @@
         <v>2400</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -1948,7 +1978,7 @@
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A21" s="27" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="B21" s="28">
         <v>44823</v>
@@ -1957,7 +1987,7 @@
         <v>40000</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="38">
@@ -1989,7 +2019,7 @@
         <v>12000</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="38">
@@ -2031,7 +2061,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" s="28">
         <v>44805</v>
@@ -2064,7 +2094,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" s="28">
         <v>44809</v>
@@ -2097,7 +2127,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -2191,7 +2221,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2212,7 +2242,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2229,7 +2259,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2247,7 +2277,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" s="35">
         <v>468340</v>
@@ -2281,7 +2311,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" s="42">
         <f>H32+H33</f>
@@ -2302,7 +2332,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="10"/>
       <c r="G35" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H35" s="46">
         <f>H31-H34</f>
@@ -2323,7 +2353,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2343,7 +2373,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2446,7 +2476,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2455,7 +2485,7 @@
         <v>4500</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2497,7 +2527,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="28">
         <v>44840</v>
@@ -2530,7 +2560,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2563,7 +2593,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="28">
         <v>44860</v>
@@ -2657,7 +2687,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2678,7 +2708,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2695,7 +2725,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2713,7 +2743,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="35">
         <v>503685</v>
@@ -2747,7 +2777,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -2768,7 +2798,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" s="46">
         <f>H11-H14</f>
@@ -2789,7 +2819,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2809,7 +2839,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -2908,7 +2938,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2917,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2992,7 +3022,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="28">
         <v>44866</v>
@@ -3025,7 +3055,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="28">
         <v>44867</v>
@@ -3124,7 +3154,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3157,7 +3187,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3251,7 +3281,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3272,7 +3302,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3289,7 +3319,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3307,7 +3337,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="35">
         <v>574815</v>
@@ -3341,7 +3371,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="42">
         <f>H16+H17</f>
@@ -3362,7 +3392,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="10"/>
       <c r="G19" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" s="46">
         <f>H15-H18</f>
@@ -3383,7 +3413,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3403,7 +3433,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3511,7 +3541,7 @@
         <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3534,7 +3564,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="28">
         <v>44901</v>
@@ -3543,7 +3573,7 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -3566,7 +3596,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3575,7 +3605,7 @@
         <v>40000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -3598,7 +3628,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3607,7 +3637,7 @@
         <v>130000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -3630,7 +3660,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3639,7 +3669,7 @@
         <v>24000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -3661,7 +3691,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" s="28">
         <v>44908</v>
@@ -3670,7 +3700,7 @@
         <v>30000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -3693,7 +3723,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="B8" s="28">
         <v>44910</v>
@@ -3702,7 +3732,7 @@
         <v>40000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -3725,7 +3755,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3734,7 +3764,7 @@
         <v>2400</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -3766,7 +3796,7 @@
         <v>20000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -3798,7 +3828,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -3873,7 +3903,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -3972,7 +4002,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="28">
         <v>44923</v>
@@ -4005,7 +4035,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="28">
         <v>44925</v>
@@ -4066,7 +4096,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -4087,7 +4117,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -4104,7 +4134,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -4122,7 +4152,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="35">
         <v>612765</v>
@@ -4156,7 +4186,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
@@ -4177,7 +4207,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" s="36">
         <f>H22-H25</f>
@@ -4198,7 +4228,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4218,7 +4248,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4315,7 +4345,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="28">
         <v>44566</v>
@@ -4345,7 +4375,7 @@
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="28">
         <v>44567</v>
@@ -4375,7 +4405,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="28">
         <v>44567</v>
@@ -4405,7 +4435,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="28">
         <v>44568</v>
@@ -4435,7 +4465,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="28">
         <v>44571</v>
@@ -4465,7 +4495,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="28">
         <v>44572</v>
@@ -4495,7 +4525,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="28">
         <v>44572</v>
@@ -4525,7 +4555,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="28">
         <v>44574</v>
@@ -4555,7 +4585,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="28">
         <v>44574</v>
@@ -4585,7 +4615,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="28">
         <v>44574</v>
@@ -4615,7 +4645,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="28">
         <v>44578</v>
@@ -4645,7 +4675,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="28">
         <v>44578</v>
@@ -4675,7 +4705,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="28">
         <v>44579</v>
@@ -4705,7 +4735,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="28">
         <v>44580</v>
@@ -4735,7 +4765,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="28">
         <v>44580</v>
@@ -4765,7 +4795,7 @@
     </row>
     <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="28">
         <v>44585</v>
@@ -4795,7 +4825,7 @@
     </row>
     <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="28">
         <v>44587</v>
@@ -4825,7 +4855,7 @@
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="28">
         <v>44588</v>
@@ -4855,7 +4885,7 @@
     </row>
     <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" s="28">
         <v>44589</v>
@@ -4885,7 +4915,7 @@
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="28">
         <v>44592</v>
@@ -4915,7 +4945,7 @@
     </row>
     <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="28">
         <v>44592</v>
@@ -4996,7 +5026,7 @@
       <c r="E26" s="32"/>
       <c r="F26" s="30"/>
       <c r="G26" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="35">
         <v>0</v>
@@ -5010,7 +5040,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="30"/>
       <c r="G27" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" s="35">
         <v>62710</v>
@@ -5024,7 +5054,7 @@
       <c r="E28" s="32"/>
       <c r="F28" s="30"/>
       <c r="G28" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" s="32">
         <f>H26+H27</f>
@@ -5039,7 +5069,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H29" s="46">
         <f>H25-H28</f>
@@ -5112,7 +5142,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="28">
         <v>44607</v>
@@ -5121,10 +5151,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="30">
         <v>0.1719</v>
@@ -5156,7 +5186,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -5186,7 +5216,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -5216,7 +5246,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -5246,7 +5276,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -5276,7 +5306,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -5306,7 +5336,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -5336,7 +5366,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -5366,7 +5396,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -5396,7 +5426,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -5426,7 +5456,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -5456,7 +5486,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5486,7 +5516,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5516,7 +5546,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5546,7 +5576,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5576,7 +5606,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5606,7 +5636,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5636,7 +5666,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5666,7 +5696,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5696,7 +5726,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5726,7 +5756,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5756,7 +5786,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5786,7 +5816,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5816,7 +5846,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5846,7 +5876,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -5936,7 +5966,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="35">
         <v>62710</v>
@@ -5953,7 +5983,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -5970,7 +6000,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" s="32">
         <f>H31+H32</f>
@@ -5988,7 +6018,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H34" s="36">
         <f>H30-H33</f>
@@ -6067,7 +6097,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -6076,10 +6106,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="38">
         <v>0.22220000000000001</v>
@@ -6095,7 +6125,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -6104,10 +6134,10 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="38">
         <v>0.26100000000000001</v>
@@ -6123,7 +6153,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -6132,10 +6162,10 @@
         <v>110000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="38">
         <v>0.25</v>
@@ -6151,7 +6181,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -6160,10 +6190,10 @@
         <v>20000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="38">
         <v>0.1195</v>
@@ -6179,7 +6209,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -6188,10 +6218,10 @@
         <v>10000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="38">
         <v>0.221</v>
@@ -6207,7 +6237,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -6216,10 +6246,10 @@
         <v>40100</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="38">
         <v>0.17380000000000001</v>
@@ -6248,7 +6278,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -6275,7 +6305,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -6302,7 +6332,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -6329,7 +6359,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6383,7 +6413,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6464,7 +6494,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6516,7 +6546,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6531,7 +6561,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6545,7 +6575,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6560,7 +6590,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="35">
         <v>89870</v>
@@ -6574,7 +6604,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6588,7 +6618,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" s="34">
         <f>H22+H23</f>
@@ -6603,7 +6633,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" s="46">
         <f>H21-H24</f>
@@ -6612,7 +6642,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6620,7 +6650,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6691,7 +6721,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6700,10 +6730,10 @@
         <v>900</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="38">
         <v>9</v>
@@ -6725,7 +6755,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6734,10 +6764,10 @@
         <v>6000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="38">
         <v>0.86</v>
@@ -6767,10 +6797,10 @@
         <v>9000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="38">
         <v>1.75</v>
@@ -6792,7 +6822,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="28">
         <v>44677</v>
@@ -6801,10 +6831,10 @@
         <v>900</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="38">
         <v>10</v>
@@ -6826,7 +6856,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6835,10 +6865,10 @@
         <v>9000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="38">
         <v>0.45</v>
@@ -6860,7 +6890,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" s="28">
         <v>44680</v>
@@ -6869,10 +6899,10 @@
         <v>9000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="38">
         <v>0.8</v>
@@ -6913,7 +6943,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="28">
         <v>44669</v>
@@ -6946,7 +6976,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="28">
         <v>44669</v>
@@ -6979,7 +7009,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -7012,7 +7042,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" s="28">
         <v>44680</v>
@@ -7045,7 +7075,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -7078,7 +7108,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" s="28">
         <v>44652</v>
@@ -7111,7 +7141,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="28">
         <v>44673</v>
@@ -7175,7 +7205,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -7196,7 +7226,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -7216,7 +7246,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -7237,7 +7267,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="35">
         <v>187090</v>
@@ -7257,7 +7287,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H21" s="35">
         <v>71150</v>
@@ -7277,7 +7307,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" s="34">
         <f>H20+H21</f>
@@ -7298,7 +7328,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" s="46">
         <f>H19-H22</f>
@@ -7319,7 +7349,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -7339,7 +7369,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -7440,7 +7470,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7449,10 +7479,10 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="38">
         <v>0.5</v>
@@ -7473,7 +7503,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7482,10 +7512,10 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="38">
         <v>0.52</v>
@@ -7507,7 +7537,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7516,10 +7546,10 @@
         <v>27000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="38">
         <v>0.36</v>
@@ -7550,10 +7580,10 @@
         <v>22500</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="38">
         <v>0.65</v>
@@ -7574,7 +7604,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="28">
         <v>44687</v>
@@ -7583,10 +7613,10 @@
         <v>27000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="38">
         <v>0.7</v>
@@ -7608,7 +7638,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="28">
         <v>44690</v>
@@ -7617,7 +7647,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -7639,7 +7669,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="28">
         <v>44693</v>
@@ -7648,7 +7678,7 @@
         <v>9000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -7671,7 +7701,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7680,7 +7710,7 @@
         <v>4500</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -7703,7 +7733,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B10" s="28">
         <v>44698</v>
@@ -7712,7 +7742,7 @@
         <v>30000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -7735,7 +7765,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="28">
         <v>44698</v>
@@ -7744,7 +7774,7 @@
         <v>60000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -7776,7 +7806,7 @@
         <v>3000</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -7799,7 +7829,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7808,7 +7838,7 @@
         <v>2000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -7831,7 +7861,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7840,7 +7870,7 @@
         <v>6000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -7863,7 +7893,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7872,7 +7902,7 @@
         <v>12000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -7894,7 +7924,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B16" s="28">
         <v>44705</v>
@@ -7903,7 +7933,7 @@
         <v>18000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -7926,7 +7956,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="28">
         <v>44705</v>
@@ -7935,7 +7965,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -7958,7 +7988,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="28">
         <v>44705</v>
@@ -7967,7 +7997,7 @@
         <v>4500</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -7990,7 +8020,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="28">
         <v>44706</v>
@@ -7999,7 +8029,7 @@
         <v>90000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -8021,7 +8051,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="28">
         <v>44712</v>
@@ -8030,7 +8060,7 @@
         <v>60000</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -8072,7 +8102,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="28">
         <v>44684</v>
@@ -8105,7 +8135,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -8138,7 +8168,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -8171,7 +8201,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A25" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="28">
         <v>44692</v>
@@ -8204,7 +8234,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -8237,7 +8267,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -8270,7 +8300,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -8303,7 +8333,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8336,7 +8366,7 @@
     </row>
     <row r="30" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A30" s="27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" s="28">
         <v>44704</v>
@@ -8369,7 +8399,7 @@
     </row>
     <row r="31" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A31" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B31" s="28">
         <v>44704</v>
@@ -8402,7 +8432,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8435,7 +8465,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8468,7 +8498,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8501,7 +8531,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8565,7 +8595,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8586,7 +8616,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8606,7 +8636,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8627,7 +8657,7 @@
       <c r="E40" s="32"/>
       <c r="F40" s="30"/>
       <c r="G40" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" s="35">
         <v>258240</v>
@@ -8647,7 +8677,7 @@
       <c r="E41" s="32"/>
       <c r="F41" s="30"/>
       <c r="G41" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" s="35">
         <v>56640</v>
@@ -8667,7 +8697,7 @@
       <c r="E42" s="32"/>
       <c r="F42" s="30"/>
       <c r="G42" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" s="42">
         <f>H40+H41</f>
@@ -8688,7 +8718,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="10"/>
       <c r="G43" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H43" s="47">
         <f>H39-H42</f>
@@ -8709,7 +8739,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8729,7 +8759,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8831,7 +8861,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8840,7 +8870,7 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -8863,7 +8893,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8872,7 +8902,7 @@
         <v>110000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -8895,7 +8925,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" s="28">
         <v>44727</v>
@@ -8904,7 +8934,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -8927,7 +8957,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8936,7 +8966,7 @@
         <v>6000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -8959,7 +8989,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="B6" s="28">
         <v>44736</v>
@@ -8968,7 +8998,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -9010,7 +9040,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -9076,7 +9106,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -9142,7 +9172,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -9208,7 +9238,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -9272,7 +9302,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -9293,7 +9323,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -9313,7 +9343,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9334,7 +9364,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="35">
         <v>314880</v>
@@ -9374,7 +9404,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" s="42">
         <f>H19+H20</f>
@@ -9395,7 +9425,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H22" s="47">
         <f>H18-H21</f>
@@ -9416,7 +9446,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -9436,7 +9466,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9534,7 +9564,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="B2" s="28">
         <v>44736</v>
@@ -9543,7 +9573,7 @@
         <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9584,7 +9614,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9617,7 +9647,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9650,7 +9680,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9683,7 +9713,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9744,7 +9774,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9765,7 +9795,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9782,7 +9812,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9800,7 +9830,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="35">
         <v>387440</v>
@@ -9834,7 +9864,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -9855,7 +9885,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" s="47">
         <f>H11-H14</f>
@@ -9876,7 +9906,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9896,7 +9926,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -10008,7 +10038,7 @@
         <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -10040,7 +10070,7 @@
         <v>900</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -10115,7 +10145,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -10176,7 +10206,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -10197,7 +10227,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -10214,7 +10244,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -10232,7 +10262,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="35">
         <v>414400</v>
@@ -10266,7 +10296,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" s="42">
         <f>H11+H12</f>
@@ -10287,7 +10317,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="10"/>
       <c r="G14" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" s="48">
         <f>H10-H13</f>
@@ -10308,7 +10338,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -10328,7 +10358,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4626" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04206C2-BF6B-46D3-A178-EE049CFE7BEA}"/>
+  <xr:revisionPtr revIDLastSave="4635" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832B9285-E520-4337-9B73-39F34D2D379F}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>WHAIR</t>
+  </si>
+  <si>
+    <t>KCE</t>
   </si>
   <si>
     <t>B/F Expense</t>
@@ -261,9 +264,6 @@
   </si>
   <si>
     <t>TMT</t>
-  </si>
-  <si>
-    <t>KCE</t>
   </si>
   <si>
     <t>SPALI</t>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D107DCB-A805-454D-A7EE-FBDCD33FF9C5}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
@@ -1139,7 +1139,7 @@
         <v>54628.74</v>
       </c>
       <c r="H8" s="32">
-        <f t="shared" ref="H8:H9" si="1">G8-E8</f>
+        <f t="shared" ref="H8:H10" si="1">G8-E8</f>
         <v>-33691.450000000004</v>
       </c>
       <c r="I8" s="15"/>
@@ -1199,44 +1199,62 @@
         <v>77827.240000000005</v>
       </c>
       <c r="H10" s="32">
-        <f t="shared" ref="H10" si="2">G10-E10</f>
+        <f t="shared" si="1"/>
         <v>656.69000000000233</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32">
-        <f>SUM(E2:E10)</f>
-        <v>1111080.4799999997</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32">
-        <f t="shared" ref="G11:H11" si="3">SUM(G2:G10)</f>
-        <v>1037496.94</v>
-      </c>
-      <c r="H11" s="34">
-        <f t="shared" si="3"/>
-        <v>-73583.539999999979</v>
-      </c>
-      <c r="K11" s="15"/>
+    <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="28">
+        <v>44957</v>
+      </c>
+      <c r="C11" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="30">
+        <v>61.25</v>
+      </c>
+      <c r="E11" s="31">
+        <v>61385.67</v>
+      </c>
+      <c r="F11" s="30">
+        <v>53.75</v>
+      </c>
+      <c r="G11" s="31">
+        <v>53630.95</v>
+      </c>
+      <c r="H11" s="32">
+        <f t="shared" ref="H11" si="2">G11-E11</f>
+        <v>-7754.7200000000012</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
       <c r="A12" s="26"/>
       <c r="B12" s="28"/>
       <c r="C12" s="29"/>
       <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
+      <c r="E12" s="32">
+        <f>SUM(E2:E11)</f>
+        <v>1172466.1499999997</v>
+      </c>
       <c r="F12" s="30"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32">
-        <v>0</v>
-      </c>
+      <c r="G12" s="32">
+        <f t="shared" ref="G12:H12" si="3">SUM(G2:G11)</f>
+        <v>1091127.8899999999</v>
+      </c>
+      <c r="H12" s="34">
+        <f t="shared" si="3"/>
+        <v>-81338.25999999998</v>
+      </c>
+      <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="26"/>
@@ -1247,8 +1265,7 @@
       <c r="F13" s="30"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32">
-        <f>SUM(H11:H12)</f>
-        <v>-73583.539999999979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
@@ -1258,11 +1275,10 @@
       <c r="D14" s="33"/>
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
-      <c r="G14" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="35">
-        <v>0</v>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32">
+        <f>SUM(H12:H13)</f>
+        <v>-81338.25999999998</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
@@ -1276,7 +1292,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="35">
-        <v>43030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1">
@@ -1289,9 +1305,8 @@
       <c r="G16" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="32">
-        <f>H14+H15</f>
-        <v>43030</v>
+      <c r="H16" s="35">
+        <v>76110</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
@@ -1304,9 +1319,24 @@
       <c r="G17" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="36">
-        <f>H13-H16</f>
-        <v>-116613.53999999998</v>
+      <c r="H17" s="32">
+        <f>H15+H16</f>
+        <v>76110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="36">
+        <f>H14-H17</f>
+        <v>-157448.25999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1382,7 +1412,7 @@
         <v>5000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -1405,7 +1435,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1414,7 +1444,7 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -1446,7 +1476,7 @@
         <v>15000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -1478,7 +1508,7 @@
         <v>30000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -1501,7 +1531,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1510,7 +1540,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -1533,7 +1563,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="28">
         <v>44809</v>
@@ -1542,7 +1572,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -1565,7 +1595,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="28">
         <v>44810</v>
@@ -1574,7 +1604,7 @@
         <v>60000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -1597,7 +1627,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1606,7 +1636,7 @@
         <v>130000</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -1638,7 +1668,7 @@
         <v>7500</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -1661,7 +1691,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1670,7 +1700,7 @@
         <v>27000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -1702,7 +1732,7 @@
         <v>22500</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -1733,7 +1763,7 @@
         <v>30000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -1756,7 +1786,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="B14" s="28">
         <v>44813</v>
@@ -1765,7 +1795,7 @@
         <v>15000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -1796,7 +1826,7 @@
         <v>105000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -1818,7 +1848,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="28">
         <v>44813</v>
@@ -1827,7 +1857,7 @@
         <v>48000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -1859,7 +1889,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -1891,7 +1921,7 @@
         <v>21000</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -1923,7 +1953,7 @@
         <v>10000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -1946,7 +1976,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -1955,7 +1985,7 @@
         <v>2400</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -1987,7 +2017,7 @@
         <v>40000</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="38">
@@ -2019,7 +2049,7 @@
         <v>12000</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="38">
@@ -2127,7 +2157,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -2221,7 +2251,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2242,7 +2272,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2259,7 +2289,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2277,7 +2307,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" s="35">
         <v>468340</v>
@@ -2311,7 +2341,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H34" s="42">
         <f>H32+H33</f>
@@ -2332,7 +2362,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="10"/>
       <c r="G35" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H35" s="46">
         <f>H31-H34</f>
@@ -2353,7 +2383,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2373,7 +2403,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2476,7 +2506,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2485,7 +2515,7 @@
         <v>4500</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2527,7 +2557,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="28">
         <v>44840</v>
@@ -2560,7 +2590,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2687,7 +2717,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2708,7 +2738,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2725,7 +2755,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2743,7 +2773,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" s="35">
         <v>503685</v>
@@ -2777,7 +2807,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -2798,7 +2828,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15" s="46">
         <f>H11-H14</f>
@@ -2819,7 +2849,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2839,7 +2869,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -2938,7 +2968,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2947,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3022,7 +3052,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="B5" s="28">
         <v>44866</v>
@@ -3055,7 +3085,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="28">
         <v>44867</v>
@@ -3154,7 +3184,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3187,7 +3217,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3281,7 +3311,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3302,7 +3332,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3319,7 +3349,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3337,7 +3367,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="35">
         <v>574815</v>
@@ -3371,7 +3401,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="42">
         <f>H16+H17</f>
@@ -3392,7 +3422,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="10"/>
       <c r="G19" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" s="46">
         <f>H15-H18</f>
@@ -3413,7 +3443,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3433,7 +3463,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3541,7 +3571,7 @@
         <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3564,7 +3594,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="28">
         <v>44901</v>
@@ -3573,7 +3603,7 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -3596,7 +3626,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3605,7 +3635,7 @@
         <v>40000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -3628,7 +3658,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3637,7 +3667,7 @@
         <v>130000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -3660,7 +3690,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3669,7 +3699,7 @@
         <v>24000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -3700,7 +3730,7 @@
         <v>30000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -3732,7 +3762,7 @@
         <v>40000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -3755,7 +3785,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3764,7 +3794,7 @@
         <v>2400</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -3796,7 +3826,7 @@
         <v>20000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -3828,7 +3858,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -3903,7 +3933,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -4002,7 +4032,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="28">
         <v>44923</v>
@@ -4035,7 +4065,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="28">
         <v>44925</v>
@@ -4096,7 +4126,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -4117,7 +4147,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -4134,7 +4164,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -4152,7 +4182,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" s="35">
         <v>612765</v>
@@ -4186,7 +4216,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
@@ -4207,7 +4237,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H26" s="36">
         <f>H22-H25</f>
@@ -4228,7 +4258,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4248,7 +4278,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4345,7 +4375,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="28">
         <v>44566</v>
@@ -4375,7 +4405,7 @@
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="28">
         <v>44567</v>
@@ -4405,7 +4435,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="28">
         <v>44567</v>
@@ -4435,7 +4465,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="28">
         <v>44568</v>
@@ -4465,7 +4495,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="28">
         <v>44571</v>
@@ -4495,7 +4525,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="28">
         <v>44572</v>
@@ -4525,7 +4555,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="28">
         <v>44572</v>
@@ -4555,7 +4585,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="28">
         <v>44574</v>
@@ -4585,7 +4615,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="28">
         <v>44574</v>
@@ -4615,7 +4645,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="28">
         <v>44574</v>
@@ -4645,7 +4675,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="28">
         <v>44578</v>
@@ -4675,7 +4705,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="28">
         <v>44578</v>
@@ -4705,7 +4735,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="28">
         <v>44579</v>
@@ -4735,7 +4765,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="28">
         <v>44580</v>
@@ -4765,7 +4795,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="28">
         <v>44580</v>
@@ -4795,7 +4825,7 @@
     </row>
     <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="28">
         <v>44585</v>
@@ -4825,7 +4855,7 @@
     </row>
     <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="28">
         <v>44587</v>
@@ -4855,7 +4885,7 @@
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="28">
         <v>44588</v>
@@ -4885,7 +4915,7 @@
     </row>
     <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" s="28">
         <v>44589</v>
@@ -4915,7 +4945,7 @@
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" s="28">
         <v>44592</v>
@@ -4945,7 +4975,7 @@
     </row>
     <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="28">
         <v>44592</v>
@@ -5026,7 +5056,7 @@
       <c r="E26" s="32"/>
       <c r="F26" s="30"/>
       <c r="G26" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H26" s="35">
         <v>0</v>
@@ -5040,7 +5070,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="30"/>
       <c r="G27" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" s="35">
         <v>62710</v>
@@ -5054,7 +5084,7 @@
       <c r="E28" s="32"/>
       <c r="F28" s="30"/>
       <c r="G28" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="32">
         <f>H26+H27</f>
@@ -5069,7 +5099,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H29" s="46">
         <f>H25-H28</f>
@@ -5142,7 +5172,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="28">
         <v>44607</v>
@@ -5151,10 +5181,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="30">
         <v>0.1719</v>
@@ -5186,7 +5216,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -5216,7 +5246,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -5246,7 +5276,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -5276,7 +5306,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -5306,7 +5336,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -5336,7 +5366,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -5366,7 +5396,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -5396,7 +5426,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -5426,7 +5456,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -5456,7 +5486,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -5486,7 +5516,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5516,7 +5546,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5546,7 +5576,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5576,7 +5606,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5606,7 +5636,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5636,7 +5666,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5666,7 +5696,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5696,7 +5726,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5726,7 +5756,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5756,7 +5786,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5786,7 +5816,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5816,7 +5846,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5846,7 +5876,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5876,7 +5906,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -5966,7 +5996,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H31" s="35">
         <v>62710</v>
@@ -5983,7 +6013,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -6000,7 +6030,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H33" s="32">
         <f>H31+H32</f>
@@ -6018,7 +6048,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="30"/>
       <c r="G34" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H34" s="36">
         <f>H30-H33</f>
@@ -6097,7 +6127,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -6106,10 +6136,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="38">
         <v>0.22220000000000001</v>
@@ -6125,7 +6155,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -6134,10 +6164,10 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="38">
         <v>0.26100000000000001</v>
@@ -6153,7 +6183,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -6162,10 +6192,10 @@
         <v>110000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="38">
         <v>0.25</v>
@@ -6181,7 +6211,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -6190,10 +6220,10 @@
         <v>20000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="38">
         <v>0.1195</v>
@@ -6209,7 +6239,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -6218,10 +6248,10 @@
         <v>10000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="38">
         <v>0.221</v>
@@ -6237,7 +6267,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -6246,10 +6276,10 @@
         <v>40100</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="38">
         <v>0.17380000000000001</v>
@@ -6278,7 +6308,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -6305,7 +6335,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -6332,7 +6362,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -6359,7 +6389,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6413,7 +6443,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6494,7 +6524,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6546,7 +6576,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6561,7 +6591,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6575,7 +6605,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6590,7 +6620,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" s="35">
         <v>89870</v>
@@ -6604,7 +6634,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6618,7 +6648,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H24" s="34">
         <f>H22+H23</f>
@@ -6633,7 +6663,7 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H25" s="46">
         <f>H21-H24</f>
@@ -6642,7 +6672,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6650,7 +6680,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6721,7 +6751,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6730,10 +6760,10 @@
         <v>900</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="38">
         <v>9</v>
@@ -6755,7 +6785,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6764,10 +6794,10 @@
         <v>6000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="38">
         <v>0.86</v>
@@ -6797,10 +6827,10 @@
         <v>9000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="38">
         <v>1.75</v>
@@ -6822,7 +6852,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="28">
         <v>44677</v>
@@ -6831,10 +6861,10 @@
         <v>900</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="38">
         <v>10</v>
@@ -6856,7 +6886,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6865,10 +6895,10 @@
         <v>9000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="38">
         <v>0.45</v>
@@ -6890,7 +6920,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="28">
         <v>44680</v>
@@ -6899,10 +6929,10 @@
         <v>9000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="38">
         <v>0.8</v>
@@ -6943,7 +6973,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="28">
         <v>44669</v>
@@ -6976,7 +7006,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="28">
         <v>44669</v>
@@ -7009,7 +7039,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -7042,7 +7072,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" s="28">
         <v>44680</v>
@@ -7075,7 +7105,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -7108,7 +7138,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="28">
         <v>44652</v>
@@ -7141,7 +7171,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" s="28">
         <v>44673</v>
@@ -7205,7 +7235,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -7226,7 +7256,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -7246,7 +7276,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -7267,7 +7297,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="35">
         <v>187090</v>
@@ -7287,7 +7317,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H21" s="35">
         <v>71150</v>
@@ -7307,7 +7337,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H22" s="34">
         <f>H20+H21</f>
@@ -7328,7 +7358,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H23" s="46">
         <f>H19-H22</f>
@@ -7349,7 +7379,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -7369,7 +7399,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -7470,7 +7500,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7479,10 +7509,10 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="38">
         <v>0.5</v>
@@ -7503,7 +7533,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7512,10 +7542,10 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="38">
         <v>0.52</v>
@@ -7537,7 +7567,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7546,10 +7576,10 @@
         <v>27000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="38">
         <v>0.36</v>
@@ -7580,10 +7610,10 @@
         <v>22500</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="38">
         <v>0.65</v>
@@ -7604,7 +7634,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="28">
         <v>44687</v>
@@ -7613,10 +7643,10 @@
         <v>27000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="38">
         <v>0.7</v>
@@ -7638,7 +7668,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="B7" s="28">
         <v>44690</v>
@@ -7647,7 +7677,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -7678,7 +7708,7 @@
         <v>9000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -7701,7 +7731,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7710,7 +7740,7 @@
         <v>4500</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -7742,7 +7772,7 @@
         <v>30000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -7774,7 +7804,7 @@
         <v>60000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -7806,7 +7836,7 @@
         <v>3000</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -7829,7 +7859,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7838,7 +7868,7 @@
         <v>2000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -7861,7 +7891,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7870,7 +7900,7 @@
         <v>6000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -7893,7 +7923,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7902,7 +7932,7 @@
         <v>12000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -7933,7 +7963,7 @@
         <v>18000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -7965,7 +7995,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -7997,7 +8027,7 @@
         <v>4500</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -8029,7 +8059,7 @@
         <v>90000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -8051,7 +8081,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="28">
         <v>44712</v>
@@ -8060,7 +8090,7 @@
         <v>60000</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -8135,7 +8165,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -8168,7 +8198,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -8234,7 +8264,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -8267,7 +8297,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -8300,7 +8330,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -8333,7 +8363,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8432,7 +8462,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8465,7 +8495,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8498,7 +8528,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8531,7 +8561,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8595,7 +8625,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8616,7 +8646,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8636,7 +8666,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8657,7 +8687,7 @@
       <c r="E40" s="32"/>
       <c r="F40" s="30"/>
       <c r="G40" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H40" s="35">
         <v>258240</v>
@@ -8697,7 +8727,7 @@
       <c r="E42" s="32"/>
       <c r="F42" s="30"/>
       <c r="G42" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H42" s="42">
         <f>H40+H41</f>
@@ -8718,7 +8748,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="10"/>
       <c r="G43" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H43" s="47">
         <f>H39-H42</f>
@@ -8739,7 +8769,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8759,7 +8789,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8861,7 +8891,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8870,7 +8900,7 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -8893,7 +8923,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8902,7 +8932,7 @@
         <v>110000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -8934,7 +8964,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -8957,7 +8987,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8966,7 +8996,7 @@
         <v>6000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -8998,7 +9028,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -9040,7 +9070,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -9106,7 +9136,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -9172,7 +9202,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -9238,7 +9268,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -9302,7 +9332,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -9323,7 +9353,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -9343,7 +9373,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9364,7 +9394,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" s="35">
         <v>314880</v>
@@ -9404,7 +9434,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" s="42">
         <f>H19+H20</f>
@@ -9425,7 +9455,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="47">
         <f>H18-H21</f>
@@ -9446,7 +9476,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -9466,7 +9496,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9573,7 +9603,7 @@
         <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9614,7 +9644,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9647,7 +9677,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9680,7 +9710,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9713,7 +9743,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9774,7 +9804,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9795,7 +9825,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9812,7 +9842,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9830,7 +9860,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" s="35">
         <v>387440</v>
@@ -9864,7 +9894,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
@@ -9885,7 +9915,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15" s="47">
         <f>H11-H14</f>
@@ -9906,7 +9936,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9926,7 +9956,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -10038,7 +10068,7 @@
         <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -10070,7 +10100,7 @@
         <v>900</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -10145,7 +10175,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -10206,7 +10236,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -10227,7 +10257,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -10244,7 +10274,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -10262,7 +10292,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="35">
         <v>414400</v>
@@ -10296,7 +10326,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" s="42">
         <f>H11+H12</f>
@@ -10317,7 +10347,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="10"/>
       <c r="G14" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" s="48">
         <f>H10-H13</f>
@@ -10338,7 +10368,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -10358,7 +10388,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4635" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832B9285-E520-4337-9B73-39F34D2D379F}"/>
+  <xr:revisionPtr revIDLastSave="4652" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F4E7680-BEB4-429A-8D48-C994CE05B37B}"/>
   <bookViews>
-    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JAN23" sheetId="58" r:id="rId1"/>
-    <sheet name="JAN22" sheetId="38" r:id="rId2"/>
+    <sheet name="FEB23" sheetId="59" r:id="rId2"/>
     <sheet name="FEB22" sheetId="39" r:id="rId3"/>
     <sheet name="MAR22" sheetId="40" r:id="rId4"/>
     <sheet name="APR22" sheetId="41" r:id="rId5"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="98">
   <si>
     <t>Name</t>
   </si>
@@ -107,46 +107,13 @@
     <t>Profit - Expense</t>
   </si>
   <si>
-    <t>IVL</t>
-  </si>
-  <si>
-    <t>DCC</t>
-  </si>
-  <si>
-    <t>EPG</t>
-  </si>
-  <si>
-    <t>IMH</t>
-  </si>
-  <si>
-    <t>KBANK</t>
-  </si>
-  <si>
-    <t>SAT</t>
-  </si>
-  <si>
-    <t>SYNEX</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>SIS</t>
-  </si>
-  <si>
-    <t>MCS</t>
-  </si>
-  <si>
-    <t>NER</t>
-  </si>
-  <si>
-    <t>TOP</t>
-  </si>
-  <si>
     <t>LPF-DIV</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>February Exp</t>
   </si>
   <si>
     <t>BGRIM</t>
@@ -161,19 +128,34 @@
     <t>DIF</t>
   </si>
   <si>
+    <t>EPG</t>
+  </si>
+  <si>
     <t>GLOBAL</t>
+  </si>
+  <si>
+    <t>IMH</t>
   </si>
   <si>
     <t>IP</t>
   </si>
   <si>
+    <t>IVL</t>
+  </si>
+  <si>
     <t>LPF</t>
+  </si>
+  <si>
+    <t>MCS</t>
   </si>
   <si>
     <t>NOBLE</t>
   </si>
   <si>
     <t>RATCH</t>
+  </si>
+  <si>
+    <t>TOP</t>
   </si>
   <si>
     <t>TSE</t>
@@ -183,9 +165,6 @@
   </si>
   <si>
     <t>TU</t>
-  </si>
-  <si>
-    <t>February Exp</t>
   </si>
   <si>
     <t>CPNCG-DIV</t>
@@ -216,6 +195,9 @@
   </si>
   <si>
     <t>DOHOME</t>
+  </si>
+  <si>
+    <t>SIS</t>
   </si>
   <si>
     <t>Div+Gain</t>
@@ -263,6 +245,9 @@
     <t>April Exp</t>
   </si>
   <si>
+    <t>NER</t>
+  </si>
+  <si>
     <t>TMT</t>
   </si>
   <si>
@@ -275,6 +260,9 @@
     <t>TPIPL</t>
   </si>
   <si>
+    <t>RCL</t>
+  </si>
+  <si>
     <t>BCH</t>
   </si>
   <si>
@@ -285,6 +273,9 @@
   </si>
   <si>
     <t>SENA</t>
+  </si>
+  <si>
+    <t>DCC</t>
   </si>
   <si>
     <t>HREIT</t>
@@ -321,6 +312,9 @@
   </si>
   <si>
     <t>VNG</t>
+  </si>
+  <si>
+    <t>SYNEX</t>
   </si>
   <si>
     <t>GVREIT</t>
@@ -1403,7 +1397,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B2" s="28">
         <v>44806</v>
@@ -1412,7 +1406,7 @@
         <v>5000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -1435,7 +1429,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1444,7 +1438,7 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -1467,7 +1461,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B4" s="28">
         <v>44806</v>
@@ -1476,7 +1470,7 @@
         <v>15000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -1499,7 +1493,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B5" s="28">
         <v>44806</v>
@@ -1508,7 +1502,7 @@
         <v>30000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -1531,7 +1525,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1540,7 +1534,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -1563,7 +1557,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="B7" s="28">
         <v>44809</v>
@@ -1572,7 +1566,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -1595,7 +1589,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="B8" s="28">
         <v>44810</v>
@@ -1604,7 +1598,7 @@
         <v>60000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -1627,7 +1621,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1636,7 +1630,7 @@
         <v>130000</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -1668,7 +1662,7 @@
         <v>7500</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -1691,7 +1685,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1700,7 +1694,7 @@
         <v>27000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -1732,7 +1726,7 @@
         <v>22500</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -1754,7 +1748,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B13" s="28">
         <v>44813</v>
@@ -1763,7 +1757,7 @@
         <v>30000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -1795,7 +1789,7 @@
         <v>15000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -1817,7 +1811,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B15" s="28">
         <v>44813</v>
@@ -1826,7 +1820,7 @@
         <v>105000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -1848,7 +1842,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B16" s="28">
         <v>44813</v>
@@ -1857,7 +1851,7 @@
         <v>48000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -1880,7 +1874,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B17" s="28">
         <v>44817</v>
@@ -1889,7 +1883,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -1912,7 +1906,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B18" s="28">
         <v>44818</v>
@@ -1921,7 +1915,7 @@
         <v>21000</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -1944,7 +1938,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B19" s="28">
         <v>44818</v>
@@ -1953,7 +1947,7 @@
         <v>10000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -1976,7 +1970,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -1985,7 +1979,7 @@
         <v>2400</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -2017,7 +2011,7 @@
         <v>40000</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="38">
@@ -2049,7 +2043,7 @@
         <v>12000</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="38">
@@ -2091,7 +2085,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B24" s="28">
         <v>44805</v>
@@ -2124,7 +2118,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B25" s="28">
         <v>44809</v>
@@ -2157,7 +2151,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -2190,7 +2184,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B27" s="28">
         <v>44816</v>
@@ -2251,7 +2245,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2272,7 +2266,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2289,7 +2283,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2324,7 +2318,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H33" s="35">
         <v>35345</v>
@@ -2383,7 +2377,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2403,7 +2397,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2506,7 +2500,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2515,7 +2509,7 @@
         <v>4500</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -2557,7 +2551,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B4" s="28">
         <v>44840</v>
@@ -2590,7 +2584,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2623,7 +2617,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B6" s="28">
         <v>44860</v>
@@ -2717,7 +2711,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2738,7 +2732,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2755,7 +2749,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2790,7 +2784,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H13" s="35">
         <v>71130</v>
@@ -2849,7 +2843,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2869,7 +2863,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -2968,7 +2962,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2977,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3085,7 +3079,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="B6" s="28">
         <v>44867</v>
@@ -3118,7 +3112,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B7" s="28">
         <v>44872</v>
@@ -3151,7 +3145,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B8" s="28">
         <v>44873</v>
@@ -3184,7 +3178,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3217,7 +3211,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3250,7 +3244,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B11" s="28">
         <v>44887</v>
@@ -3311,7 +3305,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3332,7 +3326,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3349,7 +3343,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3384,7 +3378,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H17" s="35">
         <v>37950</v>
@@ -3443,7 +3437,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3463,7 +3457,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3562,7 +3556,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B2" s="28">
         <v>44897</v>
@@ -3571,7 +3565,7 @@
         <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -3594,7 +3588,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="B3" s="28">
         <v>44901</v>
@@ -3603,7 +3597,7 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -3626,7 +3620,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3635,7 +3629,7 @@
         <v>40000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -3658,7 +3652,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3667,7 +3661,7 @@
         <v>130000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -3690,7 +3684,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3699,7 +3693,7 @@
         <v>24000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -3721,7 +3715,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B7" s="28">
         <v>44908</v>
@@ -3730,7 +3724,7 @@
         <v>30000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -3762,7 +3756,7 @@
         <v>40000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -3785,7 +3779,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3794,7 +3788,7 @@
         <v>2400</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -3817,7 +3811,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B10" s="28">
         <v>44918</v>
@@ -3826,7 +3820,7 @@
         <v>20000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -3849,7 +3843,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B11" s="28">
         <v>44923</v>
@@ -3858,7 +3852,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -3933,7 +3927,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -4032,7 +4026,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B17" s="28">
         <v>44923</v>
@@ -4065,7 +4059,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="B18" s="28">
         <v>44925</v>
@@ -4126,7 +4120,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -4147,7 +4141,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -4164,7 +4158,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -4199,7 +4193,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H24" s="35">
         <v>29530</v>
@@ -4258,7 +4252,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4278,7 +4272,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4326,25 +4320,29 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5674D68-3DFE-4CE9-AFD6-DD45A9A60264}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.5703125" style="6"/>
+    <col min="1" max="1" width="8.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4373,747 +4371,215 @@
       <c r="J1" s="16"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="28">
-        <v>44566</v>
+        <v>44607</v>
       </c>
       <c r="C2" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D2" s="30">
-        <v>42</v>
-      </c>
-      <c r="E2" s="31">
-        <v>126279.08</v>
+        <v>0</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>21</v>
       </c>
       <c r="F2" s="30">
-        <v>44.5</v>
+        <v>0.1719</v>
       </c>
       <c r="G2" s="31">
-        <v>133204.31</v>
+        <f>C2*F2</f>
+        <v>0</v>
       </c>
       <c r="H2" s="32">
-        <f t="shared" ref="H2:H22" si="0">G2-E2</f>
-        <v>6925.2299999999959</v>
+        <f>G2*0.9</f>
+        <v>0</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="28">
-        <v>44567</v>
-      </c>
-      <c r="C3" s="29">
-        <v>40000</v>
-      </c>
-      <c r="D3" s="30">
-        <v>2.9</v>
-      </c>
-      <c r="E3" s="31">
-        <v>116256.93</v>
-      </c>
-      <c r="F3" s="30">
-        <v>3</v>
-      </c>
-      <c r="G3" s="31">
-        <v>119734.21</v>
-      </c>
-      <c r="H3" s="32">
-        <f t="shared" si="0"/>
-        <v>3477.2800000000134</v>
-      </c>
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B4" s="28">
-        <v>44567</v>
+        <v>44958</v>
       </c>
       <c r="C4" s="29">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D4" s="30">
-        <v>11.2</v>
+        <v>62.75</v>
       </c>
       <c r="E4" s="31">
-        <v>22449.62</v>
+        <v>62888.98</v>
       </c>
       <c r="F4" s="30">
-        <v>12.3</v>
+        <v>56</v>
       </c>
       <c r="G4" s="31">
-        <v>24545.52</v>
+        <v>55875.97</v>
       </c>
       <c r="H4" s="32">
-        <f t="shared" si="0"/>
-        <v>2095.9000000000015</v>
+        <f t="shared" ref="H4" si="0">G4-E4</f>
+        <v>-7013.010000000002</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="28">
-        <v>44568</v>
-      </c>
-      <c r="C5" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D5" s="30">
-        <v>11</v>
-      </c>
-      <c r="E5" s="31">
-        <v>16536.55</v>
-      </c>
-      <c r="F5" s="30">
-        <v>16.8</v>
-      </c>
-      <c r="G5" s="31">
-        <v>25144.19</v>
-      </c>
-      <c r="H5" s="32">
-        <f t="shared" si="0"/>
-        <v>8607.64</v>
+    <row r="5" spans="1:12" ht="15" customHeight="1">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>62888.98</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>55875.97</v>
+      </c>
+      <c r="H5" s="44">
+        <f>SUM(H4:H4)</f>
+        <v>-7013.010000000002</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="28">
-        <v>44571</v>
-      </c>
-      <c r="C6" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D6" s="30">
-        <v>11</v>
-      </c>
-      <c r="E6" s="31">
-        <v>16536.55</v>
-      </c>
-      <c r="F6" s="30">
-        <v>16.8</v>
-      </c>
-      <c r="G6" s="31">
-        <v>25144.19</v>
-      </c>
+      <c r="K5" s="15"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="32">
-        <f t="shared" si="0"/>
-        <v>8607.64</v>
+        <v>-81338.25999999998</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="28">
-        <v>44572</v>
-      </c>
-      <c r="C7" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="30">
-        <v>11</v>
-      </c>
-      <c r="E7" s="31">
-        <v>11024.36</v>
-      </c>
-      <c r="F7" s="30">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="G7" s="31">
-        <v>20055.48</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" si="0"/>
-        <v>9031.119999999999</v>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="34">
+        <f>SUM(H2,H5,H6)</f>
+        <v>-88351.26999999999</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="28">
-        <v>44572</v>
-      </c>
-      <c r="C8" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D8" s="30">
-        <v>42</v>
-      </c>
-      <c r="E8" s="31">
-        <v>126279.08</v>
-      </c>
-      <c r="F8" s="30">
-        <v>46.25</v>
-      </c>
-      <c r="G8" s="31">
-        <v>138442.69</v>
-      </c>
-      <c r="H8" s="32">
-        <f t="shared" si="0"/>
-        <v>12163.61</v>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="35">
+        <v>76110</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="28">
-        <v>44574</v>
-      </c>
-      <c r="C9" s="29">
-        <v>800</v>
-      </c>
-      <c r="D9" s="30">
-        <v>136.88</v>
-      </c>
-      <c r="E9" s="31">
-        <v>109746.54</v>
-      </c>
-      <c r="F9" s="30">
-        <v>144.5</v>
-      </c>
-      <c r="G9" s="31">
-        <v>115343.96</v>
-      </c>
-      <c r="H9" s="32">
-        <f t="shared" si="0"/>
-        <v>5597.4200000000128</v>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="35">
+        <v>40000</v>
       </c>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="28">
-        <v>44574</v>
-      </c>
-      <c r="C10" s="29">
-        <v>2500</v>
-      </c>
-      <c r="D10" s="30">
-        <v>21.1</v>
-      </c>
-      <c r="E10" s="31">
-        <v>52866.83</v>
-      </c>
-      <c r="F10" s="30">
-        <v>24.4</v>
-      </c>
-      <c r="G10" s="31">
-        <v>60864.89</v>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="H10" s="32">
-        <f t="shared" si="0"/>
-        <v>7998.0599999999977</v>
+        <f>H8+H9</f>
+        <v>116110</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="28">
-        <v>44574</v>
-      </c>
-      <c r="C11" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D11" s="30">
-        <v>31.5</v>
-      </c>
-      <c r="E11" s="31">
-        <v>47354.66</v>
-      </c>
-      <c r="F11" s="30">
-        <v>33</v>
-      </c>
-      <c r="G11" s="31">
-        <v>49390.36</v>
-      </c>
-      <c r="H11" s="32">
-        <f t="shared" si="0"/>
-        <v>2035.6999999999971</v>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="36">
+        <f>H7-H10</f>
+        <v>-204461.27</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="28">
-        <v>44578</v>
-      </c>
-      <c r="C12" s="29">
-        <v>800</v>
-      </c>
-      <c r="D12" s="30">
-        <v>136.88</v>
-      </c>
-      <c r="E12" s="31">
-        <v>109746.54</v>
-      </c>
-      <c r="F12" s="30">
-        <v>144.5</v>
-      </c>
-      <c r="G12" s="31">
-        <v>115343.96</v>
-      </c>
-      <c r="H12" s="32">
-        <f t="shared" si="0"/>
-        <v>5597.4200000000128</v>
-      </c>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" ht="13.9">
+      <c r="B12" s="18"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="28">
-        <v>44578</v>
-      </c>
-      <c r="C13" s="29">
-        <v>800</v>
-      </c>
-      <c r="D13" s="30">
-        <v>136.88</v>
-      </c>
-      <c r="E13" s="31">
-        <v>109746.54</v>
-      </c>
-      <c r="F13" s="30">
-        <v>140</v>
-      </c>
-      <c r="G13" s="31">
-        <v>111751.93</v>
-      </c>
-      <c r="H13" s="32">
-        <f t="shared" si="0"/>
-        <v>2005.3899999999994</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="28">
-        <v>44579</v>
-      </c>
-      <c r="C14" s="29">
-        <v>5000</v>
-      </c>
-      <c r="D14" s="30">
-        <v>21.1</v>
-      </c>
-      <c r="E14" s="31">
-        <v>105733.68</v>
-      </c>
-      <c r="F14" s="30">
-        <v>23.2</v>
-      </c>
-      <c r="G14" s="31">
-        <v>115743.07</v>
-      </c>
-      <c r="H14" s="32">
-        <f t="shared" si="0"/>
-        <v>10009.390000000014</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="28">
-        <v>44580</v>
-      </c>
-      <c r="C15" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D15" s="30">
-        <v>44.5</v>
-      </c>
-      <c r="E15" s="31">
-        <v>66897.84</v>
-      </c>
-      <c r="F15" s="30">
-        <v>49.5</v>
-      </c>
-      <c r="G15" s="31">
-        <v>74085.539999999994</v>
-      </c>
-      <c r="H15" s="32">
-        <f t="shared" si="0"/>
-        <v>7187.6999999999971</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="28">
-        <v>44580</v>
-      </c>
-      <c r="C16" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D16" s="30">
-        <v>40.5</v>
-      </c>
-      <c r="E16" s="31">
-        <v>60884.55</v>
-      </c>
-      <c r="F16" s="30">
-        <v>42.75</v>
-      </c>
-      <c r="G16" s="31">
-        <v>63982.97</v>
-      </c>
-      <c r="H16" s="32">
-        <f t="shared" si="0"/>
-        <v>3098.4199999999983</v>
-      </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="28">
-        <v>44585</v>
-      </c>
-      <c r="C17" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D17" s="30">
-        <v>42</v>
-      </c>
-      <c r="E17" s="31">
-        <v>126279.08</v>
-      </c>
-      <c r="F17" s="30">
-        <v>46.25</v>
-      </c>
-      <c r="G17" s="31">
-        <v>138442.69</v>
-      </c>
-      <c r="H17" s="32">
-        <f t="shared" si="0"/>
-        <v>12163.61</v>
-      </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="28">
-        <v>44587</v>
-      </c>
-      <c r="C18" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="30">
-        <v>42</v>
-      </c>
-      <c r="E18" s="31">
-        <v>126279.08</v>
-      </c>
-      <c r="F18" s="30">
-        <v>48.25</v>
-      </c>
-      <c r="G18" s="31">
-        <v>144429.4</v>
-      </c>
-      <c r="H18" s="32">
-        <f t="shared" si="0"/>
-        <v>18150.319999999992</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="28">
-        <v>44588</v>
-      </c>
-      <c r="C19" s="29">
-        <v>5000</v>
-      </c>
-      <c r="D19" s="30">
-        <v>16.7</v>
-      </c>
-      <c r="E19" s="31">
-        <v>83684.95</v>
-      </c>
-      <c r="F19" s="30">
-        <v>14.6</v>
-      </c>
-      <c r="G19" s="31">
-        <v>72838.31</v>
-      </c>
-      <c r="H19" s="32">
-        <f t="shared" si="0"/>
-        <v>-10846.64</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="28">
-        <v>44589</v>
-      </c>
-      <c r="C20" s="29">
-        <v>6000</v>
-      </c>
-      <c r="D20" s="30">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E20" s="31">
-        <v>105833.89</v>
-      </c>
-      <c r="F20" s="30">
-        <v>17.7</v>
-      </c>
-      <c r="G20" s="31">
-        <v>105964.78</v>
-      </c>
-      <c r="H20" s="32">
-        <f t="shared" si="0"/>
-        <v>130.88999999999942</v>
-      </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A21" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="28">
-        <v>44592</v>
-      </c>
-      <c r="C21" s="29">
-        <v>9000</v>
-      </c>
-      <c r="D21" s="30">
-        <v>7.45</v>
-      </c>
-      <c r="E21" s="31">
-        <v>67198.509999999995</v>
-      </c>
-      <c r="F21" s="30">
-        <v>7.3</v>
-      </c>
-      <c r="G21" s="31">
-        <v>65554.48</v>
-      </c>
-      <c r="H21" s="32">
-        <f t="shared" si="0"/>
-        <v>-1644.0299999999988</v>
-      </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A22" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="28">
-        <v>44592</v>
-      </c>
-      <c r="C22" s="29">
-        <v>2000</v>
-      </c>
-      <c r="D22" s="30">
-        <v>50.5</v>
-      </c>
-      <c r="E22" s="31">
-        <v>101223.7</v>
-      </c>
-      <c r="F22" s="30">
-        <v>53.25</v>
-      </c>
-      <c r="G22" s="31">
-        <v>106264.11</v>
-      </c>
-      <c r="H22" s="32">
-        <f t="shared" si="0"/>
-        <v>5040.4100000000035</v>
-      </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1">
-      <c r="A23" s="26"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="32">
-        <f>SUM(E2:E22)</f>
-        <v>1708838.5599999998</v>
-      </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="32">
-        <f>SUM(G2:G22)</f>
-        <v>1826271.04</v>
-      </c>
-      <c r="H23" s="44">
-        <f>SUM(H2:H22)</f>
-        <v>117432.48000000004</v>
-      </c>
-      <c r="K23" s="15"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1">
-      <c r="A24" s="26"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1">
-      <c r="A25" s="26"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32">
-        <f>SUM(H23:H24)</f>
-        <v>117432.48000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1">
-      <c r="A26" s="26"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1">
-      <c r="A27" s="26"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="35">
-        <v>62710</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="32">
-        <f>H26+H27</f>
-        <v>62710</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="46">
-        <f>H25-H28</f>
-        <v>54722.48000000004</v>
-      </c>
+      <c r="L12" s="6"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H22">
-    <sortCondition ref="B2:B22"/>
-    <sortCondition ref="A2:A22"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
@@ -5172,7 +4638,7 @@
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B2" s="28">
         <v>44607</v>
@@ -5181,10 +4647,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F2" s="30">
         <v>0.1719</v>
@@ -5216,7 +4682,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -5246,7 +4712,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -5276,7 +4742,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -5306,7 +4772,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -5336,7 +4802,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -5366,7 +4832,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -5396,7 +4862,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -5426,7 +4892,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -5456,7 +4922,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -5486,7 +4952,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -5516,7 +4982,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5546,7 +5012,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5576,7 +5042,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5606,7 +5072,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5636,7 +5102,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5666,7 +5132,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5696,7 +5162,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5726,7 +5192,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5756,7 +5222,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5786,7 +5252,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5816,7 +5282,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5846,7 +5312,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5876,7 +5342,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5906,7 +5372,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -6013,7 +5479,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -6127,7 +5593,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -6136,10 +5602,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F2" s="38">
         <v>0.22220000000000001</v>
@@ -6155,7 +5621,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -6164,10 +5630,10 @@
         <v>60000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F3" s="38">
         <v>0.26100000000000001</v>
@@ -6183,7 +5649,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -6192,10 +5658,10 @@
         <v>110000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F4" s="38">
         <v>0.25</v>
@@ -6211,7 +5677,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -6220,10 +5686,10 @@
         <v>20000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F5" s="38">
         <v>0.1195</v>
@@ -6239,7 +5705,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -6248,10 +5714,10 @@
         <v>10000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F6" s="38">
         <v>0.221</v>
@@ -6267,7 +5733,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -6276,10 +5742,10 @@
         <v>40100</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F7" s="38">
         <v>0.17380000000000001</v>
@@ -6308,7 +5774,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -6335,7 +5801,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -6362,7 +5828,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -6389,7 +5855,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6443,7 +5909,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6524,7 +5990,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6576,7 +6042,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6591,7 +6057,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6605,7 +6071,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6634,7 +6100,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6672,7 +6138,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6680,7 +6146,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6751,7 +6217,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6760,10 +6226,10 @@
         <v>900</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F2" s="38">
         <v>9</v>
@@ -6785,7 +6251,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6794,10 +6260,10 @@
         <v>6000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F3" s="38">
         <v>0.86</v>
@@ -6827,10 +6293,10 @@
         <v>9000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F4" s="38">
         <v>1.75</v>
@@ -6852,7 +6318,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B5" s="28">
         <v>44677</v>
@@ -6861,10 +6327,10 @@
         <v>900</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F5" s="38">
         <v>10</v>
@@ -6886,7 +6352,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6895,10 +6361,10 @@
         <v>9000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F6" s="38">
         <v>0.45</v>
@@ -6920,7 +6386,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B7" s="28">
         <v>44680</v>
@@ -6929,10 +6395,10 @@
         <v>9000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F7" s="38">
         <v>0.8</v>
@@ -6973,7 +6439,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B9" s="28">
         <v>44669</v>
@@ -7006,7 +6472,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B10" s="28">
         <v>44669</v>
@@ -7039,7 +6505,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -7072,7 +6538,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B12" s="28">
         <v>44680</v>
@@ -7105,7 +6571,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -7138,7 +6604,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B14" s="28">
         <v>44652</v>
@@ -7171,7 +6637,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="27" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B15" s="28">
         <v>44673</v>
@@ -7235,7 +6701,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -7256,7 +6722,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -7276,7 +6742,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -7317,7 +6783,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H21" s="35">
         <v>71150</v>
@@ -7379,7 +6845,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -7399,7 +6865,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -7500,7 +6966,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7509,10 +6975,10 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F2" s="38">
         <v>0.5</v>
@@ -7533,7 +6999,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7542,10 +7008,10 @@
         <v>15000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F3" s="38">
         <v>0.52</v>
@@ -7567,7 +7033,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7576,10 +7042,10 @@
         <v>27000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F4" s="38">
         <v>0.36</v>
@@ -7610,10 +7076,10 @@
         <v>22500</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F5" s="38">
         <v>0.65</v>
@@ -7634,7 +7100,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B6" s="28">
         <v>44687</v>
@@ -7643,10 +7109,10 @@
         <v>27000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F6" s="38">
         <v>0.7</v>
@@ -7677,7 +7143,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="38">
@@ -7699,7 +7165,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B8" s="28">
         <v>44693</v>
@@ -7708,7 +7174,7 @@
         <v>9000</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="38">
@@ -7731,7 +7197,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7740,7 +7206,7 @@
         <v>4500</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="38">
@@ -7763,7 +7229,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B10" s="28">
         <v>44698</v>
@@ -7772,7 +7238,7 @@
         <v>30000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="38">
@@ -7795,7 +7261,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B11" s="28">
         <v>44698</v>
@@ -7804,7 +7270,7 @@
         <v>60000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="38">
@@ -7836,7 +7302,7 @@
         <v>3000</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="38">
@@ -7859,7 +7325,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7868,7 +7334,7 @@
         <v>2000</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="38">
@@ -7891,7 +7357,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7900,7 +7366,7 @@
         <v>6000</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="38">
@@ -7923,7 +7389,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7932,7 +7398,7 @@
         <v>12000</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="38">
@@ -7954,7 +7420,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16" s="28">
         <v>44705</v>
@@ -7963,7 +7429,7 @@
         <v>18000</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="38">
@@ -7986,7 +7452,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B17" s="28">
         <v>44705</v>
@@ -7995,7 +7461,7 @@
         <v>45000</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="38">
@@ -8018,7 +7484,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B18" s="28">
         <v>44705</v>
@@ -8027,7 +7493,7 @@
         <v>4500</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="38">
@@ -8050,7 +7516,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B19" s="28">
         <v>44706</v>
@@ -8059,7 +7525,7 @@
         <v>90000</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="38">
@@ -8081,7 +7547,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="B20" s="28">
         <v>44712</v>
@@ -8090,7 +7556,7 @@
         <v>60000</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="38">
@@ -8132,7 +7598,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="27" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B22" s="28">
         <v>44684</v>
@@ -8165,7 +7631,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -8198,7 +7664,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -8231,7 +7697,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A25" s="27" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B25" s="28">
         <v>44692</v>
@@ -8264,7 +7730,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -8297,7 +7763,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -8330,7 +7796,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -8363,7 +7829,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8396,7 +7862,7 @@
     </row>
     <row r="30" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A30" s="27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B30" s="28">
         <v>44704</v>
@@ -8429,7 +7895,7 @@
     </row>
     <row r="31" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A31" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B31" s="28">
         <v>44704</v>
@@ -8462,7 +7928,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8495,7 +7961,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8528,7 +7994,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8561,7 +8027,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8625,7 +8091,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8646,7 +8112,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8666,7 +8132,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8707,7 +8173,7 @@
       <c r="E41" s="32"/>
       <c r="F41" s="30"/>
       <c r="G41" s="32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H41" s="35">
         <v>56640</v>
@@ -8769,7 +8235,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8789,7 +8255,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8891,7 +8357,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8900,7 +8366,7 @@
         <v>50000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -8923,7 +8389,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8932,7 +8398,7 @@
         <v>110000</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -8955,7 +8421,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="28">
         <v>44727</v>
@@ -8964,7 +8430,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="38">
@@ -8987,7 +8453,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8996,7 +8462,7 @@
         <v>6000</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="38">
@@ -9028,7 +8494,7 @@
         <v>40000</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="38">
@@ -9070,7 +8536,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -9136,7 +8602,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -9169,7 +8635,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B11" s="28">
         <v>44735</v>
@@ -9202,7 +8668,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -9235,7 +8701,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B13" s="28">
         <v>44739</v>
@@ -9268,7 +8734,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -9332,7 +8798,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -9353,7 +8819,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -9373,7 +8839,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9414,7 +8880,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H20" s="35">
         <v>72560</v>
@@ -9476,7 +8942,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -9496,7 +8962,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9603,7 +9069,7 @@
         <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -9644,7 +9110,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9677,7 +9143,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9710,7 +9176,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9743,7 +9209,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9804,7 +9270,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9825,7 +9291,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9842,7 +9308,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9877,7 +9343,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H13" s="35">
         <v>26960</v>
@@ -9936,7 +9402,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9956,7 +9422,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -10059,7 +9525,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B2" s="28">
         <v>44799</v>
@@ -10068,7 +9534,7 @@
         <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="38">
@@ -10091,7 +9557,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B3" s="28">
         <v>44799</v>
@@ -10100,7 +9566,7 @@
         <v>900</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="38">
@@ -10142,7 +9608,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B5" s="28">
         <v>44788</v>
@@ -10175,7 +9641,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -10236,7 +9702,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -10257,7 +9723,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -10274,7 +9740,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -10309,7 +9775,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H12" s="35">
         <v>53940</v>
@@ -10368,7 +9834,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -10388,7 +9854,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26202"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4652" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F4E7680-BEB4-429A-8D48-C994CE05B37B}"/>
+  <xr:revisionPtr revIDLastSave="4673" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEB77B6F-ADEC-445F-92F2-16B7B4660DD0}"/>
   <bookViews>
-    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JAN23" sheetId="58" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="98">
   <si>
     <t>Name</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>DCC</t>
   </si>
   <si>
     <t>February Exp</t>
@@ -273,9 +276,6 @@
   </si>
   <si>
     <t>SENA</t>
-  </si>
-  <si>
-    <t>DCC</t>
   </si>
   <si>
     <t>HREIT</t>
@@ -450,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -519,6 +519,7 @@
     <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="188" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1429,7 +1430,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1525,7 +1526,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1589,7 +1590,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="B8" s="28">
         <v>44810</v>
@@ -1621,7 +1622,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1685,7 +1686,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1748,7 +1749,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="28">
         <v>44813</v>
@@ -1811,7 +1812,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B15" s="28">
         <v>44813</v>
@@ -1842,7 +1843,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="28">
         <v>44813</v>
@@ -1874,7 +1875,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="28">
         <v>44817</v>
@@ -1906,7 +1907,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" s="28">
         <v>44818</v>
@@ -1970,7 +1971,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -2085,7 +2086,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="28">
         <v>44805</v>
@@ -2118,7 +2119,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="28">
         <v>44809</v>
@@ -2151,7 +2152,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -2245,7 +2246,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2266,7 +2267,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2283,7 +2284,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2377,7 +2378,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2397,7 +2398,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2500,7 +2501,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2551,7 +2552,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="28">
         <v>44840</v>
@@ -2584,7 +2585,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2617,7 +2618,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="28">
         <v>44860</v>
@@ -2711,7 +2712,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2732,7 +2733,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2749,7 +2750,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2843,7 +2844,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2863,7 +2864,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -2962,7 +2963,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -3178,7 +3179,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3211,7 +3212,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3305,7 +3306,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3326,7 +3327,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3343,7 +3344,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3437,7 +3438,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3457,7 +3458,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3588,7 +3589,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="B3" s="28">
         <v>44901</v>
@@ -3620,7 +3621,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3652,7 +3653,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3684,7 +3685,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3779,7 +3780,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3927,7 +3928,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -4026,7 +4027,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="28">
         <v>44923</v>
@@ -4120,7 +4121,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -4141,7 +4142,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -4158,7 +4159,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -4252,7 +4253,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4272,7 +4273,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4321,7 +4322,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5674D68-3DFE-4CE9-AFD6-DD45A9A60264}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="5" bestFit="1" customWidth="1"/>
@@ -4438,82 +4439,124 @@
         <v>55875.97</v>
       </c>
       <c r="H4" s="32">
-        <f t="shared" ref="H4" si="0">G4-E4</f>
+        <f t="shared" ref="H4:H6" si="0">G4-E4</f>
         <v>-7013.010000000002</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <f>SUM(E4:E4)</f>
-        <v>62888.98</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="32">
-        <f>SUM(G4:G4)</f>
-        <v>55875.97</v>
-      </c>
-      <c r="H5" s="44">
-        <f>SUM(H4:H4)</f>
-        <v>-7013.010000000002</v>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="28">
+        <v>44965</v>
+      </c>
+      <c r="C5" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="30">
+        <v>64.25</v>
+      </c>
+      <c r="E5" s="31">
+        <v>64392.31</v>
+      </c>
+      <c r="F5" s="30">
+        <v>54.5</v>
+      </c>
+      <c r="G5" s="31">
+        <v>54379.28</v>
+      </c>
+      <c r="H5" s="32">
+        <f t="shared" si="0"/>
+        <v>-10013.029999999999</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="28">
+        <v>44965</v>
+      </c>
+      <c r="C6" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="30">
+        <v>58</v>
+      </c>
+      <c r="E6" s="31">
+        <v>58128.46</v>
+      </c>
+      <c r="F6" s="30">
+        <v>54.5</v>
+      </c>
+      <c r="G6" s="31">
+        <v>54379.28</v>
+      </c>
       <c r="H6" s="32">
-        <v>-81338.25999999998</v>
+        <f t="shared" si="0"/>
+        <v>-3749.1800000000003</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="34">
-        <f>SUM(H2,H5,H6)</f>
-        <v>-88351.26999999999</v>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A7" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="28">
+        <v>44965</v>
+      </c>
+      <c r="C7" s="29">
+        <v>60000</v>
+      </c>
+      <c r="D7" s="30">
+        <v>2.96</v>
+      </c>
+      <c r="E7" s="31">
+        <v>177993.36</v>
+      </c>
+      <c r="F7" s="30">
+        <v>2.86</v>
+      </c>
+      <c r="G7" s="31">
+        <v>171219.93</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" ref="H7" si="1">G7-E7</f>
+        <v>-6773.429999999993</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
-      <c r="L7" s="6"/>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1">
       <c r="A8" s="26"/>
       <c r="B8" s="28"/>
       <c r="C8" s="29"/>
       <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
+      <c r="E8" s="50">
+        <f>SUM(E4:E7)</f>
+        <v>363403.11</v>
+      </c>
       <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="35">
-        <v>76110</v>
+      <c r="G8" s="50">
+        <f>SUM(G4:G7)</f>
+        <v>335854.45999999996</v>
+      </c>
+      <c r="H8" s="34">
+        <f>SUM(H4:H7)</f>
+        <v>-27548.649999999994</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1">
@@ -4523,11 +4566,9 @@
       <c r="D9" s="33"/>
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="35">
-        <v>40000</v>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32">
+        <v>-81338.25999999998</v>
       </c>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
@@ -4540,12 +4581,10 @@
       <c r="D10" s="33"/>
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="32">
-        <f>H8+H9</f>
-        <v>116110</v>
+      <c r="G10" s="32"/>
+      <c r="H10" s="34">
+        <f>SUM(H2,H8,H9)</f>
+        <v>-108886.90999999997</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
@@ -4559,22 +4598,74 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="36">
-        <f>H7-H10</f>
-        <v>-204461.27</v>
+        <v>16</v>
+      </c>
+      <c r="H11" s="35">
+        <v>76110</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="1:12" ht="13.9">
-      <c r="B12" s="18"/>
-      <c r="H12" s="6"/>
+    <row r="12" spans="1:12" ht="15" customHeight="1">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="35">
+        <v>40000</v>
+      </c>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
       <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="32">
+        <f>H11+H12</f>
+        <v>116110</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1">
+      <c r="A14" s="26"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="36">
+        <f>H10-H13</f>
+        <v>-224996.90999999997</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" ht="13.9">
+      <c r="B15" s="18"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="L15" s="6"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -4682,7 +4773,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -4712,7 +4803,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -4742,7 +4833,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -4772,7 +4863,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -4802,7 +4893,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -4832,7 +4923,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -4862,7 +4953,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -4892,7 +4983,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -4922,7 +5013,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -4952,7 +5043,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -4982,7 +5073,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5012,7 +5103,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5042,7 +5133,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5072,7 +5163,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5102,7 +5193,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5132,7 +5223,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5162,7 +5253,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5192,7 +5283,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5222,7 +5313,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5252,7 +5343,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5282,7 +5373,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5312,7 +5403,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5342,7 +5433,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5372,7 +5463,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -5479,7 +5570,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -5593,7 +5684,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -5621,7 +5712,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -5649,7 +5740,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -5677,7 +5768,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -5705,7 +5796,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -5733,7 +5824,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -5774,7 +5865,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -5801,7 +5892,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -5828,7 +5919,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -5855,7 +5946,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -5909,7 +6000,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -5990,7 +6081,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6042,7 +6133,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6057,7 +6148,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6071,7 +6162,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6100,7 +6191,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6138,7 +6229,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6146,7 +6237,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6217,7 +6308,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6251,7 +6342,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6318,7 +6409,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="28">
         <v>44677</v>
@@ -6352,7 +6443,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6386,7 +6477,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="28">
         <v>44680</v>
@@ -6439,7 +6530,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9" s="28">
         <v>44669</v>
@@ -6472,7 +6563,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="28">
         <v>44669</v>
@@ -6505,7 +6596,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -6538,7 +6629,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" s="28">
         <v>44680</v>
@@ -6571,7 +6662,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -6604,7 +6695,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="28">
         <v>44652</v>
@@ -6637,7 +6728,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="28">
         <v>44673</v>
@@ -6701,7 +6792,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -6722,7 +6813,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -6742,7 +6833,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -6783,7 +6874,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H21" s="35">
         <v>71150</v>
@@ -6845,7 +6936,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -6865,7 +6956,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -6966,7 +7057,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -6999,7 +7090,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7033,7 +7124,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7100,7 +7191,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="28">
         <v>44687</v>
@@ -7165,7 +7256,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="28">
         <v>44693</v>
@@ -7197,7 +7288,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7229,7 +7320,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" s="28">
         <v>44698</v>
@@ -7261,7 +7352,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="28">
         <v>44698</v>
@@ -7325,7 +7416,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7357,7 +7448,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7389,7 +7480,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7420,7 +7511,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="28">
         <v>44705</v>
@@ -7452,7 +7543,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="28">
         <v>44705</v>
@@ -7484,7 +7575,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="28">
         <v>44705</v>
@@ -7516,7 +7607,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="28">
         <v>44706</v>
@@ -7547,7 +7638,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="B20" s="28">
         <v>44712</v>
@@ -7598,7 +7689,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="28">
         <v>44684</v>
@@ -7631,7 +7722,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -7664,7 +7755,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -7697,7 +7788,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A25" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B25" s="28">
         <v>44692</v>
@@ -7730,7 +7821,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -7763,7 +7854,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -7796,7 +7887,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -7829,7 +7920,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -7895,7 +7986,7 @@
     </row>
     <row r="31" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A31" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="28">
         <v>44704</v>
@@ -7928,7 +8019,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -7961,7 +8052,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -7994,7 +8085,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8027,7 +8118,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8091,7 +8182,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8112,7 +8203,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8132,7 +8223,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8235,7 +8326,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8255,7 +8346,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8357,7 +8448,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8389,7 +8480,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8453,7 +8544,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8536,7 +8627,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -8602,7 +8693,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -8668,7 +8759,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -8734,7 +8825,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -8798,7 +8889,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -8819,7 +8910,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -8839,7 +8930,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -8942,7 +9033,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -8962,7 +9053,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9110,7 +9201,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9143,7 +9234,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9176,7 +9267,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9209,7 +9300,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9270,7 +9361,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9291,7 +9382,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9308,7 +9399,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9402,7 +9493,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9422,7 +9513,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -9641,7 +9732,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -9702,7 +9793,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -9723,7 +9814,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -9740,7 +9831,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -9834,7 +9925,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -9854,7 +9945,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4673" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEB77B6F-ADEC-445F-92F2-16B7B4660DD0}"/>
+  <xr:revisionPtr revIDLastSave="4680" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65227BA7-C9DA-4DB5-9A46-F95A39FB0DF6}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="98">
   <si>
     <t>Name</t>
   </si>
@@ -450,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -519,7 +519,6 @@
     <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="188" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4322,7 +4321,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5674D68-3DFE-4CE9-AFD6-DD45A9A60264}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="5" bestFit="1" customWidth="1"/>
@@ -4439,7 +4438,7 @@
         <v>55875.97</v>
       </c>
       <c r="H4" s="32">
-        <f t="shared" ref="H4:H6" si="0">G4-E4</f>
+        <f t="shared" ref="H4:H7" si="0">G4-E4</f>
         <v>-7013.010000000002</v>
       </c>
       <c r="I4" s="15"/>
@@ -4529,49 +4528,64 @@
         <v>171219.93</v>
       </c>
       <c r="H7" s="32">
-        <f t="shared" ref="H7" si="1">G7-E7</f>
+        <f t="shared" si="0"/>
         <v>-6773.429999999993</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="50">
-        <f>SUM(E4:E7)</f>
-        <v>363403.11</v>
-      </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="50">
-        <f>SUM(G4:G7)</f>
-        <v>335854.45999999996</v>
-      </c>
-      <c r="H8" s="34">
-        <f>SUM(H4:H7)</f>
-        <v>-27548.649999999994</v>
+    <row r="8" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="28">
+        <v>44965</v>
+      </c>
+      <c r="C8" s="29">
+        <v>2500</v>
+      </c>
+      <c r="D8" s="30">
+        <v>37.75</v>
+      </c>
+      <c r="E8" s="31">
+        <v>94584.04</v>
+      </c>
+      <c r="F8" s="30">
+        <v>24.1</v>
+      </c>
+      <c r="G8" s="31">
+        <v>60116.55</v>
+      </c>
+      <c r="H8" s="32">
+        <f t="shared" ref="H8" si="1">G8-E8</f>
+        <v>-34467.489999999991</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="6"/>
+      <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1">
       <c r="A9" s="26"/>
       <c r="B9" s="28"/>
       <c r="C9" s="29"/>
       <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
+      <c r="E9" s="32">
+        <f>SUM(E4:E8)</f>
+        <v>457987.14999999997</v>
+      </c>
       <c r="F9" s="30"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32">
-        <v>-81338.25999999998</v>
+      <c r="G9" s="32">
+        <f>SUM(G4:G8)</f>
+        <v>395971.00999999995</v>
+      </c>
+      <c r="H9" s="34">
+        <f>SUM(H4:H8)</f>
+        <v>-62016.139999999985</v>
       </c>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1">
@@ -4582,9 +4596,8 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32"/>
-      <c r="H10" s="34">
-        <f>SUM(H2,H8,H9)</f>
-        <v>-108886.90999999997</v>
+      <c r="H10" s="32">
+        <v>-81338.25999999998</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
@@ -4597,11 +4610,10 @@
       <c r="D11" s="33"/>
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="35">
-        <v>76110</v>
+      <c r="G11" s="32"/>
+      <c r="H11" s="34">
+        <f>SUM(H2,H9,H10)</f>
+        <v>-143354.39999999997</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -4615,10 +4627,10 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H12" s="35">
-        <v>40000</v>
+        <v>76110</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
@@ -4632,11 +4644,10 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="32">
-        <f>H11+H12</f>
-        <v>116110</v>
+        <v>23</v>
+      </c>
+      <c r="H13" s="35">
+        <v>40000</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
@@ -4650,22 +4661,40 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="36">
-        <f>H10-H13</f>
-        <v>-224996.90999999997</v>
+        <v>18</v>
+      </c>
+      <c r="H14" s="32">
+        <f>H12+H13</f>
+        <v>116110</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:12" ht="13.9">
-      <c r="B15" s="18"/>
-      <c r="H15" s="6"/>
+    <row r="15" spans="1:12" ht="15" customHeight="1">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="36">
+        <f>H11-H14</f>
+        <v>-259464.39999999997</v>
+      </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:12" ht="13.9">
+      <c r="B16" s="18"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="L16" s="6"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26202"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4680" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65227BA7-C9DA-4DB5-9A46-F95A39FB0DF6}"/>
+  <xr:revisionPtr revIDLastSave="4688" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE62CA4-7B4C-4A44-84FB-69A9627C3302}"/>
   <bookViews>
     <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="98">
   <si>
     <t>Name</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>DCC</t>
+  </si>
+  <si>
+    <t>SCCC</t>
   </si>
   <si>
     <t>February Exp</t>
@@ -219,9 +222,6 @@
   </si>
   <si>
     <t>Net Profit/Loss</t>
-  </si>
-  <si>
-    <t>SCCC</t>
   </si>
   <si>
     <t xml:space="preserve">SCC </t>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -2245,7 +2245,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2266,7 +2266,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2283,7 +2283,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H31" s="42">
         <f>H29+H30</f>
@@ -2377,7 +2377,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
       <c r="G36" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H36" s="39">
         <v>112000</v>
@@ -2397,7 +2397,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
       <c r="G37" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H37" s="43">
         <f>H35+H36</f>
@@ -2711,7 +2711,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2732,7 +2732,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2749,7 +2749,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="42">
         <f>H9+H10</f>
@@ -2843,7 +2843,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -2863,7 +2863,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H17" s="43">
         <f>H15+H16</f>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3305,7 +3305,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" s="44">
         <f>H3+H12</f>
@@ -3326,7 +3326,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3343,7 +3343,7 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H15" s="42">
         <f>H13+H14</f>
@@ -3437,7 +3437,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
       <c r="G20" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H20" s="39">
         <v>112000</v>
@@ -3457,7 +3457,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
       <c r="G21" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H21" s="43">
         <f>H19+H20</f>
@@ -3620,7 +3620,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3927,7 +3927,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -4120,7 +4120,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -4141,7 +4141,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -4158,7 +4158,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H22" s="42">
         <f>H20+H21</f>
@@ -4252,7 +4252,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H27" s="39">
         <v>112000</v>
@@ -4272,7 +4272,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
       <c r="G28" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H28" s="49">
         <f>H26+H27</f>
@@ -4321,7 +4321,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5674D68-3DFE-4CE9-AFD6-DD45A9A60264}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="5" bestFit="1" customWidth="1"/>
@@ -4438,7 +4438,7 @@
         <v>55875.97</v>
       </c>
       <c r="H4" s="32">
-        <f t="shared" ref="H4:H7" si="0">G4-E4</f>
+        <f t="shared" ref="H4:H8" si="0">G4-E4</f>
         <v>-7013.010000000002</v>
       </c>
       <c r="I4" s="15"/>
@@ -4558,49 +4558,64 @@
         <v>60116.55</v>
       </c>
       <c r="H8" s="32">
-        <f t="shared" ref="H8" si="1">G8-E8</f>
+        <f t="shared" si="0"/>
         <v>-34467.489999999991</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32">
-        <f>SUM(E4:E8)</f>
-        <v>457987.14999999997</v>
-      </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32">
-        <f>SUM(G4:G8)</f>
-        <v>395971.00999999995</v>
-      </c>
-      <c r="H9" s="34">
-        <f>SUM(H4:H8)</f>
-        <v>-62016.139999999985</v>
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="28">
+        <v>44970</v>
+      </c>
+      <c r="C9" s="29">
+        <v>1200</v>
+      </c>
+      <c r="D9" s="30">
+        <v>171</v>
+      </c>
+      <c r="E9" s="31">
+        <v>205654.49</v>
+      </c>
+      <c r="F9" s="30">
+        <v>158.5</v>
+      </c>
+      <c r="G9" s="31">
+        <v>189778.73</v>
+      </c>
+      <c r="H9" s="32">
+        <f t="shared" ref="H9" si="1">G9-E9</f>
+        <v>-15875.75999999998</v>
       </c>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="6"/>
+      <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1">
       <c r="A10" s="26"/>
       <c r="B10" s="28"/>
       <c r="C10" s="29"/>
       <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
+      <c r="E10" s="32">
+        <f>SUM(E4:E9)</f>
+        <v>663641.6399999999</v>
+      </c>
       <c r="F10" s="30"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32">
-        <v>-81338.25999999998</v>
+      <c r="G10" s="32">
+        <f>SUM(G4:G9)</f>
+        <v>585749.74</v>
+      </c>
+      <c r="H10" s="34">
+        <f>SUM(H4:H9)</f>
+        <v>-77891.899999999965</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
       <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1">
@@ -4611,9 +4626,8 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32"/>
-      <c r="H11" s="34">
-        <f>SUM(H2,H9,H10)</f>
-        <v>-143354.39999999997</v>
+      <c r="H11" s="32">
+        <v>-81338.25999999998</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -4626,11 +4640,10 @@
       <c r="D12" s="33"/>
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
-      <c r="G12" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="35">
-        <v>76110</v>
+      <c r="G12" s="32"/>
+      <c r="H12" s="34">
+        <f>SUM(H2,H10,H11)</f>
+        <v>-159230.15999999995</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
@@ -4644,10 +4657,10 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H13" s="35">
-        <v>40000</v>
+        <v>76110</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
@@ -4661,11 +4674,10 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="32">
-        <f>H12+H13</f>
-        <v>116110</v>
+        <v>24</v>
+      </c>
+      <c r="H14" s="35">
+        <v>40000</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
@@ -4679,22 +4691,40 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="36">
-        <f>H11-H14</f>
-        <v>-259464.39999999997</v>
+        <v>18</v>
+      </c>
+      <c r="H15" s="32">
+        <f>H13+H14</f>
+        <v>116110</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" ht="13.9">
-      <c r="B16" s="18"/>
-      <c r="H16" s="6"/>
+    <row r="16" spans="1:12" ht="15" customHeight="1">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="36">
+        <f>H12-H15</f>
+        <v>-275340.15999999992</v>
+      </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
       <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="2:12" ht="13.9">
+      <c r="B17" s="18"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="L17" s="6"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -4802,7 +4832,7 @@
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="28">
         <v>44617</v>
@@ -4832,7 +4862,7 @@
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="28">
         <v>44614</v>
@@ -4862,7 +4892,7 @@
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="28">
         <v>44594</v>
@@ -4892,7 +4922,7 @@
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="28">
         <v>44610</v>
@@ -4922,7 +4952,7 @@
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="28">
         <v>44606</v>
@@ -4952,7 +4982,7 @@
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="28">
         <v>44613</v>
@@ -4982,7 +5012,7 @@
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="28">
         <v>44616</v>
@@ -5012,7 +5042,7 @@
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="28">
         <v>44601</v>
@@ -5042,7 +5072,7 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="28">
         <v>44602</v>
@@ -5072,7 +5102,7 @@
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="28">
         <v>44603</v>
@@ -5102,7 +5132,7 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="28">
         <v>44593</v>
@@ -5132,7 +5162,7 @@
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="28">
         <v>44614</v>
@@ -5162,7 +5192,7 @@
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="28">
         <v>44601</v>
@@ -5192,7 +5222,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="28">
         <v>44620</v>
@@ -5222,7 +5252,7 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="28">
         <v>44620</v>
@@ -5252,7 +5282,7 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="28">
         <v>44595</v>
@@ -5282,7 +5312,7 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" s="28">
         <v>44617</v>
@@ -5312,7 +5342,7 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" s="28">
         <v>44613</v>
@@ -5342,7 +5372,7 @@
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="28">
         <v>44601</v>
@@ -5372,7 +5402,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="28">
         <v>44606</v>
@@ -5402,7 +5432,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="28">
         <v>44617</v>
@@ -5432,7 +5462,7 @@
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="28">
         <v>44607</v>
@@ -5462,7 +5492,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="28">
         <v>44609</v>
@@ -5492,7 +5522,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="28">
         <v>44615</v>
@@ -5599,7 +5629,7 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" s="37">
         <v>27160</v>
@@ -5713,7 +5743,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -5741,7 +5771,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -5769,7 +5799,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -5797,7 +5827,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -5825,7 +5855,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -5853,7 +5883,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -5894,7 +5924,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -5921,7 +5951,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -5948,7 +5978,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -5975,7 +6005,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6029,7 +6059,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6110,7 +6140,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6162,7 +6192,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6177,7 +6207,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6191,7 +6221,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6220,7 +6250,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6258,7 +6288,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6">
       <c r="G26" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H26" s="39">
         <v>112000</v>
@@ -6266,7 +6296,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6">
       <c r="G27" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H27" s="40">
         <f>H25+H26</f>
@@ -6337,7 +6367,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="B2" s="28">
         <v>44659</v>
@@ -6371,7 +6401,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6472,7 +6502,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6625,7 +6655,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -6691,7 +6721,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -6821,7 +6851,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -6842,7 +6872,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -6862,7 +6892,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -6965,7 +6995,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H24" s="39">
         <v>112000</v>
@@ -6985,7 +7015,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H25" s="40">
         <f>H23+H24</f>
@@ -7086,7 +7116,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7119,7 +7149,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7317,7 +7347,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7477,7 +7507,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7784,7 +7814,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -7850,7 +7880,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -7883,7 +7913,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -7949,7 +7979,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8048,7 +8078,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8081,7 +8111,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8114,7 +8144,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8147,7 +8177,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8211,7 +8241,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8232,7 +8262,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8252,7 +8282,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8355,7 +8385,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
       <c r="G44" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H44" s="39">
         <v>112000</v>
@@ -8375,7 +8405,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
       <c r="G45" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H45" s="40">
         <f>H43+H44</f>
@@ -8477,7 +8507,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8573,7 +8603,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8656,7 +8686,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -8722,7 +8752,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -8788,7 +8818,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -8854,7 +8884,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -8918,7 +8948,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -8939,7 +8969,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -8959,7 +8989,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9062,7 +9092,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H23" s="39">
         <v>112000</v>
@@ -9082,7 +9112,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
       <c r="G24" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H24" s="40">
         <f>H22+H23</f>
@@ -9296,7 +9326,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9329,7 +9359,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9390,7 +9420,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9411,7 +9441,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9428,7 +9458,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9522,7 +9552,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="39">
         <v>112000</v>
@@ -9542,7 +9572,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
       <c r="G17" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H17" s="40">
         <f>H15+H16</f>
@@ -9761,7 +9791,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -9822,7 +9852,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H8" s="42">
         <f>H4+H7</f>
@@ -9843,7 +9873,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -9860,7 +9890,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="42">
         <f>H8+H9</f>
@@ -9954,7 +9984,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H15" s="39">
         <v>112000</v>
@@ -9974,7 +10004,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H16" s="43">
         <f>H14+H15</f>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26307"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4688" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE62CA4-7B4C-4A44-84FB-69A9627C3302}"/>
+  <xr:revisionPtr revIDLastSave="4730" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA723DD9-A40C-49EE-8801-738135D873B5}"/>
   <bookViews>
-    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8076" yWindow="1416" windowWidth="13908" windowHeight="9516" tabRatio="445" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JAN23" sheetId="58" r:id="rId1"/>
     <sheet name="FEB23" sheetId="59" r:id="rId2"/>
-    <sheet name="FEB22" sheetId="39" r:id="rId3"/>
+    <sheet name="MAR23" sheetId="60" r:id="rId3"/>
     <sheet name="MAR22" sheetId="40" r:id="rId4"/>
     <sheet name="APR22" sheetId="41" r:id="rId5"/>
     <sheet name="MAY22" sheetId="50" r:id="rId6"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -122,55 +122,16 @@
     <t>February Exp</t>
   </si>
   <si>
-    <t>BGRIM</t>
-  </si>
-  <si>
-    <t>CKP</t>
-  </si>
-  <si>
-    <t>CLP</t>
-  </si>
-  <si>
     <t>DIF</t>
   </si>
   <si>
-    <t>EPG</t>
+    <t>GVREIT</t>
   </si>
   <si>
-    <t>GLOBAL</t>
+    <t>Div+Gain</t>
   </si>
   <si>
-    <t>IMH</t>
-  </si>
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>IVL</t>
-  </si>
-  <si>
-    <t>LPF</t>
-  </si>
-  <si>
-    <t>MCS</t>
-  </si>
-  <si>
-    <t>NOBLE</t>
-  </si>
-  <si>
-    <t>RATCH</t>
-  </si>
-  <si>
-    <t>TOP</t>
-  </si>
-  <si>
-    <t>TSE</t>
-  </si>
-  <si>
-    <t>TSTH</t>
-  </si>
-  <si>
-    <t>TU</t>
+    <t>March Exp</t>
   </si>
   <si>
     <t>CPNCG-DIV</t>
@@ -206,16 +167,10 @@
     <t>SIS</t>
   </si>
   <si>
-    <t>Div+Gain</t>
-  </si>
-  <si>
     <t>Carry Over</t>
   </si>
   <si>
     <t>Div+Gain+CO</t>
-  </si>
-  <si>
-    <t>March Exp</t>
   </si>
   <si>
     <t>Tax Refund</t>
@@ -237,6 +192,9 @@
   </si>
   <si>
     <t>JASIF</t>
+  </si>
+  <si>
+    <t>MCS</t>
   </si>
   <si>
     <t>PTT</t>
@@ -263,6 +221,9 @@
     <t>TPIPL</t>
   </si>
   <si>
+    <t>RATCH</t>
+  </si>
+  <si>
     <t>RCL</t>
   </si>
   <si>
@@ -281,13 +242,25 @@
     <t>HREIT</t>
   </si>
   <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>IVL</t>
+  </si>
+  <si>
     <t>May Exp</t>
   </si>
   <si>
     <t>WHART</t>
   </si>
   <si>
+    <t>TOP</t>
+  </si>
+  <si>
     <t>BDMS</t>
+  </si>
+  <si>
+    <t>GLOBAL</t>
   </si>
   <si>
     <t>TTB</t>
@@ -315,9 +288,6 @@
   </si>
   <si>
     <t>SYNEX</t>
-  </si>
-  <si>
-    <t>GVREIT</t>
   </si>
   <si>
     <t>BANPU</t>
@@ -450,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -506,7 +476,6 @@
     <xf numFmtId="188" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="190" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="188" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="188" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1397,7 +1366,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B2" s="28">
         <v>44806</v>
@@ -1409,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>0.28000000000000003</v>
       </c>
       <c r="G2" s="31">
@@ -1429,7 +1398,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B3" s="28">
         <v>44806</v>
@@ -1441,7 +1410,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="31"/>
-      <c r="F3" s="38">
+      <c r="F3" s="37">
         <v>1.75</v>
       </c>
       <c r="G3" s="31">
@@ -1461,7 +1430,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B4" s="28">
         <v>44806</v>
@@ -1473,7 +1442,7 @@
         <v>21</v>
       </c>
       <c r="E4" s="31"/>
-      <c r="F4" s="38">
+      <c r="F4" s="37">
         <v>0.1</v>
       </c>
       <c r="G4" s="31">
@@ -1493,7 +1462,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B5" s="28">
         <v>44806</v>
@@ -1505,7 +1474,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="31"/>
-      <c r="F5" s="38">
+      <c r="F5" s="37">
         <v>0.192</v>
       </c>
       <c r="G5" s="31">
@@ -1525,7 +1494,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B6" s="28">
         <v>44809</v>
@@ -1537,7 +1506,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="31"/>
-      <c r="F6" s="38">
+      <c r="F6" s="37">
         <v>0.26</v>
       </c>
       <c r="G6" s="31">
@@ -1557,7 +1526,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B7" s="28">
         <v>44809</v>
@@ -1569,7 +1538,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="31"/>
-      <c r="F7" s="38">
+      <c r="F7" s="37">
         <v>0.18</v>
       </c>
       <c r="G7" s="31">
@@ -1601,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="31"/>
-      <c r="F8" s="38">
+      <c r="F8" s="37">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G8" s="31">
@@ -1621,7 +1590,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B9" s="28">
         <v>44810</v>
@@ -1633,7 +1602,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="31"/>
-      <c r="F9" s="38">
+      <c r="F9" s="37">
         <v>0.23</v>
       </c>
       <c r="G9" s="31">
@@ -1665,7 +1634,7 @@
         <v>21</v>
       </c>
       <c r="E10" s="31"/>
-      <c r="F10" s="38">
+      <c r="F10" s="37">
         <v>0.18</v>
       </c>
       <c r="G10" s="31">
@@ -1685,7 +1654,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B11" s="28">
         <v>44811</v>
@@ -1697,7 +1666,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="31"/>
-      <c r="F11" s="38">
+      <c r="F11" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G11" s="31">
@@ -1729,7 +1698,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="31"/>
-      <c r="F12" s="38">
+      <c r="F12" s="37">
         <v>1</v>
       </c>
       <c r="G12" s="31">
@@ -1748,7 +1717,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B13" s="28">
         <v>44813</v>
@@ -1760,7 +1729,7 @@
         <v>21</v>
       </c>
       <c r="E13" s="31"/>
-      <c r="F13" s="38">
+      <c r="F13" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G13" s="31">
@@ -1792,7 +1761,7 @@
         <v>21</v>
       </c>
       <c r="E14" s="31"/>
-      <c r="F14" s="38">
+      <c r="F14" s="37">
         <v>1</v>
       </c>
       <c r="G14" s="31">
@@ -1811,7 +1780,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B15" s="28">
         <v>44813</v>
@@ -1823,7 +1792,7 @@
         <v>21</v>
       </c>
       <c r="E15" s="31"/>
-      <c r="F15" s="38">
+      <c r="F15" s="37">
         <v>0.12692000000000001</v>
       </c>
       <c r="G15" s="31">
@@ -1842,7 +1811,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B16" s="28">
         <v>44813</v>
@@ -1854,7 +1823,7 @@
         <v>21</v>
       </c>
       <c r="E16" s="31"/>
-      <c r="F16" s="38">
+      <c r="F16" s="37">
         <v>0.15</v>
       </c>
       <c r="G16" s="31">
@@ -1874,7 +1843,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B17" s="28">
         <v>44817</v>
@@ -1886,7 +1855,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="31"/>
-      <c r="F17" s="38">
+      <c r="F17" s="37">
         <v>0.15</v>
       </c>
       <c r="G17" s="31">
@@ -1906,7 +1875,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B18" s="28">
         <v>44818</v>
@@ -1918,7 +1887,7 @@
         <v>21</v>
       </c>
       <c r="E18" s="31"/>
-      <c r="F18" s="38">
+      <c r="F18" s="37">
         <v>0.4</v>
       </c>
       <c r="G18" s="31">
@@ -1938,7 +1907,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="27" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="B19" s="28">
         <v>44818</v>
@@ -1950,7 +1919,7 @@
         <v>21</v>
       </c>
       <c r="E19" s="31"/>
-      <c r="F19" s="38">
+      <c r="F19" s="37">
         <v>0.20100000000000001</v>
       </c>
       <c r="G19" s="31">
@@ -1970,7 +1939,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A20" s="27" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B20" s="28">
         <v>44819</v>
@@ -1982,7 +1951,7 @@
         <v>21</v>
       </c>
       <c r="E20" s="31"/>
-      <c r="F20" s="38">
+      <c r="F20" s="37">
         <v>0.4</v>
       </c>
       <c r="G20" s="31">
@@ -2014,7 +1983,7 @@
         <v>21</v>
       </c>
       <c r="E21" s="31"/>
-      <c r="F21" s="38">
+      <c r="F21" s="37">
         <v>0.15559999999999999</v>
       </c>
       <c r="G21" s="31">
@@ -2046,7 +2015,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="31"/>
-      <c r="F22" s="38">
+      <c r="F22" s="37">
         <v>0.75</v>
       </c>
       <c r="G22" s="31">
@@ -2085,7 +2054,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B24" s="28">
         <v>44805</v>
@@ -2118,7 +2087,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B25" s="28">
         <v>44809</v>
@@ -2151,7 +2120,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B26" s="28">
         <v>44813</v>
@@ -2184,7 +2153,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B27" s="28">
         <v>44816</v>
@@ -2229,7 +2198,7 @@
         <f>SUM(G24:G27)</f>
         <v>350072.9</v>
       </c>
-      <c r="H28" s="44">
+      <c r="H28" s="43">
         <f>SUM(H24:H27)</f>
         <v>8317.6100000000079</v>
       </c>
@@ -2245,7 +2214,7 @@
       <c r="E29" s="32"/>
       <c r="F29" s="30"/>
       <c r="G29" s="32" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="H29" s="34">
         <f>H23+H28</f>
@@ -2266,7 +2235,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H30" s="32">
         <v>378717.68200000009</v>
@@ -2283,9 +2252,9 @@
       <c r="E31" s="32"/>
       <c r="F31" s="30"/>
       <c r="G31" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H31" s="42">
+        <v>41</v>
+      </c>
+      <c r="H31" s="41">
         <f>H29+H30</f>
         <v>551927.90200000012</v>
       </c>
@@ -2318,7 +2287,7 @@
       <c r="E33" s="32"/>
       <c r="F33" s="30"/>
       <c r="G33" s="32" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H33" s="35">
         <v>35345</v>
@@ -2337,7 +2306,7 @@
       <c r="G34" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="42">
+      <c r="H34" s="41">
         <f>H32+H33</f>
         <v>503685</v>
       </c>
@@ -2358,7 +2327,7 @@
       <c r="G35" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H35" s="46">
+      <c r="H35" s="45">
         <f>H31-H34</f>
         <v>48242.902000000118</v>
       </c>
@@ -2376,10 +2345,10 @@
       <c r="D36" s="9"/>
       <c r="E36" s="7"/>
       <c r="F36" s="10"/>
-      <c r="G36" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H36" s="39">
+      <c r="G36" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="38">
         <v>112000</v>
       </c>
       <c r="I36" s="11"/>
@@ -2396,10 +2365,10 @@
       <c r="D37" s="10"/>
       <c r="E37" s="14"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H37" s="43">
+      <c r="G37" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H37" s="42">
         <f>H35+H36</f>
         <v>160242.90200000012</v>
       </c>
@@ -2500,7 +2469,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2512,7 +2481,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>1.3</v>
       </c>
       <c r="G2" s="31">
@@ -2551,7 +2520,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B4" s="28">
         <v>44840</v>
@@ -2571,7 +2540,7 @@
       <c r="G4" s="31">
         <v>156028.64000000001</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="40">
         <f>G4-E4</f>
         <v>-10840.149999999994</v>
       </c>
@@ -2584,7 +2553,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B5" s="28">
         <v>44853</v>
@@ -2604,7 +2573,7 @@
       <c r="G5" s="31">
         <v>87555.65</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="40">
         <f>G5-E5</f>
         <v>4121.2599999999948</v>
       </c>
@@ -2617,7 +2586,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B6" s="28">
         <v>44860</v>
@@ -2637,7 +2606,7 @@
       <c r="G6" s="31">
         <v>55077.74</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="40">
         <f>G6-E6</f>
         <v>-6558.4800000000032</v>
       </c>
@@ -2670,7 +2639,7 @@
       <c r="G7" s="31">
         <v>130210.95</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="40">
         <f>G7-E7</f>
         <v>-23879.590000000011</v>
       </c>
@@ -2695,7 +2664,7 @@
         <f>SUM(G4:G7)</f>
         <v>428872.98000000004</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="40">
         <f>SUM(H4:H7)</f>
         <v>-37156.960000000014</v>
       </c>
@@ -2711,7 +2680,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -2732,7 +2701,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H10" s="32">
         <v>551927.90200000012</v>
@@ -2749,9 +2718,9 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="42">
+        <v>41</v>
+      </c>
+      <c r="H11" s="41">
         <f>H9+H10</f>
         <v>520035.9420000001</v>
       </c>
@@ -2784,7 +2753,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H13" s="35">
         <v>71130</v>
@@ -2803,7 +2772,7 @@
       <c r="G14" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="41">
         <f>H12+H13</f>
         <v>574815</v>
       </c>
@@ -2824,7 +2793,7 @@
       <c r="G15" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="46">
+      <c r="H15" s="45">
         <f>H11-H14</f>
         <v>-54779.057999999903</v>
       </c>
@@ -2842,10 +2811,10 @@
       <c r="D16" s="9"/>
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="39">
+      <c r="G16" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="38">
         <v>112000</v>
       </c>
       <c r="I16" s="11"/>
@@ -2862,10 +2831,10 @@
       <c r="D17" s="10"/>
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" s="43">
+      <c r="G17" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="42">
         <f>H15+H16</f>
         <v>57220.942000000097</v>
       </c>
@@ -2962,7 +2931,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -2974,7 +2943,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>1.3</v>
       </c>
       <c r="G2" s="31">
@@ -3079,7 +3048,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B6" s="28">
         <v>44867</v>
@@ -3112,7 +3081,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B7" s="28">
         <v>44872</v>
@@ -3145,7 +3114,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B8" s="28">
         <v>44873</v>
@@ -3178,7 +3147,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B9" s="28">
         <v>44880</v>
@@ -3211,7 +3180,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B10" s="28">
         <v>44886</v>
@@ -3244,7 +3213,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B11" s="28">
         <v>44887</v>
@@ -3305,9 +3274,9 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="44">
+        <v>27</v>
+      </c>
+      <c r="H13" s="43">
         <f>H3+H12</f>
         <v>-104006.85000000002</v>
       </c>
@@ -3326,7 +3295,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="30"/>
       <c r="G14" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H14" s="32">
         <v>520035.9420000001</v>
@@ -3343,9 +3312,9 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="42">
+        <v>41</v>
+      </c>
+      <c r="H15" s="41">
         <f>H13+H14</f>
         <v>416029.09200000006</v>
       </c>
@@ -3378,7 +3347,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H17" s="35">
         <v>37950</v>
@@ -3397,7 +3366,7 @@
       <c r="G18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="41">
         <f>H16+H17</f>
         <v>612765</v>
       </c>
@@ -3418,7 +3387,7 @@
       <c r="G19" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="46">
+      <c r="H19" s="45">
         <f>H15-H18</f>
         <v>-196735.90799999994</v>
       </c>
@@ -3436,10 +3405,10 @@
       <c r="D20" s="9"/>
       <c r="E20" s="7"/>
       <c r="F20" s="10"/>
-      <c r="G20" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" s="39">
+      <c r="G20" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="38">
         <v>112000</v>
       </c>
       <c r="I20" s="11"/>
@@ -3456,10 +3425,10 @@
       <c r="D21" s="10"/>
       <c r="E21" s="14"/>
       <c r="F21" s="10"/>
-      <c r="G21" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="43">
+      <c r="G21" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="42">
         <f>H19+H20</f>
         <v>-84735.907999999938</v>
       </c>
@@ -3556,7 +3525,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B2" s="28">
         <v>44897</v>
@@ -3568,7 +3537,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>0.3</v>
       </c>
       <c r="G2" s="31">
@@ -3600,7 +3569,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="31"/>
-      <c r="F3" s="38">
+      <c r="F3" s="37">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G3" s="31">
@@ -3620,7 +3589,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B4" s="28">
         <v>44901</v>
@@ -3632,7 +3601,7 @@
         <v>21</v>
       </c>
       <c r="E4" s="31"/>
-      <c r="F4" s="38">
+      <c r="F4" s="37">
         <v>0.26</v>
       </c>
       <c r="G4" s="31">
@@ -3652,7 +3621,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B5" s="28">
         <v>44903</v>
@@ -3664,7 +3633,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="31"/>
-      <c r="F5" s="38">
+      <c r="F5" s="37">
         <v>0.23</v>
       </c>
       <c r="G5" s="31">
@@ -3684,7 +3653,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B6" s="28">
         <v>44904</v>
@@ -3696,7 +3665,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="31"/>
-      <c r="F6" s="38">
+      <c r="F6" s="37">
         <v>2.25</v>
       </c>
       <c r="G6" s="31">
@@ -3715,7 +3684,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B7" s="28">
         <v>44908</v>
@@ -3727,7 +3696,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="31"/>
-      <c r="F7" s="38">
+      <c r="F7" s="37">
         <v>0.25530000000000003</v>
       </c>
       <c r="G7" s="31">
@@ -3759,7 +3728,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="31"/>
-      <c r="F8" s="38">
+      <c r="F8" s="37">
         <v>0.18940000000000001</v>
       </c>
       <c r="G8" s="31">
@@ -3779,7 +3748,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B9" s="28">
         <v>44910</v>
@@ -3791,7 +3760,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="31"/>
-      <c r="F9" s="38">
+      <c r="F9" s="37">
         <v>0.4</v>
       </c>
       <c r="G9" s="31">
@@ -3811,7 +3780,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="B10" s="28">
         <v>44918</v>
@@ -3823,7 +3792,7 @@
         <v>21</v>
       </c>
       <c r="E10" s="31"/>
-      <c r="F10" s="38">
+      <c r="F10" s="37">
         <v>0.19109999999999999</v>
       </c>
       <c r="G10" s="31">
@@ -3843,7 +3812,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B11" s="28">
         <v>44923</v>
@@ -3855,7 +3824,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="31"/>
-      <c r="F11" s="38">
+      <c r="F11" s="37">
         <v>0.1003</v>
       </c>
       <c r="G11" s="31">
@@ -3927,7 +3896,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B14" s="28">
         <v>44918</v>
@@ -4026,7 +3995,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B17" s="28">
         <v>44923</v>
@@ -4059,7 +4028,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B18" s="28">
         <v>44925</v>
@@ -4104,7 +4073,7 @@
         <f>SUM(G13:G18)</f>
         <v>384686.06</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="40">
         <f>SUM(H13:H18)</f>
         <v>-72223.72000000003</v>
       </c>
@@ -4120,7 +4089,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="H20" s="34">
         <f>H12+H19</f>
@@ -4141,7 +4110,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H21" s="32">
         <v>416029.09200000006</v>
@@ -4158,9 +4127,9 @@
       <c r="E22" s="32"/>
       <c r="F22" s="30"/>
       <c r="G22" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="42">
+        <v>41</v>
+      </c>
+      <c r="H22" s="41">
         <f>H20+H21</f>
         <v>459673.67200000002</v>
       </c>
@@ -4193,7 +4162,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="30"/>
       <c r="G24" s="32" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="H24" s="35">
         <v>29530</v>
@@ -4212,7 +4181,7 @@
       <c r="G25" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="42">
+      <c r="H25" s="41">
         <f>H23+H24</f>
         <v>642295</v>
       </c>
@@ -4251,10 +4220,10 @@
       <c r="D27" s="9"/>
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
-      <c r="G27" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H27" s="39">
+      <c r="G27" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="38">
         <v>112000</v>
       </c>
       <c r="I27" s="11"/>
@@ -4271,10 +4240,10 @@
       <c r="D28" s="10"/>
       <c r="E28" s="14"/>
       <c r="F28" s="10"/>
-      <c r="G28" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H28" s="49">
+      <c r="G28" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="48">
         <f>H26+H27</f>
         <v>-70621.32799999998</v>
       </c>
@@ -4677,7 +4646,7 @@
         <v>24</v>
       </c>
       <c r="H14" s="35">
-        <v>40000</v>
+        <v>63980</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
@@ -4695,7 +4664,7 @@
       </c>
       <c r="H15" s="32">
         <f>H13+H14</f>
-        <v>116110</v>
+        <v>140090</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
@@ -4713,7 +4682,7 @@
       </c>
       <c r="H16" s="36">
         <f>H12-H15</f>
-        <v>-275340.15999999992</v>
+        <v>-299320.15999999992</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
@@ -4735,9 +4704,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EA11ED3-C20C-4156-9EBA-059780905D86}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" style="12" customWidth="1"/>
@@ -4757,7 +4726,7 @@
     <col min="16" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4786,15 +4755,15 @@
       <c r="J1" s="16"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" s="28">
-        <v>44607</v>
+        <v>44992</v>
       </c>
       <c r="C2" s="29">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>21</v>
@@ -4803,891 +4772,247 @@
         <v>21</v>
       </c>
       <c r="F2" s="30">
-        <v>0.1719</v>
+        <v>0.2535</v>
       </c>
       <c r="G2" s="31">
         <f>C2*F2</f>
-        <v>1719</v>
+        <v>10140</v>
       </c>
       <c r="H2" s="32">
         <f>G2*0.9</f>
-        <v>1547.1000000000001</v>
+        <v>9126</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32"/>
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="28">
+        <v>44995</v>
+      </c>
+      <c r="C3" s="29">
+        <v>40000</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="30">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="G3" s="31">
+        <f>C3*F3</f>
+        <v>7920</v>
+      </c>
+      <c r="H3" s="32">
+        <f>G3*0.9</f>
+        <v>7128</v>
+      </c>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="28">
-        <v>44617</v>
-      </c>
-      <c r="C4" s="29">
-        <v>9000</v>
-      </c>
-      <c r="D4" s="30">
-        <v>40</v>
-      </c>
-      <c r="E4" s="31">
-        <v>360797.36</v>
-      </c>
-      <c r="F4" s="30">
-        <v>33</v>
-      </c>
-      <c r="G4" s="31">
-        <v>296342.17</v>
-      </c>
-      <c r="H4" s="41">
-        <f>G4-E4</f>
-        <v>-64455.19</v>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32">
+        <f>SUM(H2:H3)</f>
+        <v>16254</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="28">
-        <v>44614</v>
+        <v>44992</v>
       </c>
       <c r="C5" s="29">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="D5" s="30">
-        <v>5</v>
+        <v>14.7</v>
       </c>
       <c r="E5" s="31">
-        <v>100221.49</v>
+        <v>147325.59</v>
       </c>
       <c r="F5" s="30">
-        <v>5.0999999999999996</v>
+        <v>13.3</v>
       </c>
       <c r="G5" s="31">
-        <v>101774.08</v>
-      </c>
-      <c r="H5" s="41">
-        <f>G5-E5</f>
-        <v>1552.5899999999965</v>
+        <v>132705.42000000001</v>
+      </c>
+      <c r="H5" s="32">
+        <f t="shared" ref="H5" si="0">G5-E5</f>
+        <v>-14620.169999999984</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="28">
-        <v>44594</v>
-      </c>
-      <c r="C6" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D6" s="30">
-        <v>5</v>
-      </c>
-      <c r="E6" s="31">
-        <v>50110.75</v>
-      </c>
-      <c r="F6" s="30">
-        <v>5.5</v>
-      </c>
-      <c r="G6" s="31">
-        <v>54878.18</v>
-      </c>
-      <c r="H6" s="41">
-        <f>G6-E6</f>
-        <v>4767.43</v>
+    <row r="6" spans="1:12" ht="15" customHeight="1">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32">
+        <f>SUM(E5:E5)</f>
+        <v>147325.59</v>
+      </c>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32">
+        <f t="shared" ref="G6:H6" si="1">SUM(G5:G5)</f>
+        <v>132705.42000000001</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" si="1"/>
+        <v>-14620.169999999984</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="28">
-        <v>44610</v>
-      </c>
-      <c r="C7" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D7" s="30">
-        <v>14.7</v>
-      </c>
-      <c r="E7" s="31">
-        <v>147325.59</v>
-      </c>
-      <c r="F7" s="30">
-        <v>14.3</v>
-      </c>
-      <c r="G7" s="31">
-        <v>142683.26999999999</v>
-      </c>
-      <c r="H7" s="41">
-        <f>G7-E7</f>
-        <v>-4642.320000000007</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="28">
-        <v>44606</v>
-      </c>
-      <c r="C8" s="29">
-        <v>24000</v>
-      </c>
-      <c r="D8" s="30">
-        <v>10.9</v>
-      </c>
-      <c r="E8" s="31">
-        <v>262179.42</v>
-      </c>
-      <c r="F8" s="30">
-        <v>10.3</v>
-      </c>
-      <c r="G8" s="31">
-        <v>246652.48</v>
-      </c>
-      <c r="H8" s="41">
-        <f>G8-E8</f>
-        <v>-15526.939999999973</v>
+      <c r="K6" s="15"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.6">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="34">
+        <f>H4+H6</f>
+        <v>1633.8300000000163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32">
+        <v>-159230.15999999995</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="28">
-        <v>44613</v>
-      </c>
-      <c r="C9" s="29">
-        <v>5000</v>
-      </c>
-      <c r="D9" s="30">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="E9" s="31">
-        <v>97214.85</v>
-      </c>
-      <c r="F9" s="30">
-        <v>21</v>
-      </c>
-      <c r="G9" s="31">
-        <v>104767.44</v>
-      </c>
-      <c r="H9" s="41">
-        <f>G9-E9</f>
-        <v>7552.5899999999965</v>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="34">
+        <f>SUM(H7,H8)</f>
+        <v>-157596.32999999993</v>
       </c>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="28">
-        <v>44616</v>
-      </c>
-      <c r="C10" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D10" s="30">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="E10" s="31">
-        <v>194429.69</v>
-      </c>
-      <c r="F10" s="30">
-        <v>21</v>
-      </c>
-      <c r="G10" s="31">
-        <v>209534.87</v>
-      </c>
-      <c r="H10" s="41">
-        <f>G10-E10</f>
-        <v>15105.179999999993</v>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="35">
+        <v>140090</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="28">
-        <v>44601</v>
-      </c>
-      <c r="C11" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D11" s="30">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E11" s="31">
-        <v>52916.95</v>
-      </c>
-      <c r="F11" s="30">
-        <v>20.7</v>
-      </c>
-      <c r="G11" s="31">
-        <v>61962.45</v>
-      </c>
-      <c r="H11" s="41">
-        <f>G11-E11</f>
-        <v>9045.5</v>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="35">
+        <v>40000</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="28">
-        <v>44602</v>
-      </c>
-      <c r="C12" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D12" s="30">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E12" s="31">
-        <v>52916.95</v>
-      </c>
-      <c r="F12" s="30">
-        <v>21.1</v>
-      </c>
-      <c r="G12" s="31">
-        <v>63159.8</v>
-      </c>
-      <c r="H12" s="41">
-        <f>G12-E12</f>
-        <v>10242.850000000006</v>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="32">
+        <f>H10+H11</f>
+        <v>180090</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="28">
-        <v>44603</v>
-      </c>
-      <c r="C13" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D13" s="30">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E13" s="31">
-        <v>52916.95</v>
-      </c>
-      <c r="F13" s="30">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="G13" s="31">
-        <v>55077.74</v>
-      </c>
-      <c r="H13" s="41">
-        <f>G13-E13</f>
-        <v>2160.7900000000009</v>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="36">
+        <f>H9-H12</f>
+        <v>-337686.32999999996</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="28">
-        <v>44593</v>
-      </c>
-      <c r="C14" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D14" s="30">
-        <v>20.2</v>
-      </c>
-      <c r="E14" s="31">
-        <v>60734.22</v>
-      </c>
-      <c r="F14" s="30">
-        <v>22</v>
-      </c>
-      <c r="G14" s="31">
-        <v>65853.820000000007</v>
-      </c>
-      <c r="H14" s="41">
-        <f>G14-E14</f>
-        <v>5119.6000000000058</v>
-      </c>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" ht="13.9">
+      <c r="B14" s="18"/>
+      <c r="H14" s="6"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="28">
-        <v>44614</v>
-      </c>
-      <c r="C15" s="29">
-        <v>1200</v>
-      </c>
-      <c r="D15" s="30">
-        <v>42</v>
-      </c>
-      <c r="E15" s="31">
-        <v>50511.63</v>
-      </c>
-      <c r="F15" s="30">
-        <v>46</v>
-      </c>
-      <c r="G15" s="31">
-        <v>55077.74</v>
-      </c>
-      <c r="H15" s="41">
-        <f>G15-E15</f>
-        <v>4566.1100000000006</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="28">
-        <v>44601</v>
-      </c>
-      <c r="C16" s="29">
-        <v>1200</v>
-      </c>
-      <c r="D16" s="30">
-        <v>42</v>
-      </c>
-      <c r="E16" s="31">
-        <v>50511.63</v>
-      </c>
-      <c r="F16" s="30">
-        <v>50.5</v>
-      </c>
-      <c r="G16" s="31">
-        <v>60465.78</v>
-      </c>
-      <c r="H16" s="41">
-        <f>G16-E16</f>
-        <v>9954.1500000000015</v>
-      </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="28">
-        <v>44620</v>
-      </c>
-      <c r="C17" s="29">
-        <v>3600</v>
-      </c>
-      <c r="D17" s="30">
-        <v>42</v>
-      </c>
-      <c r="E17" s="31">
-        <v>151534.89000000001</v>
-      </c>
-      <c r="F17" s="30">
-        <v>45.5</v>
-      </c>
-      <c r="G17" s="31">
-        <v>163437.20000000001</v>
-      </c>
-      <c r="H17" s="41">
-        <f>G17-E17</f>
-        <v>11902.309999999998</v>
-      </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="28">
-        <v>44620</v>
-      </c>
-      <c r="C18" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D18" s="30">
-        <v>14</v>
-      </c>
-      <c r="E18" s="31">
-        <v>140310.09</v>
-      </c>
-      <c r="F18" s="30">
-        <v>14.1</v>
-      </c>
-      <c r="G18" s="31">
-        <v>140687.70000000001</v>
-      </c>
-      <c r="H18" s="41">
-        <f>G18-E18</f>
-        <v>377.61000000001513</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="28">
-        <v>44595</v>
-      </c>
-      <c r="C19" s="29">
-        <v>5000</v>
-      </c>
-      <c r="D19" s="30">
-        <v>16.7</v>
-      </c>
-      <c r="E19" s="31">
-        <v>83684.95</v>
-      </c>
-      <c r="F19" s="30">
-        <v>14.7</v>
-      </c>
-      <c r="G19" s="31">
-        <v>73337.2</v>
-      </c>
-      <c r="H19" s="41">
-        <f>G19-E19</f>
-        <v>-10347.75</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="28">
-        <v>44617</v>
-      </c>
-      <c r="C20" s="29">
-        <v>63000</v>
-      </c>
-      <c r="D20" s="30">
-        <v>7</v>
-      </c>
-      <c r="E20" s="31">
-        <v>441976.77</v>
-      </c>
-      <c r="F20" s="30">
-        <v>6</v>
-      </c>
-      <c r="G20" s="31">
-        <v>377162.77</v>
-      </c>
-      <c r="H20" s="41">
-        <f>G20-E20</f>
-        <v>-64814</v>
-      </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A21" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="28">
-        <v>44613</v>
-      </c>
-      <c r="C21" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D21" s="30">
-        <v>45.75</v>
-      </c>
-      <c r="E21" s="31">
-        <v>137554</v>
-      </c>
-      <c r="F21" s="30">
-        <v>46</v>
-      </c>
-      <c r="G21" s="31">
-        <v>137694.34</v>
-      </c>
-      <c r="H21" s="41">
-        <f>G21-E21</f>
-        <v>140.33999999999651</v>
-      </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A22" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="28">
-        <v>44601</v>
-      </c>
-      <c r="C22" s="29">
-        <v>2000</v>
-      </c>
-      <c r="D22" s="30">
-        <v>50.5</v>
-      </c>
-      <c r="E22" s="31">
-        <v>101223.7</v>
-      </c>
-      <c r="F22" s="30">
-        <v>54</v>
-      </c>
-      <c r="G22" s="31">
-        <v>107760.79</v>
-      </c>
-      <c r="H22" s="41">
-        <f>G22-E22</f>
-        <v>6537.0899999999965</v>
-      </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="28">
-        <v>44606</v>
-      </c>
-      <c r="C23" s="29">
-        <v>2000</v>
-      </c>
-      <c r="D23" s="30">
-        <v>50.5</v>
-      </c>
-      <c r="E23" s="31">
-        <v>101223.7</v>
-      </c>
-      <c r="F23" s="30">
-        <v>53.75</v>
-      </c>
-      <c r="G23" s="31">
-        <v>107261.89</v>
-      </c>
-      <c r="H23" s="41">
-        <f>G23-E23</f>
-        <v>6038.1900000000023</v>
-      </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="6"/>
-    </row>
-    <row r="24" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="28">
-        <v>44617</v>
-      </c>
-      <c r="C24" s="29">
-        <v>40000</v>
-      </c>
-      <c r="D24" s="30">
-        <v>2.6</v>
-      </c>
-      <c r="E24" s="31">
-        <v>104230.35</v>
-      </c>
-      <c r="F24" s="30">
-        <v>2.5</v>
-      </c>
-      <c r="G24" s="31">
-        <v>99778.51</v>
-      </c>
-      <c r="H24" s="41">
-        <f>G24-E24</f>
-        <v>-4451.8400000000111</v>
-      </c>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="28">
-        <v>44607</v>
-      </c>
-      <c r="C25" s="29">
-        <v>64700</v>
-      </c>
-      <c r="D25" s="30">
-        <v>1.5</v>
-      </c>
-      <c r="E25" s="31">
-        <v>97264.95</v>
-      </c>
-      <c r="F25" s="30">
-        <v>1.43</v>
-      </c>
-      <c r="G25" s="31">
-        <v>92316.07</v>
-      </c>
-      <c r="H25" s="41">
-        <f>G25-E25</f>
-        <v>-4948.8799999999901</v>
-      </c>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="28">
-        <v>44609</v>
-      </c>
-      <c r="C26" s="29">
-        <v>10300</v>
-      </c>
-      <c r="D26" s="30">
-        <v>1.5</v>
-      </c>
-      <c r="E26" s="31">
-        <v>15484.22</v>
-      </c>
-      <c r="F26" s="30">
-        <v>1.43</v>
-      </c>
-      <c r="G26" s="31">
-        <v>14696.38</v>
-      </c>
-      <c r="H26" s="41">
-        <f>G26-E26</f>
-        <v>-787.84000000000015</v>
-      </c>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="28">
-        <v>44615</v>
-      </c>
-      <c r="C27" s="29">
-        <v>18000</v>
-      </c>
-      <c r="D27" s="30">
-        <v>20.8</v>
-      </c>
-      <c r="E27" s="31">
-        <v>375229.26</v>
-      </c>
-      <c r="F27" s="30">
-        <v>20.5</v>
-      </c>
-      <c r="G27" s="31">
-        <v>368182.7</v>
-      </c>
-      <c r="H27" s="41">
-        <f>G27-E27</f>
-        <v>-7046.5599999999977</v>
-      </c>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32">
-        <f>SUM(E4:E27)</f>
-        <v>3282504.3600000003</v>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="32">
-        <f t="shared" ref="G28" si="0">SUM(G4:G27)</f>
-        <v>3200545.3699999992</v>
-      </c>
-      <c r="H28" s="44">
-        <f>SUM(H4:H27)</f>
-        <v>-81958.989999999976</v>
-      </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32">
-        <v>117432.48000000004</v>
-      </c>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="L29" s="6"/>
-    </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="34">
-        <f>SUM(H2,H28,H29)</f>
-        <v>37020.590000000069</v>
-      </c>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="L30" s="6"/>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1">
-      <c r="A31" s="26"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" s="35">
-        <v>62710</v>
-      </c>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="37">
-        <v>27160</v>
-      </c>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="L32" s="6"/>
-    </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1">
-      <c r="A33" s="26"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="32">
-        <f>H31+H32</f>
-        <v>89870</v>
-      </c>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1">
-      <c r="A34" s="26"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="36">
-        <f>H30-H33</f>
-        <v>-52849.409999999931</v>
-      </c>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="B35" s="18"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="L35" s="6"/>
+      <c r="L14" s="6"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:O27">
-    <sortCondition ref="A4:A27"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
@@ -5743,7 +5068,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="27" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B2" s="28">
         <v>44624</v>
@@ -5757,7 +5082,7 @@
       <c r="E2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>0.22220000000000001</v>
       </c>
       <c r="G2" s="31">
@@ -5771,7 +5096,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="27" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B3" s="28">
         <v>44624</v>
@@ -5785,7 +5110,7 @@
       <c r="E3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="37">
         <v>0.26100000000000001</v>
       </c>
       <c r="G3" s="31">
@@ -5799,7 +5124,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="27" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B4" s="28">
         <v>44641</v>
@@ -5813,7 +5138,7 @@
       <c r="E4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="37">
         <v>0.25</v>
       </c>
       <c r="G4" s="31">
@@ -5827,7 +5152,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="27" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B5" s="28">
         <v>44645</v>
@@ -5841,7 +5166,7 @@
       <c r="E5" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="37">
         <v>0.1195</v>
       </c>
       <c r="G5" s="31">
@@ -5855,7 +5180,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="27" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B6" s="28">
         <v>44648</v>
@@ -5869,7 +5194,7 @@
       <c r="E6" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="37">
         <v>0.221</v>
       </c>
       <c r="G6" s="31">
@@ -5883,7 +5208,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.6">
       <c r="A7" s="27" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B7" s="28">
         <v>44650</v>
@@ -5897,7 +5222,7 @@
       <c r="E7" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="37">
         <v>0.17380000000000001</v>
       </c>
       <c r="G7" s="31">
@@ -5924,7 +5249,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="27" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B9" s="28">
         <v>44621</v>
@@ -5951,7 +5276,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="27" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B10" s="28">
         <v>44622</v>
@@ -5978,7 +5303,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="27" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B11" s="28">
         <v>44623</v>
@@ -6005,7 +5330,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="27" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B12" s="28">
         <v>44629</v>
@@ -6059,7 +5384,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="27" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B14" s="28">
         <v>44630</v>
@@ -6140,7 +5465,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="27" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B17" s="28">
         <v>44651</v>
@@ -6179,7 +5504,7 @@
         <f>SUM(G9:G17)</f>
         <v>1070398.9000000001</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="43">
         <f>SUM(H9:H17)</f>
         <v>35536.859999999986</v>
       </c>
@@ -6192,7 +5517,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="H19" s="34">
         <f>H8+H18</f>
@@ -6207,7 +5532,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H20" s="32">
         <v>37020.590000000069</v>
@@ -6221,7 +5546,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H21" s="34">
         <f>H19+H20</f>
@@ -6250,7 +5575,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H23" s="35">
         <v>97220</v>
@@ -6281,24 +5606,24 @@
       <c r="G25" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="46">
+      <c r="H25" s="45">
         <f>H21-H24</f>
         <v>-58960.307999999946</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.6">
-      <c r="G26" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H26" s="39">
+      <c r="G26" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="38">
         <v>112000</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6">
-      <c r="G27" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H27" s="40">
+      <c r="G27" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" s="39">
         <f>H25+H26</f>
         <v>53039.692000000054</v>
       </c>
@@ -6381,14 +5706,14 @@
       <c r="E2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>9</v>
       </c>
       <c r="G2" s="31">
         <f t="shared" ref="G2:G7" si="0">C2*F2</f>
         <v>8100</v>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="40">
         <f>G2*0.9</f>
         <v>7290</v>
       </c>
@@ -6401,7 +5726,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B3" s="28">
         <v>44673</v>
@@ -6415,14 +5740,14 @@
       <c r="E3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="37">
         <v>0.86</v>
       </c>
       <c r="G3" s="31">
         <f t="shared" si="0"/>
         <v>5160</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="40">
         <v>4980</v>
       </c>
       <c r="I3" s="11"/>
@@ -6448,14 +5773,14 @@
       <c r="E4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="37">
         <v>1.75</v>
       </c>
       <c r="G4" s="31">
         <f t="shared" si="0"/>
         <v>15750</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="40">
         <f>G4*0.9</f>
         <v>14175</v>
       </c>
@@ -6468,7 +5793,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B5" s="28">
         <v>44677</v>
@@ -6482,7 +5807,7 @@
       <c r="E5" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="37">
         <v>10</v>
       </c>
       <c r="G5" s="31">
@@ -6502,7 +5827,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B6" s="28">
         <v>44678</v>
@@ -6516,7 +5841,7 @@
       <c r="E6" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="37">
         <v>0.45</v>
       </c>
       <c r="G6" s="31">
@@ -6536,7 +5861,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B7" s="28">
         <v>44680</v>
@@ -6550,7 +5875,7 @@
       <c r="E7" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="37">
         <v>0.8</v>
       </c>
       <c r="G7" s="31">
@@ -6589,7 +5914,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A9" s="27" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="28">
         <v>44669</v>
@@ -6609,7 +5934,7 @@
       <c r="G9" s="31">
         <v>126718.71</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="40">
         <f>G9-E9</f>
         <v>-3569.2299999999959</v>
       </c>
@@ -6622,7 +5947,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A10" s="27" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B10" s="28">
         <v>44669</v>
@@ -6642,7 +5967,7 @@
       <c r="G10" s="31">
         <v>241463.99</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="40">
         <f>G10-E10</f>
         <v>-7085.3099999999977</v>
       </c>
@@ -6655,7 +5980,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A11" s="27" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B11" s="28">
         <v>44671</v>
@@ -6675,7 +6000,7 @@
       <c r="G11" s="31">
         <v>53640.93</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="40">
         <f>G11-E11</f>
         <v>2407.6999999999971</v>
       </c>
@@ -6688,7 +6013,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A12" s="27" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B12" s="28">
         <v>44680</v>
@@ -6708,7 +6033,7 @@
       <c r="G12" s="31">
         <v>109756.36</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="40">
         <f>G12-E12</f>
         <v>-2491.7100000000064</v>
       </c>
@@ -6721,7 +6046,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A13" s="27" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B13" s="28">
         <v>44679</v>
@@ -6741,7 +6066,7 @@
       <c r="G13" s="31">
         <v>187084.7</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="40">
         <f>G13-E13</f>
         <v>5182.6900000000023</v>
       </c>
@@ -6754,7 +6079,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A14" s="27" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B14" s="28">
         <v>44652</v>
@@ -6774,7 +6099,7 @@
       <c r="G14" s="31">
         <v>115992.52</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="40">
         <f>G14-E14</f>
         <v>236.69000000000233</v>
       </c>
@@ -6787,7 +6112,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75">
       <c r="A15" s="27" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B15" s="28">
         <v>44673</v>
@@ -6807,7 +6132,7 @@
       <c r="G15" s="31">
         <v>202550.38</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="40">
         <f>G15-E15</f>
         <v>6116.2600000000093</v>
       </c>
@@ -6851,7 +6176,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="H17" s="34">
         <f>H8+H16</f>
@@ -6872,7 +6197,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H18" s="32">
         <v>128129.69200000005</v>
@@ -6892,7 +6217,7 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H19" s="34">
         <f>H17+H18</f>
@@ -6933,7 +6258,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="H21" s="35">
         <v>71150</v>
@@ -6976,7 +6301,7 @@
       <c r="G23" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="46">
+      <c r="H23" s="45">
         <f>H19-H22</f>
         <v>-84643.217999999935</v>
       </c>
@@ -6994,10 +6319,10 @@
       <c r="D24" s="9"/>
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
-      <c r="G24" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H24" s="39">
+      <c r="G24" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="38">
         <v>112000</v>
       </c>
       <c r="I24" s="11"/>
@@ -7014,10 +6339,10 @@
       <c r="D25" s="10"/>
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
-      <c r="G25" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H25" s="40">
+      <c r="G25" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="39">
         <f>H23+H24</f>
         <v>27356.782000000065</v>
       </c>
@@ -7116,7 +6441,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B2" s="28">
         <v>44686</v>
@@ -7130,7 +6455,7 @@
       <c r="E2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>0.5</v>
       </c>
       <c r="G2" s="31">
@@ -7149,7 +6474,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B3" s="28">
         <v>44686</v>
@@ -7163,7 +6488,7 @@
       <c r="E3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="37">
         <v>0.52</v>
       </c>
       <c r="G3" s="31">
@@ -7183,7 +6508,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B4" s="28">
         <v>44687</v>
@@ -7197,7 +6522,7 @@
       <c r="E4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="37">
         <v>0.36</v>
       </c>
       <c r="G4" s="31">
@@ -7231,7 +6556,7 @@
       <c r="E5" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="37">
         <v>0.65</v>
       </c>
       <c r="G5" s="31">
@@ -7250,7 +6575,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B6" s="28">
         <v>44687</v>
@@ -7264,7 +6589,7 @@
       <c r="E6" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="37">
         <v>0.7</v>
       </c>
       <c r="G6" s="31">
@@ -7296,7 +6621,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="31"/>
-      <c r="F7" s="38">
+      <c r="F7" s="37">
         <v>1</v>
       </c>
       <c r="G7" s="31">
@@ -7315,7 +6640,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B8" s="28">
         <v>44693</v>
@@ -7327,7 +6652,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="31"/>
-      <c r="F8" s="38">
+      <c r="F8" s="37">
         <v>0.75</v>
       </c>
       <c r="G8" s="31">
@@ -7347,7 +6672,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A9" s="27" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B9" s="28">
         <v>44694</v>
@@ -7359,7 +6684,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="31"/>
-      <c r="F9" s="38">
+      <c r="F9" s="37">
         <v>1.2</v>
       </c>
       <c r="G9" s="31">
@@ -7379,7 +6704,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B10" s="28">
         <v>44698</v>
@@ -7391,7 +6716,7 @@
         <v>21</v>
       </c>
       <c r="E10" s="31"/>
-      <c r="F10" s="38">
+      <c r="F10" s="37">
         <v>0.2</v>
       </c>
       <c r="G10" s="31">
@@ -7411,7 +6736,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B11" s="28">
         <v>44698</v>
@@ -7423,7 +6748,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="31"/>
-      <c r="F11" s="38">
+      <c r="F11" s="37">
         <v>0.06</v>
       </c>
       <c r="G11" s="31">
@@ -7455,7 +6780,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="31"/>
-      <c r="F12" s="38">
+      <c r="F12" s="37">
         <v>0.32</v>
       </c>
       <c r="G12" s="31">
@@ -7475,7 +6800,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B13" s="28">
         <v>44700</v>
@@ -7487,7 +6812,7 @@
         <v>21</v>
       </c>
       <c r="E13" s="31"/>
-      <c r="F13" s="38">
+      <c r="F13" s="37">
         <v>7.15</v>
       </c>
       <c r="G13" s="31">
@@ -7507,7 +6832,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B14" s="28">
         <v>44701</v>
@@ -7519,7 +6844,7 @@
         <v>21</v>
       </c>
       <c r="E14" s="31"/>
-      <c r="F14" s="38">
+      <c r="F14" s="37">
         <v>1.35</v>
       </c>
       <c r="G14" s="31">
@@ -7539,7 +6864,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A15" s="27" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B15" s="28">
         <v>44701</v>
@@ -7551,7 +6876,7 @@
         <v>21</v>
       </c>
       <c r="E15" s="31"/>
-      <c r="F15" s="38">
+      <c r="F15" s="37">
         <v>3</v>
       </c>
       <c r="G15" s="31">
@@ -7570,7 +6895,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A16" s="27" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B16" s="28">
         <v>44705</v>
@@ -7582,7 +6907,7 @@
         <v>21</v>
       </c>
       <c r="E16" s="31"/>
-      <c r="F16" s="38">
+      <c r="F16" s="37">
         <v>1</v>
       </c>
       <c r="G16" s="31">
@@ -7602,7 +6927,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A17" s="27" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B17" s="28">
         <v>44705</v>
@@ -7614,7 +6939,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="31"/>
-      <c r="F17" s="38">
+      <c r="F17" s="37">
         <v>0.42</v>
       </c>
       <c r="G17" s="31">
@@ -7634,7 +6959,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A18" s="27" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B18" s="28">
         <v>44705</v>
@@ -7646,7 +6971,7 @@
         <v>21</v>
       </c>
       <c r="E18" s="31"/>
-      <c r="F18" s="38">
+      <c r="F18" s="37">
         <v>1</v>
       </c>
       <c r="G18" s="31">
@@ -7666,7 +6991,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A19" s="27" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B19" s="28">
         <v>44706</v>
@@ -7678,7 +7003,7 @@
         <v>21</v>
       </c>
       <c r="E19" s="31"/>
-      <c r="F19" s="38">
+      <c r="F19" s="37">
         <v>0.211477</v>
       </c>
       <c r="G19" s="31">
@@ -7709,7 +7034,7 @@
         <v>21</v>
       </c>
       <c r="E20" s="31"/>
-      <c r="F20" s="38">
+      <c r="F20" s="37">
         <v>5.5E-2</v>
       </c>
       <c r="G20" s="31">
@@ -7748,7 +7073,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A22" s="27" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B22" s="28">
         <v>44684</v>
@@ -7781,7 +7106,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A23" s="27" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B23" s="28">
         <v>44687</v>
@@ -7814,7 +7139,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A24" s="27" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B24" s="28">
         <v>44691</v>
@@ -7847,7 +7172,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A25" s="27" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B25" s="28">
         <v>44692</v>
@@ -7880,7 +7205,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A26" s="27" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B26" s="28">
         <v>44693</v>
@@ -7913,7 +7238,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A27" s="27" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B27" s="28">
         <v>44694</v>
@@ -7946,7 +7271,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A28" s="27" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B28" s="28">
         <v>44698</v>
@@ -7979,7 +7304,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A29" s="27" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B29" s="28">
         <v>44698</v>
@@ -8012,7 +7337,7 @@
     </row>
     <row r="30" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A30" s="27" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B30" s="28">
         <v>44704</v>
@@ -8045,7 +7370,7 @@
     </row>
     <row r="31" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A31" s="27" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B31" s="28">
         <v>44704</v>
@@ -8078,7 +7403,7 @@
     </row>
     <row r="32" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A32" s="27" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B32" s="28">
         <v>44707</v>
@@ -8111,7 +7436,7 @@
     </row>
     <row r="33" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A33" s="27" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B33" s="28">
         <v>44707</v>
@@ -8144,7 +7469,7 @@
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A34" s="27" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B34" s="28">
         <v>44711</v>
@@ -8177,7 +7502,7 @@
     </row>
     <row r="35" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A35" s="27" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B35" s="28">
         <v>44712</v>
@@ -8222,7 +7547,7 @@
         <f>SUM(G22:G35)</f>
         <v>1406427.98</v>
       </c>
-      <c r="H36" s="45">
+      <c r="H36" s="44">
         <f>SUM(H22:H35)</f>
         <v>-44273.119999999959</v>
       </c>
@@ -8241,7 +7566,7 @@
       <c r="E37" s="32"/>
       <c r="F37" s="30"/>
       <c r="G37" s="32" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="H37" s="34">
         <f>H21+H36</f>
@@ -8262,7 +7587,7 @@
       <c r="E38" s="32"/>
       <c r="F38" s="30"/>
       <c r="G38" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H38" s="34">
         <v>173596.78200000006</v>
@@ -8282,7 +7607,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="30"/>
       <c r="G39" s="32" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H39" s="34">
         <f>H37+H38</f>
@@ -8323,7 +7648,7 @@
       <c r="E41" s="32"/>
       <c r="F41" s="30"/>
       <c r="G41" s="32" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H41" s="35">
         <v>56640</v>
@@ -8345,7 +7670,7 @@
       <c r="G42" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H42" s="42">
+      <c r="H42" s="41">
         <f>H40+H41</f>
         <v>314880</v>
       </c>
@@ -8366,7 +7691,7 @@
       <c r="G43" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H43" s="47">
+      <c r="H43" s="46">
         <f>H39-H42</f>
         <v>29328.352000000072</v>
       </c>
@@ -8384,10 +7709,10 @@
       <c r="D44" s="9"/>
       <c r="E44" s="7"/>
       <c r="F44" s="10"/>
-      <c r="G44" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H44" s="39">
+      <c r="G44" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="38">
         <v>112000</v>
       </c>
       <c r="I44" s="11"/>
@@ -8404,10 +7729,10 @@
       <c r="D45" s="10"/>
       <c r="E45" s="14"/>
       <c r="F45" s="10"/>
-      <c r="G45" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H45" s="40">
+      <c r="G45" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" s="39">
         <f>H43+H44</f>
         <v>141328.35200000007</v>
       </c>
@@ -8507,7 +7832,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B2" s="28">
         <v>44718</v>
@@ -8519,7 +7844,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>0.26</v>
       </c>
       <c r="G2" s="31">
@@ -8539,7 +7864,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B3" s="28">
         <v>44720</v>
@@ -8551,7 +7876,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="31"/>
-      <c r="F3" s="38">
+      <c r="F3" s="37">
         <v>0.23</v>
       </c>
       <c r="G3" s="31">
@@ -8571,7 +7896,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B4" s="28">
         <v>44727</v>
@@ -8583,7 +7908,7 @@
         <v>21</v>
       </c>
       <c r="E4" s="31"/>
-      <c r="F4" s="38">
+      <c r="F4" s="37">
         <v>0.1915</v>
       </c>
       <c r="G4" s="31">
@@ -8603,7 +7928,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B5" s="28">
         <v>44728</v>
@@ -8615,7 +7940,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="31"/>
-      <c r="F5" s="38">
+      <c r="F5" s="37">
         <v>0.4</v>
       </c>
       <c r="G5" s="31">
@@ -8647,7 +7972,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="31"/>
-      <c r="F6" s="38">
+      <c r="F6" s="37">
         <v>0.15559999999999999</v>
       </c>
       <c r="G6" s="31">
@@ -8686,7 +8011,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="B8" s="28">
         <v>44720</v>
@@ -8752,7 +8077,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A10" s="27" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="28">
         <v>44725</v>
@@ -8785,7 +8110,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A11" s="27" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B11" s="28">
         <v>44735</v>
@@ -8818,7 +8143,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A12" s="27" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="B12" s="28">
         <v>44735</v>
@@ -8851,7 +8176,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A13" s="27" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B13" s="28">
         <v>44739</v>
@@ -8884,7 +8209,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A14" s="27" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B14" s="28">
         <v>44741</v>
@@ -8929,7 +8254,7 @@
         <f>SUM(G8:G14)</f>
         <v>726986.21000000008</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="44">
         <f>SUM(H8:H14)</f>
         <v>-9641.7599999999948</v>
       </c>
@@ -8948,7 +8273,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="H16" s="34">
         <f>H7+H15</f>
@@ -8969,7 +8294,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H17" s="32">
         <v>344208.35200000007</v>
@@ -8989,7 +8314,7 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H18" s="34">
         <f>H16+H17</f>
@@ -9030,7 +8355,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="30"/>
       <c r="G20" s="32" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H20" s="35">
         <v>72560</v>
@@ -9052,7 +8377,7 @@
       <c r="G21" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="41">
         <f>H19+H20</f>
         <v>387440</v>
       </c>
@@ -9073,7 +8398,7 @@
       <c r="G22" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="47">
+      <c r="H22" s="46">
         <f>H18-H21</f>
         <v>-1641.3079999999027</v>
       </c>
@@ -9091,10 +8416,10 @@
       <c r="D23" s="9"/>
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
-      <c r="G23" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H23" s="39">
+      <c r="G23" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="38">
         <v>112000</v>
       </c>
       <c r="I23" s="11"/>
@@ -9111,10 +8436,10 @@
       <c r="D24" s="10"/>
       <c r="E24" s="14"/>
       <c r="F24" s="10"/>
-      <c r="G24" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" s="40">
+      <c r="G24" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="39">
         <f>H22+H23</f>
         <v>110358.6920000001</v>
       </c>
@@ -9222,7 +8547,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>0.15559999999999999</v>
       </c>
       <c r="G2" s="31">
@@ -9260,7 +8585,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A4" s="27" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B4" s="28">
         <v>44746</v>
@@ -9293,7 +8618,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A5" s="27" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B5" s="28">
         <v>44764</v>
@@ -9326,7 +8651,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A6" s="27" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B6" s="28">
         <v>44767</v>
@@ -9359,7 +8684,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A7" s="27" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="B7" s="28">
         <v>44767</v>
@@ -9404,7 +8729,7 @@
         <f>SUM(G4:G7)</f>
         <v>363393.31999999995</v>
       </c>
-      <c r="H8" s="45">
+      <c r="H8" s="44">
         <f>SUM(H4:H7)</f>
         <v>-17849.250000000015</v>
       </c>
@@ -9420,7 +8745,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="H9" s="34">
         <f>H3+H8</f>
@@ -9441,7 +8766,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H10" s="32">
         <v>385798.6920000001</v>
@@ -9458,7 +8783,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
       <c r="G11" s="32" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H11" s="34">
         <f>H9+H10</f>
@@ -9493,7 +8818,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
       <c r="G13" s="32" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H13" s="35">
         <v>26960</v>
@@ -9512,7 +8837,7 @@
       <c r="G14" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="41">
         <f>H12+H13</f>
         <v>414400</v>
       </c>
@@ -9533,7 +8858,7 @@
       <c r="G15" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="47">
+      <c r="H15" s="46">
         <f>H11-H14</f>
         <v>-46450.557999999903</v>
       </c>
@@ -9551,10 +8876,10 @@
       <c r="D16" s="9"/>
       <c r="E16" s="7"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="39">
+      <c r="G16" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="38">
         <v>112000</v>
       </c>
       <c r="I16" s="11"/>
@@ -9571,10 +8896,10 @@
       <c r="D17" s="10"/>
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" s="40">
+      <c r="G17" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="39">
         <f>H15+H16</f>
         <v>65549.442000000097</v>
       </c>
@@ -9675,7 +9000,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A2" s="27" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B2" s="28">
         <v>44799</v>
@@ -9687,7 +9012,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>4.25</v>
       </c>
       <c r="G2" s="31">
@@ -9707,7 +9032,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21">
       <c r="A3" s="27" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B3" s="28">
         <v>44799</v>
@@ -9719,7 +9044,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="31"/>
-      <c r="F3" s="38">
+      <c r="F3" s="37">
         <v>6</v>
       </c>
       <c r="G3" s="31">
@@ -9745,7 +9070,7 @@
       <c r="E4" s="31"/>
       <c r="F4" s="30"/>
       <c r="G4" s="31"/>
-      <c r="H4" s="42">
+      <c r="H4" s="41">
         <f>SUM(H2:H3)</f>
         <v>7155</v>
       </c>
@@ -9758,7 +9083,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B5" s="28">
         <v>44788</v>
@@ -9791,7 +9116,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="B6" s="28">
         <v>44796</v>
@@ -9836,7 +9161,7 @@
         <f>SUM(G5:G6)</f>
         <v>269701.31</v>
       </c>
-      <c r="H7" s="45">
+      <c r="H7" s="44">
         <f>SUM(H5:H6)</f>
         <v>3613.2400000000052</v>
       </c>
@@ -9852,9 +9177,9 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="42">
+        <v>27</v>
+      </c>
+      <c r="H8" s="41">
         <f>H4+H7</f>
         <v>10768.240000000005</v>
       </c>
@@ -9873,7 +9198,7 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H9" s="32">
         <v>367949.4420000001</v>
@@ -9890,9 +9215,9 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="42">
+        <v>41</v>
+      </c>
+      <c r="H10" s="41">
         <f>H8+H9</f>
         <v>378717.68200000009</v>
       </c>
@@ -9925,7 +9250,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H12" s="35">
         <v>53940</v>
@@ -9944,7 +9269,7 @@
       <c r="G13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="41">
         <f>H11+H12</f>
         <v>468340</v>
       </c>
@@ -9965,7 +9290,7 @@
       <c r="G14" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="48">
+      <c r="H14" s="47">
         <f>H10-H13</f>
         <v>-89622.317999999912</v>
       </c>
@@ -9983,10 +9308,10 @@
       <c r="D15" s="9"/>
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="39">
+      <c r="G15" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="38">
         <v>112000</v>
       </c>
       <c r="I15" s="11"/>
@@ -10003,10 +9328,10 @@
       <c r="D16" s="10"/>
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="43">
+      <c r="G16" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="42">
         <f>H14+H15</f>
         <v>22377.682000000088</v>
       </c>
